--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -1406,34 +1406,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>confetti_confetti mini gelatinas_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.3365384615384615</v>
+        <v>2.788461538461538</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.942307692307693</v>
+        <v>1.394230769230769</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>-91.46341463414633</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -1457,34 +1457,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>confetti_confetti mini gelatinas_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.942307692307693</v>
+        <v>2.788461538461538</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3365384615384615</v>
+        <v>0.7211538461538461</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1071.428571428572</v>
+        <v>286.6666666666666</v>
       </c>
     </row>
     <row r="22">
@@ -1508,34 +1508,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>instorebakery_holiday cheeze puffs_unknown</t>
+          <t>confetti_confetti mini gelatinas_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.730769230769231</v>
+        <v>1.394230769230769</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4326923076923077</v>
+        <v>2.788461538461538</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>300</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="23">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>instorebakery_holiday cheeze puffs_unknown</t>
+          <t>confetti_confetti mini gelatinas_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.4326923076923077</v>
+        <v>1.394230769230769</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.730769230769231</v>
+        <v>0.7211538461538461</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>-75</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -1610,34 +1610,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>confetti_confetti mini gelatinas_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.682692307692308</v>
+        <v>0.7211538461538461</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.086538461538462</v>
+        <v>2.788461538461538</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>-58.82352941176471</v>
+        <v>-74.13793103448275</v>
       </c>
     </row>
     <row r="25">
@@ -1661,34 +1661,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>confetti_confetti mini gelatinas_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.086538461538462</v>
+        <v>0.7211538461538461</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Confetti</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Confetti Mini Gelatinas</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.682692307692308</v>
+        <v>1.394230769230769</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>142.8571428571429</v>
+        <v>-48.27586206896552</v>
       </c>
     </row>
     <row r="26">
@@ -1712,34 +1712,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.682692307692308</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.086538461538462</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>-58.82352941176471</v>
+        <v>-91.46341463414633</v>
       </c>
     </row>
     <row r="27">
@@ -1763,34 +1763,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.086538461538462</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.682692307692308</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>142.8571428571429</v>
+        <v>1071.428571428572</v>
       </c>
     </row>
     <row r="28">
@@ -1814,34 +1814,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>oh snacks_oh snacks quinoa_unknown</t>
+          <t>instorebakery_holiday cheeze puffs_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.576923076923077</v>
+        <v>1.730769230769231</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.35576923076923</v>
+        <v>0.4326923076923077</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-54.86381322957198</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29">
@@ -1865,34 +1865,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>oh snacks_oh snacks quinoa_unknown</t>
+          <t>instorebakery_holiday cheeze puffs_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12.35576923076923</v>
+        <v>0.4326923076923077</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.576923076923077</v>
+        <v>1.730769230769231</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>121.551724137931</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30">
@@ -1916,34 +1916,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>other_toppers caramel popcorn_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.326923076923077</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.057692307692308</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>309.0909090909091</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="31">
@@ -1967,34 +1967,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>other_toppers caramel popcorn_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.057692307692308</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.326923076923077</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>-75.55555555555556</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -2018,34 +2018,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>other_toppers frosted popcorn_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.326923076923077</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.105769230769231</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>291.3043478260869</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="33">
@@ -2069,34 +2069,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>other_toppers frosted popcorn_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.105769230769231</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.326923076923077</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>-74.44444444444444</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="34">
@@ -2120,34 +2120,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>other_toppers kettle popcorn_unknown</t>
+          <t>oh snacks_oh snacks quinoa_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.134615384615385</v>
+        <v>5.576923076923077</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.057692307692308</v>
+        <v>12.35576923076923</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>290.9090909090909</v>
+        <v>-54.86381322957198</v>
       </c>
     </row>
     <row r="35">
@@ -2171,34 +2171,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>other_toppers kettle popcorn_unknown</t>
+          <t>oh snacks_oh snacks quinoa_unknown</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.057692307692308</v>
+        <v>12.35576923076923</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.134615384615385</v>
+        <v>5.576923076923077</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>-74.41860465116279</v>
+        <v>121.551724137931</v>
       </c>
     </row>
     <row r="36">
@@ -2222,34 +2222,34 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+          <t>other_toppers caramel popcorn_unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.201923076923077</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Goldfish Cheddar</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8653846153846154</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>38.88888888888888</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="37">
@@ -2273,34 +2273,34 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+          <t>other_toppers caramel popcorn_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Goldfish Cheddar</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.8653846153846154</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.201923076923077</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-27.99999999999999</v>
+        <v>-75.55555555555556</v>
       </c>
     </row>
     <row r="38">
@@ -2324,34 +2324,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>other_toppers frosted popcorn_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.254807692307693</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>70.19230769230769</v>
+        <v>291.3043478260869</v>
       </c>
     </row>
     <row r="39">
@@ -2375,34 +2375,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>other_toppers frosted popcorn_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.5</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.254807692307693</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>-41.24293785310735</v>
+        <v>-74.44444444444444</v>
       </c>
     </row>
     <row r="40">
@@ -2426,34 +2426,34 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>other_toppers kettle popcorn_unknown</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>10.86538461538462</v>
+        <v>4.134615384615385</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.826923076923077</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>494.7368421052633</v>
+        <v>290.9090909090909</v>
       </c>
     </row>
     <row r="41">
@@ -2477,34 +2477,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>other_toppers kettle popcorn_unknown</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.826923076923077</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.86538461538462</v>
+        <v>4.134615384615385</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>-83.18584070796462</v>
+        <v>-74.41860465116279</v>
       </c>
     </row>
     <row r="42">
@@ -2528,34 +2528,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.778846153846154</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Pepperidge Farm Goldfish Cheddar</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.105769230769231</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>60.86956521739126</v>
+        <v>38.88888888888888</v>
       </c>
     </row>
     <row r="43">
@@ -2579,34 +2579,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Pepperidge Farm Goldfish Cheddar</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.105769230769231</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.778846153846154</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>-37.83783783783782</v>
+        <v>-27.99999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -2630,34 +2630,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.610576923076923</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.346153846153846</v>
+        <v>2.5</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>19.64285714285712</v>
+        <v>70.19230769230769</v>
       </c>
     </row>
     <row r="45">
@@ -2681,34 +2681,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.610576923076923</v>
+        <v>2.5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5769230769230769</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>179.1666666666667</v>
+        <v>-41.24293785310735</v>
       </c>
     </row>
     <row r="46">
@@ -2732,34 +2732,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.346153846153846</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.610576923076923</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>-16.41791044776118</v>
+        <v>494.7368421052633</v>
       </c>
     </row>
     <row r="47">
@@ -2783,34 +2783,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.346153846153846</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5769230769230769</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>133.3333333333334</v>
+        <v>-83.18584070796462</v>
       </c>
     </row>
     <row r="48">
@@ -2834,34 +2834,34 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.610576923076923</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>-64.17910447761194</v>
+        <v>60.86956521739126</v>
       </c>
     </row>
     <row r="49">
@@ -2885,34 +2885,34 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.346153846153846</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>-57.14285714285716</v>
+        <v>-37.83783783783782</v>
       </c>
     </row>
     <row r="50">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>unknown_confetti mini gelatinas_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.788461538461538</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.394230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>19.64285714285712</v>
       </c>
     </row>
     <row r="51">
@@ -2987,34 +2987,34 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>unknown_confetti mini gelatinas_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.788461538461538</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7211538461538461</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>286.6666666666666</v>
+        <v>179.1666666666667</v>
       </c>
     </row>
     <row r="52">
@@ -3038,34 +3038,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unknown_confetti mini gelatinas_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.394230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.788461538461538</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>-50</v>
+        <v>-16.41791044776118</v>
       </c>
     </row>
     <row r="53">
@@ -3089,34 +3089,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unknown_confetti mini gelatinas_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.394230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7211538461538461</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>93.33333333333333</v>
+        <v>133.3333333333334</v>
       </c>
     </row>
     <row r="54">
@@ -3140,34 +3140,34 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unknown_confetti mini gelatinas_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.7211538461538461</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.788461538461538</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>-74.13793103448275</v>
+        <v>-64.17910447761194</v>
       </c>
     </row>
     <row r="55">
@@ -3191,34 +3191,34 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unknown_confetti mini gelatinas_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.7211538461538461</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Confetti Mini Gelatinas</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.394230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>-48.27586206896552</v>
+        <v>-57.14285714285716</v>
       </c>
     </row>
     <row r="56">
@@ -3342,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3401,45 +3401,6 @@
           <t>price_change_pct</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>post_mezcla reposteria duncan hines bizcocho fresa_0.43</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Post</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Mezcla Reposteria Duncan Hines Bizcocho Fresa</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3452,7 +3413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3512,45 +3473,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>unknown_mezcla reposteria duncan hines bizcocho fresa_0.43</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Mezcla Reposteria Duncan Hines Bizcocho Fresa</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -3342,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3401,6 +3401,1527 @@
           <t>price_change_pct</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bisco_bisco pan galleta clas integral_0.22</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Clas Integral</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bisco_bisco pan galleta constanza_0.28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Constanza</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bisco_bisco pan pan integral mielpasas_0.38</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bisco Pan Pan Integral Mielpasas</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bisco_bisco pan viga integral_0.45</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bisco Pan Viga Integral</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>carrefour_bizcocho de chocolate conejo carrefour_unknown</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bizcocho De Chocolate Conejo Carrefour</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>carrefour_bizcocho frambuesa carrefour_0.15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bizcocho Frambuesa Carrefour</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>carrefour_bizcocho ptit dej carrefour_0.4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bizcocho Ptit Dej Carrefour</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>carrefour_bizcochos 6 carrefour classic de cereales_0.3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bizcochos 6 Carrefour Classic De Cereales</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>carrefour_bizcochos carrefour classic naturales_0.3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Bizcochos Carrefour Classic Naturales</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>carrefour_bizcochos carrefour naranja_0.15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Bizcochos Carrefour Naranja</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>carrefour_brownies carrefour pepites choco_0.28</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Brownies Carrefour Pepites Choco</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour chocograni chocolat noir_0.2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocograni Chocolat Noir</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour chocolate avellas_0.24</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocolate Avellas</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour chocolate caramelo_0.12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocolate Caramelo</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour chocolate con leche_0.15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocolate Con Leche</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour cocoa sin_0.12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Cocoa Sin Gluten</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour de pepitas de limon verde_0.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour De Pepitas De Limon Verde</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour dorada de guijarros de coco_0.12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Dorada De Guijarros De Coco</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour mantequilla_0.12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Mantequilla</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour praline de avellanas_0.11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Praline De Avellanas</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour proteinas_0.15</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Proteinas</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>carrefour_galleta carrefour speculoos x2_0.17</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Speculoos X2</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>carrefour_galleta maiz con chocolate x carrefour bio_0.09</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Galleta Maiz Con Chocolate X Carrefour Bio</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>carrefour_galletas carrefour finas de gofre pura mantequilla_0.3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Galletas Carrefour Finas De Gofre Pura Mantequilla</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>carrefour_galletas carrefour sensation tortillas simples_0.15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Galletas Carrefour Sensation Tortillas Simples</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>carrefour_galletas de aperitivo carrefour classic galletas de emmental_0.1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Galletas De Aperitivo Carrefour Classic Galletas De Emmental</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>carrefour_levadura para panes y brioches carrefour original_0.03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Levadura Para Panes Y Brioches Carrefour Original</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>carrefour_surtido de galletas carrefour extra_0.2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Surtido De Galletas Carrefour Extra</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>carrefour_tortillas de trigo carrefour sensation_0.37</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Tortillas De Trigo Carrefour Sensation</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>can can_galleta can can rell duplex_0.48</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Can Can</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Galleta Can Can Rell Duplex</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bisco_bisco pan galleta clas integral_0.22</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Clas Integral</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>bisco_bisco pan galleta constanza_0.28</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bisco</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Constanza</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Milka</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>can can_galleta can can rell duplex_0.48</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Can Can</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Galleta Can Can Rell Duplex</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Milka</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>milka_chocolate milka nutty wafer_0.27</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Milka</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Chocolate Milka Nutty Wafer</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>milka_galleta milka choco brownie_0.15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Milka</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Galleta Milka Choco Brownie</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3413,7 +4934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3473,6 +4994,1527 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>unknown_bisco pan galleta clas integral_0.22</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Clas Integral</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>unknown_bisco pan galleta constanza_0.28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Constanza</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>unknown_bisco pan pan integral mielpasas_0.38</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bisco Pan Pan Integral Mielpasas</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>unknown_bisco pan viga integral_0.45</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bisco Pan Viga Integral</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lu_galleta carrefour cocoa sin_0.12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Cocoa Sin Gluten</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>unknown_bizcocho de chocolate conejo carrefour_unknown</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bizcocho De Chocolate Conejo Carrefour</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>unknown_bizcocho frambuesa carrefour_0.15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bizcocho Frambuesa Carrefour</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>unknown_bizcocho ptit dej carrefour_0.4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Bizcocho Ptit Dej Carrefour</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>unknown_bizcochos 6 carrefour classic de cereales_0.3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bizcochos 6 Carrefour Classic De Cereales</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>unknown_bizcochos carrefour classic naturales_0.3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bizcochos Carrefour Classic Naturales</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unknown_bizcochos carrefour naranja_0.15</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bizcochos Carrefour Naranja</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>unknown_brownies carrefour pepites choco_0.28</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Brownies Carrefour Pepites Choco</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour chocograni chocolat noir_0.2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocograni Chocolat Noir</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour chocolate avellas_0.24</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocolate Avellas</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour chocolate caramelo_0.12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocolate Caramelo</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour chocolate con leche_0.15</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Chocolate Con Leche</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour de pepitas de limon verde_0.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour De Pepitas De Limon Verde</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour dorada de guijarros de coco_0.12</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Dorada De Guijarros De Coco</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour mantequilla_0.12</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Mantequilla</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour praline de avellanas_0.11</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Praline De Avellanas</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour proteinas_0.15</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Proteinas</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>unknown_galleta carrefour speculoos x2_0.17</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Galleta Carrefour Speculoos X2</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unknown_galleta maiz con chocolate x carrefour bio_0.09</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Galleta Maiz Con Chocolate X Carrefour Bio</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unknown_galletas carrefour finas de gofre pura mantequilla_0.3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Galletas Carrefour Finas De Gofre Pura Mantequilla</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>unknown_galletas carrefour sensation tortillas simples_0.15</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Galletas Carrefour Sensation Tortillas Simples</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unknown_galletas de aperitivo carrefour classic galletas de emmental_0.1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Galletas De Aperitivo Carrefour Classic Galletas De Emmental</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unknown_levadura para panes y brioches carrefour original_0.03</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Levadura Para Panes Y Brioches Carrefour Original</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unknown_surtido de galletas carrefour extra_0.2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Surtido De Galletas Carrefour Extra</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unknown_tortillas de trigo carrefour sensation_0.37</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Tortillas De Trigo Carrefour Sensation</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unknown_galleta can can rell duplex_0.48</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Galleta Can Can Rell Duplex</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unknown_bisco pan galleta clas integral_0.22</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Clas Integral</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>unknown_bisco pan galleta constanza_0.28</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Bisco Pan Galleta Constanza</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>unknown_chocolate milka nutty wafer_0.27</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Chocolate Milka Nutty Wafer</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>unknown_galleta can can rell duplex_0.48</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Galleta Can Can Rell Duplex</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>unknown_galleta milka choco brownie_0.15</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Galleta Milka Choco Brownie</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2742,11 +2742,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>SHOON FATT BUTTER CRACKERS</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10.86538461538462</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2755,11 +2755,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>Shoon Fatt Butter Crackers</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.826923076923077</v>
+        <v>4.182692307692307</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>494.7368421052633</v>
+        <v>-57.4712643678161</v>
       </c>
     </row>
     <row r="47">
@@ -2793,32 +2793,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Shoon Fatt Cream Crackers</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>10.86538461538462</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="I47" t="n">
         <v>1.826923076923077</v>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Cream Crackers</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>10.86538461538462</v>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>-83.18584070796462</v>
+        <v>494.7368421052633</v>
       </c>
     </row>
     <row r="48">
@@ -2834,34 +2834,34 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.778846153846154</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.105769230769231</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>60.86956521739126</v>
+        <v>-83.18584070796462</v>
       </c>
     </row>
     <row r="49">
@@ -2899,28 +2899,28 @@
         </is>
       </c>
       <c r="F49" t="n">
+        <v>1.778846153846154</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sunshine Snacks</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sunshine Cashew Nuts Light Salt</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
         <v>1.105769230769231</v>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Sunshine Snacks</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1.778846153846154</v>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>-37.83783783783782</v>
+        <v>60.86956521739126</v>
       </c>
     </row>
     <row r="50">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.610576923076923</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.346153846153846</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>19.64285714285712</v>
+        <v>-37.83783783783782</v>
       </c>
     </row>
     <row r="51">
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>179.1666666666667</v>
+        <v>19.64285714285712</v>
       </c>
     </row>
     <row r="52">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.346153846153846</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.610576923076923</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>-16.41791044776118</v>
+        <v>179.1666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>133.3333333333334</v>
+        <v>-16.41791044776118</v>
       </c>
     </row>
     <row r="54">
@@ -3154,28 +3154,28 @@
         </is>
       </c>
       <c r="F54" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1.610576923076923</v>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>-64.17910447761194</v>
+        <v>133.3333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.346153846153846</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>-57.14285714285716</v>
+        <v>-64.17910447761194</v>
       </c>
     </row>
     <row r="56">
@@ -3242,34 +3242,34 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wibisco_wibisco tea time chocolate_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wibisco Tea Time Chocolate</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>4.086538461538462</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Wibisco Tea Time Chocolate</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4326923076923077</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>844.4444444444445</v>
+        <v>-57.14285714285716</v>
       </c>
     </row>
     <row r="57">
@@ -3307,27 +3307,78 @@
         </is>
       </c>
       <c r="F57" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Wibisco</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Wibisco Tea Time Chocolate</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
         <v>0.4326923076923077</v>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>844.4444444444445</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wibisco_wibisco tea time chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Wibisco</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Wibisco Tea Time Chocolate</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="F58" t="n">
+        <v>0.4326923076923077</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Wibisco</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Wibisco Tea Time Chocolate</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
         <v>4.086538461538462</v>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>-89.41176470588236</v>
       </c>
     </row>
@@ -3342,7 +3393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3405,31 +3456,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bisco_bisco pan galleta clas integral_0.22</t>
+          <t>becky s_becky s tomato bread 190_0.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Becky's</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
+          <t>BECKY'S TOMATO BREAD | 190 g</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3444,31 +3495,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bisco_bisco pan galleta constanza_0.28</t>
+          <t>dove_dove vanilla ice cream bars coated with dark chocolate individually wrapped dessert 3 bars 16_0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Constanza</t>
+          <t>DOVE Vanilla Ice Cream Bars Coated With Dark Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 16 oz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3483,31 +3534,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bisco_bisco pan pan integral mielpasas_0.38</t>
+          <t>dove_dove vanilla ice cream bars coated with milk chocolate individually wrapped dessert 3 bars 11_0.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Dove</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bisco Pan Pan Integral Mielpasas</t>
+          <t>DOVE Vanilla Ice Cream Bars Coated With Milk Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 11 oz</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3522,31 +3573,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bisco_bisco pan viga integral_0.45</t>
+          <t>kinder_kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bisco Pan Viga Integral</t>
+          <t>Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>2.955307262569832</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3561,31 +3612,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>carrefour_bizcocho de chocolate conejo carrefour_unknown</t>
+          <t>kinder_liga kinder biscuits 12 36 maanden 300_0.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bizcocho De Chocolate Conejo Carrefour</t>
+          <t>LIGA KINDER BISCUITS 12-36 MAANDEN | 300 g</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.06</v>
+        <v>2.731843575418994</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3600,31 +3651,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>carrefour_bizcocho frambuesa carrefour_0.15</t>
+          <t>kraft_kraft america s classic individually wrapped candy caramels bag 240_0.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Kraft</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bizcocho Frambuesa Carrefour</t>
+          <t>Kraft America's Classic Individually Wrapped Candy Caramels, Bag | 240 g</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.74</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3639,31 +3690,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>carrefour_bizcocho ptit dej carrefour_0.4</t>
+          <t>nutella_nutella b ready 142_0.14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bizcocho Ptit Dej Carrefour</t>
+          <t>NUTELLA B-READY | 142 g</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.96</v>
+        <v>1.223463687150838</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3678,31 +3729,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>carrefour_bizcochos 6 carrefour classic de cereales_0.3</t>
+          <t>nutella_nutella biscuits 260_0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bizcochos 6 Carrefour Classic De Cereales</t>
+          <t>NUTELLA BISCUITS | 260 g</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.69</v>
+        <v>4.072625698324022</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3717,31 +3768,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>carrefour_bizcochos carrefour classic naturales_0.3</t>
+          <t>santitas_santitas tortilla chips tortilla triangles 10_0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Santitas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bizcochos Carrefour Classic Naturales</t>
+          <t>SANTITAS TORTILLA CHIPS, TORTILLA TRIANGLES | 10 oz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>6.698324022346369</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3756,31 +3807,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>carrefour_bizcochos carrefour naranja_0.15</t>
+          <t>toblerone_toblerone cheesecake 2x 225_0.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Toblerone</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bizcochos Carrefour Naranja</t>
+          <t>TOBLERONE CHEESECAKE 2X | 225 g</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.452513966480447</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -3795,31 +3846,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>carrefour_brownies carrefour pepites choco_0.28</t>
+          <t>twix_twix caramel cookie milk chocolate candy bars full size 3 02_0.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Brownies Carrefour Pepites Choco</t>
+          <t>TWIX Caramel Cookie Milk Chocolate Candy Bars, Full Size, Pack | 3.02 oz</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.49</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -3834,31 +3885,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>carrefour_galleta carrefour chocograni chocolat noir_0.2</t>
+          <t>twix_twix milk chocolate caramel cookie candy bar share size 5 3_0.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Twix</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocograni Chocolat Noir</t>
+          <t>TWIX Milk Chocolate Caramel Cookie Candy Bar, Share Size, | 5.3 oz</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.61</v>
+        <v>2.508379888268156</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -3878,26 +3929,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>carrefour_galleta carrefour chocolate avellas_0.24</t>
+          <t>nutella_galletas b ready nutella_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocolate Avellas</t>
+          <t>Galletas B Ready Nutella</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.8</v>
+        <v>7.68</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -3917,26 +3968,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>carrefour_galleta carrefour chocolate caramelo_0.12</t>
+          <t>nutella_galletas biscuit nutella_0.34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocolate Caramelo</t>
+          <t>Galletas Biscuit Nutella</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.01</v>
+        <v>7.53</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -3956,26 +4007,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>carrefour_galleta carrefour chocolate con leche_0.15</t>
+          <t>nutella_galletas b ready nutella_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocolate Con Leche</t>
+          <t>Galletas B Ready Nutella</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.06</v>
+        <v>7.68</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -3990,31 +4041,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>carrefour_galleta carrefour cocoa sin_0.12</t>
+          <t>chiefeez_chiefeez cheese ball_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Chiefeez</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Cocoa Sin Gluten</t>
+          <t>Chiefeez Cheese Ball</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.64</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -4029,31 +4080,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>carrefour_galleta carrefour de pepitas de limon verde_0.1</t>
+          <t>shoon_shoon fatt veggie crackers_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galleta Carrefour De Pepitas De Limon Verde</t>
+          <t>Shoon Fatt Veggie Crackers</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.85</v>
+        <v>3.557692307692307</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4064,864 +4115,6 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>carrefour_galleta carrefour dorada de guijarros de coco_0.12</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Dorada De Guijarros De Coco</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>carrefour_galleta carrefour mantequilla_0.12</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Mantequilla</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>carrefour_galleta carrefour praline de avellanas_0.11</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Praline De Avellanas</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>carrefour_galleta carrefour proteinas_0.15</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Proteinas</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>carrefour_galleta carrefour speculoos x2_0.17</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Speculoos X2</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>carrefour_galleta maiz con chocolate x carrefour bio_0.09</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Galleta Maiz Con Chocolate X Carrefour Bio</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>carrefour_galletas carrefour finas de gofre pura mantequilla_0.3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Galletas Carrefour Finas De Gofre Pura Mantequilla</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>carrefour_galletas carrefour sensation tortillas simples_0.15</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Galletas Carrefour Sensation Tortillas Simples</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>carrefour_galletas de aperitivo carrefour classic galletas de emmental_0.1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Galletas De Aperitivo Carrefour Classic Galletas De Emmental</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>carrefour_levadura para panes y brioches carrefour original_0.03</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Levadura Para Panes Y Brioches Carrefour Original</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>carrefour_surtido de galletas carrefour extra_0.2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Surtido De Galletas Carrefour Extra</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>carrefour_tortillas de trigo carrefour sensation_0.37</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Tortillas De Trigo Carrefour Sensation</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Garrido</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>can can_galleta can can rell duplex_0.48</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Can Can</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Galleta Can Can Rell Duplex</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Jumbo</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Bisco</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>bisco_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Bisco</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>bisco_bisco pan galleta clas integral_0.22</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Bisco</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>bisco_bisco pan galleta constanza_0.28</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Bisco</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Bisco Pan Galleta Constanza</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Milka</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>can can_galleta can can rell duplex_0.48</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Can Can</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Galleta Can Can Rell Duplex</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>milka_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Milka</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>milka_chocolate milka nutty wafer_0.27</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Milka</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Chocolate Milka Nutty Wafer</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>milka_galleta milka choco brownie_0.15</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Milka</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Galleta Milka Choco Brownie</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4934,7 +4127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4997,17 +4190,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unknown_bisco pan galleta clas integral_0.22</t>
+          <t>liga_liga kinder biscuits 12 36 maanden 300_0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5015,16 +4208,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Liga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
+          <t>LIGA KINDER BISCUITS 12-36 MAANDEN | 300 g</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>2.731843575418994</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5036,17 +4229,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unknown_bisco pan galleta constanza_0.28</t>
+          <t>unknown_becky s tomato bread 190_0.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -5059,11 +4252,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Constanza</t>
+          <t>BECKY'S TOMATO BREAD | 190 g</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.73</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5075,17 +4268,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_bisco pan pan integral mielpasas_0.38</t>
+          <t>unknown_dove vanilla ice cream bars coated with dark chocolate individually wrapped dessert 3 bars 16_0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5098,11 +4291,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bisco Pan Pan Integral Mielpasas</t>
+          <t>DOVE Vanilla Ice Cream Bars Coated With Dark Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 16 oz</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.89</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5114,17 +4307,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown_bisco pan viga integral_0.45</t>
+          <t>unknown_dove vanilla ice cream bars coated with milk chocolate individually wrapped dessert 3 bars 11_0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5137,11 +4330,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bisco Pan Viga Integral</t>
+          <t>DOVE Vanilla Ice Cream Bars Coated With Milk Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 11 oz</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5153,17 +4346,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lu_galleta carrefour cocoa sin_0.12</t>
+          <t>unknown_kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5171,16 +4364,16 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Cocoa Sin Gluten</t>
+          <t>Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.64</v>
+        <v>2.955307262569832</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5192,17 +4385,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de chocolate conejo carrefour_unknown</t>
+          <t>unknown_kraft america s classic individually wrapped candy caramels bag 240_0.24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5215,11 +4408,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bizcocho De Chocolate Conejo Carrefour</t>
+          <t>Kraft America's Classic Individually Wrapped Candy Caramels, Bag | 240 g</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5231,17 +4424,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_bizcocho frambuesa carrefour_0.15</t>
+          <t>unknown_nutella b ready 142_0.14</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5254,11 +4447,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bizcocho Frambuesa Carrefour</t>
+          <t>NUTELLA B-READY | 142 g</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.74</v>
+        <v>1.223463687150838</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5270,17 +4463,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_bizcocho ptit dej carrefour_0.4</t>
+          <t>unknown_nutella biscuits 260_0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -5293,11 +4486,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bizcocho Ptit Dej Carrefour</t>
+          <t>NUTELLA BISCUITS | 260 g</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.96</v>
+        <v>4.072625698324022</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5309,17 +4502,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_bizcochos 6 carrefour classic de cereales_0.3</t>
+          <t>unknown_santitas tortilla chips tortilla triangles 10_0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5332,11 +4525,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bizcochos 6 Carrefour Classic De Cereales</t>
+          <t>SANTITAS TORTILLA CHIPS, TORTILLA TRIANGLES | 10 oz</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.69</v>
+        <v>6.698324022346369</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5348,17 +4541,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unknown_bizcochos carrefour classic naturales_0.3</t>
+          <t>unknown_toblerone cheesecake 2x 225_0.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5371,11 +4564,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bizcochos Carrefour Classic Naturales</t>
+          <t>TOBLERONE CHEESECAKE 2X | 225 g</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.73</v>
+        <v>2.452513966480447</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5387,17 +4580,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown_bizcochos carrefour naranja_0.15</t>
+          <t>unknown_twix caramel cookie milk chocolate candy bars full size 3 02_0.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -5410,11 +4603,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bizcochos Carrefour Naranja</t>
+          <t>TWIX Caramel Cookie Milk Chocolate Candy Bars, Full Size, Pack | 3.02 oz</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.06</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5426,17 +4619,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unknown_brownies carrefour pepites choco_0.28</t>
+          <t>unknown_twix milk chocolate caramel cookie candy bar share size 5 3_0.15</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5449,11 +4642,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Brownies Carrefour Pepites Choco</t>
+          <t>TWIX Milk Chocolate Caramel Cookie Candy Bar, Share Size, | 5.3 oz</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.49</v>
+        <v>2.508379888268156</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5470,12 +4663,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocograni chocolat noir_0.2</t>
+          <t>unknown_galletas b ready nutella_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5488,11 +4681,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocograni Chocolat Noir</t>
+          <t>Galletas B Ready Nutella</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.61</v>
+        <v>7.68</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5509,12 +4702,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate avellas_0.24</t>
+          <t>unknown_galletas biscuit nutella_0.34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5527,11 +4720,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocolate Avellas</t>
+          <t>Galletas Biscuit Nutella</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.8</v>
+        <v>7.53</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5548,12 +4741,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate caramelo_0.12</t>
+          <t>unknown_galletas b ready nutella_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5566,11 +4759,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocolate Caramelo</t>
+          <t>Galletas B Ready Nutella</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.01</v>
+        <v>7.68</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5582,17 +4775,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour chocolate con leche_0.15</t>
+          <t>unknown_chiefeez cheese ball_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -5605,11 +4798,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Chocolate Con Leche</t>
+          <t>Chiefeez Cheese Ball</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.06</v>
+        <v>0.4086538461538461</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5621,17 +4814,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour de pepitas de limon verde_0.1</t>
+          <t>unknown_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5644,11 +4837,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Galleta Carrefour De Pepitas De Limon Verde</t>
+          <t>SHOON FATT BUTTER CRACKERS</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.85</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5660,17 +4853,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown_galleta carrefour dorada de guijarros de coco_0.12</t>
+          <t>unknown_shoon fatt veggie crackers_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5683,11 +4876,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Galleta Carrefour Dorada De Guijarros De Coco</t>
+          <t>Shoon Fatt Veggie Crackers</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.79</v>
+        <v>3.557692307692307</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5695,825 +4888,6 @@
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>unknown_galleta carrefour mantequilla_0.12</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Mantequilla</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>unknown_galleta carrefour praline de avellanas_0.11</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Praline De Avellanas</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>unknown_galleta carrefour proteinas_0.15</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Proteinas</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>unknown_galleta carrefour speculoos x2_0.17</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Galleta Carrefour Speculoos X2</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>unknown_galleta maiz con chocolate x carrefour bio_0.09</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Galleta Maiz Con Chocolate X Carrefour Bio</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>unknown_galletas carrefour finas de gofre pura mantequilla_0.3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Galletas Carrefour Finas De Gofre Pura Mantequilla</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>unknown_galletas carrefour sensation tortillas simples_0.15</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Galletas Carrefour Sensation Tortillas Simples</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>unknown_galletas de aperitivo carrefour classic galletas de emmental_0.1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Galletas De Aperitivo Carrefour Classic Galletas De Emmental</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>unknown_levadura para panes y brioches carrefour original_0.03</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Levadura Para Panes Y Brioches Carrefour Original</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>unknown_surtido de galletas carrefour extra_0.2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Surtido De Galletas Carrefour Extra</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Carrefour</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>unknown_tortillas de trigo carrefour sensation_0.37</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Tortillas De Trigo Carrefour Sensation</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Garrido</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>unknown_galleta can can rell duplex_0.48</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Galleta Can Can Rell Duplex</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Jumbo</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>unknown_galletas biscuit mood rellenas de chocolate biscolata_0.12</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Galletas Biscuit Mood Rellenas De Chocolate Biscolata</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>unknown_bisco pan galleta clas integral_0.22</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>unknown_bisco pan galleta constanza_0.28</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Bisco Pan Galleta Constanza</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>unknown_choco wafer galletas de barquillo cubiertas de chocolate milka_0.18</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Choco Wafer Galletas De Barquillo Cubiertas De Chocolate Milka</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>unknown_chocolate milka nutty wafer_0.27</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Chocolate Milka Nutty Wafer</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>unknown_galleta can can rell duplex_0.48</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Galleta Can Can Rell Duplex</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>unknown_galleta milka choco brownie_0.15</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Galleta Milka Choco Brownie</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,34 +2528,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.201923076923077</v>
+        <v>1.442307692307692</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Goldfish Cheddar</t>
+          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8653846153846154</v>
+        <v>7.115384615384615</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>38.88888888888888</v>
+        <v>-79.72972972972973</v>
       </c>
     </row>
     <row r="43">
@@ -2579,34 +2579,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Goldfish Cheddar</t>
+          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.8653846153846154</v>
+        <v>7.115384615384615</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.201923076923077</v>
+        <v>1.442307692307692</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>-27.99999999999999</v>
+        <v>393.3333333333333</v>
       </c>
     </row>
     <row r="44">
@@ -2630,34 +2630,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4.254807692307693</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Pepperidge Farm Goldfish Cheddar</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.5</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>70.19230769230769</v>
+        <v>38.88888888888888</v>
       </c>
     </row>
     <row r="45">
@@ -2681,34 +2681,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Pepperidge Farm Goldfish Cheddar</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.5</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.254807692307693</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>-41.24293785310735</v>
+        <v>-27.99999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2732,34 +2732,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.778846153846154</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Shoon Fatt Butter Crackers</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.182692307692307</v>
+        <v>2.5</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>-57.4712643678161</v>
+        <v>70.19230769230769</v>
       </c>
     </row>
     <row r="47">
@@ -2783,34 +2783,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10.86538461538462</v>
+        <v>2.5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.826923076923077</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>494.7368421052633</v>
+        <v>-41.24293785310735</v>
       </c>
     </row>
     <row r="48">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2844,11 +2844,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>Shoon Fatt Butter Crackers</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.826923076923077</v>
+        <v>4.182692307692307</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2857,11 +2857,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>SHOON FATT BUTTER CRACKERS</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10.86538461538462</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>-83.18584070796462</v>
+        <v>135.1351351351352</v>
       </c>
     </row>
     <row r="49">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>SHOON FATT BUTTER CRACKERS</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2903,16 +2903,16 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Shoon Fatt Butter Crackers</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.105769230769231</v>
+        <v>4.182692307692307</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>60.86956521739126</v>
+        <v>-57.4712643678161</v>
       </c>
     </row>
     <row r="50">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.105769230769231</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.778846153846154</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>-37.83783783783782</v>
+        <v>494.7368421052633</v>
       </c>
     </row>
     <row r="51">
@@ -2987,34 +2987,34 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.610576923076923</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.346153846153846</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>19.64285714285712</v>
+        <v>-83.18584070796462</v>
       </c>
     </row>
     <row r="52">
@@ -3038,34 +3038,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.610576923076923</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>179.1666666666667</v>
+        <v>60.86956521739126</v>
       </c>
     </row>
     <row r="53">
@@ -3089,34 +3089,34 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.346153846153846</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.610576923076923</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>-16.41791044776118</v>
+        <v>-37.83783783783782</v>
       </c>
     </row>
     <row r="54">
@@ -3154,28 +3154,28 @@
         </is>
       </c>
       <c r="F54" t="n">
+        <v>1.610576923076923</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>1.346153846153846</v>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>0.5769230769230769</v>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>133.3333333333334</v>
+        <v>19.64285714285712</v>
       </c>
     </row>
     <row r="55">
@@ -3205,28 +3205,28 @@
         </is>
       </c>
       <c r="F55" t="n">
+        <v>1.610576923076923</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>1.610576923076923</v>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>-64.17910447761194</v>
+        <v>179.1666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.346153846153846</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>-57.14285714285716</v>
+        <v>-16.41791044776118</v>
       </c>
     </row>
     <row r="57">
@@ -3293,34 +3293,34 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wibisco_wibisco tea time chocolate_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wibisco Tea Time Chocolate</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>4.086538461538462</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Wibisco Tea Time Chocolate</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4326923076923077</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>844.4444444444445</v>
+        <v>133.3333333333334</v>
       </c>
     </row>
     <row r="58">
@@ -3344,41 +3344,194 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1.610576923076923</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>-64.17910447761194</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>-57.14285714285716</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>wibisco_wibisco tea time chocolate_unknown</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Wibisco</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Wibisco Tea Time Chocolate</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F60" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Wibisco</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Wibisco Tea Time Chocolate</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
         <v>0.4326923076923077</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>844.4444444444445</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>wibisco_wibisco tea time chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>Wibisco</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Wibisco Tea Time Chocolate</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="F61" t="n">
+        <v>0.4326923076923077</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Wibisco</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Wibisco Tea Time Chocolate</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
         <v>4.086538461538462</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="K58" t="n">
+      <c r="K61" t="n">
         <v>-89.41176470588236</v>
       </c>
     </row>
@@ -3393,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3456,31 +3609,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>becky s_becky s tomato bread 190_0.19</t>
+          <t>bolin_pan de hot dog bolin_unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Becky's</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BECKY'S TOMATO BREAD | 190 g</t>
+          <t>Pan De Hot Dog Bolin</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.681564245810056</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3495,31 +3648,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dove_dove vanilla ice cream bars coated with dark chocolate individually wrapped dessert 3 bars 16_0.45</t>
+          <t>bolin_pan viga bolin mini club integral_0.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DOVE Vanilla Ice Cream Bars Coated With Dark Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 16 oz</t>
+          <t>Pan Viga Bolin Mini Club Integral</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.223463687150838</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3534,31 +3687,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dove_dove vanilla ice cream bars coated with milk chocolate individually wrapped dessert 3 bars 11_0.31</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dove</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DOVE Vanilla Ice Cream Bars Coated With Milk Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 11 oz</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.301675977653631</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3573,31 +3726,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kinder_kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
+          <t>pepin_pan viga pepin club sandwich blanca_0.68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
+          <t>Pan Viga Pepin Club Sandwich Blanca</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.955307262569832</v>
+        <v>2.36</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3612,31 +3765,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kinder_liga kinder biscuits 12 36 maanden 300_0.3</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LIGA KINDER BISCUITS 12-36 MAANDEN | 300 g</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.731843575418994</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3651,31 +3804,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kraft_kraft america s classic individually wrapped candy caramels bag 240_0.24</t>
+          <t>pepin_tortilla integral de harina de trigo pepin_0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kraft</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kraft America's Classic Individually Wrapped Candy Caramels, Bag | 240 g</t>
+          <t>Tortilla Integral De Harina De Trigo Pepin</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.223463687150838</v>
+        <v>2.77</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3690,31 +3843,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nutella_nutella b ready 142_0.14</t>
+          <t>pepin_tortillas de harina de trigo pepin_0.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NUTELLA B-READY | 142 g</t>
+          <t>Tortillas De Harina De Trigo Pepin</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.223463687150838</v>
+        <v>2.77</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3729,31 +3882,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nutella_nutella biscuits 260_0.26</t>
+          <t>bolin_pan de hot dog bolin_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NUTELLA BISCUITS | 260 g</t>
+          <t>Pan De Hot Dog Bolin</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.072625698324022</v>
+        <v>1.58</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3768,31 +3921,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>santitas_santitas tortilla chips tortilla triangles 10_0.28</t>
+          <t>pepin_pan viga integral pepin_0.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Santitas</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SANTITAS TORTILLA CHIPS, TORTILLA TRIANGLES | 10 oz</t>
+          <t>Pan Viga Integral Pepin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.698324022346369</v>
+        <v>1.74</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3807,31 +3960,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>toblerone_toblerone cheesecake 2x 225_0.17</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Toblerone</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOBLERONE CHEESECAKE 2X | 225 g</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.452513966480447</v>
+        <v>2.38</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -3846,31 +3999,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>twix_twix caramel cookie milk chocolate candy bars full size 3 02_0.09</t>
+          <t>pepin_pan viga mini club integral pepin_0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TWIX Caramel Cookie Milk Chocolate Candy Bars, Full Size, Pack | 3.02 oz</t>
+          <t>Pan Viga Mini Club Integral Pepin</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.899441340782123</v>
+        <v>2.61</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -3885,31 +4038,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>twix_twix milk chocolate caramel cookie candy bar share size 5 3_0.15</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Twix</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TWIX Milk Chocolate Caramel Cookie Candy Bar, Share Size, | 5.3 oz</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.508379888268156</v>
+        <v>1.51</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -3929,26 +4082,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nutella_galletas b ready nutella_unknown</t>
+          <t>bolin_pan de hamburguesa bolin_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galletas B Ready Nutella</t>
+          <t>Pan De Hamburguesa Bolin</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.68</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -3968,26 +4121,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nutella_galletas biscuit nutella_0.34</t>
+          <t>bolin_pan de hot dog bolin_unknown</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galletas Biscuit Nutella</t>
+          <t>Pan De Hot Dog Bolin</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.53</v>
+        <v>1.66</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -4007,26 +4160,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nutella_galletas b ready nutella_unknown</t>
+          <t>bolin_pan mini club bolin_0.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galletas B Ready Nutella</t>
+          <t>Pan Mini Club Bolin</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.68</v>
+        <v>1.93</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -4041,31 +4194,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>chiefeez_chiefeez cheese ball_unknown</t>
+          <t>bolin_pan viga club bolin_1.28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chiefeez</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chiefeez Cheese Ball</t>
+          <t>Pan Viga Club Bolin</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.4086538461538461</v>
+        <v>4.2</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -4080,31 +4233,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt veggie crackers_unknown</t>
+          <t>bolin_pan viga mini club integral bolin_0.45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shoon Fatt Veggie Crackers</t>
+          <t>Pan Viga Mini Club Integral Bolin</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.557692307692307</v>
+        <v>1.96</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4115,6 +4268,1449 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bolin_viga mediana de pan integral blanco bolin_0.68</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>holsum_pan de hamburguesa holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Holsum</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>pepin_pan viga mediana pepin_0.85</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pan Viga Mediana Pepin</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>pepin_pan viga mini club integral pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Pepin</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>pepin_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>bolin_pan de hamburguesa bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Bolin</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>bolin_pan de hot dog bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Bolin</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bolin_pan mini club bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pan Mini Club Bolin</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>bolin_pan viga club bolin_1.28</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Pan Viga Club Bolin</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bolin_pan viga mini club integral bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Bolin</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>bolin_viga mediana de pan integral blanco bolin_0.68</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>holsum_pan de hamburguesa holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Holsum</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>holsum_pan de hot dog holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Holsum</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>holsum_pan viga de mantequilla holsum_0.56</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pan Viga De Mantequilla Holsum</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>holsum_pan viga de papa holsum_0.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pan Viga De Papa Holsum</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>pepin_pan viga mediana pepin_0.85</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pan Viga Mediana Pepin</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pepin_pan viga mini club integral pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Pepin</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pepin_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bolin_pan mini club bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Pan Mini Club Bolin</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>holsum_pan de hot dog holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Holsum</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>pepin_pan viga integral pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pan Viga Integral Pepin</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bolin_pan de hamburguesa bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Bolin</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bolin_pan de hot dog bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Bolin</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bolin_pan mini club bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Pan Mini Club Bolin</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bolin_pan viga club bolin_1.28</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pan Viga Club Bolin</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bolin_pan viga mini club integral bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Bolin</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bolin_viga mediana de pan integral blanco bolin_0.68</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bolin</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>crich_galleta crich wafer cacao_0.18</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Cacao</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>crich_galleta crich wafer nocciola_0.12</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Nocciola</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>crich_galleta crich wafer nocciola_0.18</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Nocciola</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>crich_galleta crich wafer vainilla_0.18</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Vainilla</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>crich_galleta crich wafers crema cappuccino_0.25</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafers Crema Cappuccino</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>crich_galletas bio snack cakes with leguminous crich_0.07</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Galletas Bio Snack Cakes With Leguminous Crich</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>crich_galletas crich chocolate wafers_0.25</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Crich</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Galletas Crich Chocolate Wafers</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>holsum_pan de hot dog holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Holsum</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Holsum</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>pepin_pan viga mediana pepin_0.85</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Pan Viga Mediana Pepin</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>pepin_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4127,7 +5723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4190,17 +5786,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>liga_liga kinder biscuits 12 36 maanden 300_0.3</t>
+          <t>lu_pan viga bolin mini club integral_0.58</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -4208,16 +5804,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Liga</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LIGA KINDER BISCUITS 12-36 MAANDEN | 300 g</t>
+          <t>Pan Viga Bolin Mini Club Integral</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.731843575418994</v>
+        <v>1.96</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4229,17 +5825,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unknown_becky s tomato bread 190_0.19</t>
+          <t>lu_pan viga pepin club sandwich blanca_0.68</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -4247,16 +5843,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BECKY'S TOMATO BREAD | 190 g</t>
+          <t>Pan Viga Pepin Club Sandwich Blanca</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.681564245810056</v>
+        <v>2.36</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4268,17 +5864,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_dove vanilla ice cream bars coated with dark chocolate individually wrapped dessert 3 bars 16_0.45</t>
+          <t>unknown_pan de hot dog bolin_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -4291,11 +5887,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DOVE Vanilla Ice Cream Bars Coated With Dark Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 16 oz</t>
+          <t>Pan De Hot Dog Bolin</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.223463687150838</v>
+        <v>1.57</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4307,17 +5903,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown_dove vanilla ice cream bars coated with milk chocolate individually wrapped dessert 3 bars 11_0.31</t>
+          <t>unknown_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4330,11 +5926,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DOVE Vanilla Ice Cream Bars Coated With Milk Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 11 oz</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.301675977653631</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4346,17 +5942,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
+          <t>unknown_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -4369,11 +5965,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.955307262569832</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4385,17 +5981,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_kraft america s classic individually wrapped candy caramels bag 240_0.24</t>
+          <t>unknown_tortilla integral de harina de trigo pepin_0.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -4408,11 +6004,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kraft America's Classic Individually Wrapped Candy Caramels, Bag | 240 g</t>
+          <t>Tortilla Integral De Harina De Trigo Pepin</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.223463687150838</v>
+        <v>2.77</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4424,17 +6020,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_nutella b ready 142_0.14</t>
+          <t>unknown_tortillas de harina de trigo pepin_0.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -4447,11 +6043,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NUTELLA B-READY | 142 g</t>
+          <t>Tortillas De Harina De Trigo Pepin</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.223463687150838</v>
+        <v>2.77</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4463,17 +6059,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_nutella biscuits 260_0.26</t>
+          <t>lu_pan viga mini club integral pepin_0.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -4481,16 +6077,16 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>NUTELLA BISCUITS | 260 g</t>
+          <t>Pan Viga Mini Club Integral Pepin</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.072625698324022</v>
+        <v>2.61</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4502,17 +6098,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_santitas tortilla chips tortilla triangles 10_0.28</t>
+          <t>unknown_pan de hot dog bolin_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4525,11 +6121,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SANTITAS TORTILLA CHIPS, TORTILLA TRIANGLES | 10 oz</t>
+          <t>Pan De Hot Dog Bolin</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6.698324022346369</v>
+        <v>1.58</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -4541,17 +6137,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unknown_toblerone cheesecake 2x 225_0.17</t>
+          <t>unknown_pan viga integral pepin_0.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -4564,11 +6160,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TOBLERONE CHEESECAKE 2X | 225 g</t>
+          <t>Pan Viga Integral Pepin</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.452513966480447</v>
+        <v>1.74</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -4580,17 +6176,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown_twix caramel cookie milk chocolate candy bars full size 3 02_0.09</t>
+          <t>unknown_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -4603,11 +6199,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TWIX Caramel Cookie Milk Chocolate Candy Bars, Full Size, Pack | 3.02 oz</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.899441340782123</v>
+        <v>2.38</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -4619,17 +6215,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unknown_twix milk chocolate caramel cookie candy bar share size 5 3_0.15</t>
+          <t>unknown_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -4642,11 +6238,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TWIX Milk Chocolate Caramel Cookie Candy Bar, Share Size, | 5.3 oz</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.508379888268156</v>
+        <v>1.51</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4663,12 +6259,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unknown_galletas b ready nutella_unknown</t>
+          <t>lu_pan mini club bolin_0.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -4676,16 +6272,16 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Galletas B Ready Nutella</t>
+          <t>Pan Mini Club Bolin</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.68</v>
+        <v>1.93</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -4702,12 +6298,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unknown_galletas biscuit nutella_0.34</t>
+          <t>lu_pan viga club bolin_1.28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -4715,16 +6311,16 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Galletas Biscuit Nutella</t>
+          <t>Pan Viga Club Bolin</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.53</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -4741,12 +6337,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unknown_galletas b ready nutella_unknown</t>
+          <t>lu_pan viga mini club integral bolin_0.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -4754,16 +6350,16 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Galletas B Ready Nutella</t>
+          <t>Pan Viga Mini Club Integral Bolin</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.68</v>
+        <v>1.96</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -4775,17 +6371,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown_chiefeez cheese ball_unknown</t>
+          <t>lu_pan viga mini club integral pepin_0.45</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -4793,16 +6389,16 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Chiefeez Cheese Ball</t>
+          <t>Pan Viga Mini Club Integral Pepin</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4086538461538461</v>
+        <v>2.34</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -4814,17 +6410,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown_shoon fatt butter crackers_unknown</t>
+          <t>unknown_pan de hamburguesa bolin_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -4837,11 +6433,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
+          <t>Pan De Hamburguesa Bolin</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.778846153846154</v>
+        <v>1.98</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -4853,17 +6449,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown_shoon fatt veggie crackers_unknown</t>
+          <t>unknown_pan de hamburguesa holsum_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -4876,11 +6472,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Shoon Fatt Veggie Crackers</t>
+          <t>Pan De Hamburguesa Holsum</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.557692307692307</v>
+        <v>2.99</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -4888,6 +6484,1410 @@
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>unknown_pan de hot dog bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Bolin</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unknown_pan viga mediana pepin_0.85</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pan Viga Mediana Pepin</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unknown_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>unknown_viga mediana de pan integral blanco bolin_0.68</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>lu_pan mini club bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pan Mini Club Bolin</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>lu_pan viga club bolin_1.28</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pan Viga Club Bolin</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lu_pan viga mini club integral bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Bolin</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>lu_pan viga mini club integral pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Pepin</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unknown_pan de hamburguesa bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Bolin</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unknown_pan de hamburguesa holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Holsum</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unknown_pan de hot dog bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Bolin</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unknown_pan de hot dog holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Holsum</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>unknown_pan viga de mantequilla holsum_0.56</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pan Viga De Mantequilla Holsum</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unknown_pan viga de papa holsum_0.56</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pan Viga De Papa Holsum</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unknown_pan viga mediana pepin_0.85</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pan Viga Mediana Pepin</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>unknown_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unknown_viga mediana de pan integral blanco bolin_0.68</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>lu_pan mini club bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Pan Mini Club Bolin</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>unknown_pan de hot dog holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Holsum</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>unknown_pan viga integral pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Pan Viga Integral Pepin</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>lu_pan mini club bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pan Mini Club Bolin</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>lu_pan viga club bolin_1.28</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pan Viga Club Bolin</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lu_pan viga mini club integral bolin_0.45</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pan Viga Mini Club Integral Bolin</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>unknown_galleta crich wafer cacao_0.18</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Cacao</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>unknown_galleta crich wafer nocciola_0.12</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Nocciola</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>unknown_galleta crich wafer nocciola_0.18</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Nocciola</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unknown_galleta crich wafer vainilla_0.18</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafer Vainilla</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unknown_galleta crich wafers crema cappuccino_0.25</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Galleta Crich Wafers Crema Cappuccino</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unknown_galletas bio snack cakes with leguminous crich_0.07</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Galletas Bio Snack Cakes With Leguminous Crich</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>unknown_galletas crich chocolate wafers_0.25</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Galletas Crich Chocolate Wafers</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unknown_pan de hamburguesa bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesa Bolin</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unknown_pan de hot dog bolin_unknown</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Bolin</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unknown_pan de hot dog holsum_unknown</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Holsum</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unknown_pan viga mediana pepin_0.85</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Pan Viga Mediana Pepin</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unknown_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unknown_viga mediana de pan integral blanco bolin_0.68</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -3546,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,26 +3614,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bolin_pan de hot dog bolin_unknown</t>
+          <t>la libanesa_la libanesa mini pizza pita_unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>La Libanesa Mini Pizza Pita</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>5.05</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bolin_pan viga bolin mini club integral_0.58</t>
+          <t>la libanesa_la libanesa pizza pita integral_unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pan Viga Bolin Mini Club Integral</t>
+          <t>La Libanesa Pizza Pita Integral</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>5.05</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3692,26 +3692,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pepin_pan viga mediana pepin_0.85</t>
+          <t>la libanesa_pan pita integral la libanesa_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pan Viga Mediana Pepin</t>
+          <t>Pan Pita Integral La Libanesa</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>1.81</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3731,26 +3731,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pepin_pan viga pepin club sandwich blanca_0.68</t>
+          <t>la libanesa_pita pizza la libanesa_unknown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pan Viga Pepin Club Sandwich Blanca</t>
+          <t>Pita Pizza La Libanesa</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.36</v>
+        <v>5.21</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3770,26 +3770,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>pepin_pan viga pequena pepin_0.45</t>
+          <t>la libanesa_pita wraps la libanesa_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pan Viga Pequena Pepin</t>
+          <t>Pita Wraps La Libanesa</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3809,26 +3809,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pepin_tortilla integral de harina de trigo pepin_0.42</t>
+          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tortilla Integral De Harina De Trigo Pepin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.77</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3848,26 +3848,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pepin_tortillas de harina de trigo pepin_0.42</t>
+          <t>princesa_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tortillas De Harina De Trigo Pepin</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.77</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3887,26 +3887,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bolin_pan de hot dog bolin_unknown</t>
+          <t>agua vivo_galleta de agua vivo_0.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>Galleta De Agua Vivo</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3926,26 +3926,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pepin_pan viga integral pepin_0.45</t>
+          <t>lavigne_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pan Viga Integral Pepin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3970,21 +3970,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pepin_pan viga mediana pepin_0.85</t>
+          <t>dollys_galletas de noni dollys_0.07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>dollys</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pan Viga Mediana Pepin</t>
+          <t>Galletas De Noni Dollys</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.38</v>
+        <v>0.29</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -4009,21 +4009,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pepin_pan viga mini club integral pepin_0.45</t>
+          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Pepin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.61</v>
+        <v>1.11</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4043,26 +4043,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pepin_pan viga pequena pepin_0.45</t>
+          <t>lavigne_galletas de ajo lavigne_0.14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pan Viga Pequena Pepin</t>
+          <t>Galletas De Ajo Lavigne</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -4087,21 +4087,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bolin_pan de hamburguesa bolin_unknown</t>
+          <t>lavigne_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Bolin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -4126,21 +4126,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bolin_pan de hot dog bolin_unknown</t>
+          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.66</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -4165,21 +4165,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bolin_pan mini club bolin_0.45</t>
+          <t>princesa_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pan Mini Club Bolin</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.93</v>
+        <v>1.09</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -4199,26 +4199,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bolin_pan viga club bolin_1.28</t>
+          <t>agua vivo_galleta de agua vivo_0.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Agua Vivo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pan Viga Club Bolin</t>
+          <t>Galleta De Agua Vivo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.2</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -4238,26 +4238,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bolin_pan viga mini club integral bolin_0.45</t>
+          <t>la libanesa_pan pita integral la libanesa_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Bolin</t>
+          <t>Pan Pita Integral La Libanesa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4277,26 +4277,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bolin_viga mediana de pan integral blanco bolin_0.68</t>
+          <t>la libanesa_pita pizza la libanesa_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+          <t>Pita Pizza La Libanesa</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.58</v>
+        <v>4.75</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -4316,26 +4316,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>holsum_pan de hamburguesa holsum_unknown</t>
+          <t>la libanesa_pita wraps la libanesa_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Holsum</t>
+          <t>Pita Wraps La Libanesa</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.99</v>
+        <v>1.98</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -4355,26 +4355,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pepin_pan viga mediana pepin_0.85</t>
+          <t>lavigne_galletas de ajo lavigne_0.14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pan Viga Mediana Pepin</t>
+          <t>Galletas De Ajo Lavigne</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.22</v>
+        <v>1.41</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -4394,26 +4394,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pepin_pan viga mini club integral pepin_0.45</t>
+          <t>lavigne_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Pepin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.34</v>
+        <v>1.73</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -4433,26 +4433,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pepin_pan viga pequena pepin_0.45</t>
+          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pepin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pan Viga Pequena Pepin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -4477,21 +4477,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bolin_pan de hamburguesa bolin_unknown</t>
+          <t>princesa_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Bolin</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.98</v>
+        <v>1.09</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -4511,26 +4511,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bolin_pan de hot dog bolin_unknown</t>
+          <t>dollys_galletas de noni dollys_0.07</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>dollys</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>Galletas De Noni Dollys</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.66</v>
+        <v>0.25</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -4550,26 +4550,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bolin_pan mini club bolin_0.45</t>
+          <t>la libanesa_pan mini pita al pesto la libanesa_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pan Mini Club Bolin</t>
+          <t>Pan Mini Pita Al Pesto La Libanesa</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -4589,26 +4589,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>bolin_pan viga club bolin_1.28</t>
+          <t>lavigne_galletas de ajo lavigne_0.14</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pan Viga Club Bolin</t>
+          <t>Galletas De Ajo Lavigne</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -4628,26 +4628,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bolin_pan viga mini club integral bolin_0.45</t>
+          <t>lavigne_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Lavigne</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Bolin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -4667,26 +4667,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bolin_viga mediana de pan integral blanco bolin_0.68</t>
+          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bolin</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.58</v>
+        <v>1.17</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -4706,26 +4706,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>holsum_pan de hamburguesa holsum_unknown</t>
+          <t>princesa_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Holsum</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.01</v>
+        <v>1.17</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -4745,26 +4745,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>holsum_pan de hot dog holsum_unknown</t>
+          <t>la libanesa_pan pita integral la libanesa_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>La Libanesa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Holsum</t>
+          <t>Pan Pita Integral La Libanesa</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.01</v>
+        <v>1.71</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -4784,26 +4784,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>holsum_pan viga de mantequilla holsum_0.56</t>
+          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pan Viga De Mantequilla Holsum</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.36</v>
+        <v>1.09</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -4823,26 +4823,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>holsum_pan viga de papa holsum_0.56</t>
+          <t>princesa_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Holsum</t>
+          <t>Princesa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pan Viga De Papa Holsum</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.36</v>
+        <v>1.09</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -4853,864 +4853,6 @@
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>pepin_pan viga mediana pepin_0.85</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Pepin</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Pan Viga Mediana Pepin</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>pepin_pan viga mini club integral pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Pepin</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Pan Viga Mini Club Integral Pepin</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>pepin_pan viga pequena pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Pepin</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Pan Viga Pequena Pepin</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>bolin_pan mini club bolin_0.45</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Pan Mini Club Bolin</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>holsum_pan de hot dog holsum_unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Holsum</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Holsum</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>pepin_pan viga integral pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Pepin</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Pan Viga Integral Pepin</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>bolin_pan de hamburguesa bolin_unknown</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Pan De Hamburguesa Bolin</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>bolin_pan de hot dog bolin_unknown</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Bolin</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>bolin_pan mini club bolin_0.45</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Pan Mini Club Bolin</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>bolin_pan viga club bolin_1.28</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Pan Viga Club Bolin</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>bolin_pan viga mini club integral bolin_0.45</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Pan Viga Mini Club Integral Bolin</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>bolin_viga mediana de pan integral blanco bolin_0.68</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Bolin</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>crich_galleta crich wafer cacao_0.18</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Cacao</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>crich_galleta crich wafer nocciola_0.12</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Nocciola</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>crich_galleta crich wafer nocciola_0.18</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Nocciola</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>crich_galleta crich wafer vainilla_0.18</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Vainilla</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>crich_galleta crich wafers crema cappuccino_0.25</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafers Crema Cappuccino</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>crich_galletas bio snack cakes with leguminous crich_0.07</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Galletas Bio Snack Cakes With Leguminous Crich</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>crich_galletas crich chocolate wafers_0.25</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Crich</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Galletas Crich Chocolate Wafers</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>holsum_pan de hot dog holsum_unknown</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Holsum</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Holsum</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>pepin_pan viga mediana pepin_0.85</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Pepin</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Pan Viga Mediana Pepin</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>pepin_pan viga pequena pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Pepin</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Pan Viga Pequena Pepin</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5723,7 +4865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5791,12 +4933,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lu_pan viga bolin mini club integral_0.58</t>
+          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5809,11 +4951,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pan Viga Bolin Mini Club Integral</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.96</v>
+        <v>1.09</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5830,12 +4972,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lu_pan viga pepin club sandwich blanca_0.68</t>
+          <t>unknown_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -5843,16 +4985,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pan Viga Pepin Club Sandwich Blanca</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>1.09</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5869,12 +5011,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_pan de hot dog bolin_unknown</t>
+          <t>unknown_la libanesa mini pizza pita_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5887,11 +5029,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>La Libanesa Mini Pizza Pita</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.57</v>
+        <v>5.05</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5908,12 +5050,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown_pan viga mediana pepin_0.85</t>
+          <t>unknown_la libanesa pizza pita integral_unknown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5926,11 +5068,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pan Viga Mediana Pepin</t>
+          <t>La Libanesa Pizza Pita Integral</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.36</v>
+        <v>5.05</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5947,12 +5089,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_pan viga pequena pepin_0.45</t>
+          <t>unknown_pan pita integral la libanesa_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5965,11 +5107,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pan Viga Pequena Pepin</t>
+          <t>Pan Pita Integral La Libanesa</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5986,12 +5128,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_tortilla integral de harina de trigo pepin_0.42</t>
+          <t>unknown_pita pizza la libanesa_unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -6004,11 +5146,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tortilla Integral De Harina De Trigo Pepin</t>
+          <t>Pita Pizza La Libanesa</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.77</v>
+        <v>5.21</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -6025,12 +5167,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_tortillas de harina de trigo pepin_0.42</t>
+          <t>unknown_pita wraps la libanesa_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -6043,11 +5185,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tortillas De Harina De Trigo Pepin</t>
+          <t>Pita Wraps La Libanesa</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6064,12 +5206,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lu_pan viga mini club integral pepin_0.45</t>
+          <t>unknown_galleta de agua vivo_0.14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -6077,16 +5219,16 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Pepin</t>
+          <t>Galleta De Agua Vivo</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.61</v>
+        <v>1.66</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -6103,12 +5245,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_pan de hot dog bolin_unknown</t>
+          <t>unknown_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -6121,11 +5263,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -6147,7 +5289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unknown_pan viga integral pepin_0.45</t>
+          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -6155,16 +5297,16 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pan Viga Integral Pepin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6186,7 +5328,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown_pan viga mediana pepin_0.85</t>
+          <t>unknown_galletas de noni dollys_0.07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -6199,11 +5341,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pan Viga Mediana Pepin</t>
+          <t>Galletas De Noni Dollys</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.38</v>
+        <v>0.29</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -6220,12 +5362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unknown_pan viga pequena pepin_0.45</t>
+          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -6233,16 +5375,16 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pan Viga Pequena Pepin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -6264,7 +5406,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lu_pan mini club bolin_0.45</t>
+          <t>unknown_galletas de ajo lavigne_0.14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -6272,16 +5414,16 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pan Mini Club Bolin</t>
+          <t>Galletas De Ajo Lavigne</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.93</v>
+        <v>1.41</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6303,7 +5445,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lu_pan viga club bolin_1.28</t>
+          <t>unknown_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -6311,16 +5453,16 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pan Viga Club Bolin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6342,7 +5484,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lu_pan viga mini club integral bolin_0.45</t>
+          <t>unknown_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6350,16 +5492,16 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Bolin</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.96</v>
+        <v>1.09</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -6376,12 +5518,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lu_pan viga mini club integral pepin_0.45</t>
+          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6394,11 +5536,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Pepin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.34</v>
+        <v>1.09</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -6415,12 +5557,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown_pan de hamburguesa bolin_unknown</t>
+          <t>unknown_galleta de agua vivo_0.14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6433,11 +5575,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Bolin</t>
+          <t>Galleta De Agua Vivo</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -6454,12 +5596,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown_pan de hamburguesa holsum_unknown</t>
+          <t>unknown_galletas de ajo lavigne_0.14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -6472,11 +5614,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Holsum</t>
+          <t>Galletas De Ajo Lavigne</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.99</v>
+        <v>1.41</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -6493,12 +5635,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unknown_pan de hot dog bolin_unknown</t>
+          <t>unknown_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -6511,11 +5653,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -6532,12 +5674,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unknown_pan viga mediana pepin_0.85</t>
+          <t>unknown_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -6550,11 +5692,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pan Viga Mediana Pepin</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.22</v>
+        <v>1.09</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -6571,12 +5713,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown_pan viga pequena pepin_0.45</t>
+          <t>unknown_pan pita integral la libanesa_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6589,11 +5731,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pan Viga Pequena Pepin</t>
+          <t>Pan Pita Integral La Libanesa</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -6610,12 +5752,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_viga mediana de pan integral blanco bolin_0.68</t>
+          <t>unknown_pita pizza la libanesa_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -6628,11 +5770,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
+          <t>Pita Pizza La Libanesa</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.58</v>
+        <v>4.75</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -6654,7 +5796,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lu_pan mini club bolin_0.45</t>
+          <t>unknown_pita wraps la libanesa_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -6662,16 +5804,16 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pan Mini Club Bolin</t>
+          <t>Pita Wraps La Libanesa</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -6688,12 +5830,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>lu_pan viga club bolin_1.28</t>
+          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -6706,11 +5848,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pan Viga Club Bolin</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>1.17</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -6727,12 +5869,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lu_pan viga mini club integral bolin_0.45</t>
+          <t>unknown_galletas de ajo lavigne_0.14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -6740,16 +5882,16 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Bolin</t>
+          <t>Galletas De Ajo Lavigne</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -6766,12 +5908,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lu_pan viga mini club integral pepin_0.45</t>
+          <t>unknown_galletas de noni dollys_0.07</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -6779,16 +5921,16 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Club Integral Pepin</t>
+          <t>Galletas De Noni Dollys</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.34</v>
+        <v>0.25</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -6805,12 +5947,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_pan de hamburguesa bolin_unknown</t>
+          <t>unknown_galletas integrales lavigne_0.2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -6823,11 +5965,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Bolin</t>
+          <t>Galletas Integrales Lavigne</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -6844,12 +5986,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_pan de hamburguesa holsum_unknown</t>
+          <t>unknown_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -6862,11 +6004,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Holsum</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.01</v>
+        <v>1.17</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -6883,12 +6025,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_pan de hot dog bolin_unknown</t>
+          <t>unknown_pan mini pita al pesto la libanesa_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6901,11 +6043,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Bolin</t>
+          <t>Pan Mini Pita Al Pesto La Libanesa</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -6922,12 +6064,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown_pan de hot dog holsum_unknown</t>
+          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6935,16 +6077,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Holsum</t>
+          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.01</v>
+        <v>1.09</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -6961,12 +6103,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown_pan viga de mantequilla holsum_0.56</t>
+          <t>unknown_galletas integrales princesa 9 und_0.31</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6979,11 +6121,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pan Viga De Mantequilla Holsum</t>
+          <t>Galletas Integrales Princesa 9 Und</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.36</v>
+        <v>1.09</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -7000,12 +6142,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown_pan viga de papa holsum_0.56</t>
+          <t>unknown_pan pita integral la libanesa_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -7018,11 +6160,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pan Viga De Papa Holsum</t>
+          <t>Pan Pita Integral La Libanesa</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.36</v>
+        <v>1.71</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -7030,864 +6172,6 @@
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>unknown_pan viga mediana pepin_0.85</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Pan Viga Mediana Pepin</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>unknown_pan viga pequena pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Pan Viga Pequena Pepin</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>unknown_viga mediana de pan integral blanco bolin_0.68</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>lu_pan mini club bolin_0.45</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Pan Mini Club Bolin</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>unknown_pan de hot dog holsum_unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Holsum</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>unknown_pan viga integral pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Pan Viga Integral Pepin</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>lu_pan mini club bolin_0.45</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Pan Mini Club Bolin</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>lu_pan viga club bolin_1.28</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Pan Viga Club Bolin</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>lu_pan viga mini club integral bolin_0.45</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Pan Viga Mini Club Integral Bolin</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>unknown_galleta crich wafer cacao_0.18</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Cacao</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>unknown_galleta crich wafer nocciola_0.12</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Nocciola</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>unknown_galleta crich wafer nocciola_0.18</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Nocciola</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>unknown_galleta crich wafer vainilla_0.18</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafer Vainilla</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>unknown_galleta crich wafers crema cappuccino_0.25</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Galleta Crich Wafers Crema Cappuccino</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>unknown_galletas bio snack cakes with leguminous crich_0.07</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Galletas Bio Snack Cakes With Leguminous Crich</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>unknown_galletas crich chocolate wafers_0.25</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Galletas Crich Chocolate Wafers</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>unknown_pan de hamburguesa bolin_unknown</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Pan De Hamburguesa Bolin</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>unknown_pan de hot dog bolin_unknown</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Bolin</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>unknown_pan de hot dog holsum_unknown</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Holsum</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>unknown_pan viga mediana pepin_0.85</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Pan Viga Mediana Pepin</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>unknown_pan viga pequena pepin_0.45</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Pan Viga Pequena Pepin</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>unknown_viga mediana de pan integral blanco bolin_0.68</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Viga Mediana De Pan Integral Blanco Bolin</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -3546,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3619,21 +3619,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>la libanesa_la libanesa mini pizza pita_unknown</t>
+          <t>bisco pan_bisco pan galleta clas integral_0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>La Libanesa Mini Pizza Pita</t>
+          <t>Bisco Pan Galleta Clas Integral</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.05</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3658,21 +3658,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>la libanesa_la libanesa pizza pita integral_unknown</t>
+          <t>bisco pan_bisco pan galleta constanza_0.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>La Libanesa Pizza Pita Integral</t>
+          <t>Bisco Pan Galleta Constanza</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.05</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3697,21 +3697,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>la libanesa_pan pita integral la libanesa_unknown</t>
+          <t>bisco pan_bisco pan pan integral mielpasas_0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pan Pita Integral La Libanesa</t>
+          <t>Bisco Pan Pan Integral Mielpasas</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3736,21 +3736,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>la libanesa_pita pizza la libanesa_unknown</t>
+          <t>bisco pan_bisco pan viga integral_0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pita Pizza La Libanesa</t>
+          <t>Bisco Pan Viga Integral</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.21</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3775,21 +3775,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>la libanesa_pita wraps la libanesa_unknown</t>
+          <t>quadratini_galletas quadratini cacao loacker_0.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pita Wraps La Libanesa</t>
+          <t>Galletas Quadratini Cacao Loacker</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3814,21 +3814,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>quadratini_galletas quadratini cocoa milk loacker_0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Galletas Quadratini Cocoa Milk Loacker</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3853,21 +3853,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>princesa_galletas integrales princesa 9 und_0.31</t>
+          <t>quadratini_galletas quadratini coconut loacker_0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Galletas Quadratini Coconut Loacker</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>2.99</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3887,26 +3887,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>agua vivo_galleta de agua vivo_0.14</t>
+          <t>quadratini_galletas quadratini tiramisu loacker_0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Agua Vivo</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galleta De Agua Vivo</t>
+          <t>Galletas Quadratini Tiramisu Loacker</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3931,21 +3931,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lavigne_galletas integrales lavigne_0.2</t>
+          <t>la real_tortilla de trigo 6 la real_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Tortilla De Trigo 6 La Real</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3965,26 +3965,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dollys_galletas de noni dollys_0.07</t>
+          <t>la real_tortillas nicaraguenses la real_0.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>dollys</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galletas De Noni Dollys</t>
+          <t>Tortillas Nicaraguenses La Real</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.29</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -4004,26 +4004,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>la real_tortilla trigo para fajitas 6 la real_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.11</v>
+        <v>3.09</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4048,21 +4048,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lavigne_galletas de ajo lavigne_0.14</t>
+          <t>quadratini_galletas wafer quadratini napolitaner loacker_0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galletas De Ajo Lavigne</t>
+          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -4087,21 +4087,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lavigne_galletas integrales lavigne_0.2</t>
+          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -4121,26 +4121,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>el charrito_mini tortilla dura el charrito_unknown</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Mini Tortilla Dura El Charrito</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>2.71</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -4160,26 +4160,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>princesa_galletas integrales princesa 9 und_0.31</t>
+          <t>royal dansk_galletas danesa royal dansk_0.34</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Galletas Danesa Royal Dansk</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.09</v>
+        <v>6.96</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -4204,21 +4204,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>agua vivo_galleta de agua vivo_0.14</t>
+          <t>el charrito_mini tortilla dura el charrito_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Agua Vivo</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galleta De Agua Vivo</t>
+          <t>Mini Tortilla Dura El Charrito</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>2.72</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -4243,21 +4243,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>la libanesa_pan pita integral la libanesa_unknown</t>
+          <t>el charrito_tortilla de maiz blanco para taco 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pan Pita Integral La Libanesa</t>
+          <t>Tortilla De Maiz Blanco Para Taco 5 El Charrito</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.71</v>
+        <v>1.12</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4282,21 +4282,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>la libanesa_pita pizza la libanesa_unknown</t>
+          <t>la real_tortilla de trigo 6 la real_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pita Pizza La Libanesa</t>
+          <t>Tortilla De Trigo 6 La Real</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.75</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -4321,21 +4321,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>la libanesa_pita wraps la libanesa_unknown</t>
+          <t>la real_tortilla integral para fajitas 6 la real_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pita Wraps La Libanesa</t>
+          <t>Tortilla Integral Para Fajitas 6 La Real</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>3.09</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -4360,21 +4360,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lavigne_galletas de ajo lavigne_0.14</t>
+          <t>la real_tortilla trigo para fajitas 6 la real_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>La Real</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Galletas De Ajo Lavigne</t>
+          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.41</v>
+        <v>3.09</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -4399,21 +4399,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lavigne_galletas integrales lavigne_0.2</t>
+          <t>quadratini_galletas quadratini cacao loacker_0.12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Galletas Quadratini Cacao Loacker</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -4438,21 +4438,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>quadratini_galletas quadratini cocoa milk loacker_0.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Galletas Quadratini Cocoa Milk Loacker</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -4477,21 +4477,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>princesa_galletas integrales princesa 9 und_0.31</t>
+          <t>quadratini_galletas quadratini coconut loacker_0.12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Galletas Quadratini Coconut Loacker</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -4511,26 +4511,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dollys_galletas de noni dollys_0.07</t>
+          <t>quadratini_galletas quadratini tiramisu loacker_0.11</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>dollys</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Galletas De Noni Dollys</t>
+          <t>Galletas Quadratini Tiramisu Loacker</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.25</v>
+        <v>3.15</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -4550,26 +4550,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>la libanesa_pan mini pita al pesto la libanesa_unknown</t>
+          <t>quadratini_galletas wafer quadratini napolitaner loacker_0.12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pan Mini Pita Al Pesto La Libanesa</t>
+          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -4589,26 +4589,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lavigne_galletas de ajo lavigne_0.14</t>
+          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Quadratini</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Galletas De Ajo Lavigne</t>
+          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -4628,26 +4628,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lavigne_galletas integrales lavigne_0.2</t>
+          <t>royal dansk_galletas danesa royal dansk_0.34</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lavigne</t>
+          <t>Royal Dansk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Galletas Danesa Royal Dansk</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.66</v>
+        <v>6.97</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -4672,21 +4672,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>bisco pan_bisco pan galleta clas integral_0.22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Bisco Pan Galleta Clas Integral</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -4711,21 +4711,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>princesa_galletas integrales princesa 9 und_0.31</t>
+          <t>bisco pan_bisco pan galleta constanza_0.28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>Bisco Pan</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Bisco Pan Galleta Constanza</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -4745,26 +4745,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Ritmo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>la libanesa_pan pita integral la libanesa_unknown</t>
+          <t>el charrito_tortilla grande de trigo el charrito 5 u_0.35</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>La Libanesa</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pan Pita Integral La Libanesa</t>
+          <t>Tortilla Grande De Trigo El Charrito 5 U</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -4784,26 +4784,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Ritmo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>princesa_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>el charrito_tortilla taco integral el charrito 10 u_0.22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Tortilla Taco Integral El Charrito 10 U</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -4828,21 +4828,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>princesa_galletas integrales princesa 9 und_0.31</t>
+          <t>el charrito_mini tortilla dura el charrito_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Princesa</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Mini Tortilla Dura El Charrito</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.09</v>
+        <v>2.77</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -4853,6 +4853,591 @@
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>el corte ingl s_galleta el corte ingles cookids d_0.6</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>El Corte Inglés</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Galleta El Corte Ingles Cookids D</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>la real_tortilla integral para fajitas 6 la real_unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>La Real</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tortilla Integral Para Fajitas 6 La Real</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>la real_tortilla trigo para fajitas 6 la real_unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>La Real</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>la real_tortillas burrito la real_unknown</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>La Real</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Tortillas Burrito La Real</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>wala_bandeja redonda wala cupcake_unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bandeja Redonda Wala Cupcake</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wala_galleta wafer fresa wala 101_0.24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Galleta Wafer Fresa Wala 101</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>wala_galleta wafer limon wala_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Galleta Wafer Limon Wala</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>wala_galleta wafer vainilla wala 101_0.24</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Galleta Wafer Vainilla Wala 101</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>wala_mezcla bizcocho red velvet wala_0.35</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Mezcla Bizcocho Red Velvet Wala</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>wala_mezcla de bizcocho wala chocolate_0.35</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mezcla De Bizcocho Wala Chocolate</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>wala_pan mini wala buffet_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Pan Mini Wala Buffet</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>wala_pan viga wala integral_0.57</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Pan Viga Wala Integral</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wala_pan wala mini croissant_0.43</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Pan Wala Mini Croissant</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wala_plastico knife wrap wala_unknown</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Plastico Knife Wrap Wala</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wala_plastico rolled wrap refill wala_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Wala</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Plastico Rolled Wrap Refill Wala</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4865,7 +5450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4938,7 +5523,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>bisco_bisco pan galleta clas integral_0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -4946,16 +5531,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Bisco Pan Galleta Clas Integral</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4977,7 +5562,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales princesa 9 und_0.31</t>
+          <t>bisco_bisco pan galleta constanza_0.28</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -4985,16 +5570,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Bisco Pan Galleta Constanza</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5016,7 +5601,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_la libanesa mini pizza pita_unknown</t>
+          <t>bisco_bisco pan pan integral mielpasas_0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5024,16 +5609,16 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>La Libanesa Mini Pizza Pita</t>
+          <t>Bisco Pan Pan Integral Mielpasas</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.05</v>
+        <v>1.89</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5055,7 +5640,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown_la libanesa pizza pita integral_unknown</t>
+          <t>bisco_bisco pan viga integral_0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5063,16 +5648,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>La Libanesa Pizza Pita Integral</t>
+          <t>Bisco Pan Viga Integral</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.05</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5094,7 +5679,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_pan pita integral la libanesa_unknown</t>
+          <t>unknown_galletas quadratini cacao loacker_0.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5107,11 +5692,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pan Pita Integral La Libanesa</t>
+          <t>Galletas Quadratini Cacao Loacker</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.81</v>
+        <v>3.15</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5133,7 +5718,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_pita pizza la libanesa_unknown</t>
+          <t>unknown_galletas quadratini cocoa milk loacker_0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5146,11 +5731,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pita Pizza La Libanesa</t>
+          <t>Galletas Quadratini Cocoa Milk Loacker</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.21</v>
+        <v>3.15</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5172,7 +5757,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_pita wraps la libanesa_unknown</t>
+          <t>unknown_galletas quadratini coconut loacker_0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5185,11 +5770,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pita Wraps La Libanesa</t>
+          <t>Galletas Quadratini Coconut Loacker</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5206,12 +5791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_galleta de agua vivo_0.14</t>
+          <t>unknown_galletas quadratini tiramisu loacker_0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -5224,11 +5809,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Galleta De Agua Vivo</t>
+          <t>Galletas Quadratini Tiramisu Loacker</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.66</v>
+        <v>3.15</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5250,7 +5835,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales lavigne_0.2</t>
+          <t>unknown_tortilla de trigo 6 la real_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5263,11 +5848,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Tortilla De Trigo 6 La Real</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5284,12 +5869,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>unknown_tortillas nicaraguenses la real_0.68</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5297,16 +5882,16 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Tortillas Nicaraguenses La Real</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5323,12 +5908,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown_galletas de noni dollys_0.07</t>
+          <t>unknown_galletas wafer quadratini napolitaner loacker_0.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -5341,11 +5926,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Galletas De Noni Dollys</t>
+          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.29</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5367,7 +5952,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>unknown_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5375,16 +5960,16 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5406,7 +5991,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unknown_galletas de ajo lavigne_0.14</t>
+          <t>unknown_tortilla trigo para fajitas 6 la real_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5419,11 +6004,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Galletas De Ajo Lavigne</t>
+          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.41</v>
+        <v>3.09</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5440,12 +6025,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales lavigne_0.2</t>
+          <t>unknown_galletas danesa royal dansk_0.34</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5458,11 +6043,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Galletas Danesa Royal Dansk</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.73</v>
+        <v>6.96</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5479,12 +6064,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales princesa 9 und_0.31</t>
+          <t>unknown_mini tortilla dura el charrito_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5497,11 +6082,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Mini Tortilla Dura El Charrito</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.09</v>
+        <v>2.71</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5523,7 +6108,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>unknown_galletas danesa royal dansk_0.34</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -5531,16 +6116,16 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Galletas Danesa Royal Dansk</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.09</v>
+        <v>6.97</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5562,7 +6147,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown_galleta de agua vivo_0.14</t>
+          <t>unknown_galletas quadratini cacao loacker_0.12</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5575,11 +6160,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Galleta De Agua Vivo</t>
+          <t>Galletas Quadratini Cacao Loacker</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.82</v>
+        <v>3.15</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5601,7 +6186,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown_galletas de ajo lavigne_0.14</t>
+          <t>unknown_galletas quadratini cocoa milk loacker_0.12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5614,11 +6199,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Galletas De Ajo Lavigne</t>
+          <t>Galletas Quadratini Cocoa Milk Loacker</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5640,7 +6225,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales lavigne_0.2</t>
+          <t>unknown_galletas quadratini coconut loacker_0.12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5653,11 +6238,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Galletas Quadratini Coconut Loacker</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.73</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5679,7 +6264,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales princesa 9 und_0.31</t>
+          <t>unknown_galletas quadratini tiramisu loacker_0.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5692,11 +6277,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Galletas Quadratini Tiramisu Loacker</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5718,7 +6303,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown_pan pita integral la libanesa_unknown</t>
+          <t>unknown_galletas wafer quadratini napolitaner loacker_0.12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -5731,11 +6316,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pan Pita Integral La Libanesa</t>
+          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5757,7 +6342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_pita pizza la libanesa_unknown</t>
+          <t>unknown_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -5770,11 +6355,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pita Pizza La Libanesa</t>
+          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -5796,7 +6381,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_pita wraps la libanesa_unknown</t>
+          <t>unknown_mini tortilla dura el charrito_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -5809,11 +6394,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pita Wraps La Libanesa</t>
+          <t>Mini Tortilla Dura El Charrito</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -5830,12 +6415,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>unknown_tortilla de maiz blanco para taco 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -5843,16 +6428,16 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Tortilla De Maiz Blanco Para Taco 5 El Charrito</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5869,12 +6454,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_galletas de ajo lavigne_0.14</t>
+          <t>unknown_tortilla de trigo 6 la real_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -5887,11 +6472,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Galletas De Ajo Lavigne</t>
+          <t>Tortilla De Trigo 6 La Real</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5908,12 +6493,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_galletas de noni dollys_0.07</t>
+          <t>unknown_tortilla integral para fajitas 6 la real_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -5926,11 +6511,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Galletas De Noni Dollys</t>
+          <t>Tortilla Integral Para Fajitas 6 La Real</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.25</v>
+        <v>3.09</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5947,12 +6532,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales lavigne_0.2</t>
+          <t>unknown_tortilla trigo para fajitas 6 la real_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -5965,11 +6550,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Galletas Integrales Lavigne</t>
+          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.66</v>
+        <v>3.09</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5991,7 +6576,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales princesa 9 und_0.31</t>
+          <t>bisco_bisco pan galleta clas integral_0.22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -5999,16 +6584,16 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Bisco Pan Galleta Clas Integral</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -6030,7 +6615,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_pan mini pita al pesto la libanesa_unknown</t>
+          <t>bisco_bisco pan galleta constanza_0.28</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6038,16 +6623,16 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bisco</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pan Mini Pita Al Pesto La Libanesa</t>
+          <t>Bisco Pan Galleta Constanza</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -6064,12 +6649,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Ritmo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lu_galleta club sabor a mantequilla princesa 9 und_0.31</t>
+          <t>unknown_tortilla grande de trigo el charrito 5 u_0.35</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6077,16 +6662,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Galleta Club Sabor A Mantequilla Princesa 9 Und</t>
+          <t>Tortilla Grande De Trigo El Charrito 5 U</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -6103,12 +6688,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Ritmo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown_galletas integrales princesa 9 und_0.31</t>
+          <t>unknown_tortilla taco integral el charrito 10 u_0.22</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6121,11 +6706,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Galletas Integrales Princesa 9 Und</t>
+          <t>Tortilla Taco Integral El Charrito 10 U</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6147,7 +6732,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown_pan pita integral la libanesa_unknown</t>
+          <t>unknown_bandeja redonda wala cupcake_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6160,11 +6745,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pan Pita Integral La Libanesa</t>
+          <t>Bandeja Redonda Wala Cupcake</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.71</v>
+        <v>0.73</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6172,6 +6757,591 @@
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unknown_galleta el corte ingles cookids d_0.6</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Galleta El Corte Ingles Cookids D</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>unknown_galleta wafer fresa wala 101_0.24</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Galleta Wafer Fresa Wala 101</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>unknown_galleta wafer limon wala_unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Galleta Wafer Limon Wala</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>unknown_galleta wafer vainilla wala 101_0.24</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Galleta Wafer Vainilla Wala 101</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>unknown_mezcla bizcocho red velvet wala_0.35</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Mezcla Bizcocho Red Velvet Wala</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>unknown_mezcla de bizcocho wala chocolate_0.35</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Mezcla De Bizcocho Wala Chocolate</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>unknown_mini tortilla dura el charrito_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Mini Tortilla Dura El Charrito</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>unknown_pan mini wala buffet_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Pan Mini Wala Buffet</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>unknown_pan viga wala integral_0.57</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pan Viga Wala Integral</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>unknown_pan wala mini croissant_0.43</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Pan Wala Mini Croissant</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>unknown_plastico knife wrap wala_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Plastico Knife Wrap Wala</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>unknown_plastico rolled wrap refill wala_unknown</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Plastico Rolled Wrap Refill Wala</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unknown_tortilla integral para fajitas 6 la real_unknown</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Tortilla Integral Para Fajitas 6 La Real</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unknown_tortilla trigo para fajitas 6 la real_unknown</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unknown_tortillas burrito la real_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Tortillas Burrito La Real</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -3546,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,26 +3614,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bisco pan_bisco pan galleta clas integral_0.22</t>
+          <t>ecovida_galleta ecovida sin coco_0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
+          <t>Galleta Ecovida Sin Gluten Coco</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>3.41</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bisco pan_bisco pan galleta constanza_0.28</t>
+          <t>ecovida_galleta sin berrie ecovida_0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Constanza</t>
+          <t>Galleta Sin Gluten Berrie Ecovida</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3692,26 +3692,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bisco pan_bisco pan pan integral mielpasas_0.38</t>
+          <t>ecovida_galletas sin azucar rellenas de higo ecovida_0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bisco Pan Pan Integral Mielpasas</t>
+          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3731,26 +3731,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bisco pan_bisco pan viga integral_0.45</t>
+          <t>gri gri_galleta integral con ajonjoli gri gri_unknown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Gri Gri</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bisco Pan Viga Integral</t>
+          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3770,26 +3770,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini cacao loacker_0.12</t>
+          <t>mestemacher_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Mestemacher</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cacao Loacker</t>
+          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3809,26 +3809,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini cocoa milk loacker_0.12</t>
+          <t>mestemacher_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Mestemacher</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cocoa Milk Loacker</t>
+          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3848,26 +3848,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini coconut loacker_0.12</t>
+          <t>over the top_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Coconut Loacker</t>
+          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.99</v>
+        <v>4.44</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3887,26 +3887,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini tiramisu loacker_0.11</t>
+          <t>over the top_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Tiramisu Loacker</t>
+          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3926,26 +3926,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>la real_tortilla de trigo 6 la real_unknown</t>
+          <t>over the top_capacillos para mini cupcakes over the top_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tortilla De Trigo 6 La Real</t>
+          <t>Capacillos Para Mini Cupcakes Over The Top</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3965,26 +3965,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>la real_tortillas nicaraguenses la real_0.68</t>
+          <t>spongy_bizcocho de vainilla spongy_0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Spongy</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tortillas Nicaraguenses La Real</t>
+          <t>Bizcocho De Vainilla Spongy</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -4009,21 +4009,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>la real_tortilla trigo para fajitas 6 la real_unknown</t>
+          <t>sweet ps_bizcocho de guineo rebanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.09</v>
+        <v>6.02</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4048,21 +4048,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>quadratini_galletas wafer quadratini napolitaner loacker_0.12</t>
+          <t>sweet ps_bizcocho marmol rabanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
+          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>6.02</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -4087,21 +4087,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
+          <t>sweet ps_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
+          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>6.02</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -4126,21 +4126,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>el charrito_mini tortilla dura el charrito_unknown</t>
+          <t>bgourmet_pan brioche chocolatechip bgourmet_0.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mini Tortilla Dura El Charrito</t>
+          <t>Pan Brioche Chocolatechip Bgourmet</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.71</v>
+        <v>5.85</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -4165,21 +4165,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>royal dansk_galletas danesa royal dansk_0.34</t>
+          <t>bgourmet_pan brioche lonjeado bgourmet_0.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Royal Dansk</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galletas Danesa Royal Dansk</t>
+          <t>Pan Brioche Lonjeado Bgourmet</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.96</v>
+        <v>6.85</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -4199,26 +4199,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>el charrito_mini tortilla dura el charrito_unknown</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mini Tortilla Dura El Charrito</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.72</v>
+        <v>3.39</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -4238,26 +4238,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz blanco para taco 5 el charrito_unknown</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Blanco Para Taco 5 El Charrito</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4277,26 +4277,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>la real_tortilla de trigo 6 la real_unknown</t>
+          <t>green is my thing_galleta de chocolate chip artesanal green is my thing_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Green Is My Thing</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tortilla De Trigo 6 La Real</t>
+          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>3.55</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -4316,26 +4316,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>la real_tortilla integral para fajitas 6 la real_unknown</t>
+          <t>green is my thing_galletas artesanales de avena green is my thing_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Green Is My Thing</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tortilla Integral Para Fajitas 6 La Real</t>
+          <t>Galletas Artesanales De Avena Green Is My Thing</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.09</v>
+        <v>3.55</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -4355,26 +4355,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>la real_tortilla trigo para fajitas 6 la real_unknown</t>
+          <t>gri gri_galleta integral con ajonjoli gri gri_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Gri Gri</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.09</v>
+        <v>1.81</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -4394,26 +4394,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini cacao loacker_0.12</t>
+          <t>ita abu_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Ita Abu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cacao Loacker</t>
+          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.15</v>
+        <v>2.44</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -4433,26 +4433,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini cocoa milk loacker_0.12</t>
+          <t>mandul_mini muffins choco chips mandul_0.2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cocoa Milk Loacker</t>
+          <t>Mini Muffins Choco Chips Mandul</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.15</v>
+        <v>3.79</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -4472,26 +4472,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini coconut loacker_0.12</t>
+          <t>mandul_mini muffins choco stars mandul_0.21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Coconut Loacker</t>
+          <t>Mini Muffins Choco Stars Mandul</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.15</v>
+        <v>3.79</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -4511,26 +4511,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>quadratini_galletas quadratini tiramisu loacker_0.11</t>
+          <t>mandul_mini muffins rellenos de fresa mandul_0.21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Tiramisu Loacker</t>
+          <t>Mini Muffins Rellenos De Fresa Mandul</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.15</v>
+        <v>3.79</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -4550,26 +4550,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>quadratini_galletas wafer quadratini napolitaner loacker_0.12</t>
+          <t>repeat_galleta de avena vegan repeat_0.04</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.15</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -4589,26 +4589,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>quadratini_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
+          <t>repeat_galleta de avena vegan repeat_0.1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Quadratini</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.15</v>
+        <v>4.74</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -4628,26 +4628,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>royal dansk_galletas danesa royal dansk_0.34</t>
+          <t>spongy_bizcocho de vainilla spongy_0.15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Royal Dansk</t>
+          <t>Spongy</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Galletas Danesa Royal Dansk</t>
+          <t>Bizcocho De Vainilla Spongy</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6.97</v>
+        <v>1.17</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -4667,26 +4667,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bisco pan_bisco pan galleta clas integral_0.22</t>
+          <t>sweet ps_cup cake de vainilla con chispas sweet ps_0.28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
+          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.41</v>
+        <v>5.05</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -4706,26 +4706,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bisco pan_bisco pan galleta constanza_0.28</t>
+          <t>sweet ps_mini brownies sweet ps_0.3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bisco Pan</t>
+          <t>Sweet Ps</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Constanza</t>
+          <t>Mini Brownies Sweet Ps</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.82</v>
+        <v>5.69</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -4745,26 +4745,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ritmo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>el charrito_tortilla grande de trigo el charrito 5 u_0.35</t>
+          <t>bgourmet_pan brioche chocolatechip bgourmet_0.4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tortilla Grande De Trigo El Charrito 5 U</t>
+          <t>Pan Brioche Chocolatechip Bgourmet</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.46</v>
+        <v>5.86</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -4784,26 +4784,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ritmo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>el charrito_tortilla taco integral el charrito 10 u_0.22</t>
+          <t>bgourmet_pan brioche lonjeado bgourmet_0.5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>BGourmet</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tortilla Taco Integral El Charrito 10 U</t>
+          <t>Pan Brioche Lonjeado Bgourmet</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.19</v>
+        <v>6.86</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -4823,26 +4823,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>el charrito_mini tortilla dura el charrito_unknown</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mini Tortilla Dura El Charrito</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.77</v>
+        <v>3.41</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -4862,26 +4862,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>el corte ingl s_galleta el corte ingles cookids d_0.6</t>
+          <t>dbl_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>El Corte Inglés</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Galleta El Corte Ingles Cookids D</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5.31</v>
+        <v>6.42</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -4901,26 +4901,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>la real_tortilla integral para fajitas 6 la real_unknown</t>
+          <t>ecovida_galleta de chocolate chips sin ecovida_0.15</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tortilla Integral Para Fajitas 6 La Real</t>
+          <t>Galleta De Chocolate Chips Sin Gluten Ecovida</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.09</v>
+        <v>3.72</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -4940,26 +4940,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>la real_tortilla trigo para fajitas 6 la real_unknown</t>
+          <t>ecovida_galletas sin azucar rellenas de higo ecovida_0.15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Ecovida</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -4979,26 +4979,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>la real_tortillas burrito la real_unknown</t>
+          <t>green is my thing_galleta de chocolate chip artesanal green is my thing_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>La Real</t>
+          <t>Green Is My Thing</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tortillas Burrito La Real</t>
+          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.93</v>
+        <v>3.56</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -5018,26 +5018,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>wala_bandeja redonda wala cupcake_unknown</t>
+          <t>green is my thing_galletas artesanales de avena green is my thing_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Green Is My Thing</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bandeja Redonda Wala Cupcake</t>
+          <t>Galletas Artesanales De Avena Green Is My Thing</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.73</v>
+        <v>3.56</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -5057,26 +5057,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>wala_galleta wafer fresa wala 101_0.24</t>
+          <t>ita abu_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Ita Abu</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galleta Wafer Fresa Wala 101</t>
+          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -5096,26 +5096,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>wala_galleta wafer limon wala_unknown</t>
+          <t>mandul_mini muffins choco chips mandul_0.2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Galleta Wafer Limon Wala</t>
+          <t>Mini Muffins Choco Chips Mandul</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -5135,26 +5135,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wala_galleta wafer vainilla wala 101_0.24</t>
+          <t>mandul_mini muffins choco stars mandul_0.21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Galleta Wafer Vainilla Wala 101</t>
+          <t>Mini Muffins Choco Stars Mandul</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.25</v>
+        <v>3.8</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -5174,26 +5174,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>wala_mezcla bizcocho red velvet wala_0.35</t>
+          <t>mandul_mini muffins rellenos de fresa mandul_0.21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Mandul</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mezcla Bizcocho Red Velvet Wala</t>
+          <t>Mini Muffins Rellenos De Fresa Mandul</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -5213,26 +5213,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>wala_mezcla de bizcocho wala chocolate_0.35</t>
+          <t>mestemacher_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Mestemacher</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mezcla De Bizcocho Wala Chocolate</t>
+          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.61</v>
+        <v>2.85</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -5252,26 +5252,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>wala_pan mini wala buffet_unknown</t>
+          <t>mestemacher_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Mestemacher</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pan Mini Wala Buffet</t>
+          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.81</v>
+        <v>2.85</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -5291,26 +5291,26 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wala_pan viga wala integral_0.57</t>
+          <t>over the top_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pan Viga Wala Integral</t>
+          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.04</v>
+        <v>4.44</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -5330,26 +5330,26 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>wala_pan wala mini croissant_0.43</t>
+          <t>over the top_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Over The Top</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pan Wala Mini Croissant</t>
+          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -5369,26 +5369,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>wala_plastico knife wrap wala_unknown</t>
+          <t>repeat_galleta de avena vegan repeat_0.04</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Plastico Knife Wrap Wala</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wala_plastico rolled wrap refill wala_unknown</t>
+          <t>repeat_galleta de avena vegan repeat_0.1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Wala</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Plastico Rolled Wrap Refill Wala</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.7</v>
+        <v>4.75</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -5438,6 +5438,747 @@
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sheila s_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sheila G's</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sheila G's</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sheila s_galletas brownie brittle salted caramel sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sheila G's</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Spongy</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Bizcocho De Vainilla Spongy</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sweet ps_bizcocho de guineo rebanado sweet ps_0.45</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sweet ps_bizcocho de limon rebanado sweet ps_0.45</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Bizcocho De Limon Rebanado Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sweet ps_bizcocho marmol rabanado sweet ps_0.45</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sweet ps_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sweet ps_cup cake de vainilla con chispas sweet ps_0.28</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sweet ps_mini brownies sweet ps_0.3</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Mini Brownies Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sweet ps_mini cup cakes red velvet sweet ps_unknown</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sweet Ps</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Mini Cup Cakes Red Velvet Sweet Ps</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Spongy</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Bizcocho De Vainilla Spongy</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>spongy_bizcocho spongy vainilla_0.23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Spongy</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Bizcocho Spongy Vainilla</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ritmo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Spongy</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Bizcocho De Vainilla Spongy</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ecovida_galleta ecovida sin coco_0.15</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ecovida</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Galleta Ecovida Sin Gluten Coco</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ecovida_galleta sin berrie ecovida_0.15</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Ecovida</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Galleta Sin Gluten Berrie Ecovida</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sheila s_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sheila G's</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sheila G's</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sheila s_galletas brownie brittle salted caramel sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sheila G's</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5450,7 +6191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5518,12 +6259,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bisco_bisco pan galleta clas integral_0.22</t>
+          <t>lu_galleta ecovida sin coco_0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5531,16 +6272,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
+          <t>Galleta Ecovida Sin Gluten Coco</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>3.41</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5557,12 +6298,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bisco_bisco pan galleta constanza_0.28</t>
+          <t>lu_galleta sin berrie ecovida_0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -5570,16 +6311,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Constanza</t>
+          <t>Galleta Sin Gluten Berrie Ecovida</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.73</v>
+        <v>3.41</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5596,12 +6337,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bisco_bisco pan pan integral mielpasas_0.38</t>
+          <t>unknown_galletas sin azucar rellenas de higo ecovida_0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5609,16 +6350,16 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bisco Pan Pan Integral Mielpasas</t>
+          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.89</v>
+        <v>2.22</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5635,12 +6376,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bisco_bisco pan viga integral_0.45</t>
+          <t>unknown_bizcocho de guineo rebanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5648,16 +6389,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bisco Pan Viga Integral</t>
+          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>6.02</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5674,12 +6415,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cacao loacker_0.12</t>
+          <t>unknown_bizcocho de vainilla spongy_0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5692,11 +6433,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cacao Loacker</t>
+          <t>Bizcocho De Vainilla Spongy</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.15</v>
+        <v>1.35</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5713,12 +6454,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cocoa milk loacker_0.12</t>
+          <t>unknown_bizcocho marmol rabanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5731,11 +6472,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cocoa Milk Loacker</t>
+          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.15</v>
+        <v>6.02</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5752,12 +6493,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini coconut loacker_0.12</t>
+          <t>unknown_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5770,11 +6511,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Coconut Loacker</t>
+          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.99</v>
+        <v>6.02</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5791,12 +6532,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini tiramisu loacker_0.11</t>
+          <t>unknown_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -5809,11 +6550,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Tiramisu Loacker</t>
+          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.15</v>
+        <v>4.44</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5830,12 +6571,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_tortilla de trigo 6 la real_unknown</t>
+          <t>unknown_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5848,11 +6589,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tortilla De Trigo 6 La Real</t>
+          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.57</v>
+        <v>2.22</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5869,12 +6610,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unknown_tortillas nicaraguenses la real_0.68</t>
+          <t>unknown_capacillos para mini cupcakes over the top_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5887,11 +6628,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tortillas Nicaraguenses La Real</t>
+          <t>Capacillos Para Mini Cupcakes Over The Top</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.06</v>
+        <v>1.74</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5913,7 +6654,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini napolitaner loacker_0.12</t>
+          <t>unknown_galleta integral con ajonjoli gri gri_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -5926,11 +6667,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
+          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.15</v>
+        <v>1.82</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5952,7 +6693,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
+          <t>unknown_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5965,11 +6706,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
+          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5991,7 +6732,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unknown_tortilla trigo para fajitas 6 la real_unknown</t>
+          <t>unknown_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -6004,11 +6745,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6030,7 +6771,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unknown_galletas danesa royal dansk_0.34</t>
+          <t>unknown_bizcocho de vainilla spongy_0.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -6043,11 +6784,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Galletas Danesa Royal Dansk</t>
+          <t>Bizcocho De Vainilla Spongy</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.96</v>
+        <v>1.17</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6069,7 +6810,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unknown_mini tortilla dura el charrito_unknown</t>
+          <t>unknown_cup cake de vainilla con chispas sweet ps_0.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6082,11 +6823,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Mini Tortilla Dura El Charrito</t>
+          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.71</v>
+        <v>5.05</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -6103,12 +6844,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown_galletas danesa royal dansk_0.34</t>
+          <t>unknown_galleta de avena vegan repeat_0.04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6121,11 +6862,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Galletas Danesa Royal Dansk</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.97</v>
+        <v>2.12</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -6142,12 +6883,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cacao loacker_0.12</t>
+          <t>unknown_galleta de avena vegan repeat_0.1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6160,11 +6901,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cacao Loacker</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.15</v>
+        <v>4.74</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -6181,12 +6922,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini cocoa milk loacker_0.12</t>
+          <t>unknown_galleta de chocolate chip artesanal green is my thing_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -6199,11 +6940,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Cocoa Milk Loacker</t>
+          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -6220,12 +6961,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini coconut loacker_0.12</t>
+          <t>unknown_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -6238,11 +6979,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Coconut Loacker</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.15</v>
+        <v>3.39</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -6259,12 +7000,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unknown_galletas quadratini tiramisu loacker_0.11</t>
+          <t>unknown_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -6277,11 +7018,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Galletas Quadratini Tiramisu Loacker</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -6298,12 +7039,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini napolitaner loacker_0.12</t>
+          <t>unknown_galleta integral con ajonjoli gri gri_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6316,11 +7057,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Napolitaner Loacker</t>
+          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>1.81</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -6337,12 +7078,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_galletas wafer quadratini sabor a vainilla loacker_0.12</t>
+          <t>unknown_galletas artesanales de avena green is my thing_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -6355,11 +7096,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Galletas Wafer Quadratini Sabor A Vainilla Loacker</t>
+          <t>Galletas Artesanales De Avena Green Is My Thing</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -6376,12 +7117,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_mini tortilla dura el charrito_unknown</t>
+          <t>unknown_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -6394,11 +7135,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Mini Tortilla Dura El Charrito</t>
+          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.72</v>
+        <v>2.44</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -6415,12 +7156,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_tortilla de maiz blanco para taco 5 el charrito_unknown</t>
+          <t>unknown_mini brownies sweet ps_0.3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -6433,11 +7174,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Blanco Para Taco 5 El Charrito</t>
+          <t>Mini Brownies Sweet Ps</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.12</v>
+        <v>5.69</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -6454,12 +7195,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_tortilla de trigo 6 la real_unknown</t>
+          <t>unknown_mini muffins choco chips mandul_0.2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -6472,11 +7213,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tortilla De Trigo 6 La Real</t>
+          <t>Mini Muffins Choco Chips Mandul</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>3.79</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -6493,12 +7234,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_tortilla integral para fajitas 6 la real_unknown</t>
+          <t>unknown_mini muffins choco stars mandul_0.21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -6511,11 +7252,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tortilla Integral Para Fajitas 6 La Real</t>
+          <t>Mini Muffins Choco Stars Mandul</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.09</v>
+        <v>3.79</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -6532,12 +7273,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_tortilla trigo para fajitas 6 la real_unknown</t>
+          <t>unknown_mini muffins rellenos de fresa mandul_0.21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -6550,11 +7291,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+          <t>Mini Muffins Rellenos De Fresa Mandul</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.09</v>
+        <v>3.79</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -6571,12 +7312,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bisco_bisco pan galleta clas integral_0.22</t>
+          <t>unknown_pan brioche chocolatechip bgourmet_0.4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -6584,16 +7325,16 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Clas Integral</t>
+          <t>Pan Brioche Chocolatechip Bgourmet</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.41</v>
+        <v>5.85</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -6610,12 +7351,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bisco_bisco pan galleta constanza_0.28</t>
+          <t>unknown_pan brioche lonjeado bgourmet_0.5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6623,16 +7364,16 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bisco</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bisco Pan Galleta Constanza</t>
+          <t>Pan Brioche Lonjeado Bgourmet</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.82</v>
+        <v>6.85</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -6649,12 +7390,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ritmo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown_tortilla grande de trigo el charrito 5 u_0.35</t>
+          <t>lu_galleta de chocolate chips sin ecovida_0.15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6662,16 +7403,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tortilla Grande De Trigo El Charrito 5 U</t>
+          <t>Galleta De Chocolate Chips Sin Gluten Ecovida</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.46</v>
+        <v>3.72</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -6688,12 +7429,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ritmo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown_tortilla taco integral el charrito 10 u_0.22</t>
+          <t>unknown_bizcocho de guineo rebanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6706,11 +7447,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tortilla Taco Integral El Charrito 10 U</t>
+          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.19</v>
+        <v>6.02</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6727,12 +7468,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown_bandeja redonda wala cupcake_unknown</t>
+          <t>unknown_bizcocho de limon rebanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6745,11 +7486,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bandeja Redonda Wala Cupcake</t>
+          <t>Bizcocho De Limon Rebanado Sweet Ps</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.73</v>
+        <v>6.02</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6766,12 +7507,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unknown_galleta el corte ingles cookids d_0.6</t>
+          <t>unknown_bizcocho de vainilla spongy_0.15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -6784,11 +7525,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Galleta El Corte Ingles Cookids D</t>
+          <t>Bizcocho De Vainilla Spongy</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5.31</v>
+        <v>1.35</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -6805,12 +7546,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>unknown_galleta wafer fresa wala 101_0.24</t>
+          <t>unknown_bizcocho marmol rabanado sweet ps_0.45</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -6823,11 +7564,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Galleta Wafer Fresa Wala 101</t>
+          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.25</v>
+        <v>6.02</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -6844,12 +7585,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unknown_galleta wafer limon wala_unknown</t>
+          <t>unknown_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -6862,11 +7603,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Galleta Wafer Limon Wala</t>
+          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.25</v>
+        <v>6.02</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -6883,12 +7624,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown_galleta wafer vainilla wala 101_0.24</t>
+          <t>unknown_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -6901,11 +7642,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Galleta Wafer Vainilla Wala 101</t>
+          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.25</v>
+        <v>4.44</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -6922,12 +7663,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>unknown_mezcla bizcocho red velvet wala_0.35</t>
+          <t>unknown_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -6940,11 +7681,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Mezcla Bizcocho Red Velvet Wala</t>
+          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6961,12 +7702,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>unknown_mezcla de bizcocho wala chocolate_0.35</t>
+          <t>unknown_cup cake de vainilla con chispas sweet ps_0.28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6979,11 +7720,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Mezcla De Bizcocho Wala Chocolate</t>
+          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.61</v>
+        <v>5.07</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -7000,12 +7741,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unknown_mini tortilla dura el charrito_unknown</t>
+          <t>unknown_galleta de avena vegan repeat_0.04</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -7018,11 +7759,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Mini Tortilla Dura El Charrito</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.77</v>
+        <v>2.14</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -7039,12 +7780,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>unknown_pan mini wala buffet_unknown</t>
+          <t>unknown_galleta de avena vegan repeat_0.1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -7057,11 +7798,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pan Mini Wala Buffet</t>
+          <t>Galleta De Avena Vegan Repeat</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.81</v>
+        <v>4.75</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -7078,12 +7819,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>unknown_pan viga wala integral_0.57</t>
+          <t>unknown_galleta de chocolate chip artesanal green is my thing_unknown</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -7096,11 +7837,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pan Viga Wala Integral</t>
+          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.04</v>
+        <v>3.56</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -7117,12 +7858,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>unknown_pan wala mini croissant_0.43</t>
+          <t>unknown_galleta de chocolate chip vegana dbl_0.07</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -7135,11 +7876,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pan Wala Mini Croissant</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>3.41</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -7156,12 +7897,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unknown_plastico knife wrap wala_unknown</t>
+          <t>unknown_galleta de chocolate chip vegana dbl_0.34</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -7174,11 +7915,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Plastico Knife Wrap Wala</t>
+          <t>Galleta De Chocolate Chip Vegana Dbl</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.52</v>
+        <v>6.42</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -7195,12 +7936,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unknown_plastico rolled wrap refill wala_unknown</t>
+          <t>unknown_galletas artesanales de avena green is my thing_unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -7213,11 +7954,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Plastico Rolled Wrap Refill Wala</t>
+          <t>Galletas Artesanales De Avena Green Is My Thing</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>3.56</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -7234,12 +7975,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>unknown_tortilla integral para fajitas 6 la real_unknown</t>
+          <t>unknown_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -7252,11 +7993,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tortilla Integral Para Fajitas 6 La Real</t>
+          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.09</v>
+        <v>2.46</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -7273,12 +8014,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>unknown_tortilla trigo para fajitas 6 la real_unknown</t>
+          <t>unknown_galletas brownie brittle chocolate chips sheila gs_0.14</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -7291,11 +8032,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tortilla Trigo Para Fajitas 6 La Real</t>
+          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.09</v>
+        <v>4.75</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -7312,12 +8053,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>unknown_tortillas burrito la real_unknown</t>
+          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -7330,11 +8071,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tortillas Burrito La Real</t>
+          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.93</v>
+        <v>4.75</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -7342,6 +8083,747 @@
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>unknown_galletas brownie brittle salted caramel sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unknown_galletas sin azucar rellenas de higo ecovida_0.15</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unknown_mini brownies sweet ps_0.3</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Mini Brownies Sweet Ps</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unknown_mini cup cakes red velvet sweet ps_unknown</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Mini Cup Cakes Red Velvet Sweet Ps</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unknown_mini muffins choco chips mandul_0.2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Mini Muffins Choco Chips Mandul</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unknown_mini muffins choco stars mandul_0.21</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Mini Muffins Choco Stars Mandul</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unknown_mini muffins rellenos de fresa mandul_0.21</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Mini Muffins Rellenos De Fresa Mandul</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>unknown_pan brioche chocolatechip bgourmet_0.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Pan Brioche Chocolatechip Bgourmet</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>unknown_pan brioche lonjeado bgourmet_0.5</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Pan Brioche Lonjeado Bgourmet</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>unknown_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>unknown_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Bizcocho De Vainilla Spongy</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>unknown_bizcocho spongy vainilla_0.23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Bizcocho Spongy Vainilla</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ritmo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bizcocho De Vainilla Spongy</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>lu_galleta ecovida sin coco_0.15</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Galleta Ecovida Sin Gluten Coco</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>lu_galleta sin berrie ecovida_0.15</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Galleta Sin Gluten Berrie Ecovida</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>unknown_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>unknown_galletas brownie brittle salted caramel sheila gs_0.14</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -3546,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,26 +3614,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ecovida_galleta ecovida sin coco_0.15</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Galleta Ecovida Sin Gluten Coco</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.41</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3653,26 +3653,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ecovida_galleta sin berrie ecovida_0.15</t>
+          <t>dante_galletas cubanas dante con ajo_0.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Galleta Sin Gluten Berrie Ecovida</t>
+          <t>Galletas Cubanas Dante Con Ajo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.41</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3692,26 +3692,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ecovida_galletas sin azucar rellenas de higo ecovida_0.15</t>
+          <t>dante_galletas cubanas dante_0.27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
+          <t>Galletas Cubanas Dante</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>1.89</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3731,26 +3731,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gri gri_galleta integral con ajonjoli gri gri_unknown</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gri Gri</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>0.48</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3770,26 +3770,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mestemacher_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
+          <t>bon_helado helados bon bizcocho_0.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mestemacher</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
+          <t>Helado Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.85</v>
+        <v>5.78</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3809,26 +3809,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mestemacher_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mestemacher</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.85</v>
+        <v>3.71</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3848,26 +3848,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>over the top_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
+          <t>bon_paleta bon de bizcocho_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Over The Top</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
+          <t>Paleta Bon De Bizcocho</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.44</v>
+        <v>0.63</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3887,26 +3887,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>over the top_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
+          <t>gavotte_galleta gavotte dentelle_0.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Over The Top</t>
+          <t>Gavotte</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
+          <t>Galleta Gavotte Dentelle</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.22</v>
+        <v>3.64</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3926,22 +3926,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>over the top_capacillos para mini cupcakes over the top_unknown</t>
+          <t>mocano_galleta manteca mocano_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Over The Top</t>
+          <t>Mocano</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Capacillos Para Mini Cupcakes Over The Top</t>
+          <t>Galleta Manteca Mocano</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3965,26 +3965,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+          <t>pozuelo_galleta pozuelo chiky chocolate_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Pozuelo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Galleta Pozuelo Chiky Chocolate</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.35</v>
+        <v>3.58</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -4004,26 +4004,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho de guineo rebanado sweet ps_0.45</t>
+          <t>pozuelo_galleta pozuelo cremas chocolate_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Pozuelo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
+          <t>Galleta Pozuelo Cremas Chocolate</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.02</v>
+        <v>1.88</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4043,26 +4043,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho marmol rabanado sweet ps_0.45</t>
+          <t>pozuelo_galleta pozuelo cremas fresa_unknown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Pozuelo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
+          <t>Galleta Pozuelo Cremas Fresa</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.02</v>
+        <v>1.88</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -4082,26 +4082,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
+          <t>pozuelo_galleta pozuelo vainilla chocolate_0.3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Pozuelo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
+          <t>Galleta Pozuelo Vainilla Chocolate</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6.02</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -4121,26 +4121,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bgourmet_pan brioche chocolatechip bgourmet_0.4</t>
+          <t>renata_galleta maizena renata_0.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BGourmet</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pan Brioche Chocolatechip Bgourmet</t>
+          <t>Galleta Maizena Renata</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.85</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -4160,26 +4160,26 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bgourmet_pan brioche lonjeado bgourmet_0.5</t>
+          <t>renata_galleta renata wafer choc_0.12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BGourmet</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pan Brioche Lonjeado Bgourmet</t>
+          <t>Galleta Renata Wafer Choc</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.85</v>
+        <v>0.95</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -4199,26 +4199,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dbl_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>renata_mezcla para bizcocho renata coco_0.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Mezcla Para Bizcocho Renata Coco</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.39</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -4238,26 +4238,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dbl_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>renata_mezcla para bizcocho renata limon_0.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Mezcla Para Bizcocho Renata Limon</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6.4</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4277,26 +4277,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>green is my thing_galleta de chocolate chip artesanal green is my thing_unknown</t>
+          <t>renata_mezcla para bizcocho renata maiz_0.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Green Is My Thing</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
+          <t>Mezcla Para Bizcocho Renata Maiz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -4316,26 +4316,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>green is my thing_galletas artesanales de avena green is my thing_unknown</t>
+          <t>renata_mezcla para bizcocho renata naranja_0.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Green Is My Thing</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Avena Green Is My Thing</t>
+          <t>Mezcla Para Bizcocho Renata Naranja</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -4355,26 +4355,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gri gri_galleta integral con ajonjoli gri gri_unknown</t>
+          <t>renata_mezcla para bizcocho renata pina_0.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Gri Gri</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
+          <t>Mezcla Para Bizcocho Renata Pina</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -4394,26 +4394,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ita abu_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
+          <t>renata_mezcla para bizcocho renata vainilla_0.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ita Abu</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
+          <t>Mezcla Para Bizcocho Renata Vainilla</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -4433,26 +4433,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mandul_mini muffins choco chips mandul_0.2</t>
+          <t>choco wow_galletas sandwich chocolate choco wow 10 und_0.48</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>Choco Wow</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Chips Mandul</t>
+          <t>Galletas Sandwich Chocolate Choco Wow 10 Und</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.79</v>
+        <v>2.14</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -4472,26 +4472,26 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mandul_mini muffins choco stars mandul_0.21</t>
+          <t>lago_galleta lago mini party cacao_0.12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Stars Mandul</t>
+          <t>Galleta Lago Mini Party Cacao</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.79</v>
+        <v>1.66</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -4511,26 +4511,26 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mandul_mini muffins rellenos de fresa mandul_0.21</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mini Muffins Rellenos De Fresa Mandul</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.79</v>
+        <v>0.46</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -4550,26 +4550,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>repeat_galleta de avena vegan repeat_0.04</t>
+          <t>muuu_galletas de chocolate muuu con crema sabor a vainilla_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Muuu</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Galletas De Chocolate Muuu Con Crema Sabor A Vainilla</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -4589,26 +4589,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>repeat_galleta de avena vegan repeat_0.1</t>
+          <t>supermoist_mezcla para bizcocho de zanahoria supermoist_0.43</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>SuperMoist</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Mezcla Para Bizcocho De Zanahoria Supermoist</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.74</v>
+        <v>4.99</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -4628,26 +4628,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+          <t>vaquita rica_leche sabor bizcocho vaquita rica uht_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Vaquita Rica</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Leche Sabor Bizcocho Vaquita Rica Uht</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.17</v>
+        <v>0.48</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -4667,26 +4667,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sweet ps_cup cake de vainilla con chispas sweet ps_0.28</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5.05</v>
+        <v>0.47</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -4706,26 +4706,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sweet ps_mini brownies sweet ps_0.3</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mini Brownies Sweet Ps</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.69</v>
+        <v>4.72</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -4745,26 +4745,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bgourmet_pan brioche chocolatechip bgourmet_0.4</t>
+          <t>bon_helado bizcocho bon 2 pintas_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BGourmet</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pan Brioche Chocolatechip Bgourmet</t>
+          <t>Helado Bizcocho Bon 2 Pintas</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5.86</v>
+        <v>5.45</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -4784,26 +4784,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bgourmet_pan brioche lonjeado bgourmet_0.5</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BGourmet</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pan Brioche Lonjeado Bgourmet</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6.86</v>
+        <v>3.69</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -4823,26 +4823,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>dbl_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>choco wow_galletas sandwich chocolate choco wow 10 und_0.48</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>Choco Wow</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Galletas Sandwich Chocolate Choco Wow 10 Und</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.41</v>
+        <v>2.2</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -4862,26 +4862,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dbl_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6.42</v>
+        <v>0.46</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -4901,26 +4901,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ecovida_galleta de chocolate chips sin ecovida_0.15</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chips Sin Gluten Ecovida</t>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -4940,26 +4940,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ecovida_galletas sin azucar rellenas de higo ecovida_0.15</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.65</v>
+        <v>4.71</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -4984,21 +4984,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>green is my thing_galleta de chocolate chip artesanal green is my thing_unknown</t>
+          <t>axa_galletas cookie n cream axa_0.14</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Green Is My Thing</t>
+          <t>AXA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
+          <t>Galletas Cookie N Cream Axa</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.56</v>
+        <v>4.69</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -5023,21 +5023,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>green is my thing_galletas artesanales de avena green is my thing_unknown</t>
+          <t>lotus_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Green Is My Thing</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Avena Green Is My Thing</t>
+          <t>Galleta De Mantequilla Lotus</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.56</v>
+        <v>4.28</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -5062,21 +5062,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ita abu_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
+          <t>lotus_galleta de mantequilla rellena de chocolate lotus_0.15</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ita Abu</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
+          <t>Galleta De Mantequilla Rellena De Chocolate Lotus</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.46</v>
+        <v>3.49</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -5101,21 +5101,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mandul_mini muffins choco chips mandul_0.2</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Chips Mandul</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3.8</v>
+        <v>0.47</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -5140,21 +5140,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mandul_mini muffins choco stars mandul_0.21</t>
+          <t>new york style_bagel crisps plain new york style_0.2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Stars Mandul</t>
+          <t>Bagel Crisps Plain New York Style</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -5179,21 +5179,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mandul_mini muffins rellenos de fresa mandul_0.21</t>
+          <t>new york style_bagel crisps sea salt new york style_0.2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mandul</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mini Muffins Rellenos De Fresa Mandul</t>
+          <t>Bagel Crisps Sea Salt New York Style</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -5218,21 +5218,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mestemacher_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mestemacher</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.85</v>
+        <v>3.64</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -5257,21 +5257,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mestemacher_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mestemacher</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.85</v>
+        <v>4.72</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -5296,21 +5296,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>over the top_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
+          <t>supermoist_mezcla para bizcocho de zanahoria supermoist_0.43</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Over The Top</t>
+          <t>SuperMoist</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
+          <t>Mezcla Para Bizcocho De Zanahoria Supermoist</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4.44</v>
+        <v>4.83</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -5335,21 +5335,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>over the top_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
+          <t>vaquita rica_leche sabor bizcocho vaquita rica uht_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Over The Top</t>
+          <t>Vaquita Rica</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
+          <t>Leche Sabor Bizcocho Vaquita Rica Uht</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.22</v>
+        <v>0.46</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -5369,26 +5369,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>repeat_galleta de avena vegan repeat_0.04</t>
+          <t>bon_helado bon de bizcocho_0.52</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Helado Bon De Bizcocho</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.14</v>
+        <v>6.32</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -5408,26 +5408,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>repeat_galleta de avena vegan repeat_0.1</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Repeat</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4.75</v>
+        <v>4.26</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -5447,26 +5447,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sheila s_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+          <t>bon_paleta bon de bizcocho_unknown</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+          <t>Paleta Bon De Bizcocho</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4.75</v>
+        <v>0.71</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
@@ -5486,26 +5486,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+          <t>dante_galletas cubanas dante con ajo_0.27</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+          <t>Galletas Cubanas Dante Con Ajo</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>4.75</v>
+        <v>2.14</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -5525,26 +5525,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sheila s_galletas brownie brittle salted caramel sheila gs_0.14</t>
+          <t>dante_galletas cubanas dante_0.27</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+          <t>Galletas Cubanas Dante</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>4.75</v>
+        <v>2.14</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -5564,26 +5564,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+          <t>lago_galleta wafers lago poker con avellanas 5 und_0.22</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Galleta Wafers Lago Poker Con Avellanas 5 Und</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.35</v>
+        <v>2.99</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
@@ -5603,26 +5603,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho de guineo rebanado sweet ps_0.45</t>
+          <t>loacker_galleta wafers loacker sabor a coconut_0.04</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
+          <t>Galleta Wafers Loacker Sabor A Coconut</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>6.02</v>
+        <v>1.09</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -5642,26 +5642,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho de limon rebanado sweet ps_0.45</t>
+          <t>loacker_galleta wafers loacker sabor a cremkakao_0.04</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bizcocho De Limon Rebanado Sweet Ps</t>
+          <t>Galleta Wafers Loacker Sabor A Cremkakao</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>6.02</v>
+        <v>1.09</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -5681,26 +5681,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho marmol rabanado sweet ps_0.45</t>
+          <t>loacker_galleta wafers loacker sabor a napolitaner_0.04</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
+          <t>Galleta Wafers Loacker Sabor A Napolitaner</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6.02</v>
+        <v>1.09</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -5720,26 +5720,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sweet ps_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
+          <t>loacker_galleta wafers loacker sabor a vainilla_0.04</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
+          <t>Galleta Wafers Loacker Sabor A Vainilla</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6.02</v>
+        <v>1.09</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -5759,26 +5759,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sweet ps_cup cake de vainilla con chispas sweet ps_0.28</t>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Mamut</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>5.07</v>
+        <v>0.48</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
@@ -5798,26 +5798,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sweet ps_mini brownies sweet ps_0.3</t>
+          <t>muuu_galletas de chocolate muuu con crema sabor a vainilla_unknown</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>Muuu</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mini Brownies Sweet Ps</t>
+          <t>Galletas De Chocolate Muuu Con Crema Sabor A Vainilla</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>5.7</v>
+        <v>2.76</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
@@ -5837,26 +5837,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sweet ps_mini cup cakes red velvet sweet ps_unknown</t>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sweet Ps</t>
+          <t>PopCorners</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mini Cup Cakes Red Velvet Sweet Ps</t>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>6.32</v>
+        <v>3.64</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -5881,21 +5881,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+          <t>quest_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Quest</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.35</v>
+        <v>4.72</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -5915,26 +5915,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>spongy_bizcocho spongy vainilla_0.23</t>
+          <t>bridge_galletas bridge wafer naranja_0.3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Bridge</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bizcocho Spongy Vainilla</t>
+          <t>Galletas Bridge Wafer Naranja</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -5954,26 +5954,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ritmo</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>spongy_bizcocho de vainilla spongy_0.15</t>
+          <t>cheez it_galleta snapd doble cheddar cheez it_0.21</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Spongy</t>
+          <t>Cheez-It</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Galleta Snapd Doble Cheddar Cheez It</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.09</v>
+        <v>4.6</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
@@ -5998,21 +5998,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ecovida_galleta ecovida sin coco_0.15</t>
+          <t>choco wow_galletas sandwich chocolate choco wow 10 und_0.48</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Choco Wow</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Galleta Ecovida Sin Gluten Coco</t>
+          <t>Galletas Sandwich Chocolate Choco Wow 10 Und</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>3.72</v>
+        <v>2.22</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
@@ -6037,21 +6037,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ecovida_galleta sin berrie ecovida_0.15</t>
+          <t>jules destrooper_galleta de mantequilla jules destrooper_0.1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ecovida</t>
+          <t>Jules Destrooper</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Galleta Sin Gluten Berrie Ecovida</t>
+          <t>Galleta De Mantequilla Jules Destrooper</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
@@ -6076,21 +6076,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sheila s_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+          <t>lago_galleta lago mini party cacao_0.12</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+          <t>Galleta Lago Mini Party Cacao</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>5.15</v>
+        <v>2.06</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
@@ -6115,21 +6115,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sheila s_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+          <t>lago_galleta wafers lago wafers mini party avellanas_0.12</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Lago</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+          <t>Galleta Wafers Lago Wafers Mini Party Avellanas</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5.15</v>
+        <v>2.06</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
@@ -6154,21 +6154,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sheila s_galletas brownie brittle salted caramel sheila gs_0.14</t>
+          <t>lotus_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sheila G's</t>
+          <t>Lotus</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+          <t>Galleta De Mantequilla Lotus</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>5.15</v>
+        <v>4.28</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
@@ -6179,6 +6179,123 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mamut_galletas de chocolate y malvavisco mamut_0.03</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mamut</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>popcorners_tortillas chips kettle corn popcorners_0.14</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PopCorners</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>cheez it_cheez it original 1 5oz_0.04</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Cheez-It</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Cheez-It Original  1.5oz</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1.201923076923077</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6191,7 +6308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6259,12 +6376,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lu_galleta ecovida sin coco_0.15</t>
+          <t>unknown_galletas cubanas dante con ajo_0.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -6272,16 +6389,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Galleta Ecovida Sin Gluten Coco</t>
+          <t>Galletas Cubanas Dante Con Ajo</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.41</v>
+        <v>1.89</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6298,12 +6415,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lu_galleta sin berrie ecovida_0.15</t>
+          <t>unknown_galletas cubanas dante_0.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -6311,16 +6428,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Galleta Sin Gluten Berrie Ecovida</t>
+          <t>Galletas Cubanas Dante</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.41</v>
+        <v>1.89</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -6337,12 +6454,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_galletas sin azucar rellenas de higo ecovida_0.15</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -6355,11 +6472,11 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.22</v>
+        <v>0.48</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6376,12 +6493,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de guineo rebanado sweet ps_0.45</t>
+          <t>unknown_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -6394,11 +6511,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.02</v>
+        <v>3.95</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -6415,12 +6532,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+          <t>unknown_galleta gavotte dentelle_0.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -6433,11 +6550,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Galleta Gavotte Dentelle</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.35</v>
+        <v>3.64</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -6454,12 +6571,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_bizcocho marmol rabanado sweet ps_0.45</t>
+          <t>unknown_galleta maizena renata_0.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -6472,11 +6589,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
+          <t>Galleta Maizena Renata</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6.02</v>
+        <v>2.06</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -6493,12 +6610,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
+          <t>unknown_galleta manteca mocano_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -6511,11 +6628,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
+          <t>Galleta Manteca Mocano</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6.02</v>
+        <v>1.74</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6532,12 +6649,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
+          <t>unknown_galleta pozuelo chiky chocolate_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -6550,11 +6667,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
+          <t>Galleta Pozuelo Chiky Chocolate</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.44</v>
+        <v>3.58</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -6571,12 +6688,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
+          <t>unknown_galleta pozuelo cremas chocolate_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -6589,11 +6706,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
+          <t>Galleta Pozuelo Cremas Chocolate</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.22</v>
+        <v>1.88</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -6610,12 +6727,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unknown_capacillos para mini cupcakes over the top_unknown</t>
+          <t>unknown_galleta pozuelo cremas fresa_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -6628,11 +6745,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Capacillos Para Mini Cupcakes Over The Top</t>
+          <t>Galleta Pozuelo Cremas Fresa</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6649,12 +6766,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>unknown_galleta integral con ajonjoli gri gri_unknown</t>
+          <t>unknown_galleta pozuelo vainilla chocolate_0.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -6667,7 +6784,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
+          <t>Galleta Pozuelo Vainilla Chocolate</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -6688,12 +6805,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>unknown_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
+          <t>unknown_galleta renata wafer choc_0.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -6706,11 +6823,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
+          <t>Galleta Renata Wafer Choc</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.85</v>
+        <v>0.95</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -6727,12 +6844,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>unknown_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
+          <t>unknown_helado helados bon bizcocho_0.52</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -6745,11 +6862,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
+          <t>Helado Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.85</v>
+        <v>5.78</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6766,12 +6883,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+          <t>unknown_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -6784,11 +6901,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.17</v>
+        <v>3.71</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6805,12 +6922,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>unknown_cup cake de vainilla con chispas sweet ps_0.28</t>
+          <t>unknown_mezcla para bizcocho renata coco_0.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6823,11 +6940,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
+          <t>Mezcla Para Bizcocho Renata Coco</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.05</v>
+        <v>2.14</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -6844,12 +6961,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.04</t>
+          <t>unknown_mezcla para bizcocho renata limon_0.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6862,11 +6979,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Mezcla Para Bizcocho Renata Limon</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -6883,12 +7000,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.1</t>
+          <t>unknown_mezcla para bizcocho renata maiz_0.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6901,11 +7018,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Mezcla Para Bizcocho Renata Maiz</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4.74</v>
+        <v>2.14</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -6922,12 +7039,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip artesanal green is my thing_unknown</t>
+          <t>unknown_mezcla para bizcocho renata naranja_0.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -6940,11 +7057,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
+          <t>Mezcla Para Bizcocho Renata Naranja</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -6961,12 +7078,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>unknown_mezcla para bizcocho renata pina_0.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -6979,11 +7096,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Mezcla Para Bizcocho Renata Pina</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.39</v>
+        <v>2.14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -7000,12 +7117,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>unknown_mezcla para bizcocho renata vainilla_0.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -7018,11 +7135,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Mezcla Para Bizcocho Renata Vainilla</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6.4</v>
+        <v>2.14</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -7039,12 +7156,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown_galleta integral con ajonjoli gri gri_unknown</t>
+          <t>unknown_paleta bon de bizcocho_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -7057,11 +7174,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Galleta Integral Con Ajonjoli Gri Gri</t>
+          <t>Paleta Bon De Bizcocho</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.81</v>
+        <v>0.63</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7078,12 +7195,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_galletas artesanales de avena green is my thing_unknown</t>
+          <t>unknown_galleta lago mini party cacao_0.12</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -7096,11 +7213,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Avena Green Is My Thing</t>
+          <t>Galleta Lago Mini Party Cacao</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.55</v>
+        <v>1.66</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -7117,12 +7234,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
+          <t>unknown_galletas de chocolate muuu con crema sabor a vainilla_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -7135,11 +7252,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
+          <t>Galletas De Chocolate Muuu Con Crema Sabor A Vainilla</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -7156,12 +7273,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_mini brownies sweet ps_0.3</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -7174,11 +7291,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Mini Brownies Sweet Ps</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.69</v>
+        <v>0.46</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -7195,12 +7312,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco chips mandul_0.2</t>
+          <t>unknown_galletas sandwich chocolate choco wow 10 und_0.48</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -7213,11 +7330,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Chips Mandul</t>
+          <t>Galletas Sandwich Chocolate Choco Wow 10 Und</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.79</v>
+        <v>2.14</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7234,12 +7351,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco stars mandul_0.21</t>
+          <t>unknown_leche sabor bizcocho vaquita rica uht_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -7252,11 +7369,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Stars Mandul</t>
+          <t>Leche Sabor Bizcocho Vaquita Rica Uht</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.79</v>
+        <v>0.48</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7273,12 +7390,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_mini muffins rellenos de fresa mandul_0.21</t>
+          <t>unknown_mezcla para bizcocho de zanahoria supermoist_0.43</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -7291,11 +7408,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Mini Muffins Rellenos De Fresa Mandul</t>
+          <t>Mezcla Para Bizcocho De Zanahoria Supermoist</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -7312,12 +7429,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_pan brioche chocolatechip bgourmet_0.4</t>
+          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -7330,11 +7447,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pan Brioche Chocolatechip Bgourmet</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.85</v>
+        <v>4.72</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -7351,12 +7468,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_pan brioche lonjeado bgourmet_0.5</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -7369,11 +7486,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pan Brioche Lonjeado Bgourmet</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.85</v>
+        <v>0.47</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -7390,12 +7507,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lu_galleta de chocolate chips sin ecovida_0.15</t>
+          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -7403,16 +7520,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chips Sin Gluten Ecovida</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.72</v>
+        <v>4.71</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -7429,12 +7546,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de guineo rebanado sweet ps_0.45</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -7447,11 +7564,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bizcocho De Guineo Rebanado Sweet Ps</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.02</v>
+        <v>0.46</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -7468,12 +7585,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de limon rebanado sweet ps_0.45</t>
+          <t>unknown_galletas sandwich chocolate choco wow 10 und_0.48</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -7486,11 +7603,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bizcocho De Limon Rebanado Sweet Ps</t>
+          <t>Galletas Sandwich Chocolate Choco Wow 10 Und</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.02</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -7507,12 +7624,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+          <t>unknown_helado bizcocho bon 2 pintas_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -7525,11 +7642,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Helado Bizcocho Bon 2 Pintas</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.35</v>
+        <v>5.45</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -7546,12 +7663,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>unknown_bizcocho marmol rabanado sweet ps_0.45</t>
+          <t>unknown_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -7564,11 +7681,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Bizcocho Marmol Rabanado Sweet Ps</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.02</v>
+        <v>3.69</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -7585,12 +7702,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unknown_bizcocho pudin de mantequilla y canela rebanao sweet ps_0.45</t>
+          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -7603,11 +7720,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bizcocho Pudin De Mantequilla Y Canela Rebanao Sweet Ps</t>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6.02</v>
+        <v>3.63</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -7629,7 +7746,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown_capacillos desechables para hornear cupcakes colores mixtos over the top_unknown</t>
+          <t>unknown_bagel crisps plain new york style_0.2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -7642,11 +7759,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Capacillos Desechables Para Hornear Cupcakes Colores Mixtos Over The Top</t>
+          <t>Bagel Crisps Plain New York Style</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.44</v>
+        <v>3.56</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -7668,7 +7785,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>unknown_capacillos grandes desechables para hornear cupcakes over the top_unknown</t>
+          <t>unknown_bagel crisps sea salt new york style_0.2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -7681,11 +7798,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Capacillos Grandes Desechables Para Hornear Cupcakes Over The Top</t>
+          <t>Bagel Crisps Sea Salt New York Style</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.22</v>
+        <v>3.56</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -7707,7 +7824,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>unknown_cup cake de vainilla con chispas sweet ps_0.28</t>
+          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -7720,11 +7837,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Cup Cake De Vainilla Con Chispas Sweet Ps</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.07</v>
+        <v>4.72</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -7746,7 +7863,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.04</t>
+          <t>unknown_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -7759,11 +7876,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Galleta De Mantequilla Lotus</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.14</v>
+        <v>4.28</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -7785,7 +7902,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>unknown_galleta de avena vegan repeat_0.1</t>
+          <t>unknown_galleta de mantequilla rellena de chocolate lotus_0.15</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -7798,11 +7915,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Galleta De Avena Vegan Repeat</t>
+          <t>Galleta De Mantequilla Rellena De Chocolate Lotus</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.75</v>
+        <v>3.49</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -7824,7 +7941,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip artesanal green is my thing_unknown</t>
+          <t>unknown_galletas cookie n cream axa_0.14</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -7837,11 +7954,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Artesanal Green Is My Thing</t>
+          <t>Galletas Cookie N Cream Axa</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.56</v>
+        <v>4.69</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -7863,7 +7980,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.07</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -7876,11 +7993,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.41</v>
+        <v>0.47</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -7902,7 +8019,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unknown_galleta de chocolate chip vegana dbl_0.34</t>
+          <t>unknown_leche sabor bizcocho vaquita rica uht_unknown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -7915,11 +8032,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Galleta De Chocolate Chip Vegana Dbl</t>
+          <t>Leche Sabor Bizcocho Vaquita Rica Uht</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.42</v>
+        <v>0.46</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -7941,7 +8058,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unknown_galletas artesanales de avena green is my thing_unknown</t>
+          <t>unknown_mezcla para bizcocho de zanahoria supermoist_0.43</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -7954,11 +8071,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Avena Green Is My Thing</t>
+          <t>Mezcla Para Bizcocho De Zanahoria Supermoist</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.56</v>
+        <v>4.83</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -7980,7 +8097,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>unknown_galletas artesanales de vainilla y guayaba ita abu_unknown</t>
+          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -7993,11 +8110,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Galletas Artesanales De Vainilla Y Guayaba Ita Abu</t>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.46</v>
+        <v>3.64</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -8014,12 +8131,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+          <t>unknown_barra de proteina sabor brownie de chocolate quest_0.06</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -8032,11 +8149,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+          <t>Barra De Proteina Sabor Brownie De Chocolate Quest</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.75</v>
+        <v>4.72</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -8053,12 +8170,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+          <t>unknown_galleta wafers lago poker con avellanas 5 und_0.22</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -8071,11 +8188,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+          <t>Galleta Wafers Lago Poker Con Avellanas 5 Und</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.75</v>
+        <v>2.99</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -8092,12 +8209,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle salted caramel sheila gs_0.14</t>
+          <t>unknown_galleta wafers loacker sabor a coconut_0.04</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -8110,11 +8227,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+          <t>Galleta Wafers Loacker Sabor A Coconut</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.75</v>
+        <v>1.09</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -8131,12 +8248,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>unknown_galletas sin azucar rellenas de higo ecovida_0.15</t>
+          <t>unknown_galleta wafers loacker sabor a cremkakao_0.04</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -8149,11 +8266,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Galletas Sin Azucar Rellenas De Higo Ecovida</t>
+          <t>Galleta Wafers Loacker Sabor A Cremkakao</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.65</v>
+        <v>1.09</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -8170,12 +8287,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>unknown_mini brownies sweet ps_0.3</t>
+          <t>unknown_galleta wafers loacker sabor a napolitaner_0.04</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -8188,11 +8305,11 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Mini Brownies Sweet Ps</t>
+          <t>Galleta Wafers Loacker Sabor A Napolitaner</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.7</v>
+        <v>1.09</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -8209,12 +8326,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unknown_mini cup cakes red velvet sweet ps_unknown</t>
+          <t>unknown_galleta wafers loacker sabor a vainilla_0.04</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -8227,11 +8344,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Mini Cup Cakes Red Velvet Sweet Ps</t>
+          <t>Galleta Wafers Loacker Sabor A Vainilla</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.32</v>
+        <v>1.09</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -8248,12 +8365,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco chips mandul_0.2</t>
+          <t>unknown_galletas cubanas dante con ajo_0.27</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -8266,11 +8383,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Chips Mandul</t>
+          <t>Galletas Cubanas Dante Con Ajo</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -8287,12 +8404,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unknown_mini muffins choco stars mandul_0.21</t>
+          <t>unknown_galletas cubanas dante_0.27</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -8305,11 +8422,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Mini Muffins Choco Stars Mandul</t>
+          <t>Galletas Cubanas Dante</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -8326,12 +8443,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unknown_mini muffins rellenos de fresa mandul_0.21</t>
+          <t>unknown_galletas de chocolate muuu con crema sabor a vainilla_unknown</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -8344,11 +8461,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Mini Muffins Rellenos De Fresa Mandul</t>
+          <t>Galletas De Chocolate Muuu Con Crema Sabor A Vainilla</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.8</v>
+        <v>2.76</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -8365,12 +8482,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>unknown_pan brioche chocolatechip bgourmet_0.4</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -8383,11 +8500,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pan Brioche Chocolatechip Bgourmet</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.86</v>
+        <v>0.48</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -8404,12 +8521,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unknown_pan brioche lonjeado bgourmet_0.5</t>
+          <t>unknown_helado bon de bizcocho_0.52</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -8422,11 +8539,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pan Brioche Lonjeado Bgourmet</t>
+          <t>Helado Bon De Bizcocho</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.86</v>
+        <v>6.32</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -8443,12 +8560,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>unknown_pan integral de centeno con semillas de calabaza mestemacher_0.5</t>
+          <t>unknown_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -8461,11 +8578,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Calabaza Mestemacher</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.85</v>
+        <v>4.26</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -8482,12 +8599,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>unknown_pan integral de centeno con semillas de girasol mestemacher_0.5</t>
+          <t>unknown_paleta bon de bizcocho_unknown</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -8500,11 +8617,11 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pan Integral De Centeno Con Semillas De Girasol Mestemacher</t>
+          <t>Paleta Bon De Bizcocho</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.85</v>
+        <v>0.71</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -8526,7 +8643,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -8539,11 +8656,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.35</v>
+        <v>3.64</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -8560,12 +8677,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>unknown_bizcocho spongy vainilla_0.23</t>
+          <t>unknown_galleta de mantequilla jules destrooper_0.1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -8578,11 +8695,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bizcocho Spongy Vainilla</t>
+          <t>Galleta De Mantequilla Jules Destrooper</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.35</v>
+        <v>3.96</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -8599,12 +8716,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ritmo</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>unknown_bizcocho de vainilla spongy_0.15</t>
+          <t>unknown_galleta de mantequilla lotus_0.25</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -8617,11 +8734,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bizcocho De Vainilla Spongy</t>
+          <t>Galleta De Mantequilla Lotus</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.09</v>
+        <v>4.28</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -8643,7 +8760,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>lu_galleta ecovida sin coco_0.15</t>
+          <t>unknown_galleta lago mini party cacao_0.12</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -8651,16 +8768,16 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Galleta Ecovida Sin Gluten Coco</t>
+          <t>Galleta Lago Mini Party Cacao</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.72</v>
+        <v>2.06</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -8682,7 +8799,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>lu_galleta sin berrie ecovida_0.15</t>
+          <t>unknown_galleta snapd doble cheddar cheez it_0.21</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -8690,16 +8807,16 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Galleta Sin Gluten Berrie Ecovida</t>
+          <t>Galleta Snapd Doble Cheddar Cheez It</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.72</v>
+        <v>4.6</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -8721,7 +8838,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle chocolate chips sheila gs_0.14</t>
+          <t>unknown_galleta wafers lago wafers mini party avellanas_0.12</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -8734,11 +8851,11 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Chocolate Chips Sheila Gs</t>
+          <t>Galleta Wafers Lago Wafers Mini Party Avellanas</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.15</v>
+        <v>2.06</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -8760,7 +8877,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle dark chocolate sea salt sheila gs_0.14</t>
+          <t>unknown_galletas bridge wafer naranja_0.3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -8773,11 +8890,11 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Dark Chocolate Sea Salt Sheila Gs</t>
+          <t>Galletas Bridge Wafer Naranja</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.15</v>
+        <v>1.51</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -8799,7 +8916,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>unknown_galletas brownie brittle salted caramel sheila gs_0.14</t>
+          <t>unknown_galletas de chocolate y malvavisco mamut_0.03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -8812,11 +8929,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Galletas Brownie Brittle Salted Caramel Sheila Gs</t>
+          <t>Galletas De Chocolate Y Malvavisco Mamut</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.15</v>
+        <v>0.48</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -8824,6 +8941,123 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>unknown_galletas sandwich chocolate choco wow 10 und_0.48</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Galletas Sandwich Chocolate Choco Wow 10 Und</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>unknown_tortillas chips kettle corn popcorners_0.14</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Tortillas Chips Kettle Corn Popcorners</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>unknown_cheez it original 1 5oz_0.04</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Cheez-It Original  1.5oz</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1.201923076923077</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,44 +529,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm bakery classics buns white slider 14_0.4</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM BAKERY CLASSICS BUNS, WHITE SLIDER | 14 oz</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>8.094972067039107</v>
+        <v>1.63</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM BAKERY CLASSICS BUNS, WHITE SLIDER | 14 oz</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.899441340782123</v>
+        <v>2.04</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>179.1907514450867</v>
+        <v>-20.09803921568628</v>
       </c>
     </row>
     <row r="4">
@@ -604,28 +604,28 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lumijor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Lumijor</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lumijor</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Lumijor</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>2.04</v>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-20.09803921568628</v>
+        <v>25.15337423312884</v>
       </c>
     </row>
     <row r="5">
@@ -641,34 +641,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>molino del sol_pan viga integral con germen de trigo molino del sol_0.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Pan Viga Integral Con Germen De Trigo Molino Del Sol</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Pan Viga Integral Con Germen De Trigo Molino Del Sol</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>25.15337423312884</v>
+        <v>16.0377358490566</v>
       </c>
     </row>
     <row r="6">
@@ -891,39 +891,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>tostitos_chips de tortilla de maiz sabor hint of lime tostitos_0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Chips De Tortilla De Maiz Sabor Hint Of Lime Tostitos</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>5.85</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Chips De Tortilla De Maiz Sabor Hint Of Lime Tostitos</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>4.99</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-46.23287671232876</v>
+        <v>17.23446893787574</v>
       </c>
     </row>
     <row r="11">
@@ -942,39 +942,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>tostitos_chips de tortillas de maiz tostitos santa elena_0.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.92</v>
+        <v>3.88</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.57</v>
+        <v>3.33</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,50 +982,50 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>85.98726114649681</v>
+        <v>16.51651651651651</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.461538461538462</v>
+        <v>1.57</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3125</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1033,50 +1033,50 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1007.692307692308</v>
+        <v>-46.23287671232876</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.3125</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.461538461538462</v>
+        <v>1.57</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-90.97222222222221</v>
+        <v>85.98726114649681</v>
       </c>
     </row>
     <row r="14">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bermudez_bermudez dixee peanut butter filled_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1110,11 +1110,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BERMUDEZ DIXEE PEANUT BUTTER FILLED</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.846153846153846</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Bermudez Dixee Peanut Butter Filled</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.625</v>
+        <v>0.3125</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>515.3846153846155</v>
+        <v>1007.692307692308</v>
       </c>
     </row>
     <row r="15">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bermudez_bermudez dixee peanut butter filled_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1161,11 +1161,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bermudez Dixee Peanut Butter Filled</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.625</v>
+        <v>0.3125</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1174,11 +1174,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BERMUDEZ DIXEE PEANUT BUTTER FILLED</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.846153846153846</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>-83.75</v>
+        <v>-90.97222222222221</v>
       </c>
     </row>
     <row r="16">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bermudez_bermudez domino vanilla_unknown</t>
+          <t>bermudez_bermudez dixee peanut butter filled_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BERMUDEZ DOMINO VANILLA</t>
+          <t>BERMUDEZ DIXEE PEANUT BUTTER FILLED</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.980769230769231</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1225,11 +1225,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bermudez Domino Vanilla</t>
+          <t>Bermudez Dixee Peanut Butter Filled</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5048076923076923</v>
+        <v>0.625</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>490.4761904761905</v>
+        <v>515.3846153846155</v>
       </c>
     </row>
     <row r="17">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bermudez_bermudez domino vanilla_unknown</t>
+          <t>bermudez_bermudez dixee peanut butter filled_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bermudez Domino Vanilla</t>
+          <t>Bermudez Dixee Peanut Butter Filled</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.5048076923076923</v>
+        <v>0.625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1276,11 +1276,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BERMUDEZ DOMINO VANILLA</t>
+          <t>BERMUDEZ DIXEE PEANUT BUTTER FILLED</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.980769230769231</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>-83.06451612903226</v>
+        <v>-83.75</v>
       </c>
     </row>
     <row r="18">
@@ -1304,34 +1304,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>bermudez_bermudez domino vanilla_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>BERMUDEZ DOMINO VANILLA</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.817307692307693</v>
+        <v>2.980769230769231</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Bermudez Domino Vanilla</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.307692307692307</v>
+        <v>0.5048076923076923</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>152.0833333333334</v>
+        <v>490.4761904761905</v>
       </c>
     </row>
     <row r="19">
@@ -1355,34 +1355,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>bermudez_bermudez domino vanilla_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Bermudez Domino Vanilla</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.307692307692307</v>
+        <v>0.5048076923076923</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>BERMUDEZ DOMINO VANILLA</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5.817307692307693</v>
+        <v>2.980769230769231</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>-60.33057851239671</v>
+        <v>-83.06451612903226</v>
       </c>
     </row>
     <row r="20">
@@ -1406,34 +1406,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>charles_charles jordan almonds_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charles Jordan Almonds</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.548076923076923</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Charles Jordan Almonds</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.346153846153846</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>89.28571428571422</v>
+        <v>152.0833333333334</v>
       </c>
     </row>
     <row r="21">
@@ -1457,34 +1457,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>charles_charles jordan almonds_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Charles Jordan Almonds</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.346153846153846</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Charles Jordan Almonds</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.548076923076923</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>-47.1698113207547</v>
+        <v>-60.33057851239671</v>
       </c>
     </row>
     <row r="22">
@@ -1508,34 +1508,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>charles_charles jordan almonds_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Charles Jordan Almonds</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.3365384615384615</v>
+        <v>2.548076923076923</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Charles Jordan Almonds</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.942307692307693</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>-91.46341463414633</v>
+        <v>89.28571428571422</v>
       </c>
     </row>
     <row r="23">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>charles_charles jordan almonds_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Charles Jordan Almonds</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.942307692307693</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Charles Jordan Almonds</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.3365384615384615</v>
+        <v>2.548076923076923</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1071.428571428572</v>
+        <v>-47.1698113207547</v>
       </c>
     </row>
     <row r="24">
@@ -1610,34 +1610,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>instorebakery_holiday cheeze puffs_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.730769230769231</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.4326923076923077</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>300</v>
+        <v>-91.46341463414633</v>
       </c>
     </row>
     <row r="25">
@@ -1661,34 +1661,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>instorebakery_holiday cheeze puffs_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.4326923076923077</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Holiday Cheeze Puffs</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.730769230769231</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>-75</v>
+        <v>1071.428571428572</v>
       </c>
     </row>
     <row r="26">
@@ -1712,34 +1712,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>instorebakery_holiday cheeze puffs_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.682692307692308</v>
+        <v>1.730769230769231</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.086538461538462</v>
+        <v>0.4326923076923077</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>-58.82352941176471</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27">
@@ -1763,34 +1763,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>instorebakery_holiday cheeze puffs_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4.086538461538462</v>
+        <v>0.4326923076923077</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Instorebakery</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Holiday Cheeze Puffs</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.682692307692308</v>
+        <v>1.730769230769231</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>142.8571428571429</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="28">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1916,34 +1916,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>oh snacks_oh snacks quinoa_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.576923076923077</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12.35576923076923</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-54.86381322957198</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="31">
@@ -1967,34 +1967,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>oh snacks_oh snacks quinoa_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12.35576923076923</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Oh Snacks</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Oh Snacks Quinoa</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.576923076923077</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>121.551724137931</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -2018,34 +2018,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>other_toppers caramel popcorn_unknown</t>
+          <t>oh snacks_oh snacks quinoa_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.326923076923077</v>
+        <v>5.576923076923077</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.057692307692308</v>
+        <v>12.35576923076923</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>309.0909090909091</v>
+        <v>-54.86381322957198</v>
       </c>
     </row>
     <row r="33">
@@ -2069,34 +2069,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>other_toppers caramel popcorn_unknown</t>
+          <t>oh snacks_oh snacks quinoa_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.057692307692308</v>
+        <v>12.35576923076923</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Oh Snacks</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Toppers Caramel Popcorn</t>
+          <t>Oh Snacks Quinoa</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.326923076923077</v>
+        <v>5.576923076923077</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>-75.55555555555556</v>
+        <v>121.551724137931</v>
       </c>
     </row>
     <row r="34">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>other_toppers frosted popcorn_unknown</t>
+          <t>other_toppers caramel popcorn_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2143,11 +2143,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.105769230769231</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>291.3043478260869</v>
+        <v>309.0909090909091</v>
       </c>
     </row>
     <row r="35">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>other_toppers frosted popcorn_unknown</t>
+          <t>other_toppers caramel popcorn_unknown</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2181,11 +2181,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.105769230769231</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Toppers Frosted Popcorn</t>
+          <t>Toppers Caramel Popcorn</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>-74.44444444444444</v>
+        <v>-75.55555555555556</v>
       </c>
     </row>
     <row r="36">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>other_toppers kettle popcorn_unknown</t>
+          <t>other_toppers frosted popcorn_unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2232,11 +2232,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.134615384615385</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2245,11 +2245,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.057692307692308</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>290.9090909090909</v>
+        <v>291.3043478260869</v>
       </c>
     </row>
     <row r="37">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>other_toppers kettle popcorn_unknown</t>
+          <t>other_toppers frosted popcorn_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.057692307692308</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2296,11 +2296,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Toppers Kettle Popcorn</t>
+          <t>Toppers Frosted Popcorn</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.134615384615385</v>
+        <v>4.326923076923077</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-74.41860465116279</v>
+        <v>-74.44444444444444</v>
       </c>
     </row>
     <row r="38">
@@ -2324,34 +2324,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+          <t>other_toppers kettle popcorn_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.201923076923077</v>
+        <v>4.134615384615385</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Goldfish Cheddar</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8653846153846154</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>38.88888888888888</v>
+        <v>290.9090909090909</v>
       </c>
     </row>
     <row r="39">
@@ -2375,34 +2375,34 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+          <t>other_toppers kettle popcorn_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Goldfish Cheddar</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.8653846153846154</v>
+        <v>1.057692307692308</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+          <t>Toppers Kettle Popcorn</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.201923076923077</v>
+        <v>4.134615384615385</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>-27.99999999999999</v>
+        <v>-74.41860465116279</v>
       </c>
     </row>
     <row r="40">
@@ -2426,34 +2426,34 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shoon Fatt Butter Crackers</t>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4.182692307692307</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
+          <t>Pepperidge Farm Goldfish Cheddar</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.778846153846154</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>135.1351351351352</v>
+        <v>38.88888888888888</v>
       </c>
     </row>
     <row r="41">
@@ -2477,34 +2477,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
+          <t>Pepperidge Farm Goldfish Cheddar</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.778846153846154</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Shoon Fatt Butter Crackers</t>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.182692307692307</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>-57.4712643678161</v>
+        <v>-27.99999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>Shoon Fatt Butter Crackers</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10.86538461538462</v>
+        <v>4.182692307692307</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2551,11 +2551,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>SHOON FATT BUTTER CRACKERS</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.826923076923077</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>494.7368421052633</v>
+        <v>135.1351351351352</v>
       </c>
     </row>
     <row r="43">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>SHOON FATT BUTTER CRACKERS</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.826923076923077</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2602,11 +2602,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>Shoon Fatt Butter Crackers</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10.86538461538462</v>
+        <v>4.182692307692307</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>-83.18584070796462</v>
+        <v>-57.4712643678161</v>
       </c>
     </row>
     <row r="44">
@@ -2630,34 +2630,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.778846153846154</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.105769230769231</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>60.86956521739126</v>
+        <v>494.7368421052633</v>
       </c>
     </row>
     <row r="45">
@@ -2681,34 +2681,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.105769230769231</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sunshine Snacks</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sunshine Cashew Nuts Light Salt</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.778846153846154</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>-37.83783783783782</v>
+        <v>-83.18584070796462</v>
       </c>
     </row>
     <row r="46">
@@ -2732,34 +2732,34 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.610576923076923</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.346153846153846</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>19.64285714285712</v>
+        <v>60.86956521739126</v>
       </c>
     </row>
     <row r="47">
@@ -2783,34 +2783,34 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>sunshine snacks_sunshine cashew nuts light salt_unknown</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.610576923076923</v>
+        <v>1.105769230769231</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Sunshine Snacks</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Sunshine Cashew Nuts Light Salt</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.778846153846154</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>179.1666666666667</v>
+        <v>-37.83783783783782</v>
       </c>
     </row>
     <row r="48">
@@ -2848,28 +2848,28 @@
         </is>
       </c>
       <c r="F48" t="n">
+        <v>1.610576923076923</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
         <v>1.346153846153846</v>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>1.610576923076923</v>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>-16.41791044776118</v>
+        <v>19.64285714285712</v>
       </c>
     </row>
     <row r="49">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.346153846153846</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>133.3333333333334</v>
+        <v>179.1666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.5769230769230769</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>-64.17910447761194</v>
+        <v>-16.41791044776118</v>
       </c>
     </row>
     <row r="51">
@@ -3001,28 +3001,28 @@
         </is>
       </c>
       <c r="F51" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>1.346153846153846</v>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>-57.14285714285716</v>
+        <v>133.3333333333334</v>
       </c>
     </row>
     <row r="52">
@@ -3038,34 +3038,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>wibisco_wibisco tea time chocolate_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wibisco Tea Time Chocolate</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4.086538461538462</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Wibisco</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Wibisco Tea Time Chocolate</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4326923076923077</v>
+        <v>1.610576923076923</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>844.4444444444445</v>
+        <v>-64.17910447761194</v>
       </c>
     </row>
     <row r="53">
@@ -3089,41 +3089,143 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>-57.14285714285716</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>wibisco_wibisco tea time chocolate_unknown</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Wibisco</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Wibisco Tea Time Chocolate</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F54" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Wibisco</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Wibisco Tea Time Chocolate</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
         <v>0.4326923076923077</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>844.4444444444445</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>wibisco_wibisco tea time chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Wibisco</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Wibisco Tea Time Chocolate</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="F55" t="n">
+        <v>0.4326923076923077</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Wibisco</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Wibisco Tea Time Chocolate</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
         <v>4.086538461538462</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="K53" t="n">
+      <c r="K55" t="n">
         <v>-89.41176470588236</v>
       </c>
     </row>
@@ -3138,7 +3240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3197,6 +3299,1410 @@
           <t>price_change_pct</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>eggo_eggo eggo frozen breakfast frozen waffles buttermilk 32_0.91</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Eggo</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Eggo | EGGO FROZEN BREAKFAST FROZEN WAFFLES, BUTTERMILK | 32 oz</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>9.770949720670391</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo 8 ea jumbo kaaskoekjes_unknown</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Jumbo | 8 ea JUMBO KAASKOEKJES</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>7.201117318435754</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo double milk chocolate cookies 10 5_0.3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO DOUBLE MILK CHOCOLATE COOKIES | 10.5 oz</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>7.145251396648044</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm tahoe crispy white chocolate macadamia nut cookies bag 8 cookies 10 5_0.3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | Pepperidge Farm Tahoe Crispy White Chocolate Macadamia Nut Cookies, Bag (8 Cookies) | 10.5 oz</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>7.145251396648044</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm texas toast frozen 5 cheese bread 1300_1.3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | Pepperidge Farm® Texas Toast Frozen 5 Cheese Bread | 1300 g</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5.860335195530726</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles original 1 4_0.04</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES ORIGINAL | 1.4 oz</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.558659217877095</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles pizza 1 4_0.04</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES PIZZA | 1.4 oz</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.558659217877095</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles potato crisps chips original grab n go 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Pringles | Pringles Potato Crisps Chips, Original, Grab N' Go | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles salt vinegar 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES SALT &amp; VINEGAR | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles salty snacks potato crisps chips sour cream and onion flavored 5 2_0.15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES SALTY SNACKS POTATO CRISPS CHIPS, SOUR CREAM AND ONION FLAVORED | 5.2 oz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>schar_schar 6 ea schar crispbread 5 3_0.15</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Schar</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Schar | 6 ea Schar Crispbread, Gluten Free | 5.3 oz</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6.865921787709497</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>siete_siete 6 ea siete grain mexican shortbread cookies 4 5_0.13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Siete | 6 ea Siete Grain Free Mexican Shortbread Cookies | 4.5 oz</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.731843575418994</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>stouffer s_stouffer s stouffer s french bread three meat frozen pizza box 29 6_0.84</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stouffer'S</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Stouffer's | STOUFFER'S French Bread Three Meat Frozen Pizza Box | 29.6 oz</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>10.02793296089386</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>totino s_totino s totino s party pizza triple cheese 175_0.18</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Totino'S</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Totino's | TOTINO'S PARTY PIZZA TRIPLE CHEESE | 175 g</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.949720670391062</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>twix_twix twix cookie bars share size 4 ea 5 3_0.15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Twix</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Twix | Twix Cookie Bars, Share Size 4 ea | 5.3 oz</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.508379888268156</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>twix_twix twix cookie bars two right 3 02_0.09</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Twix</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Twix | Twix Cookie Bars, Two Right | 3.02 oz</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>unknown_cookie pasta 2 6_0.07</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COOKIE PASTA | 2.6 oz</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.905027932960894</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>unknown_hershey s cookie n creme candy share 6_0.17</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Hershey's Cookie 'N' Creme Candy Share Pack | 6 oz</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.620111731843576</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>unknown_seara breaded chicken burger 350_0.35</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SEARA BREADED CHICKEN BURGER | 350 g</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>wow_galletas con chispas de chocolate choco wow_unknown</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wow</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Choco Wow</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>la panera_pan brioche la panera_unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>La Panera</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pan Brioche La Panera</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lenny larry s_galletas con chips de chocolate lenny y larry ll_0.11</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lenny &amp; Larry'S</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Galletas Con Chips De Chocolate Lenny Y Larry Ll</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>wow_galletas con chispas de chocolate choco wow_unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Wow</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Choco Wow</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>l der_galletas con chispas de chocolate lider_unknown</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Lider</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>la panera_pan brioche la panera_unknown</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>La Panera</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pan Brioche La Panera</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>lenny larry s_galletas con chips de chocolate lenny y larry ll_0.11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lenny &amp; Larry'S</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Galletas Con Chips De Chocolate Lenny Y Larry Ll</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>wow_galletas con chispas de chocolate choco wow_unknown</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Wow</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Choco Wow</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>gullon_galletas con avena y naranja sin azucar gullon_unknown</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Gullon</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Galletas Con Avena Y Naranja Sin Azucar Gullon</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>l der_galletas con chispas de chocolate lider_unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Lider</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>la panera_pan brioche la panera_unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>La Panera</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pan Brioche La Panera</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>lenny larry s_galletas con chips de chocolate lenny y larry ll_0.11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lenny &amp; Larry'S</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Galletas Con Chips De Chocolate Lenny Y Larry Ll</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>wow_galletas con chispas de chocolate choco wow_unknown</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Wow</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Choco Wow</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>wow_galletas con chispas de chocolate choco wow_unknown</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wow</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Choco Wow</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>gullon_galletas con avena y naranja sin azucar gullon_unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Gullon</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Galletas Con Avena Y Naranja Sin Azucar Gullon</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>lenny larry s_galletas con chips de chocolate lenny y larry ll_0.11</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lenny &amp; Larry'S</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Galletas Con Chips De Chocolate Lenny Y Larry Ll</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>wow_galletas con chispas de chocolate choco wow_unknown</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Wow</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Galletas Con Chispas De Chocolate Choco Wow</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3209,7 +4715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3269,6 +4775,5739 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>badia_badia 6 pc badia everything bagel_unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Badia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Badia | 6 pc BADIA EVERYTHING BAGEL</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>badia_badia badia everything bagels 2 8_0.08</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Badia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Badia | Badia Everything Bagels | 2.8 oz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2.340782122905028</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites 18 bagel bites three cheese pizza snacks party size 40 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bagel Bites | 18 ct Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>8.910614525139664</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites 7z bagel bites cheese pepperoni pizza snacks_unknown</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bagel Bites | 7z BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 7_0.2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 7 oz</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks 9 ea 510_0.51</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks 9 ea | 510 g</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bigelow_bigelow 19 pc bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bigelow</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bigelow | 19 pc Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.134078212290502</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>crav n_crav n crav n flavor tortilla chips ranch flavored 300_0.3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crav'N</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, Ranch Flavored | 300 g</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.005586592178771</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>crav n_crav n crav n flavor tortilla chips white corn restaurant style 300_0.3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crav'N</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Restaurant Style | 300 g</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.005586592178771</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>doritos_doritos doritos cool ranch flavored tortilla chips 320_0.32</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Doritos</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Doritos | Doritos Cool Ranch Flavored Tortilla Chips | 320 g</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.949720670391062</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>dove_dove 50 ml dove original deo roll on_unknown</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dove</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Dove | 50 ml DOVE ORIGINAL DEO ROLL-ON</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dove_dove dove vanilla ice cream bars coated with dark chocolate individually wrapped dessert 3 bars 16_0.45</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dove</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Dove | DOVE Vanilla Ice Cream Bars Coated With Dark Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 16 oz</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.223463687150838</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dove_dove dove vanilla ice cream bars coated with milk chocolate individually wrapped dessert 3 bars 11_0.31</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dove</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Dove | DOVE Vanilla Ice Cream Bars Coated With Milk Chocolate, Individually Wrapped Dessert, 3 Pack, Bars | 11 oz</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.301675977653631</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>eggo_eggo 12 count eggo frozen breakfast frozen waffles buttermilk_unknown</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Eggo</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Eggo | 12 count EGGO FROZEN BREAKFAST FROZEN WAFFLES, BUTTERMILK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9.882681564245811</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>elina_elina 50 ml elina deo roll on cool fm_unknown</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Elina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Elina | 50 ml ELINA DEO ROLL-ON COOL FM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>elina_elina 50 ml elina deo roll on sensuel care women_unknown</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Elina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Elina | 50 ml ELINA DEO ROLL-ON SENSUEL CARE WOMEN</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.787709497206704</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>elina_elina 50 ml elina roll on active unisex_unknown</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Elina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Elina | 50 ml ELINA ROLL-ON ACTIVE UNISEX</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.787709497206704</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>food club_food club 6 ea food club tortillas whole wheat wrap style 8 inch 10 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Food Club</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Food Club | 6 ea Food Club Tortillas, Whole Wheat, Wrap Style, 8 Inch 10 ea</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6.675977653631285</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>food club_food club food club tortillas whole wheat wrap style 8 inch 10 ea 370_0.37</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Food Club</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Food Club | Food Club Tortillas, Whole Wheat, Wrap Style, 8 Inch 10 ea | 370 g</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>glad_glad 20 bg glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Glad</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Glad | 20 bg Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>5.575418994413408</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>glad_glad 50 ml glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Glad</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Glad | 50 ml Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo 10 jumbo double milk chocolate cookies 5_0.14</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Jumbo | 10 . JUMBO DOUBLE MILK CHOCOLATE COOKIES | 5 oz</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>7.145251396648044</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo kaaskoekjes 11 6_0.33</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO KAASKOEKJES | 11.6 oz</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>7.201117318435754</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo pita volkoren 5st 14_0.4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO PITA VOLKOREN 5ST | 14 oz</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo s tortilla wortel 740_0.74</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO'S TORTILLA WORTEL | 740 g</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3.960893854748603</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo supercroissantdeeg 24_0.68</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO SUPERCROISSANTDEEG | 24 oz</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>7.251396648044693</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla chips cheese 370_0.37</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA CHIPS CHEESE | 370 g</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.229050279329609</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla dip hot 9 75_0.28</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA DIP HOT | 9.75 oz</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla dip mild 300_0.3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA DIP MILD | 300 g</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.675977653631285</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla nat 8st 740_0.74</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA NAT.8ST | 740 g</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3.960893854748603</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla natur xl 12 10_0.28</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA NATUR XL 12 | 10 oz</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>6.977653631284916</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla naturel xl 6st 10_0.28</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA NATUREL XL 6ST | 10 oz</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>6.698324022346369</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla volkoren 8 10_0.28</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA VOLKOREN 8 CT | 10 oz</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>6.698324022346369</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo tortilla volkoren xl 6st 325_0.32</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO TORTILLA VOLKOREN XL 6ST | 325 g</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1.893854748603352</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo vrij tortilla multigrain 16_0.45</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO GLUTEN VRIJ TORTILLA (MULTIGRAIN) | 16 oz</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>2.223463687150838</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>kinder_kinder kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Kinder</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kinder | Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kiss_kiss hershey s kisses cookies n creme candy share 6_0.17</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Kiss</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kiss | HERSHEY'S KISSES Cookies 'n' Creme Candy Share Pack, | 6 oz</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.620111731843576</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>kraft_kraft kraft america s classic individually wrapped candy caramels bag 240_0.24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Kraft</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kraft | Kraft America's Classic Individually Wrapped Candy Caramels, Bag | 240 g</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>2.223463687150838</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita 18z la dulcerita assorted muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>La Dulcerita | 18z LA DULCERITA ASSORTED MUFFIN</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita la dulcerita blueberry muffins 24_0.68</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>La Dulcerita | LA DULCERITA BLUEBERRY MUFFINS | 24 oz</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>7.251396648044693</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lewis bake shop_lewis bake shop 2 pc lewis bake shop white hot dog buns 8 count 15_0.43</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lewis Bake Shop</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Lewis Bake Shop | 2 pc Lewis Bake Shop White Hot Dog Buns, , 8 Count | 15 oz</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1.396648044692737</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lewis bake shop_lewis bake shop 6 pc lewis bake shop white hot dog buns 8 count 15_0.43</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lewis Bake Shop</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Lewis Bake Shop | 6 pc Lewis Bake Shop White Hot Dog Buns, , 8 Count | 15 oz</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3.016759776536313</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lu_lu tf blueberry bagel 567_0.57</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LU | Tf Blueberry Bagel | 567 g</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>lu_lu udi s classic hamburger buns 10 6_0.3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>LU | UDI'S GLUTEN FREE CLASSIC HAMBURGER BUNS | 10.6 oz</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>8.87709497206704</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lu_lu udi s classic hot dog buns frozen 6 count 10 4oz_0.29</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>LU | Udi's Gluten Free Classic Hot Dog Buns, Frozen, . 6 Count | 10.4oz</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>7.793296089385474</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lu_lu udi s classic hot dog buns frozen 6 count 29 6_0.84</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>LU | Udi's Gluten Free Classic Hot Dog Buns, Frozen, . 6 Count | 29.6 oz</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>10.02793296089386</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>maria_maria 24 pc santa maria wrap salsa mild_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Maria | 24 pc SANTA MARIA WRAP SALSA MILD</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>5.134078212290502</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>milka_milka 4 ea milka oreo_unknown</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Milka</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Milka | 4 ea MILKA OREO</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>5.558659217877095</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>odorex_odorex odorex deo roll 0 perfume_unknown</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Odorex</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Odorex | ODOREX DEO ROLL 0 % PERFUME</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>10.60893854748603</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>oreo_oreo 12 cookies oreo original_unknown</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Oreo | 12 ct COOKIES OREO ORIGINAL</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3.346368715083799</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>oreo_oreo joy sugar cones oreo cookie pieces 12 ea 246g_0.25</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Oreo | Joy Sugar Cones, Oreo Cookie Pieces 12 ea | 246g</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>4.999999999999999</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>oreo_oreo oreo cornetto 175_0.18</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Oreo | OREO CORNETTO | 175 g</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 8_0.23</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 8 oz</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>6.307262569832401</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>oreo_oreo oreo ice sandwich 100_0.1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Oreo | OREO ICE SANDWICH | 100 g</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>2.787709497206704</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>oreo_oreo oreo minis chocolate sandwich cookies snack cup 16_0.45</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Oreo | OREO Minis Chocolate Sandwich Cookies, Snack Cup | 16 oz</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>9.46927374301676</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 13 29_0.38</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 13.29 oz</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>7.368715083798882</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>oreo_oreo oreo thins golden sandwich cookies family size 3 5_0.1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Oreo | OREO Thins Golden Sandwich Cookies, Family Size, | 3.5 oz</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oreo_oreo yo crunch vanilla with oreo cookie pieces low fat yogurt 4 ea 5 25_0.15</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Oreo</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Oreo | Yo Crunch Vanilla With Oreo Cookie Pieces Low Fat Yogurt 4 ea | 5.25 oz</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>4.351955307262569</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm bakery classics hot dog buns side sliced 15_0.43</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | PEPPERIDGE FARM BAKERY CLASSICS HOT DOG BUNS, SIDE SLICED | 15 oz</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>3.88268156424581</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm bread jewish rye seeded 340_0.34</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | PEPPERIDGE FARM BREAD, JEWISH RYE, SEEDED | 340 g</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>4.999999999999999</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm bread pumpernickel dark pump 8_0.23</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | PEPPERIDGE FARM BREAD, PUMPERNICKEL, DARK PUMP | 8 oz</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm tahoe crispy white chocolate macadamia nut cookies bag 8 cookies 10 60_0.3</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | Pepperidge Farm Tahoe Crispy White Chocolate Macadamia Nut Cookies, Bag (8 Cookies) | 10.60 oz</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>7.145251396648044</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm texas toast frozen 5 cheese bread 6 slices box 1300_1.3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | Pepperidge Farm® Texas Toast Frozen 5 Cheese Bread, 6 Slices, . Box | 1300 g</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>5.860335195530726</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm texas toast frozen garlic bread 8 slices box 12 9oz_0.37</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | Pepperidge Farm® Texas Toast Frozen Garlic Bread, 8 Slices, . Box | 12.9oz</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>8.910614525139664</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>pepperidge farm_pepperidge farm pepperidge farm whole grain 100 whole wheat bread 24_0.68</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm | PEPPERIDGE FARM WHOLE GRAIN 100% WHOLE WHEAT BREAD | 24 oz</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>8.87709497206704</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pillsbury_pillsbury 12 roll pillsbury cinnamon rolls with icing_unknown</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pillsbury</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Pillsbury | 12 roll PILLSBURY CINNAMON ROLLS, WITH ICING</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>21.72625698324022</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pillsbury_pillsbury 9 pc pillsbury cinnamon rolls cream cheese icing_unknown</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Pillsbury</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Pillsbury | 9 pc PILLSBURY CINNAMON ROLLS, CREAM CHEESE ICING</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>18.0391061452514</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pirucream_pirucream 50 ml pirucream wafer rolls coconut 5 46_0.15</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pirucream</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Pirucream | 50 ml Pirucream Wafer Rolls, Coconut | 5.46 oz</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>3.17877094972067</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pirulin_pirulin 50 ml pirulin chocolate wafer rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Pirulin</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Pirulin | 50 ml PIRULIN CHOCOLATE WAFER ROLLS</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles original 1 41_0.04</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES ORIGINAL | 1.41 oz</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1.558659217877095</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles pizza 1 41_0.04</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES PIZZA | 1.41 oz</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1.558659217877095</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles potato crisps chips lunch snacks office and kids snacks grab n go original can 1 can 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Pringles | Pringles Potato Crisps Chips, Lunch Snacks, Office and Kids Snacks, Grab N' Go, Original, Can, 1 Can | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles salt vinegar 4 8_0.14</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES SALT &amp; VINEGAR | 4.8 oz</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles salty snacks potato crisps chips sour cream and onion flavored 5 3_0.15</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES SALTY SNACKS POTATO CRISPS CHIPS, SOUR CREAM AND ONION FLAVORED | 5.3 oz</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>reynolds_reynolds 75 ft reynolds wrap everyday 25 ft aluminum foil 1 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Reynolds</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Reynolds | 75 ft Reynolds Wrap Everyday 25 Ft Aluminum Foil 1 ea</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>8.76536312849162</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ricola_ricola 3 ricola wrapped drops honey herb cough drops 24 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ricola</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Ricola | 3 ct Ricola Wrapped Drops Honey Herb Cough Drops 24 ea</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>7.234636871508379</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ricola_ricola ricola wrapped drops cherry oral anesthetic 19 ea 250_0.25</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ricola</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Ricola | Ricola Wrapped Drops Cherry Oral Anesthetic 19 ea | 250 g</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1.837988826815642</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>roomboter_roomboter roomboter croissant 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Roomboter</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Roomboter | ROOMBOTER CROISSANT | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>3.513966480446927</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>santitas_santitas santitas tortilla chips tortilla triangles 10_0.28</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Santitas</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Santitas | SANTITAS TORTILLA CHIPS, TORTILLA TRIANGLES | 10 oz</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>6.698324022346369</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>schar_schar 12 schar hamburger buns_unknown</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Schar</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schar | 12 ct SCHAR HAMBURGER BUNS, GLUTEN FREE</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>8.653631284916202</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>schar_schar schar crispbread 7 4_0.21</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Schar</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Schar | Schar Crispbread, Gluten Free | 7.4 oz</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>6.865921787709497</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>schar_schar schar hamburger buns 16_0.45</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Schar</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Schar | SCHAR HAMBURGER BUNS, GLUTEN FREE | 16 oz</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>6.083798882681564</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>siete_siete siete grain mexican shortbread cookies 11_0.31</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Siete | Siete Grain Free Mexican Shortbread Cookies | 11 oz</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>2.731843575418994</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>siete_siete siete tortillas grain almond flour 8 ea 250_0.25</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Siete</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Siete | Siete Tortillas, Grain Free, Almond Flour 8 ea | 250 g</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1.837988826815642</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>stouffer s_stouffer s 27z stouffer s french bread three meat frozen pizza box 12 875oz_0.36</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Stouffer'S</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Stouffer's | 27z STOUFFER'S French Bread Three Meat Frozen Pizza Box | 12.875oz</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>10.02793296089386</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>tostitos_tostitos 8 ea tostitos restaurant style original tortilla chips 10_0.28</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tostitos</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Tostitos | 8 ea Tostitos Restaurant Style Original Tortilla Chips | 10 oz</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>13.37988826815642</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>tostitos_tostitos tostitos tortilla chips crispy rounds 370_0.37</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tostitos</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Tostitos | TOSTITOS TORTILLA CHIPS CRISPY ROUNDS | 370 g</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>2.229050279329609</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>tostitos_tostitos tostitos triangles hint of lime flavored tortilla chips 7_0.2</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tostitos</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Tostitos | Tostitos Triangles Hint Of Lime Flavored Tortilla Chips | 7 oz</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>5.245810055865922</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 100 ft toufayan bakeries restaurant style wraps_unknown</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Toufayan | 100 ft TOUFAYAN BAKERIES RESTAURANT STYLE WRAPS</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>3.905027932960894</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 25 ft toufayan bakeries wraps savory spinach_unknown</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Toufayan | 25 ft TOUFAYAN BAKERIES WRAPS SAVORY SPINACH</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>3.458100558659218</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 40 ea toufayan cinnamon raisin bagels_unknown</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Toufayan | 40 ea TOUFAYAN CINNAMON RAISIN BAGELS</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>16.1731843575419</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6 ea toufayan bakeries spinach wraps_unknown</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Toufayan | 6 ea TOUFAYAN BAKERIES GLUTEN FREE SPINACH WRAPS</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>6.675977653631285</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6 pc toufayan hearth baked whole wheat pita 6 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Toufayan | 6 pc Toufayan Hearth Baked Whole Wheat Pita 6 ea</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6 pc toufayan vegan everything bagels 6pc_unknown</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Toufayan | 6 pc TOUFAYAN VEGAN EVERYTHING BAGELS 6PC</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6 pc toufayan vegan mini bagels cinnamon raisin_unknown</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Toufayan | 6 pc TOUFAYAN VEGAN MINI BAGELS CINNAMON RAISIN</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6ct toufayan bakeries garlic pesto wraps_unknown</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Toufayan | 6ct TOUFAYAN BAKERIES GARLIC PESTO WRAPS</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bagels vegan whole wheat 20_0.57</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAGELS VEGAN WHOLE WHEAT | 20 oz</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bagels vegan whole wheat 24_0.68</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAGELS VEGAN WHOLE WHEAT | 24 oz</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>8.87709497206704</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries classic plain wraps 11_0.31</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES CLASSIC PLAIN WRAPS | 11 oz</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries low carb low sodium wraps 42_1.19</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES LOW CARB-LOW SODIUM WRAPS | 42 oz</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>5.301675977653631</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries original wraps 11_0.31</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES GLUTEN FREE ORIGINAL WRAPS | 11 oz</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>4.072625698324022</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries pita classic white 14_0.4</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES PITA CLASSIC WHITE | 14 oz</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries pita sweet onion 7 33_0.21</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES PITA SWEET ONION | 7.33 oz</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>3.290502793296089</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries sundried tomato wraps 11_0.31</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES SUNDRIED TOMATO WRAPS | 11 oz</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 1 5_0.04</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 1.5 oz</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>1.670391061452514</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan hearth baked whole wheat pita 6 ea 7 33_0.21</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Toufayan | Toufayan Hearth Baked Whole Wheat Pita 6 ea | 7.33 oz</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>5.575418994413408</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan mini bagelplain 14_0.4</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN MINI BAGELPLAIN | 14 oz</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>6.083798882681564</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>twix_twix twix caramel cookie milk chocolate candy bars full size 3 02_0.09</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Twix</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Twix | TWIX Caramel Cookie Milk Chocolate Candy Bars, Full Size, Pack | 3.02 oz</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>twix_twix twix milk chocolate caramel cookie candy bar share size 5 3_0.15</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Twix</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Twix | TWIX Milk Chocolate Caramel Cookie Candy Bar, Share Size, | 5.3 oz</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>2.508379888268156</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>unknown_1 pc white dinner rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1 pc WHITE DINNER ROLLS</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0.8324022346368715</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>unknown_10 pc bruine dinner rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>10 pc BRUINE DINNER ROLLS</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>2.094972067039106</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>unknown_10 pc suave ultra large roll_unknown</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>10 pc SUAVE ULTRA LARGE ROLL</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>2.061452513966481</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>unknown_20 pc soft rolls assorted_unknown</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>20 pc SOFT ROLLS ASSORTED</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1.614525139664805</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>unknown_3 tortilla wraps tomato_unknown</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>3 ct TORTILLA WRAPS TOMATO</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>7.234636871508379</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>unknown_4 pc kaasbol cheese roll_unknown</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4 pc KAASBOL / CHEESE ROLL</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>3.491620111731844</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>unknown_4 pc witte bollen white rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>4 pc WITTE BOLLEN / WHITE ROLLS</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>3.240223463687151</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>unknown_50 ml bob s red mill organic old fashioned rolled oats 32_0.91</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>50 ml Bob's Red Mill Organic Old Fashioned Rolled Oats | 32 oz</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>unknown_50 ml charmin ultra soft mega rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>50 ml CHARMIN ULTRA SOFT MEGA ROLLS</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>unknown_50 ml rock n roll strawberry licor de tequila_unknown</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>50 ml ROCK N ROLL STRAWBERRY LICOR DE TEQUILA</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>unknown_6 ea diamond cling wrap_unknown</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>6 ea Diamond Cling Wrap</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>unknown_6 pc rozijnen bollen raisin rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>6 pc ROZIJNEN BOLLEN / RAISIN ROLLS</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>2.513966480446927</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>unknown_6 pc witte puntjes white buns_unknown</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>6 pc WITTE PUNTJES / WHITE BUNS</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>2.793296089385475</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>unknown_6 pcs bruine bollen whole wheat rolls_unknown</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>6 pcs BRUINE BOLLEN / WHOLE WHEAT ROLLS</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1.709497206703911</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>unknown_6 stuks buns bruin bright bakery_unknown</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>6 stuks BUNS BRUIN (Bright Bakery)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1.709497206703911</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>unknown_afl 39 90 per kilo charmin 2 ply unscented mega rolls bathroom tissue 9 ea 500_0.5</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Afl.39.90 Per Kilo Charmin 2 Ply Unscented Mega Rolls Bathroom Tissue 9 ea | 500 g</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>11.14525139664804</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>unknown_charmin 2 ply unscented mega rolls bathroom tissue 12 ea 12 4_0.35</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Charmin 2 Ply Unscented Mega Rolls Bathroom Tissue 12 ea | 12.4 oz</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>unknown_colombian bread 12 9oz_0.37</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>COLOMBIAN BREAD | 12.9oz</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>8.910614525139664</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>unknown_cookie pasta 73_0.07</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>COOKIE PASTA | 73 g</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>3.905027932960894</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>unknown_tex mex mini tortilla original 240_0.24</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>TEX MEX MINI TORTILLA ORIGINAL | 240 g</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>2.223463687150838</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>unknown_tortilla wraps tomato 160_0.16</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>TORTILLA WRAPS TOMATO | 160 g</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>5.022346368715084</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>unknown_wei chuan spring rolls shells 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>WEI-CHUAN SPRING ROLLS SHELLS | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>5.46927374301676</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>unknown_wraps whole grain wheat flour tortillas 200g_0.2</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>WRAPS WHOLE GRAIN WHEAT FLOUR TORTILLAS | 200g</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>3.346368715083799</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>unknown_wraps whole grain wheat flour tortillas 230_0.23</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>WRAPS WHOLE GRAIN WHEAT FLOUR TORTILLAS | 230 g</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>bisco pan_bisco pan pan integral mielpasas_0.38</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Bisco Pan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Bisco Pan Pan Integral Mielpasas</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>unknown_moulind or pan integral sazucar_0.63</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Moulind Or Pan Integral Sazucar</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>PriceSmart</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>member s selection_members selection pan integral recien horneado_unknown</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Member'S Selection</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Members Selection Pan Integral Recien Horneado</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>biskitop_biskitop rose chocolate cream_unknown</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Biskitop</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Biskitop Rose Chocolate Cream</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1.586538461538462</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>chester_chester cake slice_unknown</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Chester</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Chester Cake Slice</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1.153846153846154</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>frito lay_frito lay variety bold mix x 24pc_unknown</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Frito Lay Variety Pack Bold Mix X 24pc</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>22.35576923076923</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>golden_golden harvest multigrain loaf_unknown</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Golden</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>2.596153846153846</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>other_nutella and go pretzel sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Nutella And Go Pretzel Sticks</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>2.644230769230769</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>other_star snacks walnuts_unknown</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Star Snacks Walnuts</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>11.10576923076923</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>other_sweet serenity chocolate chip_unknown</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sweet Serenity Chocolate Chip</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1.105769230769231</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>other_whytes wholesome bites garlic cheese bread_unknown</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Whytes Wholesome Bites Garlic/Cheese Bread</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>3.028846153846154</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan wraps garlic pesto 18oz_0.51</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Toufayan Wraps Garlic Pesto 18oz</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>5</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>unknown_bakery 9 chocolate cake_unknown</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Bakery 9” Chocolate Cake</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>6.009615384615385</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>unknown_bakewell tennis rolls 5_unknown</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Bakewell Tennis Rolls 5 ct</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1.730769230769231</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,44 +478,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>siete_siete tortilla chip lime 5oz_0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>SIETE TORTILLA CHIP LIME 5oz</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>6.81</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Siete</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>SIETE TORTILLA CHIP LIME 5oz</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>7.65</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,50 +523,50 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-20.09803921568628</v>
+        <v>-10.98039215686275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>unknown_waybetter chip tortilla avocado ranch 5 5oz_0.16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>WAYBETTER CHIP TORTILLA AVOCADO RANCH 5.5OZ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>6.08</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>WAYBETTER CHIP TORTILLA AVOCADO RANCH 5.5OZ</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.63</v>
+        <v>6.47</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -574,50 +574,50 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>25.15337423312884</v>
+        <v>-6.02782071097372</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>unknown_wholesome pancake syrup organic 20oz_0.57</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>WHOLESOME PANCAKE SYRUP ORGANIC 20oz</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>11.84</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>WHOLESOME PANCAKE SYRUP ORGANIC 20oz</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.92</v>
+        <v>10.78</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -625,50 +625,50 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>-46.23287671232876</v>
+        <v>9.833024118738409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>lays_lays lay s stax original potato crisps 6 5_0.18</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Lays | LAY'S STAX ORIGINAL POTATO CRISPS | 6.5 oz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.92</v>
+        <v>5.078212290502793</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Lays | LAY'S STAX ORIGINAL POTATO CRISPS | 6.5 oz</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.57</v>
+        <v>3.905027932960894</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,50 +676,50 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>85.98726114649681</v>
+        <v>30.04291845493561</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>unknown_tiramisu gebak_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>TIRAMISU GEBAK</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.461538461538462</v>
+        <v>3.569832402234637</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>TIRAMISU GEBAK</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.3125</v>
+        <v>3.067039106145252</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -727,50 +727,50 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1007.692307692308</v>
+        <v>16.3934426229508</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3125</v>
+        <v>1.63</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.461538461538462</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -778,50 +778,50 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-90.97222222222221</v>
+        <v>-20.09803921568628</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.817307692307693</v>
+        <v>2.04</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.307692307692307</v>
+        <v>1.63</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -829,50 +829,50 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>152.0833333333334</v>
+        <v>25.15337423312884</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>food club_tortilla de maiz para tacos food club_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Food Club</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Tortilla De Maiz Para Tacos Food Club</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.307692307692307</v>
+        <v>2.44</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Food Club</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Tortilla De Maiz Para Tacos Food Club</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.817307692307693</v>
+        <v>2.68</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,50 +880,50 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-60.33057851239671</v>
+        <v>-8.955223880597023</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>pirulin_barquilla rellena de crema de coco pirulin_0.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Barquilla Rellena De Crema De Coco Pirulin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.3365384615384615</v>
+        <v>3.09</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Pirulin</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Barquilla Rellena De Crema De Coco Pirulin</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.942307692307693</v>
+        <v>3.49</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,50 +931,50 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-91.46341463414633</v>
+        <v>-11.46131805157594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.942307692307693</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.3365384615384615</v>
+        <v>2.92</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,50 +982,50 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1071.428571428572</v>
+        <v>-46.23287671232876</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.682692307692308</v>
+        <v>2.92</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.086538461538462</v>
+        <v>1.57</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-58.82352941176471</v>
+        <v>85.98726114649681</v>
       </c>
     </row>
     <row r="13">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>4.086538461538462</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.682692307692308</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>142.8571428571429</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="14">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1110,32 +1110,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>1.682692307692308</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.086538461538462</v>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>-58.82352941176471</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="15">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>4.086538461538462</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.682692307692308</v>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>142.8571428571429</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="16">
@@ -1202,34 +1202,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>29.08653846153846</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15.04807692307692</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>93.29073482428115</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="17">
@@ -1267,28 +1267,28 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>29.08653846153846</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>15.04807692307692</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>New York Style</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>29.08653846153846</v>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>-48.26446280991735</v>
+        <v>93.29073482428115</v>
       </c>
     </row>
     <row r="18">
@@ -1304,34 +1304,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.442307692307692</v>
+        <v>15.04807692307692</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.115384615384615</v>
+        <v>29.08653846153846</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>-79.72972972972973</v>
+        <v>-48.26446280991735</v>
       </c>
     </row>
     <row r="19">
@@ -1365,32 +1365,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.442307692307692</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Otis Spunkmeyer</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>7.115384615384615</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Otis Spunkmeyer</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.442307692307692</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>393.3333333333333</v>
+        <v>-79.72972972972973</v>
       </c>
     </row>
     <row r="20">
@@ -1406,34 +1406,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.254807692307693</v>
+        <v>7.115384615384615</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Otis Spunkmeyer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1.442307692307692</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>70.19230769230769</v>
+        <v>393.3333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -1467,32 +1467,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>PRINGLES PIZZA</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4.254807692307693</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>Pringles Pizza</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>2.5</v>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PRINGLES PIZZA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4.254807692307693</v>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>-41.24293785310735</v>
+        <v>70.19230769230769</v>
       </c>
     </row>
     <row r="22">
@@ -1508,34 +1508,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shoon Fatt Butter Crackers</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.182692307692307</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.778846153846154</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>135.1351351351352</v>
+        <v>-41.24293785310735</v>
       </c>
     </row>
     <row r="23">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.778846153846154</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Shoon Fatt Butter Crackers</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.182692307692307</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>-57.4712643678161</v>
+        <v>24.99999999999997</v>
       </c>
     </row>
     <row r="24">
@@ -1610,34 +1610,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10.86538461538462</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.826923076923077</v>
+        <v>0.625</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>494.7368421052633</v>
+        <v>169.2307692307692</v>
       </c>
     </row>
     <row r="25">
@@ -1661,34 +1661,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.826923076923077</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10.86538461538462</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>-83.18584070796462</v>
+        <v>-19.99999999999998</v>
       </c>
     </row>
     <row r="26">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.682692307692308</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.346153846153846</v>
+        <v>0.625</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>24.99999999999997</v>
+        <v>115.3846153846154</v>
       </c>
     </row>
     <row r="27">
@@ -1777,28 +1777,28 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>1.682692307692308</v>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0.625</v>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>169.2307692307692</v>
+        <v>-62.85714285714285</v>
       </c>
     </row>
     <row r="28">
@@ -1828,180 +1828,27 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>1.346153846153846</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1.682692307692308</v>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-19.99999999999998</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>115.3846153846154</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>-62.85714285714285</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
         <v>-53.57142857142858</v>
       </c>
     </row>
@@ -2016,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2075,6 +1922,4062 @@
           <t>price_change_pct</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks 9 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks 9 ea</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 510_0.51</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 510 g</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks party size 40 ea 7_0.2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea | 7 oz</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>eggo_eggo eggo waffles blueberry 14_0.4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Eggo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Eggo | EGGO WAFFLES, BLUEBERRY | 14 oz</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>frito lay_frito lay frito lay snacks classic mix 24 ea 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Frito-Lay | Frito Lay Snacks, Classic Mix 24 ea | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>goldfish_goldfish goldfish baked snack crackers cheddar 250_0.25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Goldfish</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 250 g</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.061452513966481</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo hartig kaas tomaat 14 2_0.4</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO HARTIG KAAS/TOMAAT | 14.2 oz</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.396648044692737</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo luchtig crack naturel vegan 155_0.16</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO LUCHTIG.CRACK NATUREL VEGAN | 155 g</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2.452513966480447</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita 2 pc la dulcerita rasin muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>La Dulcerita | 2 pc LA DULCERITA RASIN MUFFIN</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita la dulcerita vanilla muffin 24_0.68</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>La Dulcerita | LA DULCERITA VANILLA MUFFIN | 24 oz</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>7.251396648044693</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita la dulcerita vanilla pound cake_unknown</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>La Dulcerita | LA DULCERITA VANILLA POUND CAKE</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6.117318435754189</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lays_lays lay s honey barbecue potato chips 6 5_0.18</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Lays | Lay's Honey Barbecue Potato Chips | 6.5 oz</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4.966480446927375</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lays_lays lay s kettle cooked jalapeno flavored potato chips 6 5_0.18</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lays | Lay's Kettle Cooked Jalapeno Flavored Potato Chips | 6.5 oz</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>5.078212290502793</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lays_lays lay s potato chips salt vinegar flavored 6 1 6 5_0.18</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Lays | Lay's Potato Chips Salt &amp; Vinegar Flavored 6 1/ | 6.5 oz</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.905027932960894</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lays_lays lays classic chips 8_0.23</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Lays | LAYS CLASSIC CHIPS | 8 oz</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>6.474860335195531</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lays_lays lays potato chips barbecue flavored 15_0.43</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Lays | LAYS POTATO CHIPS, BARBECUE FLAVORED | 15 oz</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>10.88826815642458</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lu_lu 6 pc bobs red mill cake mix vanilla yellow 19_0.54</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LU | 6 pc Bobs Red Mill Cake Mix, Gluten Free, Vanilla Yellow | 19 oz</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lu_lu lu bastogne original 200_0.2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LU | LU BASTOGNE ORIGINAL | 200 g</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4.407821229050279</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>noel_noel noel chocolate chip 200_0.2</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Noel</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Noel | NOEL CHOCOLATE CHIP | 200 g</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.949720670391062</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unknown_2 fl tompouce_unknown</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2 fl oz TOMPOUCE :</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5.916201117318436</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unknown_2 pc aardbeienslof_unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2 pc AARDBEIENSLOF</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>unknown_8 ea haagen dazs caramel biscuit and cream speculoos_unknown</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8 ea HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unknown_cheesecake punt_unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CHEESECAKE PUNT</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unknown_each fruit cake 400_0.4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>each FRUIT CAKE | 400 G</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6.117318435754189</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>unknown_fjord knackebrod volkoren 6 6_0.19</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>FJORD KNACKEBROD VOLKOREN | 6.6 oz</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>4.072625698324022</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unknown_home made choco cake 425_0.42</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>HOME MADE CHOCO CAKE | 425 g</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>6.117318435754189</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unknown_papagena biscuit assorted 415_0.42</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PAPAGENA BISCUIT ASSORTED | 415 g</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>9.491620111731844</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unknown_pruimentaart klein_unknown</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PRUIMENTAART KLEIN</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>18.40782122905028</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unknown_slagroompunt_unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SLAGROOMPUNT</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unknown_spring home roti paratha plain 5 ea 600g_0.6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Spring Home Roti Paratha, Plain 5 ea | 600g</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4.441340782122905</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bravo_bravo pan hamburger ajonjoli_unknown</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Bravo Pan Hamburger Ajonjoli</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bravo_bravo pan hamburger poppy seed_unknown</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Bravo Pan Hamburger Poppy Seed</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>unknown_pan mini hamburger rebanado_unknown</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pan Mini Hamburger Rebanado</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jumbo_pan de hamburguesas gourmet jumbo_unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Pan De Hamburguesas Gourmet Jumbo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>buenhorno_pan hamburgesa brioche buenhorno_unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Buenhorno</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pan Hamburgesa Brioche Buenhorno</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>gullon_galleta gullon barquilimon_0.15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Gullon</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Galleta Gullon Barquilimon</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>unknown_galleta qii wafer limon_unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Galleta Qii Wafer Limon</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>unknown_pan hamburgesa ajonjoli_unknown</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Pan Hamburgesa Ajonjoli</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bounty Supermarket</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>unknown_additional information_0.1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Additional information</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7211538461538461</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3.461538461538462</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bermudez Bourbon Cream Cookies</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez bran oats crix crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Bermudez Bran &amp; Oats Crix Crackers</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>7.115384615384615</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez cookies jumbies 40 gr_0.04</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Bermudez Cookies Jumbies 40 gr</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0.4326923076923077</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez crackers dixee 3pk_unknown</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Bermudez Crackers Dixee 3pk</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez crix crackers original 9oz_0.26</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Bermudez Crix Crackers Original 9oz</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez crix crackers whole wheat 9oz_0.26</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bermudez Crix Crackers Whole Wheat  9oz</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez dixee original crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BERMUDEZ DIXEE ORIGINAL CRACKERS</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7.596153846153846</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez dixee peanut butter filled_unknown</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BERMUDEZ DIXEE PEANUT BUTTER FILLED</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3.846153846153846</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez domino vanilla_unknown</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BERMUDEZ DOMINO VANILLA</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2.980769230769231</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez multigrain crix crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BERMUDEZ  MULTIGRAIN CRIX CRACKERS</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>7.115384615384615</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez rough tops_unknown</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Bermudez Rough Tops</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.5288461538461539</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez vanilla cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>BERMUDEZ VANILLA COOKIES</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.057692307692308</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez wheat crisps garden herb 9x32g_0.29</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Bermudez Wheat Crisps Garden Herb 9x32g</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2.403846153846154</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez whole wheat crix crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bermudez Whole Wheat Crix Crackers</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>7.115384615384615</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bermudez_cbean delight cookies omeal raisin 145g_0.14</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Cbean Delight Cookies Omeal &amp;Raisin 145g</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cadbury</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Daim</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5.817307692307693</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Cadbury</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Daim</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>colombina_colombina moments butter cookies gold_unknown</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Colombina</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>COLOMBINA MOMENTS BUTTER COOKIES GOLD</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2.403846153846154</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>danisha_royal dansk danish butter cookies 50 years_unknown</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Danisha</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ROYAL DANSK DANISH BUTTER COOKIES 50 YEARS</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>devon_devon digestive premium 41 gr_0.04</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Devon Digestive Premium 41 gr</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0.4567307692307692</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>devon_devon rolls chocolate chips 200 gr_0.2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Devon Rolls Chocolate Chips 200 gr</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>festival_festival cookie chips_unknown</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Festival Cookie Chips</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>3.365384615384615</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate cookies 12x50g_0.6</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Noel Festival Chocolate Cookies 12x50g</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>4.423076923076923</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0.3365384615384615</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>3.942307692307693</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>festival_noel festival strawberry 12x32g_0.38</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Noel Festival Strawberry 12x32g</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>3.942307692307693</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>festival_noel festival strawberry cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Noel Festival Strawberry Cookies</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0.4807692307692308</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>festival_noel festival vanilla 12x32g_0.38</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Noel Festival Vanilla 12x32g</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>4.038461538461538</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>highland_highland shortbread fringers_unknown</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Highland</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Highland Shortbread Fringers</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>2.884615384615385</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>keeber_keebler fudge stripes minis original_unknown</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Keeber</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Keebler Fudge Stripes Minis Original</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1.057692307692308</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>knotts_knotts raspberry short bread_unknown</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Knotts</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Knotts Raspberry Short Bread</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>knotts_knotts strawbery short bread_unknown</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Knotts</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Knotts Strawbery Short Bread</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>noel_noel mini chips_unknown</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Noel</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>NOEL MINI CHIPS</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>other_nutella and go pretzel sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Nutella And Go Pretzel Sticks</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>2.644230769230769</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm bordeaux cookies 6 75_0.19</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Bordeaux Cookies 6.75 Oz</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>4.951923076923077</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm captiva dark chocolate 8 6oz_0.24</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Captiva Dark Chocolate 8.6oz</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm double chocolate dark choc cookie 7 75oz_0.22</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Double Chocolate Dark Choc Cookie 7.75oz</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>6.346153846153846</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm dublin shortbread_unknown</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Dublin Shortbread</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>6.730769230769231</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm goldfish cheddar 6 6oz_0.19</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Goldfish Cheddar 6.6oz</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>4.278846153846154</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1.201923076923077</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano double dark chocolate 7 75oz_0.22</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Double Dark Chocolate 7.75oz</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano milk chocolate 6oz_0.17</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Milk Chocolate 6oz</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano orange chocolate 7oz_0.2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Orange Chocolate 7oz</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano raspberry chocolate 7oz_0.2</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Raspberry Chocolate 7oz</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>6.009615384615385</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm strawberry cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PEPPERIDGE FARM STRAWBERRY COOKIES</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>6.538461538461538</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm white choc macadamia 7 2oz_0.2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm White Choc Macadamia 7.2oz</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Butter Crackers</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>4.182692307692307</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>SHOON FATT BUTTER CRACKERS</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1.778846153846154</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cheese crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Cheese Crackers</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1.730769230769231</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers 136_0.14</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>SHOON FATT CREAM CRACKERS 136 G</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>3.221153846153846</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Cream Crackers</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>10.86538461538462</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>SHOON FATT CREAM CRACKERS</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt lavish cheese crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Lavish Cheese Crackers</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>3.605769230769231</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt lavish veggie crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Lavish Veggie Crackers</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>3.509615384615385</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt pop corn crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Pop Corn Crackers</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt veggie crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Veggie Crackers</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>3.557692307692307</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>tiffany_tiffany choco chip cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Tiffany</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>TIFFANY CHOCO CHIP COOKIES</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0.9134615384615384</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>tiffany_tiffany choco chip sandwich_unknown</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Tiffany</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>TIFFANY CHOCO CHIP SANDWICH</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0.9134615384615384</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>unknown_tiffany nutty bites almond_unknown</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Tiffany Nutty Bites Almond</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1.586538461538462</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>walkers_walkers chocolate chip shortbread_unknown</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Walkers Chocolate Chip Shortbread</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>8.076923076923077</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>walkers_walkers piper dancer tin shortbread assorted 150g_0.15</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>WALKERS PIPER &amp; DANCER TIN SHORTBREAD ASSORTED 150G</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>14.61538461538462</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>walkers_walkers shortbread fingers_unknown</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Walkers Shortbread Fingers</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>5.384615384615385</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>walkers_walkers shortbread rounds_unknown</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Walkers Shortbread Rounds</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>5.865384615384615</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>walkers_walkers shortbread triangles_unknown</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Walkers Shortbread Triangles</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2087,7 +5990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2147,6 +6050,1527 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks party size 40 ea_unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 7_0.2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 7 oz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks 9 ea 510_0.51</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bagel Bites</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks 9 ea | 510 g</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>eggo_eggo eggo waffles blueberry 600g_0.6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eggo</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Eggo | EGGO WAFFLES, BLUEBERRY | 600g</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4.441340782122905</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>frito lay_frito lay frito lay snacks classic mix 24 ea 6 5_0.18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Frito-Lay | Frito Lay Snacks, Classic Mix 24 ea | 6.5 oz</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5.078212290502793</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>goldfish_goldfish goldfish baked snack crackers cheddar 155_0.16</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goldfish</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 155 g</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.452513966480447</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo hartig kaas tomaat 200_0.2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO HARTIG KAAS/TOMAAT | 200 g</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.949720670391062</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jumbo_jumbo jumbo luchtig crack naturel vegan 6 6_0.19</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Jumbo | JUMBO LUCHTIG.CRACK NATUREL VEGAN | 6.6 oz</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.072625698324022</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita 12 ea la dulcerita rasin muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>La Dulcerita | 12 ea LA DULCERITA RASIN MUFFIN</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5.016759776536313</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita 2 pc la dulcerita vanilla muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>La Dulcerita | 2 pc LA DULCERITA VANILLA MUFFIN</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>la dulcerita_la dulcerita each la dulcerita vanilla pound cake_unknown</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>La Dulcerita</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>La Dulcerita | each LA DULCERITA VANILLA POUND CAKE</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.117318435754189</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lays_lays lay s honey barbecue potato chips 5 5_0.16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lays | Lay's Honey Barbecue Potato Chips | 5.5 oz</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lays_lays lay s kettle cooked jalapeno flavored potato chips 15_0.43</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Lays | Lay's Kettle Cooked Jalapeno Flavored Potato Chips | 15 oz</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>10.88826815642458</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lays_lays lays classic chips 6 5_0.18</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Lays | LAYS CLASSIC CHIPS | 6.5 oz</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5.078212290502793</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lays_lays lays potato chips barbecue flavored 8_0.23</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lays</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Lays | LAYS POTATO CHIPS, BARBECUE FLAVORED | 8 oz</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.474860335195531</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lu_lu bobs red mill cake mix vanilla yellow 10 75_0.3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LU | Bobs Red Mill Cake Mix, Gluten Free, Vanilla Yellow | 10.75 oz</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.977653631284916</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lu_lu lu bastogne original 415_0.42</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LU | LU BASTOGNE ORIGINAL | 415 g</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>9.491620111731844</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>noel_noel noel chocolate chip 166_0.17</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Noel</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Noel | NOEL CHOCOLATE CHIP | 166 g</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.508379888268156</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sara lee_sara lee 6 pc sara lee pound cake classic 10 75_0.3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sara Lee</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sara Lee | 6 pc Sara Lee Pound Cake, Classic | 10.75 oz</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tostitos_tostitos tostitos restaurant style original tortilla chips 6 5_0.18</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tostitos</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Tostitos | Tostitos Restaurant Style Original Tortilla Chips | 6.5 oz</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.575418994413408</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>unknown_2 fl cheesecake punt_unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2 fl oz CHEESECAKE PUNT</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5.916201117318436</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>unknown_2 pc tompouce_unknown</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2 pc TOMPOUCE :</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>unknown_8 ea papagena biscuit assorted_unknown</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>8 ea PAPAGENA BISCUIT ASSORTED</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>unknown_aardbeienslof_unknown</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AARDBEIENSLOF</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3.569832402234637</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>unknown_fjord knackebrod volkoren 250_0.25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>FJORD KNACKEBROD VOLKOREN | 250 g</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.061452513966481</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>unknown_fruit cake 425_0.42</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>FRUIT CAKE | 425 g</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6.117318435754189</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unknown_haagen dazs caramel biscuit and cream speculoos 200_0.2</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS | 200 g</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4.407821229050279</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>unknown_home made choco cake 420_0.42</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>HOME MADE CHOCO CAKE | 420 G</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>6.117318435754189</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>unknown_spring home roti paratha plain 5 ea 14_0.4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Spring Home Roti Paratha, Plain 5 ea | 14 oz</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>unknown_tiramisutaartje_unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TIRAMISUTAARTJE</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bon_paleta bon de bizcocho_unknown</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paleta Bon De Bizcocho</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>unknown_gold pan viga mediana integral_0.82</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Gold Pan Viga Mediana Integral</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>golden_golden harvest multigrain loaf_unknown</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Golden</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2.596153846153846</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>golden_golden harvest whole slice bread_unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Golden</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Golden Harvest Whole Slice Bread</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2.163461538461538</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>instorebakery_salara red cake_unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Instorebakery</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Salara Red Cake</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>other_1 2 sheet base w rose dome 30_unknown</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1/2 Sheet Base W Rose Dome 30 Ct</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>5.745192307692307</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>other_dbli panel window bag 8 3 15_unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DBLI PANEL WINDOW BAG 8″*3*15</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>other_essential everyday wax paper_unknown</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Essential Everyday Wax Paper</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>5.576923076923077</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>other_pactiv med meal master black 252ct_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Pactiv Med Meal Master Black 252ct</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3365384615384615</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,34 +488,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>siete_siete tortilla chip lime 5oz_0.14</t>
+          <t>unknown_cafe valley banana nut mini muffins 12ct 10 5oz_0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SIETE TORTILLA CHIP LIME 5oz</t>
+          <t>CAFE VALLEY BANANA NUT MINI MUFFINS 12CT 10.5oz</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.81</v>
+        <v>5.86</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SIETE TORTILLA CHIP LIME 5oz</t>
+          <t>CAFE VALLEY BANANA NUT MINI MUFFINS 12CT 10.5oz</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7.65</v>
+        <v>5.25</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-10.98039215686275</v>
+        <v>11.61904761904762</v>
       </c>
     </row>
     <row r="3">
@@ -539,7 +539,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unknown_waybetter chip tortilla avocado ranch 5 5oz_0.16</t>
+          <t>unknown_cafe valley chocolate fudge ring cake 26oz_0.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,11 +549,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WAYBETTER CHIP TORTILLA AVOCADO RANCH 5.5OZ</t>
+          <t>CAFE VALLEY CHOCOLATE FUDGE RING CAKE 26oz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6.08</v>
+        <v>11.06</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -562,11 +562,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WAYBETTER CHIP TORTILLA AVOCADO RANCH 5.5OZ</t>
+          <t>CAFE VALLEY CHOCOLATE FUDGE RING CAKE 26oz</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>6.47</v>
+        <v>9.99</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-6.02782071097372</v>
+        <v>10.71071071071071</v>
       </c>
     </row>
     <row r="4">
@@ -585,39 +585,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_wholesome pancake syrup organic 20oz_0.57</t>
+          <t>jumbo_jumbo jumbo bladerdeeg 175_0.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>WHOLESOME PANCAKE SYRUP ORGANIC 20oz</t>
+          <t>Jumbo | JUMBO BLADERDEEG | 175 g</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11.84</v>
+        <v>2.782122905027933</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WHOLESOME PANCAKE SYRUP ORGANIC 20oz</t>
+          <t>Jumbo | JUMBO BLADERDEEG | 175 g</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>10.78</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9.833024118738409</v>
+        <v>42.69340974212034</v>
       </c>
     </row>
     <row r="5">
@@ -641,7 +641,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lays_lays lay s stax original potato crisps 6 5_0.18</t>
+          <t>lays_lays lay s cheddar flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -651,11 +651,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lays | LAY'S STAX ORIGINAL POTATO CRISPS | 6.5 oz</t>
+          <t>Lays | Lay's Cheddar Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.078212290502793</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lays | LAY'S STAX ORIGINAL POTATO CRISPS | 6.5 oz</t>
+          <t>Lays | Lay's Cheddar Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.905027932960894</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>30.04291845493561</v>
+        <v>23.25581395348837</v>
       </c>
     </row>
     <row r="6">
@@ -692,7 +692,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_tiramisu gebak_unknown</t>
+          <t>unknown_bolo di druif klein_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -702,11 +702,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TIRAMISU GEBAK</t>
+          <t>BOLO DI DRUIF KLEIN</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.569832402234637</v>
+        <v>26.53072625698324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -715,11 +715,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TIRAMISU GEBAK</t>
+          <t>BOLO DI DRUIF KLEIN</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.067039106145252</v>
+        <v>23.43575418994413</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -727,50 +727,50 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>16.3934426229508</v>
+        <v>13.20619785458879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>unknown_bosvruchten muffin_unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.63</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>29.58100558659218</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -778,50 +778,50 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-20.09803921568628</v>
+        <v>-93.4088762983947</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>unknown_cherry pineapple klein_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>CHERRY/ PINEAPPLE KLEIN</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.04</v>
+        <v>22.31843575418995</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>CHERRY/ PINEAPPLE KLEIN</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.63</v>
+        <v>26.53072625698324</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25.15337423312884</v>
+        <v>-15.8770267424721</v>
       </c>
     </row>
     <row r="9">
@@ -840,39 +840,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>food club_tortilla de maiz para tacos food club_unknown</t>
+          <t>carrefour_pan tostado carrefour bio_0.25</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Para Tacos Food Club</t>
+          <t>Pan Tostado Carrefour Bio</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Para Tacos Food Club</t>
+          <t>Pan Tostado Carrefour Bio</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-8.955223880597023</v>
+        <v>-9.881422924901187</v>
       </c>
     </row>
     <row r="10">
@@ -891,39 +891,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pirulin_barquilla rellena de crema de coco pirulin_0.16</t>
+          <t>guarina_galleta waffer sabor vainilla guarina 106 onz_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Guarina</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barquilla Rellena De Crema De Coco Pirulin</t>
+          <t>Galleta Waffer Sabor Vainilla Guarina 106 Onz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.09</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Guarina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Barquilla Rellena De Crema De Coco Pirulin</t>
+          <t>Galleta Waffer Sabor Vainilla Guarina 106 Onz</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.49</v>
+        <v>1.27</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-11.46131805157594</v>
+        <v>18.11023622047244</v>
       </c>
     </row>
     <row r="11">
@@ -942,39 +942,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>guarina_galletas wafer limon guarina_0.26</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Guarina</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Galletas Wafer Limon Guarina</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Guarina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Galletas Wafer Limon Guarina</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>1.27</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-46.23287671232876</v>
+        <v>18.11023622047244</v>
       </c>
     </row>
     <row r="12">
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>oreo_galletas oreo original_0.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Galletas Oreo Original</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Galletas Oreo Original</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.57</v>
+        <v>3.64</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1033,50 +1033,50 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>85.98726114649681</v>
+        <v>-12.91208791208792</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>tostitos_chips de tortillas de maiz tostitos santa elena_0.43</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.682692307692308</v>
+        <v>3.09</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.086538461538462</v>
+        <v>3.72</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1084,50 +1084,50 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-58.82352941176471</v>
+        <v>-16.93548387096775</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>jumbo_pan de hamburguesas gourmet jumbo_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Pan De Hamburguesas Gourmet Jumbo</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.086538461538462</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Pan De Hamburguesas Gourmet Jumbo</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.682692307692308</v>
+        <v>1.49</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1135,50 +1135,50 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>142.8571428571429</v>
+        <v>27.51677852348993</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>jumbo_pan de sandwich mini club jumbo_unknown</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>Pan De Sandwich Mini Club Jumbo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.682692307692308</v>
+        <v>1.66</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>Pan De Sandwich Mini Club Jumbo</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.086538461538462</v>
+        <v>1.33</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1186,50 +1186,50 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>-58.82352941176471</v>
+        <v>24.81203007518796</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>jumbo_pan de sandwich viga mediana jumbo_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>Pan De Sandwich Viga Mediana Jumbo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.086538461538462</v>
+        <v>2.14</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>Pan De Sandwich Viga Mediana Jumbo</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.682692307692308</v>
+        <v>1.73</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1237,50 +1237,50 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>142.8571428571429</v>
+        <v>23.69942196531793</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>jumbo_pan integral viga mediana jumbo_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Pan Integral Viga Mediana Jumbo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>29.08653846153846</v>
+        <v>2.38</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Pan Integral Viga Mediana Jumbo</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>15.04807692307692</v>
+        <v>1.81</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1288,50 +1288,50 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>93.29073482428115</v>
+        <v>31.49171270718231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>jumbo_pan para hot dog jumbo_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Pan Para Hot Dog Jumbo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15.04807692307692</v>
+        <v>1.58</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Pan Para Hot Dog Jumbo</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>29.08653846153846</v>
+        <v>1.25</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1339,50 +1339,50 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>-48.26446280991735</v>
+        <v>26.40000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
+          <t>la panera_pan para mini hamburguesa la panera_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
+          <t>Pan Para Mini Hamburguesa La Panera</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.442307692307692</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
+          <t>Pan Para Mini Hamburguesa La Panera</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7.115384615384615</v>
+        <v>1.25</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1390,50 +1390,50 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>-79.72972972972973</v>
+        <v>26.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7.115384615384615</v>
+        <v>1.63</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Otis Spunkmeyer</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.442307692307692</v>
+        <v>2.04</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,50 +1441,50 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>393.3333333333333</v>
+        <v>-20.09803921568628</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.254807692307693</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1492,50 +1492,50 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>70.19230769230769</v>
+        <v>25.15337423312884</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>bon_helados bon bizcocho_0.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Helados Bon Bizcocho</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.254807692307693</v>
+        <v>3.69</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,50 +1543,50 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>-41.24293785310735</v>
+        <v>-25.20325203252033</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>la panera_pan para mini hamburguesa la panera_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan Para Mini Hamburguesa La Panera</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.682692307692308</v>
+        <v>1.57</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan Para Mini Hamburguesa La Panera</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.346153846153846</v>
+        <v>1.25</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,50 +1594,50 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>24.99999999999997</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>lu_pan de sandwich mini club nacional_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan De Sandwich Mini Club Nacional</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.682692307692308</v>
+        <v>1.65</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan De Sandwich Mini Club Nacional</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.625</v>
+        <v>1.33</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,50 +1645,50 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>169.2307692307692</v>
+        <v>24.06015037593984</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>unknown_pan de hamburguesas gourmet nacional_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan De Hamburguesas Gourmet Nacional</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.346153846153846</v>
+        <v>1.89</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan De Hamburguesas Gourmet Nacional</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.682692307692308</v>
+        <v>1.51</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,50 +1696,50 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>-19.99999999999998</v>
+        <v>25.16556291390728</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>unknown_pan de sandwich viga mediana nacional_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan De Sandwich Viga Mediana Nacional</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.346153846153846</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan De Sandwich Viga Mediana Nacional</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.625</v>
+        <v>1.73</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,50 +1747,50 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>115.3846153846154</v>
+        <v>22.54335260115608</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>unknown_pan integral viga mediana nacional_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan Integral Viga Mediana Nacional</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.625</v>
+        <v>2.36</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Pan Integral Viga Mediana Nacional</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.682692307692308</v>
+        <v>1.81</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1798,57 +1798,1740 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>-62.85714285714285</v>
+        <v>30.3867403314917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>unknown_pan para hot dog nacional_unknown</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pan Para Hot Dog Nacional</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pan Para Hot Dog Nacional</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>glutino_muffin ingles sin glutino_0.48</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Glutino</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Muffin Ingles Sin Gluten Glutino</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Glutino</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Muffin Ingles Sin Gluten Glutino</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>-11.90817790530847</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>lu_pan baguette congelado sin panamar_0.1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pan Baguette Congelado Sin Gluten Panamar</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pan Baguette Congelado Sin Gluten Panamar</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>-11.34453781512605</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>pirulin_barquilla rellena de chocolate y avellanas pirulin_0.16</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pirulin</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Barquilla Rellena De Chocolate Y Avellanas Pirulin</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pirulin</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Barquilla Rellena De Chocolate Y Avellanas Pirulin</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>-11.46131805157594</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>toufayan_pan pita blanco toufayan_0.34</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pan Pita Blanco Toufayan</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Pan Pita Blanco Toufayan</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>-14.59459459459459</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>toufayan_pan pita integral toufayan_0.34</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Pan Pita Integral Toufayan</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Pan Pita Integral Toufayan</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>-15.33333333333333</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>toufayan_pan pita keto toufayan_0.25</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pan Pita Keto Toufayan</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Pan Pita Keto Toufayan</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>-12.21052631578948</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>El Charrito</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>El Charrito</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>-46.23287671232876</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>El Charrito</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>El Charrito</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>85.98726114649681</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Guyana</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Massy Stores Guyana</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3.461538461538462</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Bermudez Bourbon Cream Cookies</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1007.692307692308</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Bermudez Bourbon Cream Cookies</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>3.461538461538462</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>-90.97222222222221</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cadbury</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Daim</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5.817307692307693</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cadbury</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Daim</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>152.0833333333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cadbury</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Daim</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.307692307692307</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cadbury</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Cadbury Dairy Milk Daim</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5.817307692307693</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>-60.33057851239671</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.3365384615384615</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>3.942307692307693</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>-91.46341463414633</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate_unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3.942307692307693</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.3365384615384615</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1071.428571428572</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kugi Chocolate Wafer Sticks</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>-58.82352941176471</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kugi Chocolate Wafer Sticks</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>142.8571428571429</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>-58.82352941176471</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>142.8571428571429</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>29.08653846153846</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>15.04807692307692</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>93.29073482428115</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>15.04807692307692</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>29.08653846153846</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>-48.26446280991735</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Otis Spunkmeyer</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.442307692307692</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Otis Spunkmeyer</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>7.115384615384615</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>-79.72972972972973</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>pringles_pringles pizza_unknown</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PRINGLES PIZZA</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>4.254807692307693</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pringles Pizza</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>70.19230769230769</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>pringles_pringles pizza_unknown</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Pringles Pizza</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PRINGLES PIZZA</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>4.254807692307693</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>-41.24293785310735</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Butter Crackers</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>4.182692307692307</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>SHOON FATT BUTTER CRACKERS</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1.778846153846154</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>135.1351351351352</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SHOON FATT BUTTER CRACKERS</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.778846153846154</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Butter Crackers</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>4.182692307692307</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>-57.4712643678161</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Cream Crackers</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>10.86538461538462</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SHOON FATT CREAM CRACKERS</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>494.7368421052633</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SHOON FATT CREAM CRACKERS</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Cream Crackers</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>10.86538461538462</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>-83.18584070796462</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Triskits</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F56" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>24.99999999999997</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
         <v>0.625</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>169.2307692307692</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>Triskits</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="F58" t="n">
         <v>1.346153846153846</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="K28" t="n">
+      <c r="K58" t="n">
+        <v>-19.99999999999998</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>115.3846153846154</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>-62.85714285714285</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>-53.57142857142858</v>
       </c>
     </row>
@@ -1863,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1936,21 +3619,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks 9 ea_unknown</t>
+          <t>crav n_crav n crav n flavor pita chips parmesan garlic herb baked 7 33_0.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks 9 ea</t>
+          <t>Crav'N | Crav'n Flavor Pita Chips, Parmesan Garlic &amp; Herb, Baked | 7.33 oz</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.184357541899441</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -1975,21 +3658,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 510_0.51</t>
+          <t>crav n_crav n crav n flavor tortilla chips white corn bite size round 13_0.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 510 g</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Bite Size Round | 13 oz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.849162011173184</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2014,21 +3697,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks party size 40 ea 7_0.2</t>
+          <t>goldfish_goldfish goldfish baked snack crackers cheddar 260_0.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea | 7 oz</t>
+          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 260 g</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.184357541899441</v>
+        <v>3.067039106145252</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2053,21 +3736,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eggo_eggo eggo waffles blueberry 14_0.4</t>
+          <t>jumbo_jumbo jumbo meergranen biscuits bosvruchten 125_0.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Eggo | EGGO WAFFLES, BLUEBERRY | 14 oz</t>
+          <t>Jumbo | JUMBO MEERGRANEN BISCUITS BOSVRUCHTEN | 125 g</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.899441340782123</v>
+        <v>2.675977653631285</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -2092,21 +3775,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>frito lay_frito lay frito lay snacks classic mix 24 ea 5 5_0.16</t>
+          <t>jumbo_jumbo jumbo puppy biscuits eend 225_0.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Frito-Lay | Frito Lay Snacks, Classic Mix 24 ea | 5.5 oz</t>
+          <t>Jumbo | JUMBO PUPPY BISCUITS EEND | 225 g</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.849162011173184</v>
+        <v>2.452513966480447</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -2131,21 +3814,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goldfish_goldfish goldfish baked snack crackers cheddar 250_0.25</t>
+          <t>kinder_kinder 6ct kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 1 5_0.04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 250 g</t>
+          <t>Kinder | 6ct Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 1.5 oz</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.061452513966481</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -2170,21 +3853,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo hartig kaas tomaat 14 2_0.4</t>
+          <t>lays_lays 24 pc lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO HARTIG KAAS/TOMAAT | 14.2 oz</t>
+          <t>Lays | 24 pc Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.396648044692737</v>
+        <v>23.23463687150839</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -2209,21 +3892,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo luchtig crack naturel vegan 155_0.16</t>
+          <t>lays_lays lay s sour cream onion flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO LUCHTIG.CRACK NATUREL VEGAN | 155 g</t>
+          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.452513966480447</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -2248,21 +3931,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita 2 pc la dulcerita rasin muffin_unknown</t>
+          <t>lu_lu cafe valley blueberry mini muffins 24_0.68</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>La Dulcerita | 2 pc LA DULCERITA RASIN MUFFIN</t>
+          <t>LU | CAFE VALLEY BLUEBERRY MINI MUFFINS | 24 oz</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.899441340782123</v>
+        <v>7.251396648044693</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -2287,21 +3970,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita la dulcerita vanilla muffin 24_0.68</t>
+          <t>mcvitie s_mcvitie s mcvitie s digestive 14 2_0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>La Dulcerita | LA DULCERITA VANILLA MUFFIN | 24 oz</t>
+          <t>McVitie's | MCVITIE'S DIGESTIVE | 14.2 oz</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7.251396648044693</v>
+        <v>2.396648044692737</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -2326,21 +4009,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita la dulcerita vanilla pound cake_unknown</t>
+          <t>milka_milka milka mmmax chocoswing biscuit 400_0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>La Dulcerita | LA DULCERITA VANILLA POUND CAKE</t>
+          <t>Milka | MILKA MMMAX CHOCOSWING BISCUIT | 400 g</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.117318435754189</v>
+        <v>4.016759776536313</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -2365,21 +4048,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lays_lays lay s honey barbecue potato chips 6 5_0.18</t>
+          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 11 78_0.33</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lays | Lay's Honey Barbecue Potato Chips | 6.5 oz</t>
+          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 11.78 oz</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.966480446927375</v>
+        <v>9.770949720670391</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -2404,21 +4087,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lays_lays lay s kettle cooked jalapeno flavored potato chips 6 5_0.18</t>
+          <t>oreo_oreo oreo golden sandwich cookies 13 29_0.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lays | Lay's Kettle Cooked Jalapeno Flavored Potato Chips | 6.5 oz</t>
+          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5.078212290502793</v>
+        <v>7.368715083798882</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -2443,21 +4126,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lays_lays lay s potato chips salt vinegar flavored 6 1 6 5_0.18</t>
+          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 8_0.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lays | Lay's Potato Chips Salt &amp; Vinegar Flavored 6 1/ | 6.5 oz</t>
+          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 8 oz</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.905027932960894</v>
+        <v>6.307262569832401</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -2482,21 +4165,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lays_lays lays classic chips 8_0.23</t>
+          <t>pringles_pringles pringles bbq 2 3_0.07</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lays | LAYS CLASSIC CHIPS | 8 oz</t>
+          <t>Pringles | PRINGLES BBQ | 2.3 oz</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.474860335195531</v>
+        <v>2.340782122905028</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -2521,21 +4204,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lays_lays lays potato chips barbecue flavored 15_0.43</t>
+          <t>pringles_pringles pringles cheddar cheese 5 5_0.16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lays | LAYS POTATO CHIPS, BARBECUE FLAVORED | 15 oz</t>
+          <t>Pringles | PRINGLES CHEDDAR CHEESE | 5.5 oz</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10.88826815642458</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -2560,21 +4243,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lu_lu 6 pc bobs red mill cake mix vanilla yellow 19_0.54</t>
+          <t>pringles_pringles pringles original 1 3_0.04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LU | 6 pc Bobs Red Mill Cake Mix, Gluten Free, Vanilla Yellow | 19 oz</t>
+          <t>Pringles | PRINGLES ORIGINAL | 1.3 oz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.067039106145252</v>
+        <v>1.558659217877095</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -2599,21 +4282,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>lu_lu lu bastogne original 200_0.2</t>
+          <t>pringles_pringles pringles potato crisps chips lunch snacks office and kids snacks grab n go original can 1 can 1 4_0.04</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LU | LU BASTOGNE ORIGINAL | 200 g</t>
+          <t>Pringles | Pringles Potato Crisps Chips, Lunch Snacks, Office and Kids Snacks, Grab N' Go, Original, Can, 1 Can | 1.4 oz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.407821229050279</v>
+        <v>1.558659217877095</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -2638,21 +4321,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>noel_noel noel chocolate chip 200_0.2</t>
+          <t>toufayan_toufayan toufayan bakeries garlic pesto wraps 1 5_0.04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Noel | NOEL CHOCOLATE CHIP | 200 g</t>
+          <t>Toufayan | TOUFAYAN BAKERIES GARLIC PESTO WRAPS | 1.5 oz</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.949720670391062</v>
+        <v>1.670391061452514</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -2677,21 +4360,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>unknown_2 fl tompouce_unknown</t>
+          <t>toufayan_toufayan toufayan bakeries pita sweet onion 400_0.4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2 fl oz TOMPOUCE :</t>
+          <t>Toufayan | TOUFAYAN BAKERIES PITA SWEET ONION | 400 g</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.916201117318436</v>
+        <v>1.614525139664805</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -2716,21 +4399,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown_2 pc aardbeienslof_unknown</t>
+          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 11_0.31</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2 pc AARDBEIENSLOF</t>
+          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 11 oz</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.899441340782123</v>
+        <v>2.955307262569832</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -2755,7 +4438,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_8 ea haagen dazs caramel biscuit and cream speculoos_unknown</t>
+          <t>unknown_coolback herb butter baguette 16_0.45</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2765,11 +4448,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8 ea HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS</t>
+          <t>COOLBACK HERB BUTTER BAGUETTE | 16 oz</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.35754189944134</v>
+        <v>9.324022346368716</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -2794,7 +4477,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_cheesecake punt_unknown</t>
+          <t>unknown_fjord knackebrod volkoren 250_0.25</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2804,11 +4487,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CHEESECAKE PUNT</t>
+          <t>FJORD KNACKEBROD VOLKOREN | 250 g</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.067039106145252</v>
+        <v>2.061452513966481</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -2833,7 +4516,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_each fruit cake 400_0.4</t>
+          <t>unknown_food for life ezekiel 4 9 bread cinnamon raisin 29 6_0.84</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2843,11 +4526,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>each FRUIT CAKE | 400 G</t>
+          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, CINNAMON RAISIN | 29.6 oz</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6.117318435754189</v>
+        <v>10.02793296089386</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -2872,7 +4555,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_fjord knackebrod volkoren 6 6_0.19</t>
+          <t>unknown_food for life flourless sprouted grain cinnamon raisin bread 24_0.68</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2882,11 +4565,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FJORD KNACKEBROD VOLKOREN | 6.6 oz</t>
+          <t>Food For Life Flourless Sprouted Grain Cinnamon Raisin Bread | 24 oz</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.072625698324022</v>
+        <v>12.82122905027933</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -2911,7 +4594,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_home made choco cake 425_0.42</t>
+          <t>unknown_udis sandwich bread soft white 680_0.68</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2921,11 +4604,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HOME MADE CHOCO CAKE | 425 g</t>
+          <t>UDIS SANDWICH BREAD, SOFT WHITE | 680 g</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6.117318435754189</v>
+        <v>11.14525139664804</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -2950,21 +4633,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_papagena biscuit assorted 415_0.42</t>
+          <t>wasa_wasa wasa knackebrod glutenvr sesam 6 6_0.19</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PAPAGENA BISCUIT ASSORTED | 415 g</t>
+          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 6.6 oz</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9.491620111731844</v>
+        <v>4.072625698324022</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -2979,31 +4662,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_pruimentaart klein_unknown</t>
+          <t>golden_golden harvest multigrain loaf_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PRUIMENTAART KLEIN</t>
+          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>18.40782122905028</v>
+        <v>2.596153846153846</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -3018,31 +4701,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_slagroompunt_unknown</t>
+          <t>golden_golden harvest whole slice bread_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SLAGROOMPUNT</t>
+          <t>Golden Harvest Whole Slice Bread</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.067039106145252</v>
+        <v>2.163461538461538</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -3057,31 +4740,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown_spring home roti paratha plain 5 ea 600g_0.6</t>
+          <t>other_1 2 sheet base w rose dome 30_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spring Home Roti Paratha, Plain 5 ea | 600g</t>
+          <t>1/2 Sheet Base W Rose Dome 30 Ct</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.441340782122905</v>
+        <v>5.745192307692307</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -3096,31 +4779,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bravo_bravo pan hamburger ajonjoli_unknown</t>
+          <t>other_dbli panel window bag 8 3 15_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bravo Pan Hamburger Ajonjoli</t>
+          <t>DBLI PANEL WINDOW BAG 8″*3*15</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.41</v>
+        <v>0.25</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -3135,31 +4818,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bravo_bravo pan hamburger poppy seed_unknown</t>
+          <t>other_essential everyday wax paper_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bravo Pan Hamburger Poppy Seed</t>
+          <t>Essential Everyday Wax Paper</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.41</v>
+        <v>5.576923076923077</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -3174,31 +4857,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unknown_pan mini hamburger rebanado_unknown</t>
+          <t>other_pactiv med meal master black 252ct_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pan Mini Hamburger Rebanado</t>
+          <t>Pactiv Med Meal Master Black 252ct</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.41</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -3209,2775 +4892,6 @@
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Jumbo</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>jumbo_pan de hamburguesas gourmet jumbo_unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Jumbo</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Pan De Hamburguesas Gourmet Jumbo</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>buenhorno_pan hamburgesa brioche buenhorno_unknown</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Buenhorno</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Pan Hamburgesa Brioche Buenhorno</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>gullon_galleta gullon barquilimon_0.15</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Gullon</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Galleta Gullon Barquilimon</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>unknown_galleta qii wafer limon_unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Galleta Qii Wafer Limon</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>unknown_pan hamburgesa ajonjoli_unknown</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Pan Hamburgesa Ajonjoli</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Bounty Supermarket</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>unknown_additional information_0.1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Additional information</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0.7211538461538461</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>3.461538461538462</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez bran oats crix crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Bermudez Bran &amp; Oats Crix Crackers</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>7.115384615384615</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez cookies jumbies 40 gr_0.04</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Bermudez Cookies Jumbies 40 gr</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0.4326923076923077</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez crackers dixee 3pk_unknown</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Bermudez Crackers Dixee 3pk</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1.923076923076923</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez crix crackers original 9oz_0.26</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Bermudez Crix Crackers Original 9oz</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1.826923076923077</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez crix crackers whole wheat 9oz_0.26</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Bermudez Crix Crackers Whole Wheat  9oz</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1.826923076923077</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez dixee original crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>BERMUDEZ DIXEE ORIGINAL CRACKERS</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>7.596153846153846</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez dixee peanut butter filled_unknown</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>BERMUDEZ DIXEE PEANUT BUTTER FILLED</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>3.846153846153846</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez domino vanilla_unknown</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>BERMUDEZ DOMINO VANILLA</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>2.980769230769231</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez multigrain crix crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>BERMUDEZ  MULTIGRAIN CRIX CRACKERS</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>7.115384615384615</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez rough tops_unknown</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Bermudez Rough Tops</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0.5288461538461539</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez vanilla cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>BERMUDEZ VANILLA COOKIES</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1.057692307692308</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez wheat crisps garden herb 9x32g_0.29</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Bermudez Wheat Crisps Garden Herb 9x32g</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>2.403846153846154</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez whole wheat crix crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Bermudez Whole Wheat Crix Crackers</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>7.115384615384615</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>bermudez_cbean delight cookies omeal raisin 145g_0.14</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Cbean Delight Cookies Omeal &amp;Raisin 145g</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Cadbury</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Cadbury Dairy Milk Daim</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>5.817307692307693</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Cadbury</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Cadbury Dairy Milk Daim</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>2.307692307692307</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>colombina_colombina moments butter cookies gold_unknown</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Colombina</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>COLOMBINA MOMENTS BUTTER COOKIES GOLD</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>2.403846153846154</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>danisha_royal dansk danish butter cookies 50 years_unknown</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Danisha</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ROYAL DANSK DANISH BUTTER COOKIES 50 YEARS</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>devon_devon digestive premium 41 gr_0.04</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Devon</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Devon Digestive Premium 41 gr</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>0.4567307692307692</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>devon_devon rolls chocolate chips 200 gr_0.2</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Devon</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Devon Rolls Chocolate Chips 200 gr</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1.923076923076923</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>festival_festival cookie chips_unknown</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Festival Cookie Chips</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>3.365384615384615</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>festival_noel festival chocolate cookies 12x50g_0.6</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Noel Festival Chocolate Cookies 12x50g</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>4.423076923076923</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>festival_noel festival chocolate_unknown</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0.3365384615384615</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>festival_noel festival chocolate_unknown</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>3.942307692307693</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>festival_noel festival strawberry 12x32g_0.38</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Noel Festival Strawberry 12x32g</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>3.942307692307693</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>festival_noel festival strawberry cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Noel Festival Strawberry Cookies</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>0.4807692307692308</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>festival_noel festival vanilla 12x32g_0.38</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Noel Festival Vanilla 12x32g</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>4.038461538461538</v>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>highland_highland shortbread fringers_unknown</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Highland</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Highland Shortbread Fringers</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>2.884615384615385</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>keeber_keebler fudge stripes minis original_unknown</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Keeber</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Keebler Fudge Stripes Minis Original</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1.057692307692308</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>knotts_knotts raspberry short bread_unknown</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Knotts</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Knotts Raspberry Short Bread</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>knotts_knotts strawbery short bread_unknown</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Knotts</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Knotts Strawbery Short Bread</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>0.9615384615384616</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>noel_noel mini chips_unknown</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Noel</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>NOEL MINI CHIPS</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>other_nutella and go pretzel sticks_unknown</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Nutella And Go Pretzel Sticks</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>2.644230769230769</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm bordeaux cookies 6 75_0.19</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Bordeaux Cookies 6.75 Oz</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>4.951923076923077</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm captiva dark chocolate 8 6oz_0.24</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Captiva Dark Chocolate 8.6oz</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm double chocolate dark choc cookie 7 75oz_0.22</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Double Chocolate Dark Choc Cookie 7.75oz</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>6.346153846153846</v>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm dublin shortbread_unknown</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Dublin Shortbread</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>6.730769230769231</v>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar 6 6oz_0.19</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Goldfish Cheddar 6.6oz</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>4.278846153846154</v>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar_unknown</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>PEPPERIDGE FARM GOLDFISH CHEDDAR</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1.201923076923077</v>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano double dark chocolate 7 75oz_0.22</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Double Dark Chocolate 7.75oz</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano milk chocolate 6oz_0.17</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Milk Chocolate 6oz</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano orange chocolate 7oz_0.2</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Orange Chocolate 7oz</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>5.769230769230769</v>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano raspberry chocolate 7oz_0.2</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Raspberry Chocolate 7oz</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>6.009615384615385</v>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm strawberry cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>PEPPERIDGE FARM STRAWBERRY COOKIES</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>6.538461538461538</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm white choc macadamia 7 2oz_0.2</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm White Choc Macadamia 7.2oz</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Butter Crackers</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>4.182692307692307</v>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1.778846153846154</v>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt cheese crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Cheese Crackers</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1.730769230769231</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt cream crackers 136_0.14</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>SHOON FATT CREAM CRACKERS 136 G</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>3.221153846153846</v>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Cream Crackers</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>10.86538461538462</v>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1.826923076923077</v>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt lavish cheese crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Lavish Cheese Crackers</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>3.605769230769231</v>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt lavish veggie crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Lavish Veggie Crackers</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>3.509615384615385</v>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt pop corn crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Pop Corn Crackers</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1.923076923076923</v>
-      </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt veggie crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Veggie Crackers</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>3.557692307692307</v>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>tiffany_tiffany choco chip cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Tiffany</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>TIFFANY CHOCO CHIP COOKIES</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>0.9134615384615384</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>tiffany_tiffany choco chip sandwich_unknown</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Tiffany</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>TIFFANY CHOCO CHIP SANDWICH</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>0.9134615384615384</v>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>unknown_tiffany nutty bites almond_unknown</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Tiffany Nutty Bites Almond</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1.586538461538462</v>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>walkers_walkers chocolate chip shortbread_unknown</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Walkers Chocolate Chip Shortbread</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>8.076923076923077</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>walkers_walkers piper dancer tin shortbread assorted 150g_0.15</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>WALKERS PIPER &amp; DANCER TIN SHORTBREAD ASSORTED 150G</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>14.61538461538462</v>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>walkers_walkers shortbread fingers_unknown</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Walkers Shortbread Fingers</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>5.384615384615385</v>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>walkers_walkers shortbread rounds_unknown</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>Walkers Shortbread Rounds</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>5.865384615384615</v>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>walkers_walkers shortbread triangles_unknown</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Walkers Shortbread Triangles</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6063,7 +4977,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks party size 40 ea_unknown</t>
+          <t>crav n_crav n crav n flavor pita chips parmesan garlic herb baked 400_0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -6071,16 +4985,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea</t>
+          <t>Crav'N | Crav'n Flavor Pita Chips, Parmesan Garlic &amp; Herb, Baked | 400 g</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.184357541899441</v>
+        <v>1.614525139664805</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6102,7 +5016,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 7_0.2</t>
+          <t>crav n_crav n crav n flavor tortilla chips yellow corn crispy round party size 13_0.37</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -6110,12 +5024,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 7 oz</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, Yellow Corn, Crispy Round, Party Size | 13 oz</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -6141,7 +5055,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks 9 ea 510_0.51</t>
+          <t>goldfish_goldfish goldfish baked snack crackers cheddar 250_0.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -6149,16 +5063,16 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks 9 ea | 510 g</t>
+          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 250 g</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.849162011173184</v>
+        <v>2.061452513966481</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -6180,7 +5094,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>eggo_eggo eggo waffles blueberry 600g_0.6</t>
+          <t>jumbo_jumbo jumbo hartig kaas tomaat 14 2_0.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -6188,16 +5102,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Eggo | EGGO WAFFLES, BLUEBERRY | 600g</t>
+          <t>Jumbo | JUMBO HARTIG KAAS/TOMAAT | 14.2 oz</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.441340782122905</v>
+        <v>2.396648044692737</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -6219,7 +5133,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>frito lay_frito lay frito lay snacks classic mix 24 ea 6 5_0.18</t>
+          <t>jumbo_jumbo jumbo knoflookboterbaguette 16_0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -6227,16 +5141,16 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Frito-Lay | Frito Lay Snacks, Classic Mix 24 ea | 6.5 oz</t>
+          <t>Jumbo | JUMBO KNOFLOOKBOTERBAGUETTE | 16 oz</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.078212290502793</v>
+        <v>9.324022346368716</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -6258,7 +5172,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>goldfish_goldfish goldfish baked snack crackers cheddar 155_0.16</t>
+          <t>jumbo_jumbo jumbo meergranen biscuits bosvruchten 400_0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -6266,16 +5180,16 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 155 g</t>
+          <t>Jumbo | JUMBO MEERGRANEN BISCUITS BOSVRUCHTEN | 400 g</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.452513966480447</v>
+        <v>4.016759776536313</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -6297,7 +5211,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo hartig kaas tomaat 200_0.2</t>
+          <t>jumbo_jumbo jumbo puppy biscuits eend 125_0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -6310,11 +5224,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO HARTIG KAAS/TOMAAT | 200 g</t>
+          <t>Jumbo | JUMBO PUPPY BISCUITS EEND | 125 g</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.949720670391062</v>
+        <v>2.675977653631285</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -6336,7 +5250,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo luchtig crack naturel vegan 6 6_0.19</t>
+          <t>kinder_kinder kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -6344,16 +5258,16 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Kinder</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO LUCHTIG.CRACK NATUREL VEGAN | 6.6 oz</t>
+          <t>Kinder | Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.072625698324022</v>
+        <v>2.955307262569832</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -6375,7 +5289,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita 12 ea la dulcerita rasin muffin_unknown</t>
+          <t>lays_lays 24 pc lay s sour cream onion flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -6383,16 +5297,16 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>La Dulcerita | 12 ea LA DULCERITA RASIN MUFFIN</t>
+          <t>Lays | 24 pc Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.016759776536313</v>
+        <v>23.23463687150839</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -6414,7 +5328,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita 2 pc la dulcerita vanilla muffin_unknown</t>
+          <t>lays_lays lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -6422,16 +5336,16 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>La Dulcerita | 2 pc LA DULCERITA VANILLA MUFFIN</t>
+          <t>Lays | Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.899441340782123</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -6453,7 +5367,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita each la dulcerita vanilla pound cake_unknown</t>
+          <t>lu_lu cafe valley blueberry mini muffins_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -6461,16 +5375,16 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>La Dulcerita | each LA DULCERITA VANILLA POUND CAKE</t>
+          <t>LU | CAFE VALLEY BLUEBERRY MINI MUFFINS</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.117318435754189</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -6492,7 +5406,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lays_lays lay s honey barbecue potato chips 5 5_0.16</t>
+          <t>milka_milka milka mmmax chocoswing biscuit 225_0.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -6500,16 +5414,16 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lays | Lay's Honey Barbecue Potato Chips | 5.5 oz</t>
+          <t>Milka | MILKA MMMAX CHOCOSWING BISCUIT | 225 g</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.849162011173184</v>
+        <v>2.452513966480447</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -6531,7 +5445,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lays_lays lay s kettle cooked jalapeno flavored potato chips 15_0.43</t>
+          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 8_0.23</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -6539,16 +5453,16 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Lays | Lay's Kettle Cooked Jalapeno Flavored Potato Chips | 15 oz</t>
+          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 8 oz</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10.88826815642458</v>
+        <v>6.307262569832401</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -6570,7 +5484,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lays_lays lays classic chips 6 5_0.18</t>
+          <t>oreo_oreo oreo golden sandwich cookies 11 78_0.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -6578,16 +5492,16 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lays | LAYS CLASSIC CHIPS | 6.5 oz</t>
+          <t>Oreo | OREO Golden Sandwich Cookies, | 11.78 oz</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5.078212290502793</v>
+        <v>9.770949720670391</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6609,7 +5523,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lays_lays lays potato chips barbecue flavored 8_0.23</t>
+          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 13 29_0.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -6617,16 +5531,16 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lays | LAYS POTATO CHIPS, BARBECUE FLAVORED | 8 oz</t>
+          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 13.29 oz</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6.474860335195531</v>
+        <v>7.368715083798882</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -6648,7 +5562,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lu_lu bobs red mill cake mix vanilla yellow 10 75_0.3</t>
+          <t>pringles_pringles pringles cheddar cheese 2 3_0.07</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -6656,16 +5570,16 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LU | Bobs Red Mill Cake Mix, Gluten Free, Vanilla Yellow | 10.75 oz</t>
+          <t>Pringles | PRINGLES CHEDDAR CHEESE | 2.3 oz</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.977653631284916</v>
+        <v>2.340782122905028</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -6687,7 +5601,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>lu_lu lu bastogne original 415_0.42</t>
+          <t>pringles_pringles pringles original 1 4_0.04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -6695,16 +5609,16 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LU | LU BASTOGNE ORIGINAL | 415 g</t>
+          <t>Pringles | PRINGLES ORIGINAL | 1.4 oz</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.491620111731844</v>
+        <v>1.558659217877095</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -6726,7 +5640,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>noel_noel noel chocolate chip 166_0.17</t>
+          <t>pringles_pringles pringles potato crisps chips original grab n go 5 5_0.16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -6734,16 +5648,16 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Noel | NOEL CHOCOLATE CHIP | 166 g</t>
+          <t>Pringles | Pringles Potato Crisps Chips, Original, Grab N' Go | 5.5 oz</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.508379888268156</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -6765,7 +5679,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sara lee_sara lee 6 pc sara lee pound cake classic 10 75_0.3</t>
+          <t>pringles_pringles pringles sour cream onion 1 3_0.04</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -6773,16 +5687,16 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sara Lee</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sara Lee | 6 pc Sara Lee Pound Cake, Classic | 10.75 oz</t>
+          <t>Pringles | PRINGLES SOUR CREAM &amp; ONION | 1.3 oz</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.067039106145252</v>
+        <v>1.558659217877095</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -6804,7 +5718,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tostitos_tostitos tostitos restaurant style original tortilla chips 6 5_0.18</t>
+          <t>toufayan_toufayan 6ct toufayan bakeries garlic pesto wraps_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -6812,16 +5726,16 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tostitos | Tostitos Restaurant Style Original Tortilla Chips | 6.5 oz</t>
+          <t>Toufayan | 6ct TOUFAYAN BAKERIES GARLIC PESTO WRAPS</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.575418994413408</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -6843,7 +5757,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unknown_2 fl cheesecake punt_unknown</t>
+          <t>toufayan_toufayan toufayan bakeries pita sweet onion 7 33_0.21</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6851,16 +5765,16 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2 fl oz CHEESECAKE PUNT</t>
+          <t>Toufayan | TOUFAYAN BAKERIES PITA SWEET ONION | 7.33 oz</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.916201117318436</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -6882,7 +5796,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_2 pc tompouce_unknown</t>
+          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 1 5_0.04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -6890,16 +5804,16 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2 pc TOMPOUCE :</t>
+          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 1.5 oz</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.899441340782123</v>
+        <v>1.670391061452514</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -6921,7 +5835,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_8 ea papagena biscuit assorted_unknown</t>
+          <t>unknown_bosvruchten muffin 24_0.68</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -6934,11 +5848,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8 ea PAPAGENA BISCUIT ASSORTED</t>
+          <t>BOSVRUCHTEN MUFFIN | 24 oz</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.35754189944134</v>
+        <v>7.251396648044693</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -6960,7 +5874,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_aardbeienslof_unknown</t>
+          <t>unknown_fjord knackebrod volkoren 6 6_0.19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -6973,11 +5887,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>AARDBEIENSLOF</t>
+          <t>FJORD KNACKEBROD VOLKOREN | 6.6 oz</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.569832402234637</v>
+        <v>4.072625698324022</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -6999,7 +5913,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_fjord knackebrod volkoren 250_0.25</t>
+          <t>unknown_food for life ezekiel 4 9 bread cinnamon raisin 680_0.68</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -7012,11 +5926,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FJORD KNACKEBROD VOLKOREN | 250 g</t>
+          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, CINNAMON RAISIN | 680 g</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.061452513966481</v>
+        <v>11.14525139664804</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -7038,7 +5952,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_fruit cake 425_0.42</t>
+          <t>unknown_food for life flourless sprouted grain cinnamon raisin bread 29 6_0.84</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -7051,11 +5965,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>FRUIT CAKE | 425 g</t>
+          <t>Food For Life Flourless Sprouted Grain Cinnamon Raisin Bread | 29.6 oz</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.117318435754189</v>
+        <v>10.02793296089386</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -7077,7 +5991,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_haagen dazs caramel biscuit and cream speculoos 200_0.2</t>
+          <t>unknown_udis sandwich bread soft white 24_0.68</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -7090,11 +6004,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS | 200 g</t>
+          <t>UDIS SANDWICH BREAD, SOFT WHITE | 24 oz</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.407821229050279</v>
+        <v>12.82122905027933</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -7116,7 +6030,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_home made choco cake 420_0.42</t>
+          <t>wasa_wasa wasa knackebrod glutenvr sesam 260_0.26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -7124,16 +6038,16 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Wasa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HOME MADE CHOCO CAKE | 420 G</t>
+          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 260 g</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.117318435754189</v>
+        <v>3.067039106145252</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -7145,17 +6059,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_spring home roti paratha plain 5 ea 14_0.4</t>
+          <t>unknown_topper cake feliz cumpleanos silver_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -7168,11 +6082,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Spring Home Roti Paratha, Plain 5 ea | 14 oz</t>
+          <t>Topper Cake Feliz Cumpleanos Silver</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.899441340782123</v>
+        <v>3.57</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -7184,17 +6098,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown_tiramisutaartje_unknown</t>
+          <t>unknown_topper cake feliz cumpleanos wood_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -7207,11 +6121,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>TIRAMISUTAARTJE</t>
+          <t>Topper Cake Feliz Cumpleanos Wood</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.067039106145252</v>
+        <v>3.57</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -7228,12 +6142,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bon_paleta bon de bizcocho_unknown</t>
+          <t>unknown_topper cake happy birthday gold_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -7241,16 +6155,16 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paleta Bon De Bizcocho</t>
+          <t>Topper Cake Happy Birthday Gold</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.71</v>
+        <v>3.57</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -7267,12 +6181,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown_gold pan viga mediana integral_0.82</t>
+          <t>unknown_topper cake happy birthday silver_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -7285,11 +6199,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Gold Pan Viga Mediana Integral</t>
+          <t>Topper Cake Happy Birthday Silver</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.89</v>
+        <v>3.57</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -7301,17 +6215,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>golden_golden harvest multigrain loaf_unknown</t>
+          <t>unknown_topper cake happy birthday star gold_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -7319,16 +6233,16 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
+          <t>Topper Cake Happy Birthday Star Gold</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.596153846153846</v>
+        <v>3.57</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -7340,17 +6254,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>golden_golden harvest whole slice bread_unknown</t>
+          <t>molino del sol_pan integral multigranos molino del sol_0.65</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -7358,16 +6272,16 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Golden Harvest Whole Slice Bread</t>
+          <t>Pan Integral Multigranos Molino Del Sol</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.163461538461538</v>
+        <v>3.33</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -7379,17 +6293,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>instorebakery_salara red cake_unknown</t>
+          <t>pringles_papas fritas mini pringles original_0.04</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -7397,16 +6311,16 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Instorebakery</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Salara Red Cake</t>
+          <t>Papas Fritas Mini Pringles Original</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.346153846153846</v>
+        <v>1.09</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -7418,17 +6332,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>other_1 2 sheet base w rose dome 30_unknown</t>
+          <t>unknown_chips bruschette sabor vegetales mediterraneos maretti_0.14</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -7436,16 +6350,16 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1/2 Sheet Base W Rose Dome 30 Ct</t>
+          <t>Chips Bruschette Sabor Vegetales Mediterraneos Maretti</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.745192307692307</v>
+        <v>1.96</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -7467,7 +6381,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>other_dbli panel window bag 8 3 15_unknown</t>
+          <t>old el paso_old el paso shell tortilla 10 in_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -7475,16 +6389,16 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Old El Paso</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DBLI PANEL WINDOW BAG 8″*3*15</t>
+          <t>Old El Paso Shell Tortilla 10 In</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.25</v>
+        <v>5.913461538461538</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -7506,7 +6420,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>other_essential everyday wax paper_unknown</t>
+          <t>unknown_bobs red mill pancake mix_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -7514,16 +6428,16 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Essential Everyday Wax Paper</t>
+          <t>Bobs Red Mill Pancake Mix</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.576923076923077</v>
+        <v>10.91346153846154</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -7545,7 +6459,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>other_pactiv med meal master black 252ct_unknown</t>
+          <t>unknown_sarojanie sugar cake 85g_0.08</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -7553,16 +6467,16 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pactiv Med Meal Master Black 252ct</t>
+          <t>Sarojanie Sugar Cake 85g</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.3365384615384615</v>
+        <v>1.201923076923077</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,39 +483,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unknown_cafe valley banana nut mini muffins 12ct 10 5oz_0.3</t>
+          <t>oreo_oreo oreo golden sandwich cookies 13 29_0.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CAFE VALLEY BANANA NUT MINI MUFFINS 12CT 10.5oz</t>
+          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.86</v>
+        <v>8.039106145251397</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CAFE VALLEY BANANA NUT MINI MUFFINS 12CT 10.5oz</t>
+          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.25</v>
+        <v>7.368715083798882</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11.61904761904762</v>
+        <v>9.097801364670213</v>
       </c>
     </row>
     <row r="3">
@@ -534,39 +534,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unknown_cafe valley chocolate fudge ring cake 26oz_0.74</t>
+          <t>oreo_oreo oreo mini cookies snak saks 13 29_0.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CAFE VALLEY CHOCOLATE FUDGE RING CAKE 26oz</t>
+          <t>Oreo | OREO MINI COOKIES SNAK-SAKS | 13.29 oz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11.06</v>
+        <v>7.089385474860335</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CAFE VALLEY CHOCOLATE FUDGE RING CAKE 26oz</t>
+          <t>Oreo | OREO MINI COOKIES SNAK-SAKS | 13.29 oz</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>9.99</v>
+        <v>8.039106145251397</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>10.71071071071071</v>
+        <v>-11.8137595552467</v>
       </c>
     </row>
     <row r="4">
@@ -590,30 +590,30 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo bladerdeeg 175_0.18</t>
+          <t>unknown_bosvruchten muffin_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO BLADERDEEG | 175 g</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.782122905027933</v>
+        <v>29.58100558659218</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO BLADERDEEG | 175 g</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>42.69340974212034</v>
+        <v>1417.191977077364</v>
       </c>
     </row>
     <row r="5">
@@ -641,34 +641,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lays_lays lay s cheddar flavored potato crisps 5 5_0.16</t>
+          <t>unknown_pruimentaart klein_unknown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lays | Lay's Cheddar Flavored Potato Crisps | 5.5 oz</t>
+          <t>PRUIMENTAART KLEIN</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.849162011173184</v>
+        <v>25.11173184357542</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lays | Lay's Cheddar Flavored Potato Crisps | 5.5 oz</t>
+          <t>PRUIMENTAART KLEIN</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.122905027932961</v>
+        <v>18.40782122905028</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23.25581395348837</v>
+        <v>36.41881638846737</v>
       </c>
     </row>
     <row r="6">
@@ -692,7 +692,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_bolo di druif klein_unknown</t>
+          <t>unknown_vruchtenschelp_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -702,11 +702,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BOLO DI DRUIF KLEIN</t>
+          <t>VRUCHTENSCHELP</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>26.53072625698324</v>
+        <v>3.569832402234637</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -715,11 +715,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOLO DI DRUIF KLEIN</t>
+          <t>VRUCHTENSCHELP</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>23.43575418994413</v>
+        <v>3.324022346368715</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -727,50 +727,50 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>13.20619785458879</v>
+        <v>7.394957983193262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_bosvruchten muffin_unknown</t>
+          <t>carrefour_pan tostado carrefour bio_0.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BOSVRUCHTEN MUFFIN</t>
+          <t>Pan Tostado Carrefour Bio</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.949720670391062</v>
+        <v>2.53</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BOSVRUCHTEN MUFFIN</t>
+          <t>Pan Tostado Carrefour Bio</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>29.58100558659218</v>
+        <v>2.28</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -778,50 +778,50 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-93.4088762983947</v>
+        <v>10.96491228070176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_cherry pineapple klein_unknown</t>
+          <t>tostitos_chips de tortillas de maiz tostitos santa elena_0.43</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CHERRY/ PINEAPPLE KLEIN</t>
+          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>22.31843575418995</v>
+        <v>3.33</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CHERRY/ PINEAPPLE KLEIN</t>
+          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>26.53072625698324</v>
+        <v>3.88</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-15.8770267424721</v>
+        <v>-14.17525773195876</v>
       </c>
     </row>
     <row r="9">
@@ -840,39 +840,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>carrefour_pan tostado carrefour bio_0.25</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pan Tostado Carrefour Bio</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pan Tostado Carrefour Bio</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-9.881422924901187</v>
+        <v>-20.09803921568628</v>
       </c>
     </row>
     <row r="10">
@@ -891,39 +891,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>guarina_galleta waffer sabor vainilla guarina 106 onz_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Guarina</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galleta Waffer Sabor Vainilla Guarina 106 Onz</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Guarina</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Galleta Waffer Sabor Vainilla Guarina 106 Onz</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>18.11023622047244</v>
+        <v>25.15337423312884</v>
       </c>
     </row>
     <row r="11">
@@ -942,39 +942,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>guarina_galletas wafer limon guarina_0.26</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Guarina</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Galletas Wafer Limon Guarina</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Guarina</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Galletas Wafer Limon Guarina</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.27</v>
+        <v>2.92</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>18.11023622047244</v>
+        <v>-46.23287671232876</v>
       </c>
     </row>
     <row r="12">
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>oreo_galletas oreo original_0.04</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Galletas Oreo Original</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Galletas Oreo Original</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.64</v>
+        <v>1.57</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1033,50 +1033,50 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-12.91208791208792</v>
+        <v>85.98726114649681</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>tostitos_chips de tortillas de maiz tostitos santa elena_0.43</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.09</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.72</v>
+        <v>0.3125</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1084,50 +1084,50 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>-16.93548387096775</v>
+        <v>1007.692307692308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jumbo_pan de hamburguesas gourmet jumbo_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesas Gourmet Jumbo</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.9</v>
+        <v>0.3125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesas Gourmet Jumbo</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.49</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1135,50 +1135,50 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>27.51677852348993</v>
+        <v>-90.97222222222221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jumbo_pan de sandwich mini club jumbo_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Mini Club Jumbo</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.66</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Mini Club Jumbo</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.33</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1186,50 +1186,50 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>24.81203007518796</v>
+        <v>152.0833333333334</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jumbo_pan de sandwich viga mediana jumbo_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Viga Mediana Jumbo</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.14</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Viga Mediana Jumbo</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.73</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1237,50 +1237,50 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.69942196531793</v>
+        <v>-60.33057851239671</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jumbo_pan integral viga mediana jumbo_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pan Integral Viga Mediana Jumbo</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.38</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pan Integral Viga Mediana Jumbo</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1288,50 +1288,50 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>31.49171270718231</v>
+        <v>-91.46341463414633</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jumbo_pan para hot dog jumbo_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pan Para Hot Dog Jumbo</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.58</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pan Para Hot Dog Jumbo</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.25</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1339,50 +1339,50 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>26.40000000000001</v>
+        <v>1071.428571428572</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>la panera_pan para mini hamburguesa la panera_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>La Panera</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pan Para Mini Hamburguesa La Panera</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.58</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>La Panera</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pan Para Mini Hamburguesa La Panera</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.25</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1390,50 +1390,50 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>26.40000000000001</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.63</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.04</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,50 +1441,50 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>-20.09803921568628</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.04</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.63</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1492,50 +1492,50 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>25.15337423312884</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bon_helados bon bizcocho_0.26</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helados Bon Bizcocho</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.76</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bon</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Helados Bon Bizcocho</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.69</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,50 +1543,50 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>-25.20325203252033</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>la panera_pan para mini hamburguesa la panera_unknown</t>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>La Panera</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pan Para Mini Hamburguesa La Panera</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.57</v>
+        <v>29.08653846153846</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>La Panera</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pan Para Mini Hamburguesa La Panera</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.25</v>
+        <v>15.04807692307692</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,50 +1594,50 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>25.6</v>
+        <v>93.29073482428115</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lu_pan de sandwich mini club nacional_unknown</t>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Mini Club Nacional</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.65</v>
+        <v>15.04807692307692</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Mini Club Nacional</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.33</v>
+        <v>29.08653846153846</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,50 +1645,50 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>24.06015037593984</v>
+        <v>-48.26446280991735</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_pan de hamburguesas gourmet nacional_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesas Gourmet Nacional</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.89</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesas Gourmet Nacional</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.51</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,50 +1696,50 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>25.16556291390728</v>
+        <v>70.19230769230769</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_pan de sandwich viga mediana nacional_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Viga Mediana Nacional</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pan De Sandwich Viga Mediana Nacional</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.73</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,50 +1747,50 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>22.54335260115608</v>
+        <v>-41.24293785310735</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_pan integral viga mediana nacional_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pan Integral Viga Mediana Nacional</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.36</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pan Integral Viga Mediana Nacional</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.81</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1798,50 +1798,50 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>30.3867403314917</v>
+        <v>494.7368421052633</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_pan para hot dog nacional_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pan Para Hot Dog Nacional</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.57</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pan Para Hot Dog Nacional</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.25</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1849,50 +1849,50 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>25.6</v>
+        <v>-83.18584070796462</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>glutino_muffin ingles sin glutino_0.48</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Muffin Ingles Sin Gluten Glutino</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12.28</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Glutino</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Muffin Ingles Sin Gluten Glutino</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>13.94</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1900,50 +1900,50 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>-11.90817790530847</v>
+        <v>24.99999999999997</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lu_pan baguette congelado sin panamar_0.1</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pan Baguette Congelado Sin Gluten Panamar</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.11</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pan Baguette Congelado Sin Gluten Panamar</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.38</v>
+        <v>0.625</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1951,50 +1951,50 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-11.34453781512605</v>
+        <v>169.2307692307692</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>pirulin_barquilla rellena de chocolate y avellanas pirulin_0.16</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barquilla Rellena De Chocolate Y Avellanas Pirulin</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.09</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pirulin</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Barquilla Rellena De Chocolate Y Avellanas Pirulin</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.49</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2002,50 +2002,50 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>-11.46131805157594</v>
+        <v>-19.99999999999998</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>toufayan_pan pita blanco toufayan_0.34</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pan Pita Blanco Toufayan</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.58</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pan Pita Blanco Toufayan</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.85</v>
+        <v>0.625</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2053,50 +2053,50 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-14.59459459459459</v>
+        <v>115.3846153846154</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>toufayan_pan pita integral toufayan_0.34</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pan Pita Integral Toufayan</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.27</v>
+        <v>0.625</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pan Pita Integral Toufayan</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.5</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2104,50 +2104,50 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>-15.33333333333333</v>
+        <v>-62.85714285714285</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>toufayan_pan pita keto toufayan_0.25</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pan Pita Keto Toufayan</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4.17</v>
+        <v>0.625</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pan Pita Keto Toufayan</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.75</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2155,1383 +2155,6 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>-12.21052631578948</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>El Charrito</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>El Charrito</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>-46.23287671232876</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>El Charrito</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>El Charrito</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>85.98726114649681</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>3.461538461538462</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>1007.692307692308</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>3.461538461538462</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>-90.97222222222221</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Cadbury</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Cadbury Dairy Milk Daim</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>5.817307692307693</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Cadbury</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Cadbury Dairy Milk Daim</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>2.307692307692307</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>152.0833333333334</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Cadbury</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Cadbury Dairy Milk Daim</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>2.307692307692307</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Cadbury</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Cadbury Dairy Milk Daim</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>5.817307692307693</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>-60.33057851239671</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>festival_noel festival chocolate_unknown</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0.3365384615384615</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>3.942307692307693</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>-91.46341463414633</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>festival_noel festival chocolate_unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>3.942307692307693</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Festival</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>0.3365384615384615</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>1071.428571428572</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>4.086538461538462</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>-58.82352941176471</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>4.086538461538462</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>142.8571428571429</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>4.086538461538462</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>-58.82352941176471</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>4.086538461538462</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>142.8571428571429</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>New York Style</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>29.08653846153846</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>New York Style</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>15.04807692307692</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>93.29073482428115</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>New York Style</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>15.04807692307692</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>New York Style</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>29.08653846153846</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>-48.26446280991735</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>otis spunkmeyer_otis spunkmeyer banana nut muffins_unknown</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Otis Spunkmeyer</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>OTIS SPUNKMEYER BANANA NUT MUFFINS</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1.442307692307692</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Otis Spunkmeyer</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>OTIS SPUNKMEYER  BANANA NUT MUFFINS</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>7.115384615384615</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>-79.72972972972973</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>pringles_pringles pizza_unknown</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>PRINGLES PIZZA</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>4.254807692307693</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Pringles Pizza</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>70.19230769230769</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>pringles_pringles pizza_unknown</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Pringles Pizza</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>PRINGLES PIZZA</t>
-        </is>
-      </c>
-      <c r="I51" t="n">
-        <v>4.254807692307693</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>-41.24293785310735</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Butter Crackers</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>4.182692307692307</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
-        </is>
-      </c>
-      <c r="I52" t="n">
-        <v>1.778846153846154</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>135.1351351351352</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1.778846153846154</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Butter Crackers</t>
-        </is>
-      </c>
-      <c r="I53" t="n">
-        <v>4.182692307692307</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>-57.4712643678161</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Cream Crackers</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>10.86538461538462</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
-        </is>
-      </c>
-      <c r="I54" t="n">
-        <v>1.826923076923077</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>494.7368421052633</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1.826923076923077</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Cream Crackers</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>10.86538461538462</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>-83.18584070796462</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>24.99999999999997</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I57" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>169.2307692307692</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>-19.99999999999998</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I59" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>115.3846153846154</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I60" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>-62.85714285714285</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
         <v>-53.57142857142858</v>
       </c>
     </row>
@@ -3546,7 +2169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3614,26 +2237,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor pita chips parmesan garlic herb baked 7 33_0.21</t>
+          <t>fritolay_lays argentina asado 1 13oz_0.03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Pita Chips, Parmesan Garlic &amp; Herb, Baked | 7.33 oz</t>
+          <t>LAYS ARGENTINA ASADO 1.13OZ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.290502793296089</v>
+        <v>0.89</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -3653,26 +2276,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor tortilla chips white corn bite size round 13_0.37</t>
+          <t>fritolay_lays argentina asado 3 7oz_0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Bite Size Round | 13 oz</t>
+          <t>LAYS ARGENTINA ASADO 3.7OZ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.184357541899441</v>
+        <v>2.51</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -3692,26 +2315,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>goldfish_goldfish goldfish baked snack crackers cheddar 260_0.26</t>
+          <t>fritolay_lays mexico taco 1 13oz_0.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 260 g</t>
+          <t>LAYS MEXICO TACO 1.13OZ</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.067039106145252</v>
+        <v>0.89</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -3731,26 +2354,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo meergranen biscuits bosvruchten 125_0.12</t>
+          <t>fritolay_lays mexico taco 3 7oz_0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Fritolay</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO MEERGRANEN BISCUITS BOSVRUCHTEN | 125 g</t>
+          <t>LAYS MEXICO TACO 3.7OZ</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.675977653631285</v>
+        <v>2.51</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -3770,26 +2393,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo puppy biscuits eend 225_0.22</t>
+          <t>unknown_64lts led light multi twinkle shimmering sphere burts silver wrap 12in_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO PUPPY BISCUITS EEND | 225 g</t>
+          <t>64LTS LED LIGHT MULTI TWINKLE SHIMMERING SPHERE BURTS SILVER WRAP 12in</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.452513966480447</v>
+        <v>23.46</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -3809,26 +2432,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kinder_kinder 6ct kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 1 5_0.04</t>
+          <t>unknown_64lts led light pure white twinkle shimmering sphere burts silver wrap 12in_unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kinder | 6ct Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 1.5 oz</t>
+          <t>64LTS LED LIGHT PURE WHITE TWINKLE SHIMMERING SPHERE BURTS SILVER WRAP 12in</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.899441340782123</v>
+        <v>23.46</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -3848,26 +2471,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lays_lays 24 pc lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
+          <t>unknown_64lts led light warm white twinkle shimmering sphere burts silver wrap 12in_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lays | 24 pc Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
+          <t>64LTS LED LIGHT WARM WHITE TWINKLE SHIMMERING SPHERE BURTS SILVER WRAP 12in</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23.23463687150839</v>
+        <v>23.46</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -3887,26 +2510,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lays_lays lay s sour cream onion flavored potato crisps 5 5_0.16</t>
+          <t>unknown_80lts led light champagne twinkle starlight burts gold wrap 16in_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
+          <t>80LTS LED LIGHT CHAMPAGNE TWINKLE STARLIGHT BURTS GOLD WRAP 16in</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.122905027932961</v>
+        <v>31.84</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -3926,26 +2549,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lu_lu cafe valley blueberry mini muffins 24_0.68</t>
+          <t>unknown_zacks tortilla chili lime chips 6_0.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LU | CAFE VALLEY BLUEBERRY MINI MUFFINS | 24 oz</t>
+          <t>ZACKS' TORTILLA CHILI LIME CHIPS 6 OZ</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.251396648044693</v>
+        <v>6.03</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -3970,21 +2593,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mcvitie s_mcvitie s mcvitie s digestive 14 2_0.4</t>
+          <t>badia_badia badia everything bagel seasoning 6 78_0.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>McVitie's | MCVITIE'S DIGESTIVE | 14.2 oz</t>
+          <t>Badia | Badia Everything Bagel Seasoning | 6.78 oz</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.396648044692737</v>
+        <v>3.513966480446927</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -4009,21 +2632,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>milka_milka milka mmmax chocoswing biscuit 400_0.4</t>
+          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks party size 40 ea_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Milka | MILKA MMMAX CHOCOSWING BISCUIT | 400 g</t>
+          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.016759776536313</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -4048,21 +2671,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 11 78_0.33</t>
+          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 7_0.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 11.78 oz</t>
+          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 7 oz</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>9.770949720670391</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -4087,21 +2710,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo golden sandwich cookies 13 29_0.38</t>
+          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks 9 ea 510_0.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
+          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks 9 ea | 510 g</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.368715083798882</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -4126,21 +2749,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 8_0.23</t>
+          <t>bigelow_bigelow bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea 12 67_0.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 8 oz</t>
+          <t>Bigelow | Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea | 12.67 oz</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6.307262569832401</v>
+        <v>14.24022346368715</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -4165,21 +2788,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles bbq 2 3_0.07</t>
+          <t>crav n_crav n 12 ea crav n flavor tortilla chips white corn bite size round 13_0.37</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES BBQ | 2.3 oz</t>
+          <t>Crav'N | 12 ea Crav'n Flavor Tortilla Chips, White Corn, Bite Size Round | 13 oz</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.340782122905028</v>
+        <v>7.234636871508379</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -4204,17 +2827,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles cheddar cheese 5 5_0.16</t>
+          <t>crav n_crav n crav n flavor crackers original rich crisp 3 ea 190_0.19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES CHEDDAR CHEESE | 5.5 oz</t>
+          <t>Crav'N | Crav'n Flavor Crackers, Original, Rich &amp; Crisp, 3 ea | 190 g</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4243,21 +2866,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles original 1 3_0.04</t>
+          <t>eggo_eggo eggo minis waffle 11_0.31</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES ORIGINAL | 1.3 oz</t>
+          <t>Eggo | EGGO MINIS WAFFLE | 11 oz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.558659217877095</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -4282,21 +2905,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles potato crisps chips lunch snacks office and kids snacks grab n go original can 1 can 1 4_0.04</t>
+          <t>frito lay_frito lay 24 pc frito lay bold mix 24 ea_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pringles | Pringles Potato Crisps Chips, Lunch Snacks, Office and Kids Snacks, Grab N' Go, Original, Can, 1 Can | 1.4 oz</t>
+          <t>Frito-Lay | 24 pc Frito Lay Bold Mix 24 ea</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.558659217877095</v>
+        <v>23.23463687150839</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -4321,21 +2944,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>toufayan_toufayan toufayan bakeries garlic pesto wraps 1 5_0.04</t>
+          <t>frito lay_frito lay frito lay doritos nacho cheese 5 5_0.16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Toufayan | TOUFAYAN BAKERIES GARLIC PESTO WRAPS | 1.5 oz</t>
+          <t>Frito-Lay | FRITO LAY DORITOS NACHO CHEESE | 5.5 oz</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.670391061452514</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -4360,21 +2983,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>toufayan_toufayan toufayan bakeries pita sweet onion 400_0.4</t>
+          <t>glad_glad 19 pc glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Toufayan | TOUFAYAN BAKERIES PITA SWEET ONION | 400 g</t>
+          <t>Glad | 19 pc Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.614525139664805</v>
+        <v>5.134078212290502</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -4399,21 +3022,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 11_0.31</t>
+          <t>jumbo_jumbo jumbo linzenwafel sweet chilli 13 7_0.39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 11 oz</t>
+          <t>Jumbo | JUMBO LINZENWAFEL SWEET CHILLI | 13.7 oz</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.955307262569832</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -4438,21 +3061,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>unknown_coolback herb butter baguette 16_0.45</t>
+          <t>jumbo_jumbo jumbo marie biscuits 300_0.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>COOLBACK HERB BUTTER BAGUETTE | 16 oz</t>
+          <t>Jumbo | JUMBO MARIE BISCUITS | 300 g</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>9.324022346368716</v>
+        <v>8.87709497206704</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -4477,21 +3100,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_fjord knackebrod volkoren 250_0.25</t>
+          <t>jumbo_jumbo jumbo tortilla dip hot 300_0.3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FJORD KNACKEBROD VOLKOREN | 250 g</t>
+          <t>Jumbo | JUMBO TORTILLA DIP HOT | 300 g</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.061452513966481</v>
+        <v>2.005586592178771</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -4516,21 +3139,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_food for life ezekiel 4 9 bread cinnamon raisin 29 6_0.84</t>
+          <t>kellogg_kellogg 2 pk kellogg s eggo blueberry pancakes_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kellogg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, CINNAMON RAISIN | 29.6 oz</t>
+          <t>Kellogg | 2 pk KELLOGG'S EGGO BLUEBERRY PANCAKES</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10.02793296089386</v>
+        <v>7.793296089385474</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -4555,21 +3178,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_food for life flourless sprouted grain cinnamon raisin bread 24_0.68</t>
+          <t>la dulcerita_la dulcerita la dulcerita chocolate chip muffin_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Food For Life Flourless Sprouted Grain Cinnamon Raisin Bread | 24 oz</t>
+          <t>La Dulcerita | LA DULCERITA CHOCOLATE CHIP MUFFIN</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12.82122905027933</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -4594,21 +3217,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_udis sandwich bread soft white 680_0.68</t>
+          <t>lays_lays 24 pc lay s sour cream onion flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UDIS SANDWICH BREAD, SOFT WHITE | 680 g</t>
+          <t>Lays | 24 pc Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11.14525139664804</v>
+        <v>23.23463687150839</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -4633,21 +3256,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wasa_wasa wasa knackebrod glutenvr sesam 6 6_0.19</t>
+          <t>lays_lays lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 6.6 oz</t>
+          <t>Lays | Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.072625698324022</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -4662,31 +3285,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>golden_golden harvest multigrain loaf_unknown</t>
+          <t>lu_lu 6 pc tf blueberry bagel_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
+          <t>LU | 6 pc Tf Blueberry Bagel</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.596153846153846</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -4701,31 +3324,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>golden_golden harvest whole slice bread_unknown</t>
+          <t>lu_lu lu cracottes naturel 250_0.25</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Golden Harvest Whole Slice Bread</t>
+          <t>LU | LU CRACOTTES NATUREL | 250 g</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.163461538461538</v>
+        <v>1.893854748603352</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -4740,31 +3363,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>other_1 2 sheet base w rose dome 30_unknown</t>
+          <t>noel_noel 6 ea noel dux saltines crackers_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1/2 Sheet Base W Rose Dome 30 Ct</t>
+          <t>Noel | 6 ea NOEL DUX SALTINES CRACKERS</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5.745192307692307</v>
+        <v>6.865921787709497</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -4779,31 +3402,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>other_dbli panel window bag 8 3 15_unknown</t>
+          <t>pepperidge farm_pepperidge farm pepperidge farm goldfish snack crackers baked colors cheddar 250_0.25</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pepperidge Farm</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DBLI PANEL WINDOW BAG 8″*3*15</t>
+          <t>Pepperidge Farm | PEPPERIDGE FARM GOLDFISH SNACK CRACKERS, BAKED, COLORS CHEDDAR | 250 g</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.25</v>
+        <v>2.061452513966481</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -4818,31 +3441,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>other_essential everyday wax paper_unknown</t>
+          <t>pepperidge farm_pepperidge farm pepperidge farm texas toast frozen garlic bread 8 slices box 14 2_0.4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pepperidge Farm</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Essential Everyday Wax Paper</t>
+          <t>Pepperidge Farm | Pepperidge Farm® Texas Toast Frozen Garlic Bread, 8 Slices, . Box | 14.2 oz</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.576923076923077</v>
+        <v>9.770949720670391</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -4857,31 +3480,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>other_pactiv med meal master black 252ct_unknown</t>
+          <t>pillsbury_pillsbury 8 ea pillsbury flaky layers honey butter biscuits 8 ea_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pactiv Med Meal Master Black 252ct</t>
+          <t>Pillsbury | 8 ea Pillsbury Flaky Layers Honey Butter Biscuits 8 ea</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.3365384615384615</v>
+        <v>5.35754189944134</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -4892,6 +3515,1644 @@
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pillsbury_pillsbury pillsbury crescents original 16_0.45</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pillsbury</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Pillsbury | PILLSBURY CRESCENTS ORIGINAL | 16 oz</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>6.083798882681564</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles original 2 5_0.07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES ORIGINAL | 2.5 oz</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.340782122905028</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles salty snacks potato crisps chips sour cream and onion flavored 5 3_0.15</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES SALTY SNACKS POTATO CRISPS CHIPS, SOUR CREAM AND ONION FLAVORED | 5.3 oz</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pringles_pringles pringles sour cream onion 1 3_0.04</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Pringles | PRINGLES SOUR CREAM &amp; ONION | 1.3 oz</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.558659217877095</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>schar_schar schar hamburger buns 8_0.23</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Schar</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Schar | SCHAR HAMBURGER BUNS, GLUTEN FREE | 8 oz</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6 ea toufayan bakeries wholesome wheat wraps_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Toufayan | 6 ea TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan plain bagels 567_0.57</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN PLAIN BAGELS | 567 g</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>unknown_2 pc tiramisu gebak_unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2 pc TIRAMISU GEBAK</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>unknown_6 lemon muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>6 ct LEMON MUFFIN</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>5.301675977653631</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>unknown_aardbeienslof_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AARDBEIENSLOF</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3.324022346368715</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>unknown_bosvruchten muffin 24_0.68</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BOSVRUCHTEN MUFFIN | 24 oz</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>7.251396648044693</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unknown_coolback garlic butter baguette 450g_0.45</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>COOLBACK GARLIC BUTTER BAGUETTE | 450g</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3.569832402234637</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unknown_each appeltaartje klein_unknown</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>each APPELTAARTJE KLEIN</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>23.43575418994413</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unknown_fjord knackebrod volkoren 240_0.24</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FJORD KNACKEBROD VOLKOREN | 240 g</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>6.698324022346369</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>unknown_food for life ezekiel 4 9 bread low sodium sprouted grain 12 9oz_0.37</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, LOW SODIUM, SPROUTED GRAIN | 12.9oz</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9.46927374301676</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unknown_food for life sprouted corn tortillas 9 75_0.28</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FOOD FOR LIFE SPROUTED CORN TORTILLAS | 9.75 oz</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unknown_french bread white 24_0.68</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FRENCH BREAD WHITE | 24 oz</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>7.201117318435754</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unknown_haagen dazs caramel biscuit and cream speculoos 16 3_0.46</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS | 16.3 oz</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unknown_koopmans deeg hartige taart 309_0.31</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>KOOPMANS DEEG HARTIGE TAART | 309 g</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>5.525139664804469</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unknown_wei chuan spring rolls shells 14 8_0.42</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>WEI-CHUAN SPRING ROLLS SHELLS | 14.8 oz</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>5.245810055865922</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unknown_white chocolate raspberry klein_unknown</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>WHITE CHOCOLATE RASPBERRY KLEIN</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>18.40782122905028</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>verkade_verkade verkade nizza 14 2_0.4</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Verkade</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Verkade | VERKADE NIZZA | 14.2 oz</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2.396648044692737</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa dun rogge volkoren 300_0.3</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>WASA | WASA DUN ROGGE VOLKOREN | 300 g</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3.290502793296089</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa knackebrod glutenvr sesam 260_0.26</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 260 g</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa vezelrijk 250_0.25</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>WASA | WASA VEZELRIJK | 250 g</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa volkoren 6 6_0.19</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>WASA | WASA VOLKOREN | 6.6 oz</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>3.849162011173184</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>unknown_topper cake feliz cumpleanos silver_unknown</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Topper Cake Feliz Cumpleanos Silver</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>unknown_topper cake feliz cumpleanos wood_unknown</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Topper Cake Feliz Cumpleanos Wood</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>unknown_topper cake happy birthday gold_unknown</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Topper Cake Happy Birthday Gold</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>unknown_topper cake happy birthday silver_unknown</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Topper Cake Happy Birthday Silver</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>unknown_topper cake happy birthday star gold_unknown</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Topper Cake Happy Birthday Star Gold</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>lumijor_pan integral familiar lumijor_0.85</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lumijor</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Pan Integral Familiar Lumijor</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>molino del sol_pan viga integral con germen de trigo molino del sol_0.62</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Molino Del Sol</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pan Viga Integral Con Germen De Trigo Molino Del Sol</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pringles_papas sabor bbq pringles_0.04</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Papas Sabor Bbq Pringles</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pringles_papitas sabor crema agria y cebolla pringles_0.04</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Papitas Sabor Crema Agria Y Cebolla Pringles</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pringles_papitas sabor queso pringles_0.04</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Papitas Sabor Queso Pringles</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez crix crackers original_unknown</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Bermudez Crix Crackers Original</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>7.163461538461538</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>devon_devon biscuits digestive 250 gr_0.25</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Devon Biscuits Digestive 250 gr</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>2.067307692307693</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>lu_canyon country white_unknown</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Canyon Gluten Free Country White</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>9.85576923076923</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>unknown_fritos brand twista honey bbq_unknown</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Fritos Brand Twista Honey Bbq</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>unknown_sarojanie sugar cake 85g_0.08</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sarojanie Sugar Cake 85g</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1.201923076923077</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>unknown_wj soup bowl lid_unknown</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Wj Soup Bowl Lid</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0.0432692307692307</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4904,7 +5165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4972,12 +5233,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor pita chips parmesan garlic herb baked 400_0.4</t>
+          <t>doritos_doritos spicy nacho 7 11oz_0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -4985,16 +5246,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Pita Chips, Parmesan Garlic &amp; Herb, Baked | 400 g</t>
+          <t>DORITOS SPICY NACHO 7/11oz</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.614525139664805</v>
+        <v>6.81</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5011,12 +5272,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor tortilla chips yellow corn crispy round party size 13_0.37</t>
+          <t>gardner bender_dropped smart electrician cable tie ty wrap 4in_unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -5024,16 +5285,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Gardner Bender</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Tortilla Chips, Yellow Corn, Crispy Round, Party Size | 13 oz</t>
+          <t>DROPPED - SMART ELECTRICIAN CABLE TIE TY-WRAP 4in</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.184357541899441</v>
+        <v>1.67</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5050,12 +5311,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>goldfish_goldfish goldfish baked snack crackers cheddar 250_0.25</t>
+          <t>lay s_lays potato chips bbq 1oz_0.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5063,16 +5324,16 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Lay'S</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 250 g</t>
+          <t>LAYS POTATO CHIPS BBQ 1OZ</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.061452513966481</v>
+        <v>0.83</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5089,12 +5350,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo hartig kaas tomaat 14 2_0.4</t>
+          <t>lays_playstation drinkware bottle 410ml_unknown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5102,16 +5363,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO HARTIG KAAS/TOMAAT | 14.2 oz</t>
+          <t>PLAYSTATION DRINKWARE BOTTLE 410ml</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.396648044692737</v>
+        <v>6.7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5128,12 +5389,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo knoflookboterbaguette 16_0.45</t>
+          <t>lays_playstation lunch box_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5141,16 +5402,16 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO KNOFLOOKBOTERBAGUETTE | 16 oz</t>
+          <t>PLAYSTATION LUNCH BOX</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>9.324022346368716</v>
+        <v>7.82</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5167,12 +5428,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo meergranen biscuits bosvruchten 400_0.4</t>
+          <t>unknown_tapas wrap carpaccio 100g_0.1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5180,16 +5441,16 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO MEERGRANEN BISCUITS BOSVRUCHTEN | 400 g</t>
+          <t>TAPAS WRAP CARPACCIO 100G</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.016759776536313</v>
+        <v>7.87</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5211,7 +5472,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo puppy biscuits eend 125_0.12</t>
+          <t>badia_badia badia everything bagel seasoning 5 5_0.16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5219,16 +5480,16 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Badia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO PUPPY BISCUITS EEND | 125 g</t>
+          <t>Badia | Badia Everything Bagel Seasoning | 5.5 oz</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.675977653631285</v>
+        <v>3.513966480446927</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5250,7 +5511,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kinder_kinder kinder bueno milk chocolate and hazelnut cream 2 individually wrapped chocolate bars 11_0.31</t>
+          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks 9 ea_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -5258,16 +5519,16 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kinder</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kinder | Kinder Bueno Milk Chocolate and Hazelnut Cream, 2 Individually Wrapped Chocolate Bars, | 11 oz</t>
+          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks 9 ea</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.955307262569832</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5289,7 +5550,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lays_lays 24 pc lay s sour cream onion flavored potato crisps 5 5_0.16</t>
+          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 510_0.51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5297,16 +5558,16 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Lays | 24 pc Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
+          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 510 g</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>23.23463687150839</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5328,7 +5589,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lays_lays lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
+          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks party size 40 ea 7_0.2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5336,16 +5597,16 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lays | Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
+          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea | 7 oz</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.849162011173184</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5367,7 +5628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lu_lu cafe valley blueberry mini muffins_unknown</t>
+          <t>bigelow_bigelow 19 pc bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -5375,16 +5636,16 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>LU | CAFE VALLEY BLUEBERRY MINI MUFFINS</t>
+          <t>Bigelow | 19 pc Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.949720670391062</v>
+        <v>5.134078212290502</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5406,7 +5667,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>milka_milka milka mmmax chocoswing biscuit 225_0.22</t>
+          <t>club social_club social nabisco club social original 216_0.22</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5414,16 +5675,16 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Milka</t>
+          <t>Club Social</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Milka | MILKA MMMAX CHOCOSWING BISCUIT | 225 g</t>
+          <t>Club Social | NABISCO CLUB SOCIAL ORIGINAL | 216 g</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.452513966480447</v>
+        <v>2.005586592178771</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5445,7 +5706,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 8_0.23</t>
+          <t>crav n_crav n crav n flavor crackers original rich crisp 3 ea 250_0.25</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5453,16 +5714,16 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 8 oz</t>
+          <t>Crav'N | Crav'n Flavor Crackers, Original, Rich &amp; Crisp, 3 ea | 250 g</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.307262569832401</v>
+        <v>2.955307262569832</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5484,7 +5745,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo golden sandwich cookies 11 78_0.33</t>
+          <t>crav n_crav n crav n flavor tortilla chips white corn bite size round 13_0.37</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5492,16 +5753,16 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Oreo | OREO Golden Sandwich Cookies, | 11.78 oz</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Bite Size Round | 13 oz</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.770949720670391</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5523,7 +5784,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 13 29_0.38</t>
+          <t>crav n_crav n crav n flavor tortilla chips white corn restaurant style 300_0.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5531,16 +5792,16 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 13.29 oz</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Restaurant Style | 300 g</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.368715083798882</v>
+        <v>2.005586592178771</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5562,7 +5823,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles cheddar cheese 2 3_0.07</t>
+          <t>eggo_eggo eggo minis waffle 14 8_0.42</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -5570,16 +5831,16 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES CHEDDAR CHEESE | 2.3 oz</t>
+          <t>Eggo | EGGO MINIS WAFFLE | 14.8 oz</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.340782122905028</v>
+        <v>5.245810055865922</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5601,7 +5862,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles original 1 4_0.04</t>
+          <t>frito lay_frito lay 24 pc frito lay doritos nacho cheese_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5609,16 +5870,16 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES ORIGINAL | 1.4 oz</t>
+          <t>Frito-Lay | 24 pc FRITO LAY DORITOS NACHO CHEESE</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.558659217877095</v>
+        <v>23.23463687150839</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5640,7 +5901,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles potato crisps chips original grab n go 5 5_0.16</t>
+          <t>frito lay_frito lay frito lay bold mix 24 ea 5 5_0.16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5648,16 +5909,16 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pringles | Pringles Potato Crisps Chips, Original, Grab N' Go | 5.5 oz</t>
+          <t>Frito-Lay | Frito Lay Bold Mix 24 ea | 5.5 oz</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.681564245810056</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5679,7 +5940,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles sour cream onion 1 3_0.04</t>
+          <t>glad_glad 20 bg glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5687,16 +5948,16 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES SOUR CREAM &amp; ONION | 1.3 oz</t>
+          <t>Glad | 20 bg Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.558659217877095</v>
+        <v>5.575418994413408</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5718,7 +5979,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>toufayan_toufayan 6ct toufayan bakeries garlic pesto wraps_unknown</t>
+          <t>goldfish_goldfish goldfish baked snack crackers cheddar 260_0.26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5726,16 +5987,16 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Goldfish</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Toufayan | 6ct TOUFAYAN BAKERIES GARLIC PESTO WRAPS</t>
+          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 260 g</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.899441340782123</v>
+        <v>3.067039106145252</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5757,7 +6018,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>toufayan_toufayan toufayan bakeries pita sweet onion 7 33_0.21</t>
+          <t>jumbo_jumbo jumbo linzenwafel sweet chilli 190_0.19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -5765,16 +6026,16 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Toufayan | TOUFAYAN BAKERIES PITA SWEET ONION | 7.33 oz</t>
+          <t>Jumbo | JUMBO LINZENWAFEL SWEET CHILLI | 190 g</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.290502793296089</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5796,7 +6057,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 1 5_0.04</t>
+          <t>jumbo_jumbo jumbo marie biscuits 16 3_0.46</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -5804,16 +6065,16 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 1.5 oz</t>
+          <t>Jumbo | JUMBO MARIE BISCUITS | 16.3 oz</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.670391061452514</v>
+        <v>5.35754189944134</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -5835,7 +6096,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>unknown_bosvruchten muffin 24_0.68</t>
+          <t>jumbo_jumbo jumbo tortilla dip hot 9 75_0.28</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -5843,16 +6104,16 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BOSVRUCHTEN MUFFIN | 24 oz</t>
+          <t>Jumbo | JUMBO TORTILLA DIP HOT | 9.75 oz</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.251396648044693</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -5874,7 +6135,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_fjord knackebrod volkoren 6 6_0.19</t>
+          <t>kellogg_kellogg kellogg s eggo blueberry pancakes 450g_0.45</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -5882,16 +6143,16 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Kellogg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>FJORD KNACKEBROD VOLKOREN | 6.6 oz</t>
+          <t>Kellogg | KELLOGG'S EGGO BLUEBERRY PANCAKES | 450g</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.072625698324022</v>
+        <v>3.569832402234637</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5913,7 +6174,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_food for life ezekiel 4 9 bread cinnamon raisin 680_0.68</t>
+          <t>la dulcerita_la dulcerita 6 la dulcerita chocolate chip muffin_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -5921,16 +6182,16 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, CINNAMON RAISIN | 680 g</t>
+          <t>La Dulcerita | 6 ct LA DULCERITA CHOCOLATE CHIP MUFFIN</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>11.14525139664804</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5952,7 +6213,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_food for life flourless sprouted grain cinnamon raisin bread 29 6_0.84</t>
+          <t>lays_lays 24 pc lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -5960,16 +6221,16 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Food For Life Flourless Sprouted Grain Cinnamon Raisin Bread | 29.6 oz</t>
+          <t>Lays | 24 pc Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.02793296089386</v>
+        <v>23.23463687150839</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5991,7 +6252,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_udis sandwich bread soft white 24_0.68</t>
+          <t>lays_lays lay s sour cream onion flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -5999,16 +6260,16 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>UDIS SANDWICH BREAD, SOFT WHITE | 24 oz</t>
+          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>12.82122905027933</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -6030,7 +6291,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>wasa_wasa wasa knackebrod glutenvr sesam 260_0.26</t>
+          <t>lu_lu lu cracottes naturel 6 6_0.19</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -6038,16 +6299,16 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 260 g</t>
+          <t>LU | LU CRACOTTES NATUREL | 6.6 oz</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.067039106145252</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -6059,17 +6320,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_topper cake feliz cumpleanos silver_unknown</t>
+          <t>lu_lu tf blueberry bagel 567_0.57</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6077,16 +6338,16 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Topper Cake Feliz Cumpleanos Silver</t>
+          <t>LU | Tf Blueberry Bagel | 567 g</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.57</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -6098,17 +6359,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown_topper cake feliz cumpleanos wood_unknown</t>
+          <t>mcvitie s_mcvitie s mcvitie s digestive 14 2_0.4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6116,16 +6377,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mcvitie'S</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Topper Cake Feliz Cumpleanos Wood</t>
+          <t>McVitie's | MCVITIE'S DIGESTIVE | 14.2 oz</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.57</v>
+        <v>2.396648044692737</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -6137,17 +6398,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>unknown_topper cake happy birthday gold_unknown</t>
+          <t>noel_noel noel saltin noel extra large 454_0.45</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6155,16 +6416,16 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Topper Cake Happy Birthday Gold</t>
+          <t>Noel | NOEL SALTIN NOEL EXTRA LARGE | 454 g</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.57</v>
+        <v>6.474860335195531</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6176,17 +6437,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>unknown_topper cake happy birthday silver_unknown</t>
+          <t>pepperidge farm_pepperidge farm pepperidge farm goldfish snack crackers baked colors cheddar 300_0.3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6194,16 +6455,16 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pepperidge Farm</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Topper Cake Happy Birthday Silver</t>
+          <t>Pepperidge Farm | PEPPERIDGE FARM GOLDFISH SNACK CRACKERS, BAKED, COLORS CHEDDAR | 300 g</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.57</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6215,17 +6476,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>unknown_topper cake happy birthday star gold_unknown</t>
+          <t>pillsbury_pillsbury pillsbury crescents original 250_0.25</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -6233,16 +6494,16 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Topper Cake Happy Birthday Star Gold</t>
+          <t>Pillsbury | PILLSBURY CRESCENTS ORIGINAL | 250 g</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.57</v>
+        <v>6.675977653631285</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -6254,17 +6515,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>molino del sol_pan integral multigranos molino del sol_0.65</t>
+          <t>pillsbury_pillsbury pillsbury flaky layers honey butter biscuits 8 ea 300_0.3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -6272,16 +6533,16 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Molino Del Sol</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pan Integral Multigranos Molino Del Sol</t>
+          <t>Pillsbury | Pillsbury Flaky Layers Honey Butter Biscuits 8 ea | 300 g</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.33</v>
+        <v>8.87709497206704</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -6293,17 +6554,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pringles_papas fritas mini pringles original_0.04</t>
+          <t>pringles_pringles pringles original 1 3_0.04</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -6316,11 +6577,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Papas Fritas Mini Pringles Original</t>
+          <t>Pringles | PRINGLES ORIGINAL | 1.3 oz</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.09</v>
+        <v>1.558659217877095</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -6332,17 +6593,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown_chips bruschette sabor vegetales mediterraneos maretti_0.14</t>
+          <t>pringles_pringles pringles salty snacks potato crisps chips sour cream and onion flavored 5 2_0.15</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -6350,16 +6611,16 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Chips Bruschette Sabor Vegetales Mediterraneos Maretti</t>
+          <t>Pringles | PRINGLES SALTY SNACKS POTATO CRISPS CHIPS, SOUR CREAM AND ONION FLAVORED | 5.2 oz</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.96</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -6371,17 +6632,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>old el paso_old el paso shell tortilla 10 in_unknown</t>
+          <t>schar_schar schar hamburger buns 16_0.45</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -6389,16 +6650,16 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Old El Paso</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Old El Paso Shell Tortilla 10 In</t>
+          <t>Schar | SCHAR HAMBURGER BUNS, GLUTEN FREE | 16 oz</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.913461538461538</v>
+        <v>6.083798882681564</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6410,17 +6671,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>unknown_bobs red mill pancake mix_unknown</t>
+          <t>schar_schar schar white bread artisan baker 12 9oz_0.37</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6428,16 +6689,16 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bobs Red Mill Pancake Mix</t>
+          <t>Schar | SCHAR WHITE BREAD, GLUTEN FREE, ARTISAN BAKER | 12.9oz</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.91346153846154</v>
+        <v>9.46927374301676</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -6449,17 +6710,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unknown_sarojanie sugar cake 85g_0.08</t>
+          <t>schar_schar schar white bread artisan baker 24_0.68</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -6467,23 +6728,2012 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
+          <t>Schar</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schar | SCHAR WHITE BREAD, GLUTEN FREE, ARTISAN BAKER | 24 oz</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>7.201117318435754</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6 pc toufayan vegan everything bagels 6pc_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Toufayan | 6 pc TOUFAYAN VEGAN EVERYTHING BAGELS 6PC</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 11_0.31</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 11 oz</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>unknown_2 pc aardbeienslof_unknown</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sarojanie Sugar Cake 85g</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>1.201923076923077</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2 pc AARDBEIENSLOF</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>unknown_2 pk wei chuan spring rolls shells_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2 pk WEI-CHUAN SPRING ROLLS SHELLS</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>7.793296089385474</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>unknown_8 ea haagen dazs caramel biscuit and cream speculoos_unknown</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8 ea HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unknown_appeltaartje klein_unknown</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>APPELTAARTJE KLEIN</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>25.11173184357542</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unknown_coolback garlic butter baguette 309_0.31</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>COOLBACK GARLIC BUTTER BAGUETTE | 309 g</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>5.525139664804469</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unknown_each white chocolate raspberry klein_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>each WHITE CHOCOLATE RASPBERRY KLEIN</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>23.43575418994413</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>unknown_fjord knackebrod volkoren 250_0.25</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>FJORD KNACKEBROD VOLKOREN | 250 g</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>2.061452513966481</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unknown_food for life ezekiel 4 9 bread low sodium sprouted grain 14 1_0.4</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, LOW SODIUM, SPROUTED GRAIN | 14.1 oz</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>10.55307262569832</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unknown_french bread white 14 1_0.4</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>FRENCH BREAD WHITE | 14.1 oz</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>10.55307262569832</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unknown_koopmans deeg hartige taart 11_0.31</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>KOOPMANS DEEG HARTIGE TAART | 11 oz</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unknown_lemon muffin 24_0.68</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LEMON MUFFIN | 24 oz</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>7.251396648044693</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unknown_tex mex mini tortilla original 250g_0.25</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>TEX MEX MINI TORTILLA ORIGINAL | 250g</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>5.525139664804469</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unknown_tiramisu gebak_unknown</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>TIRAMISU GEBAK</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>3.569832402234637</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa dun rogge volkoren 13 7_0.39</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>WASA | WASA DUN ROGGE VOLKOREN | 13.7 oz</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>3.290502793296089</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa knackebrod glutenvr sesam 6 6_0.19</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 6.6 oz</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>4.072625698324022</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa vezelrijk 240_0.24</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>WASA | WASA VEZELRIJK | 240 g</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>6.698324022346369</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa volkoren 250_0.25</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>WASA | WASA VOLKOREN | 250 g</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>1.893854748603352</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>loacker_galleta wafers loacker sabor a napolitaner_0.04</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Loacker</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Galleta Wafers Loacker Sabor A Napolitaner</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>aviva_galleta de soda saltina aviva 20 und_0.6</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Aviva</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Galleta De Soda Saltina Aviva 20 Und</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez crackers dixee 3pk_unknown</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bermudez Crackers Dixee 3pk</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez multigrain crix crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>BERMUDEZ  MULTIGRAIN CRIX CRACKERS</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>7.115384615384615</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez rough tops_unknown</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Bermudez Rough Tops</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>0.5288461538461539</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>bermudez_bermudez whole wheat crix crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Bermudez</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Bermudez Whole Wheat Crix Crackers</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>7.115384615384615</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>devon_devon rolls chocolate chips 200 gr_0.2</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Devon Rolls Chocolate Chips 200 gr</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>festival_festival cookie chips_unknown</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Festival Cookie Chips</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>3.365384615384615</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate cookies 12x50g_0.6</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Noel Festival Chocolate Cookies 12x50g</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>4.423076923076923</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>festival_noel festival strawberry 12x32g_0.38</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Noel Festival Strawberry 12x32g</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>3.942307692307693</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>festival_noel festival strawberry cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Noel Festival Strawberry Cookies</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0.4807692307692308</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>festival_noel festival vanilla 12x32g_0.38</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Noel Festival Vanilla 12x32g</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>4.038461538461538</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>knotts_knotts raspberry short bread_unknown</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Knotts</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Knotts Raspberry Short Bread</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>knotts_knotts strawbery short bread_unknown</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Knotts</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Knotts Strawbery Short Bread</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>other_nutella and go pretzel sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Nutella And Go Pretzel Sticks</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>2.644230769230769</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ovaltine_ovaltine biscuits_unknown</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ovaltine</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OVALTINE BISCUITS</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm bordeaux cookies 6 75_0.19</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Bordeaux Cookies 6.75 Oz</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>4.951923076923077</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm double chocolate dark choc cookie 7 75oz_0.22</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Double Chocolate Dark Choc Cookie 7.75oz</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>6.346153846153846</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm goldfish cheddar 6 6oz_0.19</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Goldfish Cheddar 6.6oz</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>4.278846153846154</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano double dark chocolate 7 75oz_0.22</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Double Dark Chocolate 7.75oz</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano milk chocolate 6oz_0.17</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Milk Chocolate 6oz</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano orange chocolate 7oz_0.2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Orange Chocolate 7oz</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>5.769230769230769</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano raspberry chocolate 7oz_0.2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Raspberry Chocolate 7oz</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>6.009615384615385</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm strawberry cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>PEPPERIDGE FARM STRAWBERRY COOKIES</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>6.538461538461538</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm white choc macadamia 7 2oz_0.2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm White Choc Macadamia 7.2oz</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Butter Crackers</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>4.182692307692307</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SHOON FATT BUTTER CRACKERS</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1.778846153846154</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt veggie crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Veggie Crackers</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>3.557692307692307</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>tiffany_tiffany choco chip cookies_unknown</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Tiffany</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>TIFFANY CHOCO CHIP COOKIES</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0.9134615384615384</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>walkers_walkers chocolate chip shortbread_unknown</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Walkers Chocolate Chip Shortbread</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>8.076923076923077</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>walkers_walkers piper dancer tin shortbread assorted 150g_0.15</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>WALKERS PIPER &amp; DANCER TIN SHORTBREAD ASSORTED 150G</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>14.61538461538462</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>walkers_walkers shortbread rounds_unknown</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Walkers Shortbread Rounds</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>5.865384615384615</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,39 +483,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo golden sandwich cookies 13 29_0.38</t>
+          <t>doritos_doritos minis nacho cheese 5 12_0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
+          <t>DORITOS MINIS NACHO CHEESE 5.12 oz</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>8.039106145251397</v>
+        <v>3.63</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
+          <t>DORITOS MINIS NACHO CHEESE 5.12 oz</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7.368715083798882</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>9.097801364670213</v>
+        <v>-5.714285714285719</v>
       </c>
     </row>
     <row r="3">
@@ -534,39 +534,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo mini cookies snak saks 13 29_0.38</t>
+          <t>essential everyday_ee oreo original creme cookies 14 3oz_0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Essential Everyday</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oreo | OREO MINI COOKIES SNAK-SAKS | 13.29 oz</t>
+          <t>EE OREO ORIGINAL CREME COOKIES 14.3oz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7.089385474860335</v>
+        <v>4.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Essential Everyday</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Oreo | OREO MINI COOKIES SNAK-SAKS | 13.29 oz</t>
+          <t>EE OREO ORIGINAL CREME COOKIES 14.3oz</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>8.039106145251397</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-11.8137595552467</v>
+        <v>-9.433962264150944</v>
       </c>
     </row>
     <row r="4">
@@ -585,39 +585,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>unknown_bosvruchten muffin_unknown</t>
+          <t>essential everyday_ee plastic wrap 200sq ft_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Essential Everyday</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BOSVRUCHTEN MUFFIN</t>
+          <t>EE PLASTIC WRAP 200sq ft</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>29.58100558659218</v>
+        <v>4.07</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Essential Everyday</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BOSVRUCHTEN MUFFIN</t>
+          <t>EE PLASTIC WRAP 200sq ft</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.949720670391062</v>
+        <v>3.57</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1417.191977077364</v>
+        <v>14.00560224089637</v>
       </c>
     </row>
     <row r="5">
@@ -636,12 +636,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>unknown_pruimentaart klein_unknown</t>
+          <t>unknown_diana tortilla nacho chips 3 52_0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -651,11 +651,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PRUIMENTAART KLEIN</t>
+          <t>DIANA TORTILLA NACHO CHIPS 3.52 OZ</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>25.11173184357542</v>
+        <v>2.73</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -664,11 +664,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PRUIMENTAART KLEIN</t>
+          <t>DIANA TORTILLA NACHO CHIPS 3.52 OZ</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>18.40782122905028</v>
+        <v>2.56</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,50 +676,50 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>36.41881638846737</v>
+        <v>6.640624999999997</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_vruchtenschelp_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VRUCHTENSCHELP</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.569832402234637</v>
+        <v>1.63</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>VRUCHTENSCHELP</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.324022346368715</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7.394957983193262</v>
+        <v>-20.09803921568628</v>
       </c>
     </row>
     <row r="7">
@@ -738,39 +738,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>carrefour_pan tostado carrefour bio_0.25</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pan Tostado Carrefour Bio</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pan Tostado Carrefour Bio</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>10.96491228070176</v>
+        <v>25.15337423312884</v>
       </c>
     </row>
     <row r="8">
@@ -789,39 +789,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carrefour</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tostitos_chips de tortillas de maiz tostitos santa elena_0.43</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.33</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Chips De Tortillas De Maiz Tostitos Santa Elena</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.88</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>-14.17525773195876</v>
+        <v>-46.23287671232876</v>
       </c>
     </row>
     <row r="9">
@@ -840,39 +840,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,50 +880,50 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-20.09803921568628</v>
+        <v>85.98726114649681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.04</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.63</v>
+        <v>0.3125</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,50 +931,50 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>25.15337423312884</v>
+        <v>1007.692307692308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>0.3125</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,50 +982,50 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>-46.23287671232876</v>
+        <v>-90.97222222222221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.92</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.57</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>85.98726114649681</v>
+        <v>152.0833333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1049,34 +1049,34 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.461538461538462</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3125</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1007.692307692308</v>
+        <v>-60.33057851239671</v>
       </c>
     </row>
     <row r="14">
@@ -1100,34 +1100,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.3125</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.461538461538462</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>-90.97222222222221</v>
+        <v>-91.46341463414633</v>
       </c>
     </row>
     <row r="15">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5.817307692307693</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.307692307692307</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>152.0833333333334</v>
+        <v>1071.428571428572</v>
       </c>
     </row>
     <row r="16">
@@ -1202,34 +1202,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.307692307692307</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.817307692307693</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>-60.33057851239671</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="17">
@@ -1253,34 +1253,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.3365384615384615</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.942307692307693</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>-91.46341463414633</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="18">
@@ -1304,34 +1304,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.942307692307693</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3365384615384615</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1071.428571428572</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1365,32 +1365,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>4.086538461538462</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kugi</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.682692307692308</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Kugi</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>4.086538461538462</v>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>-58.82352941176471</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="20">
@@ -1406,34 +1406,34 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.086538461538462</v>
+        <v>29.08653846153846</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.682692307692308</v>
+        <v>15.04807692307692</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>142.8571428571429</v>
+        <v>93.29073482428115</v>
       </c>
     </row>
     <row r="21">
@@ -1457,34 +1457,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.682692307692308</v>
+        <v>15.04807692307692</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>New York Style</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.086538461538462</v>
+        <v>29.08653846153846</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>-58.82352941176471</v>
+        <v>-48.26446280991735</v>
       </c>
     </row>
     <row r="22">
@@ -1508,34 +1508,34 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.086538461538462</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.682692307692308</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>142.8571428571429</v>
+        <v>70.19230769230769</v>
       </c>
     </row>
     <row r="23">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>pringles_pringles pizza_unknown</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Pringles Pizza</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>29.08653846153846</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Pringles</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>PRINGLES PIZZA</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>15.04807692307692</v>
+        <v>4.254807692307693</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>93.29073482428115</v>
+        <v>-41.24293785310735</v>
       </c>
     </row>
     <row r="24">
@@ -1610,34 +1610,34 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15.04807692307692</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>29.08653846153846</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>-48.26446280991735</v>
+        <v>494.7368421052633</v>
       </c>
     </row>
     <row r="25">
@@ -1661,34 +1661,34 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>SHOON FATT CREAM CRACKERS</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.254807692307693</v>
+        <v>1.826923076923077</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Shoon Fatt Cream Crackers</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>10.86538461538462</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>70.19230769230769</v>
+        <v>-83.18584070796462</v>
       </c>
     </row>
     <row r="26">
@@ -1712,34 +1712,34 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.254807692307693</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>-41.24293785310735</v>
+        <v>24.99999999999997</v>
       </c>
     </row>
     <row r="27">
@@ -1763,34 +1763,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10.86538461538462</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.826923076923077</v>
+        <v>0.625</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>494.7368421052633</v>
+        <v>169.2307692307692</v>
       </c>
     </row>
     <row r="28">
@@ -1814,34 +1814,34 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.826923076923077</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Triskits</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10.86538461538462</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>-83.18584070796462</v>
+        <v>-19.99999999999998</v>
       </c>
     </row>
     <row r="29">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.682692307692308</v>
+        <v>1.346153846153846</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.346153846153846</v>
+        <v>0.625</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>24.99999999999997</v>
+        <v>115.3846153846154</v>
       </c>
     </row>
     <row r="30">
@@ -1930,28 +1930,28 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>1.682692307692308</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>0.625</v>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>169.2307692307692</v>
+        <v>-62.85714285714285</v>
       </c>
     </row>
     <row r="31">
@@ -1981,180 +1981,27 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>1.346153846153846</v>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1.682692307692308</v>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>-19.99999999999998</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>115.3846153846154</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>1.682692307692308</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>-62.85714285714285</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Triskits</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>1.346153846153846</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
         <v>-53.57142857142858</v>
       </c>
     </row>
@@ -2169,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2237,26 +2084,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fritolay_lays argentina asado 1 13oz_0.03</t>
+          <t>club social_club social nabisco club social original 216_0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Club Social</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LAYS ARGENTINA ASADO 1.13OZ</t>
+          <t>Club Social | NABISCO CLUB SOCIAL ORIGINAL | 216 g</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.89</v>
+        <v>2.005586592178771</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2276,26 +2123,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fritolay_lays argentina asado 3 7oz_0.1</t>
+          <t>lays_lays lay s lays salt vinegar 6 5_0.18</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LAYS ARGENTINA ASADO 3.7OZ</t>
+          <t>Lays | Lay's Lays Salt/Vinegar | 6.5 oz</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.51</v>
+        <v>3.905027932960894</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2315,26 +2162,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fritolay_lays mexico taco 1 13oz_0.03</t>
+          <t>noel_noel noel saltin noel extra large 454_0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LAYS MEXICO TACO 1.13OZ</t>
+          <t>Noel | NOEL SALTIN NOEL EXTRA LARGE | 454 g</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>6.474860335195531</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2354,26 +2201,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fritolay_lays mexico taco 3 7oz_0.1</t>
+          <t>unknown_tex mex mini tortilla original 250g_0.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Fritolay</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LAYS MEXICO TACO 3.7OZ</t>
+          <t>TEX MEX MINI TORTILLA ORIGINAL | 250g</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.51</v>
+        <v>5.525139664804469</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -2388,31 +2235,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>unknown_64lts led light multi twinkle shimmering sphere burts silver wrap 12in_unknown</t>
+          <t>bon_paleta bon de bizcocho_unknown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bon</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>64LTS LED LIGHT MULTI TWINKLE SHIMMERING SPHERE BURTS SILVER WRAP 12in</t>
+          <t>Paleta Bon De Bizcocho</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23.46</v>
+        <v>0.71</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -2427,31 +2274,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_64lts led light pure white twinkle shimmering sphere burts silver wrap 12in_unknown</t>
+          <t>bagel bites_oreida bagel bites pizza snacks three cheese_unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>64LTS LED LIGHT PURE WHITE TWINKLE SHIMMERING SPHERE BURTS SILVER WRAP 12in</t>
+          <t>Oreida Bagel Bites Pizza Snacks Three Cheese</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23.46</v>
+        <v>13.65384615384615</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -2466,31 +2313,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_64lts led light warm white twinkle shimmering sphere burts silver wrap 12in_unknown</t>
+          <t>bermudez_bermudez crackers dixee 3pk_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>64LTS LED LIGHT WARM WHITE TWINKLE SHIMMERING SPHERE BURTS SILVER WRAP 12in</t>
+          <t>Bermudez Crackers Dixee 3pk</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23.46</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -2505,31 +2352,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_80lts led light champagne twinkle starlight burts gold wrap 16in_unknown</t>
+          <t>bermudez_bermudez multigrain crix crackers_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80LTS LED LIGHT CHAMPAGNE TWINKLE STARLIGHT BURTS GOLD WRAP 16in</t>
+          <t>BERMUDEZ  MULTIGRAIN CRIX CRACKERS</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>31.84</v>
+        <v>7.115384615384615</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -2544,31 +2391,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unknown_zacks tortilla chili lime chips 6_0.17</t>
+          <t>bermudez_bermudez rough tops_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ZACKS' TORTILLA CHILI LIME CHIPS 6 OZ</t>
+          <t>Bermudez Rough Tops</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.03</v>
+        <v>0.5288461538461539</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -2583,31 +2430,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>badia_badia badia everything bagel seasoning 6 78_0.19</t>
+          <t>bermudez_bermudez whole wheat crix crackers_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Badia | Badia Everything Bagel Seasoning | 6.78 oz</t>
+          <t>Bermudez Whole Wheat Crix Crackers</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.513966480446927</v>
+        <v>7.115384615384615</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -2622,31 +2469,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks party size 40 ea_unknown</t>
+          <t>devon_devon rolls chocolate chips 200 gr_0.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Devon</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea</t>
+          <t>Devon Rolls Chocolate Chips 200 gr</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.184357541899441</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -2661,31 +2508,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 7_0.2</t>
+          <t>festival_festival cookie chips_unknown</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 7 oz</t>
+          <t>Festival Cookie Chips</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4.184357541899441</v>
+        <v>3.365384615384615</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -2700,31 +2547,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks 9 ea 510_0.51</t>
+          <t>festival_noel festival chocolate cookies 12x50g_0.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks 9 ea | 510 g</t>
+          <t>Noel Festival Chocolate Cookies 12x50g</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.849162011173184</v>
+        <v>4.423076923076923</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -2739,31 +2586,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bigelow_bigelow bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea 12 67_0.36</t>
+          <t>festival_noel festival strawberry 12x32g_0.38</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bigelow | Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea | 12.67 oz</t>
+          <t>Noel Festival Strawberry 12x32g</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14.24022346368715</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -2778,31 +2625,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>crav n_crav n 12 ea crav n flavor tortilla chips white corn bite size round 13_0.37</t>
+          <t>festival_noel festival strawberry cookies_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crav'N | 12 ea Crav'n Flavor Tortilla Chips, White Corn, Bite Size Round | 13 oz</t>
+          <t>Noel Festival Strawberry Cookies</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>7.234636871508379</v>
+        <v>0.4807692307692308</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -2817,31 +2664,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor crackers original rich crisp 3 ea 190_0.19</t>
+          <t>festival_noel festival vanilla 12x32g_0.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Crackers, Original, Rich &amp; Crisp, 3 ea | 190 g</t>
+          <t>Noel Festival Vanilla 12x32g</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.681564245810056</v>
+        <v>4.038461538461538</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -2856,31 +2703,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eggo_eggo eggo minis waffle 11_0.31</t>
+          <t>knotts_knotts raspberry short bread_unknown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eggo | EGGO MINIS WAFFLE | 11 oz</t>
+          <t>Knotts Raspberry Short Bread</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.899441340782123</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -2895,31 +2742,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>frito lay_frito lay 24 pc frito lay bold mix 24 ea_unknown</t>
+          <t>knotts_knotts strawbery short bread_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Knotts</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Frito-Lay | 24 pc Frito Lay Bold Mix 24 ea</t>
+          <t>Knotts Strawbery Short Bread</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>23.23463687150839</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -2934,31 +2781,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>frito lay_frito lay frito lay doritos nacho cheese 5 5_0.16</t>
+          <t>lu_kimberleys frosted sugar cookies blue_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Frito-Lay | FRITO LAY DORITOS NACHO CHEESE | 5.5 oz</t>
+          <t>Kimberleys Frosted Sugar Cookies Blue</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.122905027932961</v>
+        <v>7.548076923076923</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -2973,31 +2820,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>glad_glad 19 pc glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
+          <t>other_nutella and go pretzel sticks_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glad | 19 pc Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
+          <t>Nutella And Go Pretzel Sticks</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.134078212290502</v>
+        <v>2.644230769230769</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -3012,31 +2859,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo linzenwafel sweet chilli 13 7_0.39</t>
+          <t>ovaltine_ovaltine biscuits_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Ovaltine</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO LINZENWAFEL SWEET CHILLI | 13.7 oz</t>
+          <t>OVALTINE BISCUITS</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.290502793296089</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -3051,31 +2898,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo marie biscuits 300_0.3</t>
+          <t>pepperidge_pepperidge farm bordeaux cookies 6 75_0.19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO MARIE BISCUITS | 300 g</t>
+          <t>Pepperidge Farm Bordeaux Cookies 6.75 Oz</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.87709497206704</v>
+        <v>4.951923076923077</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -3090,31 +2937,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo tortilla dip hot 300_0.3</t>
+          <t>pepperidge_pepperidge farm double chocolate dark choc cookie 7 75oz_0.22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO TORTILLA DIP HOT | 300 g</t>
+          <t>Pepperidge Farm Double Chocolate Dark Choc Cookie 7.75oz</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.005586592178771</v>
+        <v>6.346153846153846</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -3129,31 +2976,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kellogg_kellogg 2 pk kellogg s eggo blueberry pancakes_unknown</t>
+          <t>pepperidge_pepperidge farm goldfish cheddar 6 6oz_0.19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kellogg</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kellogg | 2 pk KELLOGG'S EGGO BLUEBERRY PANCAKES</t>
+          <t>Pepperidge Farm Goldfish Cheddar 6.6oz</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.793296089385474</v>
+        <v>4.278846153846154</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -3168,31 +3015,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita la dulcerita chocolate chip muffin_unknown</t>
+          <t>pepperidge_pepperidge farm milano double dark chocolate 7 75oz_0.22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>La Dulcerita | LA DULCERITA CHOCOLATE CHIP MUFFIN</t>
+          <t>Pepperidge Farm Milano Double Dark Chocolate 7.75oz</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.949720670391062</v>
+        <v>6.490384615384615</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -3207,31 +3054,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lays_lays 24 pc lay s sour cream onion flavored potato crisps 5 5_0.16</t>
+          <t>pepperidge_pepperidge farm milano milk chocolate 6oz_0.17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lays | 24 pc Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
+          <t>Pepperidge Farm Milano Milk Chocolate 6oz</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>23.23463687150839</v>
+        <v>6.490384615384615</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -3246,31 +3093,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lays_lays lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
+          <t>pepperidge_pepperidge farm milano orange chocolate 7oz_0.2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lays | Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
+          <t>Pepperidge Farm Milano Orange Chocolate 7oz</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.849162011173184</v>
+        <v>5.769230769230769</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -3285,31 +3132,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>lu_lu 6 pc tf blueberry bagel_unknown</t>
+          <t>pepperidge_pepperidge farm milano raspberry chocolate 7oz_0.2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LU | 6 pc Tf Blueberry Bagel</t>
+          <t>Pepperidge Farm Milano Raspberry Chocolate 7oz</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.184357541899441</v>
+        <v>6.009615384615385</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -3324,31 +3171,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lu_lu lu cracottes naturel 250_0.25</t>
+          <t>pepperidge_pepperidge farm strawberry cookies_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LU | LU CRACOTTES NATUREL | 250 g</t>
+          <t>PEPPERIDGE FARM STRAWBERRY COOKIES</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.893854748603352</v>
+        <v>6.538461538461538</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -3363,31 +3210,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>noel_noel 6 ea noel dux saltines crackers_unknown</t>
+          <t>pepperidge_pepperidge farm white choc macadamia 7 2oz_0.2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Pepperidge</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Noel | 6 ea NOEL DUX SALTINES CRACKERS</t>
+          <t>Pepperidge Farm White Choc Macadamia 7.2oz</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6.865921787709497</v>
+        <v>6.490384615384615</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -3402,31 +3249,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm goldfish snack crackers baked colors cheddar 250_0.25</t>
+          <t>shoon_shoon fatt butter crackers_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM GOLDFISH SNACK CRACKERS, BAKED, COLORS CHEDDAR | 250 g</t>
+          <t>Shoon Fatt Butter Crackers</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.061452513966481</v>
+        <v>4.182692307692307</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -3441,31 +3288,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm texas toast frozen garlic bread 8 slices box 14 2_0.4</t>
+          <t>shoon_shoon fatt veggie crackers_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | Pepperidge Farm® Texas Toast Frozen Garlic Bread, 8 Slices, . Box | 14.2 oz</t>
+          <t>Shoon Fatt Veggie Crackers</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9.770949720670391</v>
+        <v>3.557692307692307</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -3480,31 +3327,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury 8 ea pillsbury flaky layers honey butter biscuits 8 ea_unknown</t>
+          <t>tiffany_tiffany choco chip cookies_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pillsbury | 8 ea Pillsbury Flaky Layers Honey Butter Biscuits 8 ea</t>
+          <t>TIFFANY CHOCO CHIP COOKIES</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5.35754189944134</v>
+        <v>0.9134615384615384</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -3519,31 +3366,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury pillsbury crescents original 16_0.45</t>
+          <t>unknown_kimberleys frosted sugar cookies pink_unknown</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pillsbury | PILLSBURY CRESCENTS ORIGINAL | 16 oz</t>
+          <t>Kimberleys Frosted Sugar Cookies Pink</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6.083798882681564</v>
+        <v>7.548076923076923</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -3558,31 +3405,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles original 2 5_0.07</t>
+          <t>unknown_merba triple chocolate cookies_unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES ORIGINAL | 2.5 oz</t>
+          <t>Merba Triple Chocolate Cookies</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.340782122905028</v>
+        <v>4.759615384615385</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -3597,31 +3444,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles salty snacks potato crisps chips sour cream and onion flavored 5 3_0.15</t>
+          <t>walkers_walkers chocolate chip shortbread_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES SALTY SNACKS POTATO CRISPS CHIPS, SOUR CREAM AND ONION FLAVORED | 5.3 oz</t>
+          <t>Walkers Chocolate Chip Shortbread</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.681564245810056</v>
+        <v>8.076923076923077</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -3636,31 +3483,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles sour cream onion 1 3_0.04</t>
+          <t>walkers_walkers piper dancer tin shortbread assorted 150g_0.15</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES SOUR CREAM &amp; ONION | 1.3 oz</t>
+          <t>WALKERS PIPER &amp; DANCER TIN SHORTBREAD ASSORTED 150G</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.558659217877095</v>
+        <v>14.61538461538462</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -3675,31 +3522,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Massy Stores Guyana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>schar_schar schar hamburger buns 8_0.23</t>
+          <t>walkers_walkers shortbread rounds_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>Walkers</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Schar | SCHAR HAMBURGER BUNS, GLUTEN FREE | 8 oz</t>
+          <t>Walkers Shortbread Rounds</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5.35754189944134</v>
+        <v>5.865384615384615</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -3710,1449 +3557,6 @@
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>toufayan_toufayan 6 ea toufayan bakeries wholesome wheat wraps_unknown</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Toufayan</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Toufayan | 6 ea TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>2.955307262569832</v>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>toufayan_toufayan toufayan plain bagels 567_0.57</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Toufayan</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Toufayan | TOUFAYAN PLAIN BAGELS | 567 g</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>4.184357541899441</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>unknown_2 pc tiramisu gebak_unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2 pc TIRAMISU GEBAK</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>3.899441340782123</v>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>unknown_6 lemon muffin_unknown</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>6 ct LEMON MUFFIN</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>5.301675977653631</v>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>unknown_aardbeienslof_unknown</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AARDBEIENSLOF</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>3.324022346368715</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>unknown_bosvruchten muffin 24_0.68</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>BOSVRUCHTEN MUFFIN | 24 oz</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>7.251396648044693</v>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>unknown_coolback garlic butter baguette 450g_0.45</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>COOLBACK GARLIC BUTTER BAGUETTE | 450g</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>3.569832402234637</v>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>unknown_each appeltaartje klein_unknown</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>each APPELTAARTJE KLEIN</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>23.43575418994413</v>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>unknown_fjord knackebrod volkoren 240_0.24</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>FJORD KNACKEBROD VOLKOREN | 240 g</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>6.698324022346369</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>unknown_food for life ezekiel 4 9 bread low sodium sprouted grain 12 9oz_0.37</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, LOW SODIUM, SPROUTED GRAIN | 12.9oz</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>9.46927374301676</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>unknown_food for life sprouted corn tortillas 9 75_0.28</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>FOOD FOR LIFE SPROUTED CORN TORTILLAS | 9.75 oz</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>3.849162011173184</v>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>unknown_french bread white 24_0.68</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>FRENCH BREAD WHITE | 24 oz</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>7.201117318435754</v>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>unknown_haagen dazs caramel biscuit and cream speculoos 16 3_0.46</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS | 16.3 oz</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>5.35754189944134</v>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>unknown_koopmans deeg hartige taart 309_0.31</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>KOOPMANS DEEG HARTIGE TAART | 309 g</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>5.525139664804469</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>unknown_wei chuan spring rolls shells 14 8_0.42</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>WEI-CHUAN SPRING ROLLS SHELLS | 14.8 oz</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>5.245810055865922</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>unknown_white chocolate raspberry klein_unknown</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>WHITE CHOCOLATE RASPBERRY KLEIN</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>18.40782122905028</v>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>verkade_verkade verkade nizza 14 2_0.4</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Verkade</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Verkade | VERKADE NIZZA | 14.2 oz</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>2.396648044692737</v>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>wasa_wasa wasa dun rogge volkoren 300_0.3</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Wasa</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>WASA | WASA DUN ROGGE VOLKOREN | 300 g</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>3.290502793296089</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>wasa_wasa wasa knackebrod glutenvr sesam 260_0.26</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Wasa</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 260 g</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>3.067039106145252</v>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>wasa_wasa wasa vezelrijk 250_0.25</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Wasa</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>WASA | WASA VEZELRIJK | 250 g</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>2.955307262569832</v>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Aruba</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Super Food Aruba</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>wasa_wasa wasa volkoren 6 6_0.19</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Wasa</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>WASA | WASA VOLKOREN | 6.6 oz</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>3.849162011173184</v>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>unknown_topper cake feliz cumpleanos silver_unknown</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Topper Cake Feliz Cumpleanos Silver</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>unknown_topper cake feliz cumpleanos wood_unknown</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Topper Cake Feliz Cumpleanos Wood</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>unknown_topper cake happy birthday gold_unknown</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Topper Cake Happy Birthday Gold</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>unknown_topper cake happy birthday silver_unknown</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Topper Cake Happy Birthday Silver</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Merca Jumbo</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>unknown_topper cake happy birthday star gold_unknown</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Topper Cake Happy Birthday Star Gold</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>lumijor_pan integral familiar lumijor_0.85</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Lumijor</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Pan Integral Familiar Lumijor</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Plaza Lama</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>molino del sol_pan viga integral con germen de trigo molino del sol_0.62</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Molino Del Sol</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Pan Viga Integral Con Germen De Trigo Molino Del Sol</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>pringles_papas sabor bbq pringles_0.04</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Papas Sabor Bbq Pringles</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>pringles_papitas sabor crema agria y cebolla pringles_0.04</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Papitas Sabor Crema Agria Y Cebolla Pringles</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Sirena</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>pringles_papitas sabor queso pringles_0.04</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Pringles</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Papitas Sabor Queso Pringles</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>bermudez_bermudez crix crackers original_unknown</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Bermudez</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Bermudez Crix Crackers Original</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>7.163461538461538</v>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>devon_devon biscuits digestive 250 gr_0.25</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Devon</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Devon Biscuits Digestive 250 gr</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>2.067307692307693</v>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>lu_canyon country white_unknown</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Canyon Gluten Free Country White</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>9.85576923076923</v>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>unknown_fritos brand twista honey bbq_unknown</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Fritos Brand Twista Honey Bbq</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1.923076923076923</v>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>unknown_sarojanie sugar cake 85g_0.08</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Sarojanie Sugar Cake 85g</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1.201923076923077</v>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>unknown_wj soup bowl lid_unknown</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Wj Soup Bowl Lid</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>0.0432692307692307</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>left_only</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5165,7 +3569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5233,12 +3637,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>doritos_doritos spicy nacho 7 11oz_0.31</t>
+          <t>lays_lays lay s potato chips salt vinegar flavored 6 1 6 5_0.18</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -5246,16 +3650,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DORITOS SPICY NACHO 7/11oz</t>
+          <t>Lays | Lay's Potato Chips Salt &amp; Vinegar Flavored 6 1/ | 6.5 oz</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.81</v>
+        <v>3.905027932960894</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -5267,17 +3671,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gardner bender_dropped smart electrician cable tie ty wrap 4in_unknown</t>
+          <t>bravo_bravo pan viga brioche_0.8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -5285,16 +3689,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gardner Bender</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DROPPED - SMART ELECTRICIAN CABLE TIE TY-WRAP 4in</t>
+          <t>Bravo Pan Viga Brioche</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -5306,17 +3710,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lay s_lays potato chips bbq 1oz_0.03</t>
+          <t>bravo_bravo pan viga linaza_0.8</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -5324,16 +3728,16 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay'S</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LAYS POTATO CHIPS BBQ 1OZ</t>
+          <t>Bravo Pan Viga Linaza</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.83</v>
+        <v>1.89</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -5345,17 +3749,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lays_playstation drinkware bottle 410ml_unknown</t>
+          <t>bravo_bravo pan viga papa_0.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -5363,16 +3767,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>PLAYSTATION DRINKWARE BOTTLE 410ml</t>
+          <t>Bravo Pan Viga Papa</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.7</v>
+        <v>1.57</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -5384,17 +3788,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lays_playstation lunch box_unknown</t>
+          <t>schar_pan de viga rustico sin schar_0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -5402,16 +3806,16 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>PLAYSTATION LUNCH BOX</t>
+          <t>Pan De Viga Rustico Sin Gluten Schar</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7.82</v>
+        <v>4.04</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -5423,17 +3827,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_tapas wrap carpaccio 100g_0.1</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -5441,16 +3845,16 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TAPAS WRAP CARPACCIO 100G</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7.87</v>
+        <v>2.36</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -5462,17 +3866,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>badia_badia badia everything bagel seasoning 5 5_0.16</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -5480,16 +3884,16 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Badia</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Badia | Badia Everything Bagel Seasoning | 5.5 oz</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.513966480446927</v>
+        <v>1.55</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -5501,17 +3905,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites 7z bagel bites three cheese pizza snacks 9 ea_unknown</t>
+          <t>unknown_dulce sandwich de naranja con leche rodriguez_0.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -5519,16 +3923,16 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bagel Bites | 7z Bagel Bites Three Cheese Pizza Snacks 9 ea</t>
+          <t>Dulce Sandwich De Naranja Con Leche Rodriguez</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.184357541899441</v>
+        <v>2.61</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5540,17 +3944,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites cheese pepperoni pizza snacks 510_0.51</t>
+          <t>club social_club social galleta mantequilla_0.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -5558,16 +3962,16 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Club Social</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bagel Bites | BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS | 510 g</t>
+          <t>Club Social Galleta Mantequilla</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.849162011173184</v>
+        <v>1.43</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -5579,17 +3983,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bagel bites_bagel bites bagel bites three cheese pizza snacks party size 40 ea 7_0.2</t>
+          <t>jumbo_parreiro pan viga jumbo natural_unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -5597,16 +4001,16 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bagel Bites</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bagel Bites | Bagel Bites Three Cheese Pizza Snacks Party Size 40 ea | 7 oz</t>
+          <t>Parreiro Pan Viga Jumbo Natural</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.184357541899441</v>
+        <v>3.57</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -5618,17 +4022,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bigelow_bigelow 19 pc bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea_unknown</t>
+          <t>lumijor_pan viga club personal lumijor_0.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -5636,16 +4040,16 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bigelow</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bigelow | 19 pc Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea</t>
+          <t>Pan Viga Club Personal Lumijor</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5.134078212290502</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -5657,17 +4061,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>club social_club social nabisco club social original 216_0.22</t>
+          <t>molino del sol_viga de pan mediana molino del sol_0.78</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5675,16 +4079,16 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Club Social</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Club Social | NABISCO CLUB SOCIAL ORIGINAL | 216 g</t>
+          <t>Viga De Pan Mediana Molino Del Sol</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.005586592178771</v>
+        <v>2.14</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -5696,17 +4100,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor crackers original rich crisp 3 ea 250_0.25</t>
+          <t>pepin_pan para hot dog pepin_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5714,16 +4118,16 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Crackers, Original, Rich &amp; Crisp, 3 ea | 250 g</t>
+          <t>Pan Para Hot Dog Pepin</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.955307262569832</v>
+        <v>1.74</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -5735,17 +4139,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor tortilla chips white corn bite size round 13_0.37</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5753,16 +4157,16 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Bite Size Round | 13 oz</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.184357541899441</v>
+        <v>2.38</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -5774,17 +4178,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor tortilla chips white corn restaurant style 300_0.3</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5792,16 +4196,16 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Restaurant Style | 300 g</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.005586592178771</v>
+        <v>1.51</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -5813,17 +4217,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eggo_eggo eggo minis waffle 14 8_0.42</t>
+          <t>unknown_parreiro pan viga mediana_unknown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -5831,16 +4235,16 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eggo</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Eggo | EGGO MINIS WAFFLE | 14.8 oz</t>
+          <t>Parreiro Pan Viga Mediana</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.245810055865922</v>
+        <v>1.74</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5852,17 +4256,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>frito lay_frito lay 24 pc frito lay doritos nacho cheese_unknown</t>
+          <t>bolin_pan viga club bolin_1.28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5870,16 +4274,16 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Frito-Lay | 24 pc FRITO LAY DORITOS NACHO CHEESE</t>
+          <t>Pan Viga Club Bolin</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>23.23463687150839</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5891,17 +4295,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>frito lay_frito lay frito lay bold mix 24 ea 5 5_0.16</t>
+          <t>jumbo_pan de sandwich mini club jumbo_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5909,16 +4313,16 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Frito-Lay | Frito Lay Bold Mix 24 ea | 5.5 oz</t>
+          <t>Pan De Sandwich Mini Club Jumbo</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.849162011173184</v>
+        <v>1.66</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5930,17 +4334,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>glad_glad 20 bg glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
+          <t>jumbo_pan de sandwich viga mediana jumbo_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5948,16 +4352,16 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Glad</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Glad | 20 bg Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
+          <t>Pan De Sandwich Viga Mediana Jumbo</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.575418994413408</v>
+        <v>2.14</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5969,17 +4373,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>goldfish_goldfish goldfish baked snack crackers cheddar 260_0.26</t>
+          <t>jumbo_pan sandwich viga grande jumbo_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5987,16 +4391,16 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goldfish</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Goldfish | GOLDFISH BAKED SNACK CRACKERS, CHEDDAR | 260 g</t>
+          <t>Pan Sandwich Viga Grande Jumbo</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.067039106145252</v>
+        <v>3.09</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -6008,17 +4412,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo linzenwafel sweet chilli 190_0.19</t>
+          <t>lumijor_pan viga club personal lumijor_0.52</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -6026,16 +4430,16 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO LINZENWAFEL SWEET CHILLI | 190 g</t>
+          <t>Pan Viga Club Personal Lumijor</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.681564245810056</v>
+        <v>1.73</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -6047,17 +4451,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo marie biscuits 16 3_0.46</t>
+          <t>molino del sol_viga de pan mediana molino del sol_0.78</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -6065,16 +4469,16 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO MARIE BISCUITS | 16.3 oz</t>
+          <t>Viga De Pan Mediana Molino Del Sol</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.35754189944134</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -6086,17 +4490,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo tortilla dip hot 9 75_0.28</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -6104,16 +4508,16 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO TORTILLA DIP HOT | 9.75 oz</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.849162011173184</v>
+        <v>2.22</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -6125,17 +4529,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kellogg_kellogg kellogg s eggo blueberry pancakes 450g_0.45</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -6143,16 +4547,16 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kellogg</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kellogg | KELLOGG'S EGGO BLUEBERRY PANCAKES | 450g</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.569832402234637</v>
+        <v>1.55</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -6164,17 +4568,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>la dulcerita_la dulcerita 6 la dulcerita chocolate chip muffin_unknown</t>
+          <t>lu_pan de sandwich ancient grain sin canyon_0.43</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -6182,16 +4586,16 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>La Dulcerita</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>La Dulcerita | 6 ct LA DULCERITA CHOCOLATE CHIP MUFFIN</t>
+          <t>Pan De Sandwich Ancient Grain Sin Gluten Canyon</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.301675977653631</v>
+        <v>6.96</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -6203,17 +4607,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lays_lays 24 pc lay s mesquite barbecue flavored potato crisps 5 5_0.16</t>
+          <t>lu_pan de sandwich mini club nacional_unknown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -6221,16 +4625,16 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lays | 24 pc Lay's Mesquite Barbecue Flavored Potato Crisps | 5.5 oz</t>
+          <t>Pan De Sandwich Mini Club Nacional</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>23.23463687150839</v>
+        <v>1.65</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -6242,17 +4646,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>lays_lays lay s sour cream onion flavored potato crisps 5 5_0.16</t>
+          <t>lumijor_pan viga club personal lumijor_0.52</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -6260,16 +4664,16 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
+          <t>Pan Viga Club Personal Lumijor</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.122905027932961</v>
+        <v>1.71</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -6281,17 +4685,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>lu_lu lu cracottes naturel 6 6_0.19</t>
+          <t>lumijor_pan viga mini brioche lumijor_0.45</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -6299,16 +4703,16 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LU | LU CRACOTTES NATUREL | 6.6 oz</t>
+          <t>Pan Viga Mini Brioche Lumijor</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.849162011173184</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -6320,17 +4724,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>lu_lu tf blueberry bagel 567_0.57</t>
+          <t>unknown_pan de sandwich bajo en carbohidratos sola_0.4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -6338,16 +4742,16 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>LU | Tf Blueberry Bagel | 567 g</t>
+          <t>Pan De Sandwich Bajo En Carbohidratos Sola</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.184357541899441</v>
+        <v>13.61</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -6359,17 +4763,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>mcvitie s_mcvitie s mcvitie s digestive 14 2_0.4</t>
+          <t>unknown_pan de sandwich deliciously seeded sola_0.4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -6377,16 +4781,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mcvitie'S</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>McVitie's | MCVITIE'S DIGESTIVE | 14.2 oz</t>
+          <t>Pan De Sandwich Deliciously Seeded Sola</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.396648044692737</v>
+        <v>13.61</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -6398,17 +4802,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>noel_noel noel saltin noel extra large 454_0.45</t>
+          <t>unknown_pan de sandwich sweet oat sola_0.4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -6416,16 +4820,16 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Noel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Noel | NOEL SALTIN NOEL EXTRA LARGE | 454 g</t>
+          <t>Pan De Sandwich Sweet Oat Sola</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.474860335195531</v>
+        <v>13.61</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -6437,17 +4841,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Merca Jumbo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm goldfish snack crackers baked colors cheddar 300_0.3</t>
+          <t>unknown_pan de sandwich viga mediana nacional_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -6455,16 +4859,16 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM GOLDFISH SNACK CRACKERS, BAKED, COLORS CHEDDAR | 300 g</t>
+          <t>Pan De Sandwich Viga Mediana Nacional</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.290502793296089</v>
+        <v>2.12</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -6476,17 +4880,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury pillsbury crescents original 250_0.25</t>
+          <t>bolin_pan viga club bolin_1.28</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -6494,16 +4898,16 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pillsbury | PILLSBURY CRESCENTS ORIGINAL | 250 g</t>
+          <t>Pan Viga Club Bolin</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.675977653631285</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -6515,17 +4919,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury pillsbury flaky layers honey butter biscuits 8 ea 300_0.3</t>
+          <t>holsum_pan de viga sobao holsum_0.45</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -6533,16 +4937,16 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pillsbury | Pillsbury Flaky Layers Honey Butter Biscuits 8 ea | 300 g</t>
+          <t>Pan De Viga Sobao Holsum</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.87709497206704</v>
+        <v>4.36</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -6554,17 +4958,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles original 1 3_0.04</t>
+          <t>holsum_pan viga de mantequilla holsum_0.56</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -6572,16 +4976,16 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES ORIGINAL | 1.3 oz</t>
+          <t>Pan Viga De Mantequilla Holsum</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.558659217877095</v>
+        <v>4.36</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -6593,17 +4997,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles salty snacks potato crisps chips sour cream and onion flavored 5 2_0.15</t>
+          <t>holsum_pan viga de papa holsum_0.56</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -6611,16 +5015,16 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Holsum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES SALTY SNACKS POTATO CRISPS CHIPS, SOUR CREAM AND ONION FLAVORED | 5.2 oz</t>
+          <t>Pan Viga De Papa Holsum</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.681564245810056</v>
+        <v>4.36</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -6632,17 +5036,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>schar_schar schar hamburger buns 16_0.45</t>
+          <t>la panera_croissant consumo directo la panera relleno chocolate_0.08</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -6650,16 +5054,16 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schar | SCHAR HAMBURGER BUNS, GLUTEN FREE | 16 oz</t>
+          <t>Croissant Consumo Directo La Panera Relleno Chocolate</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.083798882681564</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -6671,17 +5075,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>schar_schar schar white bread artisan baker 12 9oz_0.37</t>
+          <t>lu_pan de sandwich ancient grain sin canyon_0.43</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -6689,16 +5093,16 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schar | SCHAR WHITE BREAD, GLUTEN FREE, ARTISAN BAKER | 12.9oz</t>
+          <t>Pan De Sandwich Ancient Grain Sin Gluten Canyon</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9.46927374301676</v>
+        <v>6.97</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -6710,17 +5114,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>schar_schar schar white bread artisan baker 24_0.68</t>
+          <t>lu_pan de sandwich mini club nacional_unknown</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -6728,16 +5132,16 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Schar</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schar | SCHAR WHITE BREAD, GLUTEN FREE, ARTISAN BAKER | 24 oz</t>
+          <t>Pan De Sandwich Mini Club Nacional</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>7.201117318435754</v>
+        <v>1.66</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -6749,17 +5153,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>toufayan_toufayan 6 pc toufayan vegan everything bagels 6pc_unknown</t>
+          <t>lu_pan de sandwich sin 7 granos canyon_0.01</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -6767,16 +5171,16 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Toufayan | 6 pc TOUFAYAN VEGAN EVERYTHING BAGELS 6PC</t>
+          <t>Pan De Sandwich Sin Gluten 7 Granos Canyon</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.184357541899441</v>
+        <v>14.26</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -6788,17 +5192,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 11_0.31</t>
+          <t>lu_pan de sandwich sin canyon_0.51</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -6806,16 +5210,16 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 11 oz</t>
+          <t>Pan De Sandwich Sin Gluten Canyon</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.955307262569832</v>
+        <v>14.26</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -6827,17 +5231,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>unknown_2 pc aardbeienslof_unknown</t>
+          <t>lumijor_pan viga club personal lumijor_0.52</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -6845,16 +5249,16 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2 pc AARDBEIENSLOF</t>
+          <t>Pan Viga Club Personal Lumijor</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.899441340782123</v>
+        <v>1.73</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -6866,17 +5270,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>unknown_2 pk wei chuan spring rolls shells_unknown</t>
+          <t>lumijor_pan viga mini brioche lumijor_0.45</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -6884,16 +5288,16 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2 pk WEI-CHUAN SPRING ROLLS SHELLS</t>
+          <t>Pan Viga Mini Brioche Lumijor</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7.793296089385474</v>
+        <v>2.52</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -6905,17 +5309,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unknown_8 ea haagen dazs caramel biscuit and cream speculoos_unknown</t>
+          <t>martin s_pan de papa para sandwich martins_0.51</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -6923,16 +5327,16 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Martin'S</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8 ea HAAGEN-DAZS CARAMEL BISCUIT AND CREAM SPECULOOS</t>
+          <t>Pan De Papa Para Sandwich Martins</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.35754189944134</v>
+        <v>5.53</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -6944,17 +5348,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>unknown_appeltaartje klein_unknown</t>
+          <t>molino del sol_pan viga mini club molino del sol_0.45</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -6962,16 +5366,16 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>APPELTAARTJE KLEIN</t>
+          <t>Pan Viga Mini Club Molino Del Sol</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>25.11173184357542</v>
+        <v>1.54</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -6983,17 +5387,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>unknown_coolback garlic butter baguette 309_0.31</t>
+          <t>molino del sol_viga de pan mediana molino del sol_0.78</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -7001,16 +5405,16 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Molino Del Sol</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>COOLBACK GARLIC BUTTER BAGUETTE | 309 g</t>
+          <t>Viga De Pan Mediana Molino Del Sol</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5.525139664804469</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -7022,17 +5426,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>unknown_each white chocolate raspberry klein_unknown</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -7040,16 +5444,16 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>each WHITE CHOCOLATE RASPBERRY KLEIN</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>23.43575418994413</v>
+        <v>2.22</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -7061,17 +5465,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>unknown_fjord knackebrod volkoren 250_0.25</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -7079,16 +5483,16 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>FJORD KNACKEBROD VOLKOREN | 250 g</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.061452513966481</v>
+        <v>1.55</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -7100,17 +5504,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>unknown_food for life ezekiel 4 9 bread low sodium sprouted grain 14 1_0.4</t>
+          <t>ritz_galletas chips original ritz_0.23</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -7118,16 +5522,16 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, LOW SODIUM, SPROUTED GRAIN | 14.1 oz</t>
+          <t>Galletas Chips Original Ritz</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10.55307262569832</v>
+        <v>5.7</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -7139,17 +5543,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>unknown_french bread white 14 1_0.4</t>
+          <t>ritz_ponche maritza_unknown</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -7157,16 +5561,16 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ritz</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>FRENCH BREAD WHITE | 14.1 oz</t>
+          <t>Ponche Maritza</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10.55307262569832</v>
+        <v>18.14</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -7178,17 +5582,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>unknown_koopmans deeg hartige taart 11_0.31</t>
+          <t>schar_pan de viga rustico sin schar_0.4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -7196,16 +5600,16 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Schar</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KOOPMANS DEEG HARTIGE TAART | 11 oz</t>
+          <t>Pan De Viga Rustico Sin Gluten Schar</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.899441340782123</v>
+        <v>3.96</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -7217,17 +5621,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unknown_lemon muffin 24_0.68</t>
+          <t>unknown_bruschettas con ajo y perejil valentina_0.15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -7240,11 +5644,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>LEMON MUFFIN | 24 oz</t>
+          <t>Bruschettas Con Ajo Y Perejil Valentina</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7.251396648044693</v>
+        <v>1.66</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -7256,17 +5660,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unknown_tex mex mini tortilla original 250g_0.25</t>
+          <t>unknown_pan de coliflor para sandwich outer aisle_0.19</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -7279,11 +5683,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>TEX MEX MINI TORTILLA ORIGINAL | 250g</t>
+          <t>Pan De Coliflor Para Sandwich Outer Aisle</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.525139664804469</v>
+        <v>12.68</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -7295,17 +5699,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>unknown_tiramisu gebak_unknown</t>
+          <t>unknown_pan de sandwich bajo en carbohidratos sola_0.4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -7318,11 +5722,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>TIRAMISU GEBAK</t>
+          <t>Pan De Sandwich Bajo En Carbohidratos Sola</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.569832402234637</v>
+        <v>13.63</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -7334,17 +5738,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>wasa_wasa wasa dun rogge volkoren 13 7_0.39</t>
+          <t>unknown_pan de sandwich deliciously seeded sola_0.4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -7352,16 +5756,16 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WASA | WASA DUN ROGGE VOLKOREN | 13.7 oz</t>
+          <t>Pan De Sandwich Deliciously Seeded Sola</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.290502793296089</v>
+        <v>13.63</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -7373,17 +5777,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>wasa_wasa wasa knackebrod glutenvr sesam 6 6_0.19</t>
+          <t>unknown_pan de sandwich golden wheat sola_0.4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -7391,16 +5795,16 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>WASA | WASA KNACKEBROD GLUTENVR SESAM | 6.6 oz</t>
+          <t>Pan De Sandwich Golden Wheat Sola</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.072625698324022</v>
+        <v>11.08</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -7412,17 +5816,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>wasa_wasa wasa vezelrijk 240_0.24</t>
+          <t>unknown_pan de sandwich sweet oat sola_0.4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -7430,16 +5834,16 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>WASA | WASA VEZELRIJK | 240 g</t>
+          <t>Pan De Sandwich Sweet Oat Sola</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.698324022346369</v>
+        <v>13.63</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -7451,17 +5855,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>wasa_wasa wasa volkoren 250_0.25</t>
+          <t>unknown_pan de sandwich viga mediana nacional_unknown</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -7469,16 +5873,16 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Wasa</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WASA | WASA VOLKOREN | 250 g</t>
+          <t>Pan De Sandwich Viga Mediana Nacional</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.893854748603352</v>
+        <v>2.14</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -7495,12 +5899,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>loacker_galleta wafers loacker sabor a napolitaner_0.04</t>
+          <t>unknown_pan sandwich viga grande nacional_unknown</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -7508,16 +5912,16 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Loacker</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Galleta Wafers Loacker Sabor A Napolitaner</t>
+          <t>Pan Sandwich Viga Grande Nacional</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.09</v>
+        <v>3.09</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -7534,12 +5938,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>aviva_galleta de soda saltina aviva 20 und_0.6</t>
+          <t>loacker_galleta wafers loacker sabor a vainilla_0.04</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -7547,16 +5951,16 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Aviva</t>
+          <t>Loacker</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Galleta De Soda Saltina Aviva 20 Und</t>
+          <t>Galleta Wafers Loacker Sabor A Vainilla</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.44</v>
+        <v>1.09</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -7568,17 +5972,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bermudez_bermudez crackers dixee 3pk_unknown</t>
+          <t>lumijor_pan viga club personal lumijor_0.52</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -7586,16 +5990,16 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bermudez Crackers Dixee 3pk</t>
+          <t>Pan Viga Club Personal Lumijor</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.923076923076923</v>
+        <v>1.96</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -7607,17 +6011,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>bermudez_bermudez multigrain crix crackers_unknown</t>
+          <t>lumijor_pan viga mini brioche lumijor_0.45</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -7625,16 +6029,16 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BERMUDEZ  MULTIGRAIN CRIX CRACKERS</t>
+          <t>Pan Viga Mini Brioche Lumijor</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.115384615384615</v>
+        <v>3.15</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -7646,17 +6050,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bermudez_bermudez rough tops_unknown</t>
+          <t>unknown_dulce sandwich de naranja con leche rodriguez_0.26</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -7664,16 +6068,16 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Bermudez Rough Tops</t>
+          <t>Dulce Sandwich De Naranja Con Leche Rodriguez</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5288461538461539</v>
+        <v>2.68</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -7685,17 +6089,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bermudez_bermudez whole wheat crix crackers_unknown</t>
+          <t>bolin_pan viga club bolin_1.28</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -7703,16 +6107,16 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Bolin</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bermudez Whole Wheat Crix Crackers</t>
+          <t>Pan Viga Club Bolin</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.115384615384615</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -7724,17 +6128,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>devon_devon rolls chocolate chips 200 gr_0.2</t>
+          <t>buenhorno_pan viga buenhorno masa madre sin azucar_unknown</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -7742,16 +6146,16 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Devon</t>
+          <t>Buenhorno</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Devon Rolls Chocolate Chips 200 gr</t>
+          <t>Pan Viga Buenhorno Masa Madre Sin Azucar</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.923076923076923</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -7763,17 +6167,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>festival_festival cookie chips_unknown</t>
+          <t>lumijor_pan viga club personal lumijor_0.52</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7781,16 +6185,16 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Festival Cookie Chips</t>
+          <t>Pan Viga Club Personal Lumijor</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.365384615384615</v>
+        <v>1.73</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -7802,17 +6206,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate cookies 12x50g_0.6</t>
+          <t>pepin_pan viga mediana pepin_0.85</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -7820,16 +6224,16 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Noel Festival Chocolate Cookies 12x50g</t>
+          <t>Pan Viga Mediana Pepin</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.423076923076923</v>
+        <v>2.06</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -7841,17 +6245,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>festival_noel festival strawberry 12x32g_0.38</t>
+          <t>pepin_pan viga pequena pepin_0.45</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -7859,16 +6263,16 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Pepin</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Noel Festival Strawberry 12x32g</t>
+          <t>Pan Viga Pequena Pepin</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.942307692307693</v>
+        <v>1.55</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -7880,17 +6284,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>festival_noel festival strawberry cookies_unknown</t>
+          <t>unknown_pan de sandwich golden wheat sola_0.4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7898,16 +6302,16 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Noel Festival Strawberry Cookies</t>
+          <t>Pan De Sandwich Golden Wheat Sola</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.4807692307692308</v>
+        <v>11.23</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -7919,17 +6323,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>festival_noel festival vanilla 12x32g_0.38</t>
+          <t>unknown_pan de sandwich sweet oat sola_0.4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7937,16 +6341,16 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Noel Festival Vanilla 12x32g</t>
+          <t>Pan De Sandwich Sweet Oat Sola</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.038461538461538</v>
+        <v>11.23</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -7958,17 +6362,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Sirena</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>knotts_knotts raspberry short bread_unknown</t>
+          <t>unknown_pan de viga mediana zerca_0.74</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7976,16 +6380,16 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Knotts Raspberry Short Bread</t>
+          <t>Pan De Viga Mediana Zerca</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9615384615384616</v>
+        <v>1.57</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -8007,7 +6411,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>knotts_knotts strawbery short bread_unknown</t>
+          <t>bermudez_caribbean delight brownie biscuits 5 1oz_0.14</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -8015,16 +6419,16 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Knotts</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Knotts Strawbery Short Bread</t>
+          <t>Caribbean Delight Brownie Biscuits 5.1oz</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9615384615384616</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -8046,7 +6450,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>other_nutella and go pretzel sticks_unknown</t>
+          <t>golden_golden harvest multigrain loaf_unknown</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -8054,16 +6458,16 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Nutella And Go Pretzel Sticks</t>
+          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.644230769230769</v>
+        <v>2.596153846153846</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -8085,7 +6489,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ovaltine_ovaltine biscuits_unknown</t>
+          <t>shoon_shoon fatt pop corn crackers_unknown</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -8093,16 +6497,16 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ovaltine</t>
+          <t>Shoon</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>OVALTINE BISCUITS</t>
+          <t>Shoon Fatt Pop Corn Crackers</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.7692307692307693</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -8124,7 +6528,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm bordeaux cookies 6 75_0.19</t>
+          <t>unknown_bakery decorated donut_unknown</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -8132,16 +6536,16 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Bordeaux Cookies 6.75 Oz</t>
+          <t>Bakery Decorated Donut</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.951923076923077</v>
+        <v>6.538461538461538</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -8163,7 +6567,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>pepperidge_pepperidge farm double chocolate dark choc cookie 7 75oz_0.22</t>
+          <t>unknown_tiffany chocolate wafer_unknown</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -8171,16 +6575,16 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pepperidge</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Pepperidge Farm Double Chocolate Dark Choc Cookie 7.75oz</t>
+          <t>TIFFANY CHOCOLATE  WAFER</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.346153846153846</v>
+        <v>2.740384615384615</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -8188,552 +6592,6 @@
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm goldfish cheddar 6 6oz_0.19</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Goldfish Cheddar 6.6oz</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>4.278846153846154</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano double dark chocolate 7 75oz_0.22</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Double Dark Chocolate 7.75oz</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano milk chocolate 6oz_0.17</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Milk Chocolate 6oz</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano orange chocolate 7oz_0.2</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Orange Chocolate 7oz</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>5.769230769230769</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm milano raspberry chocolate 7oz_0.2</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm Milano Raspberry Chocolate 7oz</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>6.009615384615385</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm strawberry cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>PEPPERIDGE FARM STRAWBERRY COOKIES</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>6.538461538461538</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>pepperidge_pepperidge farm white choc macadamia 7 2oz_0.2</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Pepperidge</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Pepperidge Farm White Choc Macadamia 7.2oz</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>6.490384615384615</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Butter Crackers</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>4.182692307692307</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt butter crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>SHOON FATT BUTTER CRACKERS</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>1.778846153846154</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>shoon_shoon fatt veggie crackers_unknown</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Shoon</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Shoon Fatt Veggie Crackers</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>3.557692307692307</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>tiffany_tiffany choco chip cookies_unknown</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Tiffany</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>TIFFANY CHOCO CHIP COOKIES</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>0.9134615384615384</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>walkers_walkers chocolate chip shortbread_unknown</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Walkers Chocolate Chip Shortbread</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>8.076923076923077</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>walkers_walkers piper dancer tin shortbread assorted 150g_0.15</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>WALKERS PIPER &amp; DANCER TIN SHORTBREAD ASSORTED 150G</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>14.61538461538462</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Massy Stores Guyana</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>walkers_walkers shortbread rounds_unknown</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Walkers</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Walkers Shortbread Rounds</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>5.865384615384615</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>right_only</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/streamlit_data/price_alerts.xlsx
+++ b/streamlit_data/price_alerts.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,39 +483,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nabisco_nabisco original saltine crackers 16oz_0.45</t>
+          <t>festival_festival noel festival strawberry cookies 240_0.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nabisco</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NABISCO ORIGINAL SALTINE CRACKERS 16oz</t>
+          <t>Festival | NOEL FESTIVAL STRAWBERRY COOKIES | 240 g</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>6.08</v>
+        <v>3.458100558659218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nabisco</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NABISCO ORIGINAL SALTINE CRACKERS 16oz</t>
+          <t>Festival | NOEL FESTIVAL STRAWBERRY COOKIES | 240 g</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6.64</v>
+        <v>2.787709497206704</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>-8.433734939759031</v>
+        <v>24.04809619238478</v>
       </c>
     </row>
     <row r="3">
@@ -534,12 +534,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury funfetti cake mix 15 25oz_0.43</t>
+          <t>pillsbury_pillsbury pillsbury blueberry pastries 6 ea 480_0.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -549,11 +549,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PILLSBURY FUNFETTI CAKE MIX 15.25oz</t>
+          <t>Pillsbury | Pillsbury Blueberry Pastries 6 ea | 480 g</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.96</v>
+        <v>6.64245810055866</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -562,11 +562,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>PILLSBURY FUNFETTI CAKE MIX 15.25oz</t>
+          <t>Pillsbury | Pillsbury Blueberry Pastries 6 ea | 480 g</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.18</v>
+        <v>6.139664804469274</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>-6.918238993710697</v>
+        <v>8.189262966333031</v>
       </c>
     </row>
     <row r="4">
@@ -585,39 +585,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pringles_pringles sour cream and onion 5 5oz_0.16</t>
+          <t>unknown_bosvruchten muffin_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PRINGLES SOUR CREAM AND ONION 5.5oz</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.68</v>
+        <v>3.067039106145252</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PRINGLES SOUR CREAM AND ONION 5.5oz</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.29</v>
+        <v>30.69832402234637</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>11.85410334346505</v>
+        <v>-90.00909918107371</v>
       </c>
     </row>
     <row r="5">
@@ -636,39 +636,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>stacy s_stacy s bagel chips toasted garlic 7oz_0.2</t>
+          <t>unknown_bosvruchten muffin_unknown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stacy'S</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>STACY'S BAGEL CHIPS TOASTED GARLIC 7oz</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.74</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Stacy'S</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>STACY'S BAGEL CHIPS TOASTED GARLIC 7oz</t>
+          <t>BOSVRUCHTEN MUFFIN</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>30.69832402234637</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>-23.54838709677419</v>
+        <v>-93.64877161055504</v>
       </c>
     </row>
     <row r="6">
@@ -687,39 +687,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>toufayan_toufayan spinach wrap 6ct_unknown</t>
+          <t>unknown_food for life ezekiel 4 9 bread cinnamon raisin 24_0.68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TOUFAYAN GLUTEN FREE SPINACH WRAP 6CT</t>
+          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, CINNAMON RAISIN | 24 oz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6.81</v>
+        <v>11.70391061452514</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>TOUFAYAN GLUTEN FREE SPINACH WRAP 6CT</t>
+          <t>FOOD FOR LIFE EZEKIEL 4:9 BREAD, CINNAMON RAISIN | 24 oz</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.58</v>
+        <v>13.93854748603352</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>22.04301075268816</v>
+        <v>-16.03206412825651</v>
       </c>
     </row>
     <row r="7">
@@ -738,12 +738,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unknown_pearl milling co pancake mix complete 2lbs_0.91</t>
+          <t>unknown_food for life flourless sprouted grain flax bread 24_0.68</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -753,11 +753,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PEARL MILLING CO PANCAKE MIX COMPLETE 2lbs</t>
+          <t>Food For Life Flourless Sprouted Grain Flax Bread | 24 oz</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.02</v>
+        <v>13.93854748603352</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -766,11 +766,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PEARL MILLING CO PANCAKE MIX COMPLETE 2lbs</t>
+          <t>Food For Life Flourless Sprouted Grain Flax Bread | 24 oz</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>11.70391061452514</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>-13.44827586206897</v>
+        <v>19.09307875894988</v>
       </c>
     </row>
     <row r="8">
@@ -789,12 +789,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unknown_pearl milling co pancake mix original 32oz_0.91</t>
+          <t>unknown_homemade mango passie cake_unknown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -804,11 +804,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PEARL MILLING CO PANCAKE MIX ORIGINAL 32oz</t>
+          <t>HOMEMADE MANGO PASSIE CAKE</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.03</v>
+        <v>16.73184357541899</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -817,11 +817,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>PEARL MILLING CO PANCAKE MIX ORIGINAL 32oz</t>
+          <t>HOMEMADE MANGO PASSIE CAKE</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5.58</v>
+        <v>18.15083798882682</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8.06451612903226</v>
+        <v>-7.817790089258245</v>
       </c>
     </row>
     <row r="9">
@@ -840,12 +840,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DOIT Aruba</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unknown_pearl milling pancake mix protein buttermilk 20_0.57</t>
+          <t>unknown_vruchtenschelp_unknown</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -855,11 +855,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PEARL MILLING PANCAKE MIX PROTEIN BUTTERMILK 20 OZ</t>
+          <t>VRUCHTENSCHELP</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>9.16</v>
+        <v>6.675977653631285</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -868,11 +868,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PEARL MILLING PANCAKE MIX PROTEIN BUTTERMILK 20 OZ</t>
+          <t>VRUCHTENSCHELP</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>9.66</v>
+        <v>3.569832402234637</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>-5.175983436853001</v>
+        <v>87.01095461658844</v>
       </c>
     </row>
     <row r="10">
@@ -891,39 +891,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garrido</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lumijor_pan viga integral lumijor_0.55</t>
+          <t>carrefour_wafer cho negro crf sel_0.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pan Viga Integral Lumijor</t>
+          <t>Wafer Cho Negro Crf Sel</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>3.01</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Carrefour</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pan Viga Integral Lumijor</t>
+          <t>Wafer Cho Negro Crf Sel</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.54</v>
+        <v>0.79</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>-12.59842519685039</v>
+        <v>281.012658227848</v>
       </c>
     </row>
     <row r="11">
@@ -942,39 +942,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lumijor_pan de hamburguesa lumijor_unknown</t>
+          <t>cuetara_cuetara galleta wafer liman_0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Lumijor</t>
+          <t>Cuetara Galleta Wafer Liman</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.14</v>
+        <v>0.95</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Lumijor</t>
+          <t>Cuetara Galleta Wafer Liman</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.96</v>
+        <v>1.43</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9.183673469387763</v>
+        <v>-33.56643356643357</v>
       </c>
     </row>
     <row r="12">
@@ -993,39 +993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Garrido</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lumijor_pan de hot dog lumijor_unknown</t>
+          <t>cuetara_cuetara galleta wafer vainilla_0.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Cuetara Galleta Wafer Vainilla</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.82</v>
+        <v>0.95</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>Cuetara</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pan De Hot Dog Lumijor</t>
+          <t>Cuetara Galleta Wafer Vainilla</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.04</v>
+        <v>1.43</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>-10.7843137254902</v>
+        <v>-33.56643356643357</v>
       </c>
     </row>
     <row r="13">
@@ -1063,28 +1063,28 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lumijor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Pan De Hot Dog Lumijor</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2.04</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Lumijor</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Pan De Hot Dog Lumijor</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.82</v>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>12.08791208791209</v>
+        <v>-10.7843137254902</v>
       </c>
     </row>
     <row r="14">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lumijor_pan hamburguesa brioche lumijor_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1110,11 +1110,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pan Hamburguesa Brioche Lumijor</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.98</v>
+        <v>2.04</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pan Hamburguesa Brioche Lumijor</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.74</v>
+        <v>1.82</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8.759124087591232</v>
+        <v>12.08791208791209</v>
       </c>
     </row>
     <row r="15">
@@ -1146,39 +1146,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lumijor_pan de hamburguesa lumijor_unknown</t>
+          <t>la panera_pan hogaza integral masa madre la panera_0.4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Lumijor</t>
+          <t>Pan Hogaza Integral Masa Madre La Panera</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pan De Hamburguesa Lumijor</t>
+          <t>Pan Hogaza Integral Masa Madre La Panera</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.95</v>
+        <v>2.69</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9.743589743589752</v>
+        <v>-14.49814126394052</v>
       </c>
     </row>
     <row r="16">
@@ -1202,34 +1202,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lumijor_pan viga mini brioche lumijor_0.45</t>
+          <t>la panera_pan multicereales masa madre la panera_0.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Brioche Lumijor</t>
+          <t>Pan Multicereales Masa Madre La Panera</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.93</v>
+        <v>2.38</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lumijor</t>
+          <t>La Panera</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pan Viga Mini Brioche Lumijor</t>
+          <t>Pan Multicereales Masa Madre La Panera</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>16.26984126984128</v>
+        <v>-14.07942238267148</v>
       </c>
     </row>
     <row r="17">
@@ -1248,39 +1248,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>lu_bizcocho choco relleno de caramelo luppo_0.04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Bizcocho Choco Relleno De Caramelo Luppo</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.57</v>
+        <v>0.32</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Bizcocho Choco Relleno De Caramelo Luppo</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.92</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>-46.23287671232876</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="18">
@@ -1299,39 +1299,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Plaza Lama</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
+          <t>lumijor_pan con macadamia nueces y pasas lumijor_0.51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Pan Con Macadamia Nueces Y Pasas Lumijor</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.92</v>
+        <v>4.28</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>El Charrito</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
+          <t>Pan Con Macadamia Nueces Y Pasas Lumijor</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.57</v>
+        <v>3.88</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1339,50 +1339,50 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>85.98726114649681</v>
+        <v>10.30927835051547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>lumijor_pan de hamburguesa lumijor_unknown</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>Pan De Hamburguesa Lumijor</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.461538461538462</v>
+        <v>2.14</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>Pan De Hamburguesa Lumijor</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.3125</v>
+        <v>1.96</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1390,50 +1390,50 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1007.692307692308</v>
+        <v>9.183673469387763</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
+          <t>lumijor_pan de hot dog lumijor_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bermudez Bourbon Cream Cookies</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.3125</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bermudez</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
+          <t>Pan De Hot Dog Lumijor</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.461538461538462</v>
+        <v>1.63</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1441,50 +1441,50 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>-90.97222222222221</v>
+        <v>11.65644171779142</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>lumijor_pan hamburguesa brioche lumijor_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Pan Hamburguesa Brioche Lumijor</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5.817307692307693</v>
+        <v>2.98</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Pan Hamburguesa Brioche Lumijor</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.307692307692307</v>
+        <v>2.74</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1492,50 +1492,50 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>152.0833333333334</v>
+        <v>8.759124087591232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cadbury_cadbury dairy milk daim_unknown</t>
+          <t>lumijor_pan integral con pasas lumijor_0.47</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Pan Integral Con Pasas Lumijor</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.307692307692307</v>
+        <v>2.53</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Daim</t>
+          <t>Pan Integral Con Pasas Lumijor</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.817307692307693</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1543,50 +1543,50 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>-60.33057851239671</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>lumijor_pan integral multigranos lumijor_0.48</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Pan Integral Multigranos Lumijor</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.3365384615384615</v>
+        <v>2.66</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Pan Integral Multigranos Lumijor</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.942307692307693</v>
+        <v>2.38</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1594,50 +1594,50 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>-91.46341463414633</v>
+        <v>11.76470588235295</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>festival_noel festival chocolate_unknown</t>
+          <t>lumijor_pan pita blanco lumijor_unknown</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Pan Pita Blanco Lumijor</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.942307692307693</v>
+        <v>1.55</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Festival</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>NOEL FESTIVAL CHOCOLATE</t>
+          <t>Pan Pita Blanco Lumijor</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.3365384615384615</v>
+        <v>1.35</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1645,50 +1645,50 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1071.428571428572</v>
+        <v>14.81481481481481</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>lumijor_pan pita integral lumijor_unknown</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Pan Pita Integral Lumijor</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.682692307692308</v>
+        <v>1.62</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Pan Pita Integral Lumijor</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.086538461538462</v>
+        <v>1.43</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1696,50 +1696,50 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>-58.82352941176471</v>
+        <v>13.2867132867133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kugi_kugi chocolate wafer sticks_unknown</t>
+          <t>lumijor_pan viga mini integral gourmet lumijor_0.5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kugi Chocolate Wafer Sticks</t>
+          <t>Pan Viga Mini Integral Gourmet Lumijor</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4.086538461538462</v>
+        <v>2.69</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Lumijor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KUGI CHOCOLATE WAFER STICKS</t>
+          <t>Pan Viga Mini Integral Gourmet Lumijor</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.682692307692308</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1747,50 +1747,50 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>142.8571428571429</v>
+        <v>16.95652173913044</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>toufayan_pan pita integral toufayan_0.34</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>Pan Pita Integral Toufayan</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.682692307692308</v>
+        <v>1.5</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>Pan Pita Integral Toufayan</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.086538461538462</v>
+        <v>1.27</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1798,50 +1798,50 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>-58.82352941176471</v>
+        <v>18.11023622047244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kugi Vanilla Milk Wafer Sticks</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.086538461538462</v>
+        <v>1.57</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Kugi</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KUGI VANILLA MILK WAFER STICKS</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.682692307692308</v>
+        <v>2.92</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1849,50 +1849,50 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>142.8571428571429</v>
+        <v>-46.23287671232876</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Plaza Lama</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>el charrito_tortilla de maiz dura para tacos 5 el charrito_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>29.08653846153846</v>
+        <v>2.92</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>El Charrito</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Tortilla De Maiz Dura Para Tacos 5 El Charrito</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>15.04807692307692</v>
+        <v>1.57</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>93.29073482428115</v>
+        <v>85.98726114649681</v>
       </c>
     </row>
     <row r="30">
@@ -1916,34 +1916,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>new york style_ft new york style cheesecake plain_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>15.04807692307692</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>New York Style</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>29.08653846153846</v>
+        <v>0.3125</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>-48.26446280991735</v>
+        <v>1007.692307692308</v>
       </c>
     </row>
     <row r="31">
@@ -1967,34 +1967,34 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>bermudez_bermudez bourbon cream cookies_unknown</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Bermudez Bourbon Cream Cookies</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.254807692307693</v>
+        <v>0.3125</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Bermudez</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>BERMUDEZ BOURBON CREAM COOKIES PACK</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>3.461538461538462</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>70.19230769230769</v>
+        <v>-90.97222222222221</v>
       </c>
     </row>
     <row r="32">
@@ -2018,34 +2018,34 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>pringles_pringles pizza_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pringles Pizza</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>PRINGLES PIZZA</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.254807692307693</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>-41.24293785310735</v>
+        <v>152.0833333333334</v>
       </c>
     </row>
     <row r="33">
@@ -2069,34 +2069,34 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>cadbury_cadbury dairy milk daim_unknown</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10.86538461538462</v>
+        <v>2.307692307692307</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>Cadbury Dairy Milk Daim</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.826923076923077</v>
+        <v>5.817307692307693</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>494.7368421052633</v>
+        <v>-60.33057851239671</v>
       </c>
     </row>
     <row r="34">
@@ -2120,34 +2120,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>shoon_shoon fatt cream crackers_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SHOON FATT CREAM CRACKERS</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.826923076923077</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Shoon</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Shoon Fatt Cream Crackers</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10.86538461538462</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>-83.18584070796462</v>
+        <v>-91.46341463414633</v>
       </c>
     </row>
     <row r="35">
@@ -2171,34 +2171,34 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>festival_noel festival chocolate_unknown</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.682692307692308</v>
+        <v>3.942307692307693</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Festival</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>NOEL FESTIVAL CHOCOLATE</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.346153846153846</v>
+        <v>0.3365384615384615</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>24.99999999999997</v>
+        <v>1071.428571428572</v>
       </c>
     </row>
     <row r="36">
@@ -2222,17 +2222,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2240,16 +2240,16 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.625</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>169.2307692307692</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="37">
@@ -2273,30 +2273,30 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>kugi_kugi chocolate wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Kugi Chocolate Wafer Sticks</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.346153846153846</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>KUGI CHOCOLATE WAFER STICKS</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>-19.99999999999998</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="38">
@@ -2324,34 +2324,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.346153846153846</v>
+        <v>1.682692307692308</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.625</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>115.3846153846154</v>
+        <v>-58.82352941176471</v>
       </c>
     </row>
     <row r="39">
@@ -2375,30 +2375,30 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>triskits_triskits vanilla crackers_unknown</t>
+          <t>kugi_kugi vanilla milk wafer sticks_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>Kugi Vanilla Milk Wafer Sticks</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.625</v>
+        <v>4.086538461538462</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Triskits</t>
+          <t>Kugi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>TRISKITS VANILLA CRACKERS</t>
+          <t>KUGI VANILLA MILK WAFER STICKS</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>-62.85714285714285</v>
+        <v>142.8571428571429</v>
       </c>
     </row>
     <row r="40">
@@ -2426,41 +2426,704 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>29.08653846153846</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>15.04807692307692</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>93.29073482428115</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>new york style_ft new york style cheesecake plain_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>15.04807692307692</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>New York Style</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>FT NEW YORK STYLE CHEESECAKE PLAIN</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>29.08653846153846</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>-48.26446280991735</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>pringles_pringles pizza_unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PRINGLES PIZZA</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>4.254807692307693</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Pringles Pizza</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>70.19230769230769</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>pringles_pringles pizza_unknown</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Pringles Pizza</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PRINGLES PIZZA</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>4.254807692307693</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>-41.24293785310735</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Cream Crackers</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>10.86538461538462</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SHOON FATT CREAM CRACKERS</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>494.7368421052633</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>shoon_shoon fatt cream crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SHOON FATT CREAM CRACKERS</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1.826923076923077</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Shoon</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Shoon Fatt Cream Crackers</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>10.86538461538462</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>-83.18584070796462</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan bagels blueberry 567g_0.57</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Toufayan Bagels Blueberry 567g</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>5.528846153846154</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Toufayan Bagels Blueberry 567g</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>5.048076923076923</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>9.523809523809526</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan bagels cinnamon raisin 567g_0.57</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Toufayan Bagels Cinnamon Raisin 567g</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>5.528846153846154</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Toufayan Bagels Cinnamon Raisin 567g</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>5.048076923076923</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>9.523809523809526</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>triskits_triskits vanilla crackers_unknown</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Triskits</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="F48" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>24.99999999999997</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
         <v>0.625</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>169.2307692307692</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Triskits</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>TRISKITS VANILLA CRACKERS</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="F50" t="n">
         <v>1.346153846153846</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="K40" t="n">
+      <c r="K50" t="n">
+        <v>-19.99999999999998</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>115.3846153846154</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>1.682692307692308</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>-62.85714285714285</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>triskits_triskits vanilla crackers_unknown</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Triskits</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>TRISKITS VANILLA CRACKERS</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
         <v>-53.57142857142858</v>
       </c>
     </row>
@@ -2475,7 +3138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2543,26 +3206,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bauducco_bauducco bauducco zero sugar chocolate wafer 1 5_0.04</t>
+          <t>gwoon_gwoon beschuit volkoren 125 gr_0.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Gwoon</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bauducco | Bauducco Zero Sugar Chocolate Wafer | 1.5 oz</t>
+          <t>GWOON BESCHUIT VOLKOREN 125 gr</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.670391061452514</v>
+        <v>1.45</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -2582,26 +3245,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor tortilla chips white corn restaurant style 9 75_0.28</t>
+          <t>unknown_david cookies chocolate overload cake slice 7 4oz_0.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Restaurant Style | 9.75 oz</t>
+          <t>DAVID COOKIES CHOCOLATE OVERLOAD CAKE SLICE 7.4OZ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.849162011173184</v>
+        <v>5.86</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -2626,21 +3289,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>doritos_doritos doritos cool american party 170_0.17</t>
+          <t>bagel bites_bagel bites 7z bagel bites cheese pepperoni pizza snacks_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doritos | DORITOS COOL AMERICAN - PARTY PACK | 170 g</t>
+          <t>Bagel Bites | 7z BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.849162011173184</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -2665,21 +3328,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>doritos_doritos doritos nacho cheese party 272_0.27</t>
+          <t>bigelow_bigelow bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea 250_0.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doritos | DORITOS NACHO CHEESE - PARTY PACK | 272 g</t>
+          <t>Bigelow | Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea | 250 g</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5.575418994413408</v>
+        <v>1.837988826815642</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -2704,21 +3367,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>food club_food club food club flour tortillas authentic fajita style 6 inch 20 ea 240_0.24</t>
+          <t>crav n_crav n crav n flavor tortilla chips white corn restaurant style 30_0.85</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Food Club | Food Club Flour Tortillas, Authentic, Fajita Style, 6 Inch 20 ea | 240 g</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Restaurant Style | 30 oz</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.223463687150838</v>
+        <v>7.536312849162011</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -2743,21 +3406,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>frito lay_frito lay frito lay doritos nacho cheese 6 5_0.18</t>
+          <t>crav n_crav n crav n flavor tortilla chips yellow corn crispy round party size 320_0.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Frito-Lay | FRITO LAY DORITOS NACHO CHEESE | 6.5 oz</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, Yellow Corn, Crispy Round, Party Size | 320 g</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.966480446927375</v>
+        <v>2.731843575418994</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -2782,21 +3445,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo marie biscuits 415_0.42</t>
+          <t>doritos_doritos doritos tortilla chips nacho cheese flavored 11_0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO MARIE BISCUITS | 415 g</t>
+          <t>Doritos | Doritos Tortilla Chips, Nacho Cheese Flavored | 11 oz</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9.491620111731844</v>
+        <v>6.64245810055866</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -2821,21 +3484,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lays_lays 24 pc lay s cheddar flavored potato crisps 5 5_0.16</t>
+          <t>doritos_doritos doritos tortilla chips nacho cheese flavored 300_0.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Doritos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lays | 24 pc Lay's Cheddar Flavored Potato Crisps | 5.5 oz</t>
+          <t>Doritos | Doritos Tortilla Chips, Nacho Cheese Flavored | 300 g</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>23.23463687150839</v>
+        <v>2.675977653631285</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -2860,21 +3523,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lays_lays lay s sour cream onion flavored potato crisps 5 5_0.16</t>
+          <t>eggo_eggo 27z eggo frozen breakfast frozen waffles strawberry_unknown</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
+          <t>Eggo | 27z EGGO FROZEN BREAKFAST FROZEN WAFFLES, STRAWBERRY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.122905027932961</v>
+        <v>10.02793296089386</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -2899,21 +3562,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lays_lays lays classic potato chips 6 5_0.18</t>
+          <t>eggo_eggo eggo minis waffle 550g_0.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lays | LAYS CLASSIC POTATO CHIPS | 6.5 oz</t>
+          <t>Eggo | EGGO MINIS WAFFLE | 550g</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.966480446927375</v>
+        <v>5.46927374301676</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -2938,21 +3601,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lays_lays lays potato chips sour cream onion flavored 5 5_0.16</t>
+          <t>eggo_eggo eggo waffles blueberry 600g_0.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lays | LAYS POTATO CHIPS, SOUR CREAM &amp; ONION FLAVORED | 5.5 oz</t>
+          <t>Eggo | EGGO WAFFLES, BLUEBERRY | 600g</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.849162011173184</v>
+        <v>4.441340782122905</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -2977,21 +3640,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo golden sandwich cookies 14 03_0.4</t>
+          <t>food club_food club food club flour tortillas authentic fajita style 6 inch 20 ea 200g_0.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Food Club</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oreo | OREO Golden Sandwich Cookies, | 14.03 oz</t>
+          <t>Food Club | Food Club Flour Tortillas, Authentic, Fajita Style, 6 Inch 20 ea | 200g</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.039106145251397</v>
+        <v>3.346368715083799</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -3016,21 +3679,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo sandwich cookies chocolate 13 29_0.38</t>
+          <t>frito lay_frito lay frito lay doritos nacho cheese 7_0.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oreo | Oreo Sandwich Cookies, Chocolate | 13.29 oz</t>
+          <t>Frito-Lay | FRITO LAY DORITOS NACHO CHEESE | 7 oz</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.368715083798882</v>
+        <v>4.854748603351955</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -3055,21 +3718,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm bread jewish rye seeded 24_0.68</t>
+          <t>glad_glad glad cling n seal plastic food wrap 400 square foot roll of 2 240_0.24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM BREAD, JEWISH RYE, SEEDED | 24 oz</t>
+          <t>Glad | Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2 | 240 g</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.251396648044693</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -3094,21 +3757,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm bread pumpernickel dark pump 250_0.25</t>
+          <t>jumbo_jumbo jumbo cafe noir koffiekoekjes 240_0.24</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM BREAD, PUMPERNICKEL, DARK PUMP | 250 g</t>
+          <t>Jumbo | JUMBO CAFE NOIR KOFFIEKOEKJES | 240 g</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.675977653631285</v>
+        <v>2.787709497206704</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -3133,21 +3796,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury pillsbury grands biscuits flaky layers 300_0.3</t>
+          <t>jumbo_jumbo jumbo linzenwafel sweet chilli 220_0.22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pillsbury | PILLSBURY GRANDS! BISCUITS, FLAKY LAYERS | 300 g</t>
+          <t>Jumbo | JUMBO LINZENWAFEL SWEET CHILLI | 220 g</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.87709497206704</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -3172,21 +3835,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury pillsbury raspberry pastries 11 7_0.33</t>
+          <t>jumbo_jumbo jumbo supercroissantdeeg 42_1.19</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pillsbury | Pillsbury Raspberry Pastries | 11.7 oz</t>
+          <t>Jumbo | JUMBO SUPERCROISSANTDEEG | 42 oz</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.558659217877095</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -3211,21 +3874,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pirucream_pirucream pirucream wafers chocolate and hazelnut 5_0.14</t>
+          <t>jumbo_jumbo jumbo tortilla nat 8st 7_0.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pirucream | Pirucream Wafers, Chocolate and Hazelnut | 5 oz</t>
+          <t>Jumbo | JUMBO TORTILLA NAT.8ST | 7 oz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.782122905027933</v>
+        <v>4.854748603351955</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -3250,21 +3913,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles bbq 1 3_0.04</t>
+          <t>la dulcerita_la dulcerita 6 la dulcerita chocolate chip muffin_unknown</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES BBQ | 1.3 oz</t>
+          <t>La Dulcerita | 6 ct LA DULCERITA CHOCOLATE CHIP MUFFIN</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.558659217877095</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -3289,21 +3952,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles potato crisps chips lunch snacks office and kids snacks grab n go original can 1 can 2 3_0.07</t>
+          <t>la dulcerita_la dulcerita la dulcerita rasin muffin 24_0.68</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pringles | Pringles Potato Crisps Chips, Lunch Snacks, Office and Kids Snacks, Grab N' Go, Original, Can, 1 Can | 2.3 oz</t>
+          <t>La Dulcerita | LA DULCERITA RASIN MUFFIN | 24 oz</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.340782122905028</v>
+        <v>7.251396648044693</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
@@ -3328,21 +3991,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles sour cream onion 1 4_0.04</t>
+          <t>lays_lays lay s sour cream onion flavored potato crisps 6 5_0.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES SOUR CREAM &amp; ONION | 1.4 oz</t>
+          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 6.5 oz</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.558659217877095</v>
+        <v>4.966480446927375</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -3367,21 +4030,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>siete_siete siete tortillas grain almond flour 8 ea 20_0.57</t>
+          <t>lays_lays lays classic potato chips 5 5_0.16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Siete | Siete Tortillas, Grain Free, Almond Flour 8 ea | 20 oz</t>
+          <t>Lays | LAYS CLASSIC POTATO CHIPS | 5.5 oz</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.011173184357542</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -3406,21 +4069,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tostitos_tostitos 8 ea tostitos restaurant style original tortilla chips 10_0.28</t>
+          <t>lu_lu food for life brown rice tortillas 6 ea 12_0.34</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tostitos | 8 ea Tostitos Restaurant Style Original Tortilla Chips | 10 oz</t>
+          <t>LU | Food For Life Gluten Free Brown Rice Tortillas 6 ea | 12 oz</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13.37988826815642</v>
+        <v>7.793296089385474</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -3445,21 +4108,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>unknown_1 pc rb amandelstaaf_unknown</t>
+          <t>lu_lu udi s classic hamburger buns 450g_0.45</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1 pc RB AMANDELSTAAF :</t>
+          <t>LU | UDI'S GLUTEN FREE CLASSIC HAMBURGER BUNS | 450g</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.76536312849162</v>
+        <v>6.675977653631285</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -3484,21 +4147,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_10 ea koopmans deeg hartige taart_unknown</t>
+          <t>lu_lu udi s classic hot dog buns frozen 6 count 24_0.68</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10 ea KOOPMANS DEEG HARTIGE TAART</t>
+          <t>LU | Udi's Gluten Free Classic Hot Dog Buns, Frozen, . 6 Count | 24 oz</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.525139664804469</v>
+        <v>12.82122905027933</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -3523,21 +4186,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_food for life sprouted flourless original tortillas 6 ea 450g_0.45</t>
+          <t>milka_milka milka mmmax chocoswing biscuit 415_0.42</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Food For Life Sprouted Flourless Original Tortillas 6 ea | 450g</t>
+          <t>Milka | MILKA MMMAX CHOCOSWING BISCUIT | 415 g</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.569832402234637</v>
+        <v>9.491620111731844</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -3562,21 +4225,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_kaneelbroodje_unknown</t>
+          <t>nature valley_nature valley nature valley chewy almond granola bars 6 ea 126_0.13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>KANEELBROODJE</t>
+          <t>Nature Valley | Nature Valley Chewy Almond Granola Bars 6 ea | 126 g</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6.675977653631285</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -3601,21 +4264,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_papagena biscuit assorted 200_0.2</t>
+          <t>noel_noel 6 ea noel dux saltines crackers_unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PAPAGENA BISCUIT ASSORTED | 200 g</t>
+          <t>Noel | 6 ea NOEL DUX SALTINES CRACKERS</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.502793296089385</v>
+        <v>6.865921787709497</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -3640,21 +4303,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_tiramisutaartje_unknown</t>
+          <t>noel_noel noel chocolate chip 360_0.36</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TIRAMISUTAARTJE</t>
+          <t>Noel | NOEL CHOCOLATE CHIP | 360 g</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.067039106145252</v>
+        <v>2.396648044692737</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -3669,31 +4332,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>food club_english muffins multigrano food club_unknown</t>
+          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 8_0.23</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>English Muffins Multigrano Food Club</t>
+          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 8 oz</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.64</v>
+        <v>6.307262569832401</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -3708,31 +4371,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>keebler_galletas de pan pita con sal marina keebler_0.27</t>
+          <t>oreo_oreo oreo mini cookies snak saks 11 78_0.33</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Keebler</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Galletas De Pan Pita Con Sal Marina Keebler</t>
+          <t>Oreo | OREO MINI COOKIES SNAK-SAKS | 11.78 oz</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.91</v>
+        <v>9.770949720670391</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
@@ -3747,31 +4410,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mestemacher_pan integral negro de westfalia mestemacher_0.5</t>
+          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 13 29_0.38</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mestemacher</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pan Integral Negro De Westfalia Mestemacher</t>
+          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 13.29 oz</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.85</v>
+        <v>7.089385474860335</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
@@ -3786,31 +4449,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>molino del sol_pan mini baguette integral mi trigo molino del sol_unknown</t>
+          <t>pillsbury_pillsbury 24 ea pillsbury cherry pastries 6 ea_unknown</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Molino Del Sol</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pan Mini Baguette Integral Mi Trigo Molino Del Sol</t>
+          <t>Pillsbury | 24 ea Pillsbury Cherry Pastries 6 ea</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.06</v>
+        <v>10.02793296089386</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -3825,31 +4488,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pringles_papas fritas mini pringles original_0.04</t>
+          <t>pillsbury_pillsbury 8 ea pillsbury cinnamon rolls cream cheese icing_unknown</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Papas Fritas Mini Pringles Original</t>
+          <t>Pillsbury | 8 ea PILLSBURY CINNAMON ROLLS, CREAM CHEESE ICING</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.08</v>
+        <v>5.35754189944134</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -3864,31 +4527,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ritz_ponche maritza_unknown</t>
+          <t>pillsbury_pillsbury 8 ea pillsbury cinnamon rolls with icing_unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ritz</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ponche Maritza</t>
+          <t>Pillsbury | 8 ea PILLSBURY CINNAMON ROLLS, WITH ICING</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>18.14</v>
+        <v>5.35754189944134</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -3903,31 +4566,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown_bruschettas con cebolla valentina_0.15</t>
+          <t>pillsbury_pillsbury 8 ea pillsbury grands biscuits flaky layers_unknown</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bruschettas Con Cebolla Valentina</t>
+          <t>Pillsbury | 8 ea PILLSBURY GRANDS! BISCUITS, FLAKY LAYERS</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.66</v>
+        <v>5.35754189944134</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -3942,31 +4605,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>aviva_galleta de soda saltina aviva 20 und_0.6</t>
+          <t>pillsbury_pillsbury pillsbury grands biscuits flaky layers 400_0.4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aviva</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Galleta De Soda Saltina Aviva 20 Und</t>
+          <t>Pillsbury | PILLSBURY GRANDS! BISCUITS, FLAKY LAYERS | 400 g</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.44</v>
+        <v>4.016759776536313</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -3981,31 +4644,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>golden_golden harvest multigrain loaf_unknown</t>
+          <t>pillsbury_pillsbury pillsbury honey butter crescents 8 ea 11_0.31</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GOLDEN HARVEST MULTIGRAIN LOAF</t>
+          <t>Pillsbury | Pillsbury Honey Butter Crescents 8 ea | 11 oz</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.596153846153846</v>
+        <v>4.072625698324022</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -4020,31 +4683,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>golden_golden harvest whole slice bread_unknown</t>
+          <t>ricola_ricola ricola wrapped drops cherry oral anesthetic 19 ea 230_0.23</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Golden Harvest Whole Slice Bread</t>
+          <t>Ricola | Ricola Wrapped Drops Cherry Oral Anesthetic 19 ea | 230 g</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.163461538461538</v>
+        <v>3.625698324022347</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -4059,31 +4722,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>oreo_nestle oreo bar 5pk_unknown</t>
+          <t>roomboter_roomboter koopmans roomboter bladerdeeg 309_0.31</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nestle Oreo Bar 5Pk</t>
+          <t>Roomboter | KOOPMANS ROOMBOTER BLADERDEEG | 309 g</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>26.25</v>
+        <v>5.525139664804469</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -4098,31 +4761,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>oreo_nestle oreo ice cream_unknown</t>
+          <t>tostitos_tostitos tostitos restaurant style original tortilla chips 250_0.25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nestle Oreo Ice Cream</t>
+          <t>Tostitos | Tostitos Restaurant Style Original Tortilla Chips | 250 g</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>25.96153846153846</v>
+        <v>1.837988826815642</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -4137,31 +4800,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>oreo_nestle oreo sandwich 4_unknown</t>
+          <t>toufayan_toufayan 18 toufayan cinnamon raisin bagels_unknown</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nestle Oreo Sandwich 4 Ct</t>
+          <t>Toufayan | 18 ct TOUFAYAN CINNAMON RAISIN BAGELS</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>17.11538461538462</v>
+        <v>8.910614525139664</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
@@ -4176,31 +4839,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>oreo_nestle oreo sandwich_unknown</t>
+          <t>toufayan_toufayan 5 ea toufayan bakeries pita classic white_unknown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nestle Oreo Sandwich</t>
+          <t>Toufayan | 5 ea TOUFAYAN BAKERIES PITA CLASSIC WHITE</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>5.288461538461538</v>
+        <v>3.625698324022347</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -4215,17 +4878,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>toufayan_toufayan bagels blueberry 567g_0.57</t>
+          <t>toufayan_toufayan 6 ea toufayan bakeries spinach wraps_unknown</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4235,11 +4898,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toufayan Bagels Blueberry 567g</t>
+          <t>Toufayan | 6 ea TOUFAYAN BAKERIES GLUTEN FREE SPINACH WRAPS</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>5.048076923076923</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -4254,17 +4917,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>toufayan_toufayan wraps 6 s_unknown</t>
+          <t>toufayan_toufayan 6 pc toufayan bakeries wraps savory spinach_unknown</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4274,11 +4937,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Toufayan Wraps Gluten Free 6’s</t>
+          <t>Toufayan | 6 pc TOUFAYAN BAKERIES WRAPS SAVORY SPINACH</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10.60096153846154</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -4293,17 +4956,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Massy Stores Guyana</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>toufayan_toufayan wraps spinach 10oz_0.28</t>
+          <t>toufayan_toufayan 6 toufayan bakeries sundried tomato wraps_unknown</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4313,11 +4976,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toufayan Wraps Spinach 10oz</t>
+          <t>Toufayan | 6 ct TOUFAYAN BAKERIES SUNDRIED TOMATO WRAPS</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10.60096153846154</v>
+        <v>5.301675977653631</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
@@ -4328,6 +4991,1839 @@
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan 6ct toufayan bakeries garlic pesto wraps_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Toufayan | 6ct TOUFAYAN BAKERIES GARLIC PESTO WRAPS</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries low carb low sodium wraps 340_0.34</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES LOW CARB-LOW SODIUM WRAPS | 340 g</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>4.999999999999999</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries wholesome wheat wraps 11_0.31</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS | 11 oz</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unknown_1 pc kaneelbroodje_unknown</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1 pc KANEELBROODJE</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>2.76536312849162</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unknown_19 pc tortilla wraps tomato_unknown</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19 pc TORTILLA WRAPS TOMATO</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>5.134078212290502</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unknown_2 pc lemon muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2 pc LEMON MUFFIN</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unknown_2 pc tiramisutaartje_unknown</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2 pc TIRAMISUTAARTJE</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unknown_24 ea food for life flourless sprouted grain cinnamon raisin bread 24_0.68</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>24 ea Food For Life Flourless Sprouted Grain Cinnamon Raisin Bread | 24 oz</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>10.02793296089386</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>unknown_6 ea consenza bruinbrood gv_unknown</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>6 ea CONSENZA BRUINBROOD GV</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>unknown_6 pc raspberry muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>6 pc RASPBERRY MUFFIN</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>5.301675977653631</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>unknown_8 ea tortilla wraps tomato_unknown</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>8 ea TORTILLA WRAPS TOMATO</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>13.37988826815642</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>unknown_aardbeien taart klein half_unknown</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AARDBEIEN TAART KLEIN HALF</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>30.69832402234637</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>unknown_bays english muffins original 12_0.34</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BAYS ENGLISH MUFFINS ORIGINAL : | 12 oz</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>7.793296089385474</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>unknown_bays english muffins sourdough 230_0.23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BAYS ENGLISH MUFFINS SOURDOUGH | 230 g</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>4.441340782122905</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>unknown_bertolli pinsa 11_0.31</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BERTOLLI PINSA | 11 oz</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>unknown_consenza witbrood gv 14_0.4</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>CONSENZA WITBROOD GV | 14 oz</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>unknown_easy filo bladerdeeg 11_0.31</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>EASY FILO BLADERDEEG | 11 oz</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>unknown_food for life flourless sprouted grain seed bread 680_0.68</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Food For Life Flourless Sprouted Grain &amp; Seed Bread | 680 g</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>11.70391061452514</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>unknown_food for life sprouted flourless original tortillas 6 ea 13_0.37</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Food For Life Sprouted Flourless Original Tortillas 6 ea | 13 oz</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>4.184357541899441</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>unknown_homemade pineapple cake_unknown</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Homemade Pineapple Cake</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>18.15083798882682</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>unknown_johnny cake 13 25_0.38</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>JOHNNY CAKE | 13.25 oz</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>4.24022346368715</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>unknown_koopmans deeg hartige taart 225g_0.22</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>KOOPMANS DEEG HARTIGE TAART | 225g</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>unknown_magioni bloemkool pizza bodem 16 3_0.46</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>MAGIONI BLOEMKOOL PIZZA BODEM | 16.3 oz</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>5.35754189944134</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>unknown_mccain vanilla cake 2 12_0.06</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MCCAIN VANILLA CAKE | 2.12 oz</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>3.905027932960894</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>unknown_one protein bar lemon cake 12 7_0.36</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>One Protein Bar, Lemon Cake | 12.7 oz</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>7.201117318435754</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>unknown_papagena biscuit assorted 300_0.3</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PAPAGENA BISCUIT ASSORTED | 300 g</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>8.87709497206704</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>unknown_rb amandelstaaf_unknown</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RB AMANDELSTAAF :</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>3.569832402234637</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>unknown_slagroompunt_unknown</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SLAGROOMPUNT</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>unknown_spring home roti paratha plain 5 ea 12 3_0.35</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Spring Home Roti Paratha, Plain 5 ea | 12.3 oz</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>6.139664804469274</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>unknown_wraps whole grain wheat flour tortillas 12 67_0.36</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>WRAPS WHOLE GRAIN WHEAT FLOUR TORTILLAS | 12.67 oz</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>14.24022346368715</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>unknown_wraps whole grain wheat flour tortillas 240_0.24</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>WRAPS WHOLE GRAIN WHEAT FLOUR TORTILLAS | 240 g</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>2.223463687150838</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>verkade_verkade verkade nizza 200_0.2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Verkade</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Verkade | VERKADE NIZZA | 200 g</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1.949720670391062</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa crisp original 190_0.19</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>WASA | WASA CRISP ORIGINAL | 190 g</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>3.681564245810056</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa delicate thin sesam 300_0.3</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>WASA | WASA DELICATE THIN SESAM | 300 g</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>3.122905027932961</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa goudbruin 250_0.25</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>WASA | WASA GOUDBRUIN : | 250 g</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa vezelrijk 245_0.24</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>WASA | WASA VEZELRIJK | 245 g</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>2.899441340782123</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>jumbo_parreiro pan viga jumbo natural_unknown</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Parreiro Pan Viga Jumbo Natural</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>pepin_pan para hot dog pepin_unknown</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pan Para Hot Dog Pepin</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>pepin_pan viga pequena pepin_0.45</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Pepin</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Pan Viga Pequena Pepin</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Garrido</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pringles_papitas sabor queso pringles_0.04</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Papitas Sabor Queso Pringles</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>food club_tortillas de maiz dura para tacos food club_unknown</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Food Club</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Tortillas De Maiz Dura Para Tacos Food Club</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>la real_tortilla de maiz taco la real_unknown</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>La Real</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Tortilla De Maiz Taco La Real</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Jumbo</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>pringles_papas sabor bbq pringles_0.04</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Papas Sabor Bbq Pringles</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Merca Jumbo</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>l der_muffin choco doble lider_0.08</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Muffin Choco Doble Lider</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>l der_muffin choco doble lider_0.08</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Líder</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Muffin Choco Doble Lider</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>aviva_galleta de soda saltina aviva 20 und_0.6</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Aviva</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Galleta De Soda Saltina Aviva 20 Und</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Sirena</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>buenhorno_pan de bonos buenhorno congelado_unknown</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Buenhorno</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Pan De Bonos Buenhorno Congelado</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>left_only</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4340,7 +6836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4408,12 +6904,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bauducco_bauducco bauducco wafer chocolate 1 5_0.04</t>
+          <t>gwoon_gwoon beschuit volkoren 140gr_0.14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -4421,16 +6917,16 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bauducco</t>
+          <t>Gwoon</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bauducco | BAUDUCCO WAFER CHOCOLATE | 1.5 oz</t>
+          <t>GWOON BESCHUIT VOLKOREN 140gr</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.670391061452514</v>
+        <v>1.45</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4447,12 +6943,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Super Food Aruba</t>
+          <t>DOIT Aruba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cheetos_cheetos cheetos puffs cheese flavored snacks 6 5_0.18</t>
+          <t>unknown_hungry jack chocolate mix pancake mix 7oz_0.2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -4460,16 +6956,16 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cheetos</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cheetos | Cheetos Puffs Cheese Flavored Snacks | 6.5 oz</t>
+          <t>HUNGRY JACK CHOCOLATE MIX PANCAKE MIX 7oz</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.575418994413408</v>
+        <v>2.12</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -4491,7 +6987,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>crav n_crav n crav n flavor tortilla chips yellow corn crispy round party size 9 75_0.28</t>
+          <t>bagel bites_bagel bites 9 ea bagel bites cheese pepperoni pizza snacks_unknown</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -4499,16 +6995,16 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crav'N</t>
+          <t>Bagel Bites</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Crav'N | Crav'n Flavor Tortilla Chips, Yellow Corn, Crispy Round, Party Size | 9.75 oz</t>
+          <t>Bagel Bites | 9 ea BAGEL BITES CHEESE &amp; PEPPERONI PIZZA SNACKS</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.849162011173184</v>
+        <v>4.184357541899441</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4530,7 +7026,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>doritos_doritos doritos cool american party 272_0.27</t>
+          <t>betty crocker_betty crocker betty crocker cake mix butter recipe yellow 13 25_0.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -4538,16 +7034,16 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Betty Crocker</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Doritos | DORITOS COOL AMERICAN - PARTY PACK | 272 g</t>
+          <t>Betty Crocker | Betty Crocker Cake Mix, Butter Recipe Yellow | 13.25 oz</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5.575418994413408</v>
+        <v>4.128491620111731</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4569,7 +7065,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>doritos_doritos doritos nacho cheese party 170_0.17</t>
+          <t>bigelow_bigelow bigelow constant comment black tea decaffeinated 20 tb case of 6 boxes 20 individually wrapped tea bags 20 ea 12 67_0.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -4577,16 +7073,16 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Doritos</t>
+          <t>Bigelow</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Doritos | DORITOS NACHO CHEESE - PARTY PACK | 170 g</t>
+          <t>Bigelow | Bigelow Constant Comment Black Tea Decaffeinated 20 Tb (Case Of 6 Boxes), 20 Individually Wrapped Tea Bags 20 ea | 12.67 oz</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.849162011173184</v>
+        <v>14.24022346368715</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4608,7 +7104,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>food club_food club 8 ea food club flour tortillas authentic fajita style 6 inch 20 ea_unknown</t>
+          <t>crav n_crav n crav n flavor crackers original rich crisp 3 ea 190_0.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -4616,16 +7112,16 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Food Club</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Food Club | 8 ea Food Club Flour Tortillas, Authentic, Fajita Style, 6 Inch 20 ea</t>
+          <t>Crav'N | Crav'n Flavor Crackers, Original, Rich &amp; Crisp, 3 ea | 190 g</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>13.37988826815642</v>
+        <v>3.681564245810056</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4647,7 +7143,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>frito lay_frito lay frito lay doritos nacho cheese 5 5_0.16</t>
+          <t>crav n_crav n crav n flavor pita chips parmesan garlic herb baked 7 33_0.21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -4655,16 +7151,16 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frito-Lay</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Frito-Lay | FRITO LAY DORITOS NACHO CHEESE | 5.5 oz</t>
+          <t>Crav'N | Crav'n Flavor Pita Chips, Parmesan Garlic &amp; Herb, Baked | 7.33 oz</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.122905027932961</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -4686,7 +7182,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jumbo_jumbo 2 pc jumbo supercroissantdeeg_unknown</t>
+          <t>crav n_crav n crav n flavor tortilla chips ranch flavored 300_0.3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -4694,16 +7190,16 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jumbo | 2 pc JUMBO SUPERCROISSANTDEEG</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, Ranch Flavored | 300 g</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.782122905027933</v>
+        <v>2.005586592178771</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -4725,7 +7221,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo marie biscuits 300_0.3</t>
+          <t>crav n_crav n crav n flavor tortilla chips white corn restaurant style 9 75_0.28</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4733,16 +7229,16 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Crav'N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO MARIE BISCUITS | 300 g</t>
+          <t>Crav'N | Crav'n Flavor Tortilla Chips, White Corn, Restaurant Style | 9.75 oz</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8.87709497206704</v>
+        <v>3.849162011173184</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -4764,7 +7260,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jumbo_jumbo jumbo supercroissantdeeg 24_0.68</t>
+          <t>eggo_eggo eggo frozen breakfast frozen waffles strawberry 29 6_0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -4772,16 +7268,16 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jumbo</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Jumbo | JUMBO SUPERCROISSANTDEEG | 24 oz</t>
+          <t>Eggo | EGGO FROZEN BREAKFAST FROZEN WAFFLES, STRAWBERRY | 29.6 oz</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.251396648044693</v>
+        <v>10.02793296089386</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -4803,7 +7299,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lays_lays 24 pc lay s sour cream onion flavored potato crisps 5 5_0.16</t>
+          <t>eggo_eggo eggo minis waffle 11_0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -4811,16 +7307,16 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lays | 24 pc Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
+          <t>Eggo | EGGO MINIS WAFFLE | 11 oz</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>23.23463687150839</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -4842,7 +7338,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lays_lays lay s cheddar flavored potato crisps 5 5_0.16</t>
+          <t>eggo_eggo eggo waffles blueberry 14_0.4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -4850,16 +7346,16 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lays</t>
+          <t>Eggo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lays | Lay's Cheddar Flavored Potato Crisps | 5.5 oz</t>
+          <t>Eggo | EGGO WAFFLES, BLUEBERRY | 14 oz</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.849162011173184</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4881,7 +7377,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo double stuf chocolate sandwich cookies 13 29_0.38</t>
+          <t>food club_food club food club flour tortillas authentic fajita style 6 inch 20 ea 240_0.24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -4889,16 +7385,16 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Food Club</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Oreo | OREO Double Stuf Chocolate Sandwich Cookies, | 13.29 oz</t>
+          <t>Food Club | Food Club Flour Tortillas, Authentic, Fajita Style, 6 Inch 20 ea | 240 g</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.368715083798882</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -4920,7 +7416,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>oreo_oreo oreo golden sandwich cookies 13 29_0.38</t>
+          <t>frito lay_frito lay frito lay doritos nacho cheese 11_0.31</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -4928,16 +7424,16 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Oreo</t>
+          <t>Frito-Lay</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Oreo | OREO Golden Sandwich Cookies, | 13.29 oz</t>
+          <t>Frito-Lay | FRITO LAY DORITOS NACHO CHEESE | 11 oz</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.039106145251397</v>
+        <v>6.64245810055866</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -4959,7 +7455,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pepperidge farm_pepperidge farm pepperidge farm bread jewish rye seeded 340_0.34</t>
+          <t>glad_glad 19 pc glad cling n seal plastic food wrap 400 square foot roll of 2_unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -4967,16 +7463,16 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pepperidge Farm</t>
+          <t>Glad</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pepperidge Farm | PEPPERIDGE FARM BREAD, JEWISH RYE, SEEDED | 340 g</t>
+          <t>Glad | 19 pc Glad Cling‘N Seal Plastic Food Wrap, 400 Square Foot Roll, Pack of 2</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.999999999999999</v>
+        <v>5.134078212290502</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -4998,7 +7494,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury 6 ea pillsbury raspberry pastries 11 7_0.33</t>
+          <t>jumbo_jumbo jumbo cafe noir koffiekoekjes 360_0.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -5006,16 +7502,16 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pillsbury | 6 ea Pillsbury Raspberry Pastries | 11.7 oz</t>
+          <t>Jumbo | JUMBO CAFE NOIR KOFFIEKOEKJES | 360 g</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.558659217877095</v>
+        <v>2.396648044692737</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -5037,7 +7533,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pillsbury_pillsbury pillsbury grands biscuits flaky layers 200_0.2</t>
+          <t>jumbo_jumbo jumbo linzenwafel sweet chilli 13 7_0.39</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -5045,16 +7541,16 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pillsbury</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pillsbury | PILLSBURY GRANDS! BISCUITS, FLAKY LAYERS | 200 g</t>
+          <t>Jumbo | JUMBO LINZENWAFEL SWEET CHILLI | 13.7 oz</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.502793296089385</v>
+        <v>3.290502793296089</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -5076,7 +7572,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pirucream_pirucream pirucream wafers chocolate and hazelnut 142_0.14</t>
+          <t>jumbo_jumbo jumbo marie biscuits 415_0.42</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -5084,16 +7580,16 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pirucream</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pirucream | Pirucream Wafers, Chocolate and Hazelnut | 142 g</t>
+          <t>Jumbo | JUMBO MARIE BISCUITS | 415 g</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.782122905027933</v>
+        <v>9.491620111731844</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -5115,7 +7611,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles bbq 2 3_0.07</t>
+          <t>jumbo_jumbo jumbo tortilla nat 8st 300_0.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -5123,16 +7619,16 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>Jumbo</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES BBQ | 2.3 oz</t>
+          <t>Jumbo | JUMBO TORTILLA NAT.8ST | 300 g</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.340782122905028</v>
+        <v>2.675977653631285</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -5154,7 +7650,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles potato crisps chips lunch snacks office and kids snacks grab n go original can 1 can 1 4_0.04</t>
+          <t>la dulcerita_la dulcerita 2 pc la dulcerita rasin muffin_unknown</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -5162,16 +7658,16 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pringles | Pringles Potato Crisps Chips, Lunch Snacks, Office and Kids Snacks, Grab N' Go, Original, Can, 1 Can | 1.4 oz</t>
+          <t>La Dulcerita | 2 pc LA DULCERITA RASIN MUFFIN</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.558659217877095</v>
+        <v>3.899441340782123</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -5193,7 +7689,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>pringles_pringles pringles sour cream onion 1 3_0.04</t>
+          <t>la dulcerita_la dulcerita la dulcerita chocolate chip muffin_unknown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -5201,16 +7697,16 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pringles</t>
+          <t>La Dulcerita</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pringles | PRINGLES SOUR CREAM &amp; ONION | 1.3 oz</t>
+          <t>La Dulcerita | LA DULCERITA CHOCOLATE CHIP MUFFIN</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.558659217877095</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -5232,7 +7728,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ruffles_ruffles ruffles potato chips sour cream onion flavored 6 5_0.18</t>
+          <t>lays_lays lay s sour cream onion flavored potato crisps 5 5_0.16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -5240,16 +7736,16 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ruffles</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ruffles | Ruffles Potato Chips, Sour Cream &amp; Onion Flavored | 6.5 oz</t>
+          <t>Lays | Lay's Sour Cream &amp; Onion Flavored Potato Crisps | 5.5 oz</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.631284916201117</v>
+        <v>3.122905027932961</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -5271,7 +7767,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>siete_siete siete tortillas grain almond flour 8 ea 240_0.24</t>
+          <t>lays_lays lays classic potato chips 6 5_0.18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -5279,16 +7775,16 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Siete</t>
+          <t>Lays</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Siete | Siete Tortillas, Grain Free, Almond Flour 8 ea | 240 g</t>
+          <t>Lays | LAYS CLASSIC POTATO CHIPS | 6.5 oz</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.223463687150838</v>
+        <v>4.966480446927375</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -5310,7 +7806,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tostitos_tostitos tostitos restaurant style original tortilla chips 20_0.57</t>
+          <t>lu_lu udi s classic hamburger buns 550g_0.55</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -5318,16 +7814,16 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tostitos</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tostitos | Tostitos Restaurant Style Original Tortilla Chips | 20 oz</t>
+          <t>LU | UDI'S GLUTEN FREE CLASSIC HAMBURGER BUNS | 550g</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.011173184357542</v>
+        <v>5.46927374301676</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -5349,7 +7845,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>unknown_1 pc kaneelbroodje_unknown</t>
+          <t>lu_lu udi s classic hot dog buns frozen 6 count 680_0.68</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -5357,16 +7853,16 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1 pc KANEELBROODJE</t>
+          <t>LU | Udi's Gluten Free Classic Hot Dog Buns, Frozen, . 6 Count | 680 g</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.76536312849162</v>
+        <v>11.70391061452514</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -5388,7 +7884,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unknown_cherry pineapple klein_unknown</t>
+          <t>milka_milka milka mmmax chocoswing biscuit 400_0.4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -5396,16 +7892,16 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Milka</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CHERRY/ PINEAPPLE KLEIN</t>
+          <t>Milka | MILKA MMMAX CHOCOSWING BISCUIT | 400 g</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>22.31843575418995</v>
+        <v>4.016759776536313</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -5427,7 +7923,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>unknown_coolback garlic butter baguette 450g_0.45</t>
+          <t>nature valley_nature valley nature valley chewy almond granola bars 6 ea 245_0.24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -5435,16 +7931,16 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nature Valley</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>COOLBACK GARLIC BUTTER BAGUETTE | 450g</t>
+          <t>Nature Valley | Nature Valley Chewy Almond Granola Bars 6 ea | 245 g</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.569832402234637</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -5466,7 +7962,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unknown_koopmans deeg hartige taart 309_0.31</t>
+          <t>noel_noel noel chocolate chip 200_0.2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -5474,16 +7970,16 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Noel</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KOOPMANS DEEG HARTIGE TAART | 309 g</t>
+          <t>Noel | NOEL CHOCOLATE CHIP | 200 g</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5.525139664804469</v>
+        <v>1.949720670391062</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -5505,7 +8001,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>unknown_papagena biscuit assorted 415_0.42</t>
+          <t>oreo_oreo oreo frozen dairy dessert sandwiches 4 count 11 78_0.33</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -5513,16 +8009,16 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PAPAGENA BISCUIT ASSORTED | 415 g</t>
+          <t>Oreo | Oreo Frozen Dairy Dessert Sandwiches, 4 Count | 11.78 oz</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.491620111731844</v>
+        <v>9.770949720670391</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -5544,7 +8040,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>unknown_slagroompunt_unknown</t>
+          <t>oreo_oreo oreo mini cookies snak saks 13 29_0.38</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -5552,16 +8048,16 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SLAGROOMPUNT</t>
+          <t>Oreo | OREO MINI COOKIES SNAK-SAKS | 13.29 oz</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.067039106145252</v>
+        <v>7.089385474860335</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -5573,17 +8069,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>toufayan_mini bagels pasa y canela toufayan_0.51</t>
+          <t>oreo_oreo oreo thins chocolate sandwich cookies family size 8_0.23</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -5591,16 +8087,16 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Oreo</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Mini Bagels Pasa Y Canela Toufayan</t>
+          <t>Oreo | OREO Thins Chocolate Sandwich Cookies, Family Size, | 8 oz</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.99</v>
+        <v>6.307262569832401</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -5612,17 +8108,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>toufayan_wrap integral toufayan_0.31</t>
+          <t>pillsbury_pillsbury pillsbury cherry pastries 6 ea 29 6_0.84</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -5630,16 +8126,16 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Toufayan</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Wrap Integral Toufayan</t>
+          <t>Pillsbury | Pillsbury Cherry Pastries 6 ea | 29.6 oz</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.36</v>
+        <v>10.02793296089386</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -5651,17 +8147,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merca Jumbo</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>l der_muffin choco doble lider_0.08</t>
+          <t>pillsbury_pillsbury pillsbury grands biscuits flaky layers 300_0.3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -5669,16 +8165,16 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Pillsbury</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Muffin Choco Doble Lider</t>
+          <t>Pillsbury | PILLSBURY GRANDS! BISCUITS, FLAKY LAYERS | 300 g</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.78</v>
+        <v>8.87709497206704</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -5690,17 +8186,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>l der_muffin choco doble lider_0.08</t>
+          <t>ricola_ricola ricola wrapped drops cherry oral anesthetic 19 ea 240_0.24</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -5708,16 +8204,16 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Líder</t>
+          <t>Ricola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Muffin Choco Doble Lider</t>
+          <t>Ricola | Ricola Wrapped Drops Cherry Oral Anesthetic 19 ea | 240 g</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.79</v>
+        <v>2.223463687150838</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -5729,17 +8225,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unknown_molde para pastel cuadrado 10_unknown</t>
+          <t>roomboter_roomboter 6 ea koopmans roomboter bladerdeeg_unknown</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -5747,16 +8243,16 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Roomboter</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Molde Para Pastel Cuadrado 10</t>
+          <t>Roomboter | 6 ea KOOPMANS ROOMBOTER BLADERDEEG</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>17.43</v>
+        <v>2.899441340782123</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -5768,17 +8264,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>unknown_molde para pastel cuadrado 8_unknown</t>
+          <t>tostitos_tostitos 8 ea tostitos restaurant style original tortilla chips 10_0.28</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -5786,16 +8282,16 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tostitos</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Molde Para Pastel Cuadrado 8</t>
+          <t>Tostitos | 8 ea Tostitos Restaurant Style Original Tortilla Chips | 10 oz</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>14.66</v>
+        <v>13.37988826815642</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -5807,17 +8303,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>unknown_molde para pastel redondo 12_unknown</t>
+          <t>toufayan_toufayan 18 ea toufayan cinnamon raisin bagels_unknown</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -5825,16 +8321,16 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Molde Para Pastel Redondo 12</t>
+          <t>Toufayan | 18 ea TOUFAYAN CINNAMON RAISIN BAGELS</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>11.88</v>
+        <v>8.910614525139664</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -5846,17 +8342,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sirena</t>
+          <t>Super Food Aruba</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>buenhorno_pan de bonos buenhorno congelado_unknown</t>
+          <t>toufayan_toufayan 6 ea toufayan bakeries wholesome wheat wraps_unknown</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -5864,16 +8360,16 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Buenhorno</t>
+          <t>Toufayan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pan De Bonos Buenhorno Congelado</t>
+          <t>Toufayan | 6 ea TOUFAYAN BAKERIES WHOLESOME WHEAT WRAPS</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.12</v>
+        <v>2.955307262569832</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -5881,6 +8377,2268 @@
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan toufayan bakeries pita classic white 225g_0.22</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Toufayan | TOUFAYAN BAKERIES PITA CLASSIC WHITE | 225g</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>unknown_1 pc rb amandelstaaf_unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1 pc RB AMANDELSTAAF :</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>2.76536312849162</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>unknown_10 ea koopmans deeg hartige taart_unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>10 ea KOOPMANS DEEG HARTIGE TAART</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>5.525139664804469</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>unknown_2 pc aardbeien taart klein half_unknown</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2 pc AARDBEIEN TAART KLEIN HALF</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3.899441340782123</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>unknown_5 ea easy filo bladerdeeg_unknown</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5 ea EASY FILO BLADERDEEG</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>unknown_6 ea raspberry muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6 ea RASPBERRY MUFFIN</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>5.301675977653631</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>unknown_6 lemon muffin_unknown</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6 ct LEMON MUFFIN</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>5.301675977653631</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>unknown_bosvruchten muffin 24_0.68</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>BOSVRUCHTEN MUFFIN | 24 oz</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>7.251396648044693</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>unknown_citroen vlaai punt_unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>CITROEN VLAAI PUNT</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3.324022346368715</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>unknown_consenza bruinbrood gv 450g_0.45</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CONSENZA BRUINBROOD GV | 450g</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>6.675977653631285</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>unknown_consenza witbrood gv 12 3_0.35</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CONSENZA WITBROOD GV | 12.3 oz</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>6.139664804469274</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>unknown_food for life flourless sprouted grain cinnamon raisin bread 29 6_0.84</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Food For Life Flourless Sprouted Grain Cinnamon Raisin Bread | 29.6 oz</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>10.02793296089386</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>unknown_food for life flourless sprouted grain seed bread 24_0.68</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Food For Life Flourless Sprouted Grain &amp; Seed Bread | 24 oz</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>12.82122905027933</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>unknown_johnny cake 2 12_0.06</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>JOHNNY CAKE | 2.12 oz</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>3.905027932960894</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>unknown_kaneelbroodje_unknown</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>KANEELBROODJE</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>6.675977653631285</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unknown_mccain vanilla cake 12 7_0.36</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>MCCAIN VANILLA CAKE | 12.7 oz</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>7.201117318435754</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>unknown_papagena biscuit assorted 200_0.2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PAPAGENA BISCUIT ASSORTED | 200 g</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>1.502793296089385</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>unknown_pruimentaart klein_unknown</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PRUIMENTAART KLEIN</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>25.11173184357542</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>unknown_spring home roti paratha plain 5 ea 600g_0.6</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Spring Home Roti Paratha, Plain 5 ea | 600g</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>4.441340782122905</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>unknown_tiramisutaartje_unknown</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>TIRAMISUTAARTJE</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>3.067039106145252</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>unknown_tortilla wraps tomato 200g_0.2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TORTILLA WRAPS TOMATO | 200g</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>3.346368715083799</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>unknown_tortilla wraps tomato 230_0.23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>TORTILLA WRAPS TOMATO | 230 g</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>3.625698324022347</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa crisp original 300_0.3</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>WASA | WASA CRISP ORIGINAL | 300 g</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>3.122905027932961</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa delicate thin sesam 220_0.22</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>WASA | WASA DELICATE THIN SESAM | 220 g</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>3.290502793296089</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa goudbruin 126_0.13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>WASA | WASA GOUDBRUIN : | 126 g</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>3.122905027932961</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Super Food Aruba</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>wasa_wasa wasa vezelrijk 250_0.25</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Wasa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>WASA | WASA VEZELRIJK | 250 g</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>2.955307262569832</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>gamesa_galletas mini chokis gamesa_0.31</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Gamesa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Galletas Mini Chokis Gamesa</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Carrefour</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pringles_papitas sabor original pringles_0.12</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Papitas Sabor Original Pringles</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>bon_paleta bon de bizcocho_unknown</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Paleta Bon De Bizcocho</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>lumijor_pan integral familiar lumijor_0.85</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lumijor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Pan Integral Familiar Lumijor</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>molino del sol_pan integral multigranos molino del sol_0.65</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Molino Del Sol</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Pan Integral Multigranos Molino Del Sol</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pringles_papas fritas original pringles_0.25</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Papas Fritas Original Pringles</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>pringles_papitas fritas sabor original pringles_0.07</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Papitas Fritas Sabor Original Pringles</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Plaza Lama</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pringles_papitas fritas sabor queso cheddar pringles_0.07</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Papitas Fritas Sabor Queso Cheddar Pringles</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>devon_devon rolls chocolate chips 200 gr_0.2</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Devon</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Devon Rolls Chocolate Chips 200 gr</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1.923076923076923</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>festival_noel festival chocolate cookies 12x50g_0.6</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Noel Festival Chocolate Cookies 12x50g</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4.423076923076923</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>festival_noel festival strawberry 12x32g_0.38</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Noel Festival Strawberry 12x32g</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>3.942307692307693</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>festival_noel festival vanilla 12x32g_0.38</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Noel Festival Vanilla 12x32g</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>4.038461538461538</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>golden_golden harvest whole slice bread_unknown</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Golden</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Golden Harvest Whole Slice Bread</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>2.163461538461538</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>instorebakery_bakery sponge log cake_unknown</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Instorebakery</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Bakery Sponge Log Cake</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>4.326923076923077</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>king s hawaiian_kings hawaiian sweet roll_unknown</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>King's Hawaiian</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>KINGS HAWAIIAN SWEET ROLL</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>17.69230769230769</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>knotts_knotts raspberry short bread_unknown</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Knotts</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Knotts Raspberry Short Bread</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>knotts_knotts strawbery short bread_unknown</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Knotts</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Knotts Strawbery Short Bread</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>lu_canyon country white_unknown</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Canyon Gluten Free Country White</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>9.85576923076923</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>mr bakewell_bakewell whole wheat tennis rolls 5ct_unknown</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mr Bakewell</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Bakewell Whole Wheat Tennis Rolls 5ct</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>1.730769230769231</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>other_jello no bake sberry cheese cake 19 6oz_0.56</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Jello No Bake Sberry Cheese Cake 19.6oz</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>8.846153846153847</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>other_nutella and go pretzel sticks_unknown</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Nutella And Go Pretzel Sticks</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>2.644230769230769</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm double chocolate dark choc cookie 7 75oz_0.22</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Double Chocolate Dark Choc Cookie 7.75oz</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>6.346153846153846</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>pepperidge_pepperidge farm milano double dark chocolate 7 75oz_0.22</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pepperidge</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Pepperidge Farm Milano Double Dark Chocolate 7.75oz</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>toufayan_toufayan wraps spinach 10oz_0.28</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Toufayan</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Toufayan Wraps Spinach 10oz</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>10.60096153846154</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>unknown_bakery 9 marble creme cake_unknown</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Bakery 9″ Marble Creme Cake</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>8.413461538461538</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>unknown_bakery sponge cake 9_unknown</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Bakery Sponge Cake 9″</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>6.009615384615385</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>unknown_hungry jack pancake mix buttermilk complete_unknown</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>HUNGRY JACK PANCAKE MIX BUTTERMILK COMPLETE</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>5.528846153846154</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>vegefarm_vegefarm vege shrimp w bread powder 454g_0.45</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Vegefarm</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Vegefarm Vege Shrimp (W/bread Powder) 454g</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>12.45192307692308</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>walkers_walkers chocolate chip shortbread_unknown</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Walkers Chocolate Chip Shortbread</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>8.076923076923077</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>walkers_walkers piper dancer tin shortbread assorted 150g_0.15</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>WALKERS PIPER &amp; DANCER TIN SHORTBREAD ASSORTED 150G</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>14.61538461538462</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>walkers_walkers shortbread fingers_unknown</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Walkers Shortbread Fingers</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>5.384615384615385</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Massy Stores Guyana</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>walkers_walkers shortbread triangles_unknown</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Walkers</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Walkers Shortbread Triangles</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>6.490384615384615</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>right_only</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
